--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
@@ -38,50 +38,46 @@
     <definedName function="false" hidden="false" name="agents_y6" vbProcedure="false">Assumptions!$B$90</definedName>
     <definedName function="false" hidden="false" name="agents_y7" vbProcedure="false">Assumptions!$B$91</definedName>
     <definedName function="false" hidden="false" name="agent_productivity" vbProcedure="false">'Scenario Parameters'!$B$12</definedName>
-    <definedName function="false" hidden="false" name="atmm_a1500" vbProcedure="false">'Scenario Parameters'!$B$53</definedName>
-    <definedName function="false" hidden="false" name="atmm_a3000" vbProcedure="false">'Scenario Parameters'!$B$54</definedName>
-    <definedName function="false" hidden="false" name="atmm_a3000p" vbProcedure="false">'Scenario Parameters'!$B$55</definedName>
-    <definedName function="false" hidden="false" name="atmm_a500" vbProcedure="false">'Scenario Parameters'!$B$52</definedName>
-    <definedName function="false" hidden="false" name="atm_a1500" vbProcedure="false">'Scenario Parameters'!$B$49</definedName>
-    <definedName function="false" hidden="false" name="atm_a3000" vbProcedure="false">'Scenario Parameters'!$B$50</definedName>
-    <definedName function="false" hidden="false" name="atm_a3000p" vbProcedure="false">'Scenario Parameters'!$B$51</definedName>
-    <definedName function="false" hidden="false" name="atm_a500" vbProcedure="false">'Scenario Parameters'!$B$48</definedName>
+    <definedName function="false" hidden="false" name="atmm_a1500" vbProcedure="false">'Scenario Parameters'!$B$51</definedName>
+    <definedName function="false" hidden="false" name="atmm_a3000" vbProcedure="false">'Scenario Parameters'!$B$52</definedName>
+    <definedName function="false" hidden="false" name="atmm_a3000p" vbProcedure="false">'Scenario Parameters'!$B$53</definedName>
+    <definedName function="false" hidden="false" name="atmm_a500" vbProcedure="false">'Scenario Parameters'!$B$50</definedName>
+    <definedName function="false" hidden="false" name="atm_a1500" vbProcedure="false">'Scenario Parameters'!$B$47</definedName>
+    <definedName function="false" hidden="false" name="atm_a3000" vbProcedure="false">'Scenario Parameters'!$B$48</definedName>
+    <definedName function="false" hidden="false" name="atm_a3000p" vbProcedure="false">'Scenario Parameters'!$B$49</definedName>
+    <definedName function="false" hidden="false" name="atm_a500" vbProcedure="false">'Scenario Parameters'!$B$46</definedName>
     <definedName function="false" hidden="false" name="atm_allowance" vbProcedure="false">Assumptions!$B$18</definedName>
     <definedName function="false" hidden="false" name="atm_fee" vbProcedure="false">Assumptions!$B$19</definedName>
-    <definedName function="false" hidden="false" name="aum_per_partner" vbProcedure="false">'Scenario Parameters'!$B$70</definedName>
+    <definedName function="false" hidden="false" name="aum_per_partner" vbProcedure="false">'Scenario Parameters'!$B$68</definedName>
     <definedName function="false" hidden="false" name="b2b_fee" vbProcedure="false">Assumptions!$B$26</definedName>
     <definedName function="false" hidden="false" name="bar_grams" vbProcedure="false">Assumptions!$B$10</definedName>
     <definedName function="false" hidden="false" name="cac_gulf" vbProcedure="false">'Scenario Parameters'!$B$14</definedName>
     <definedName function="false" hidden="false" name="cac_india" vbProcedure="false">'Scenario Parameters'!$B$15</definedName>
     <definedName function="false" hidden="false" name="cac_uae" vbProcedure="false">'Scenario Parameters'!$B$13</definedName>
-    <definedName function="false" hidden="false" name="card_activation" vbProcedure="false">'Scenario Parameters'!$B$42</definedName>
-    <definedName function="false" hidden="false" name="card_txns_per_draw" vbProcedure="false">'Scenario Parameters'!$B$43</definedName>
-    <definedName function="false" hidden="false" name="card_txns_per_month" vbProcedure="false">'Scenario Parameters'!$B$44</definedName>
+    <definedName function="false" hidden="false" name="card_activation" vbProcedure="false">'Scenario Parameters'!$B$41</definedName>
+    <definedName function="false" hidden="false" name="card_txns_per_draw" vbProcedure="false">'Scenario Parameters'!$B$42</definedName>
     <definedName function="false" hidden="false" name="ceil_gulf" vbProcedure="false">Assumptions!$B$82</definedName>
     <definedName function="false" hidden="false" name="ceil_india" vbProcedure="false">Assumptions!$B$83</definedName>
     <definedName function="false" hidden="false" name="ceil_total" vbProcedure="false">Assumptions!$B$84</definedName>
     <definedName function="false" hidden="false" name="ceil_uae" vbProcedure="false">Assumptions!$B$81</definedName>
     <definedName function="false" hidden="false" name="decline_uplift" vbProcedure="false">Assumptions!$B$16</definedName>
-    <definedName function="false" hidden="false" name="drawn_share" vbProcedure="false">'Scenario Parameters'!$B$59</definedName>
-    <definedName function="false" hidden="false" name="draw_events" vbProcedure="false">'Scenario Parameters'!$B$61</definedName>
+    <definedName function="false" hidden="false" name="drawn_share" vbProcedure="false">'Scenario Parameters'!$B$57</definedName>
+    <definedName function="false" hidden="false" name="draw_events" vbProcedure="false">'Scenario Parameters'!$B$59</definedName>
     <definedName function="false" hidden="false" name="entry_fee" vbProcedure="false">Assumptions!$B$8</definedName>
     <definedName function="false" hidden="false" name="ever_qualify" vbProcedure="false">'Scenario Parameters'!$B$26</definedName>
     <definedName function="false" hidden="false" name="fab_premium" vbProcedure="false">Assumptions!$B$9</definedName>
-    <definedName function="false" hidden="false" name="facility_turnover" vbProcedure="false">'Scenario Parameters'!$B$60</definedName>
-    <definedName function="false" hidden="false" name="family_attach" vbProcedure="false">'Scenario Parameters'!$B$62</definedName>
+    <definedName function="false" hidden="false" name="facility_turnover" vbProcedure="false">'Scenario Parameters'!$B$58</definedName>
+    <definedName function="false" hidden="false" name="family_attach" vbProcedure="false">'Scenario Parameters'!$B$60</definedName>
     <definedName function="false" hidden="false" name="family_price" vbProcedure="false">Assumptions!$B$25</definedName>
-    <definedName function="false" hidden="false" name="foreign_spend_share" vbProcedure="false">'Scenario Parameters'!$B$45</definedName>
+    <definedName function="false" hidden="false" name="foreign_spend_share" vbProcedure="false">'Scenario Parameters'!$B$43</definedName>
     <definedName function="false" hidden="false" name="fx_margin" vbProcedure="false">Assumptions!$B$17</definedName>
     <definedName function="false" hidden="false" name="gate_run" vbProcedure="false">Assumptions!$B$39</definedName>
     <definedName function="false" hidden="false" name="gold_price" vbProcedure="false">Assumptions!$B$6</definedName>
     <definedName function="false" hidden="false" name="ic_gold" vbProcedure="false">Assumptions!$B$14</definedName>
-    <definedName function="false" hidden="false" name="issuance_events" vbProcedure="false">'Scenario Parameters'!$B$46</definedName>
+    <definedName function="false" hidden="false" name="issuance_events" vbProcedure="false">'Scenario Parameters'!$B$44</definedName>
     <definedName function="false" hidden="false" name="issuance_fee" vbProcedure="false">Assumptions!$B$20</definedName>
     <definedName function="false" hidden="false" name="lapsed_redemption_mult" vbProcedure="false">'Scenario Parameters'!$B$33</definedName>
     <definedName function="false" hidden="false" name="ltv_gold" vbProcedure="false">Assumptions!$B$31</definedName>
-    <definedName function="false" hidden="false" name="mix_gulf" vbProcedure="false">'Scenario Parameters'!$B$78</definedName>
-    <definedName function="false" hidden="false" name="mix_india" vbProcedure="false">'Scenario Parameters'!$B$79</definedName>
-    <definedName function="false" hidden="false" name="mix_uae" vbProcedure="false">'Scenario Parameters'!$B$77</definedName>
     <definedName function="false" hidden="false" name="mktg_y1" vbProcedure="false">Assumptions!$B$92</definedName>
     <definedName function="false" hidden="false" name="mktg_y2" vbProcedure="false">Assumptions!$B$93</definedName>
     <definedName function="false" hidden="false" name="mktg_y3" vbProcedure="false">Assumptions!$B$94</definedName>
@@ -97,15 +93,15 @@
     <definedName function="false" hidden="false" name="organic_share" vbProcedure="false">'Scenario Parameters'!$B$21</definedName>
     <definedName function="false" hidden="false" name="origination_gross" vbProcedure="false">Assumptions!$B$27</definedName>
     <definedName function="false" hidden="false" name="origination_share" vbProcedure="false">Assumptions!$B$28</definedName>
-    <definedName function="false" hidden="false" name="partners_y1" vbProcedure="false">'Scenario Parameters'!$B$63</definedName>
-    <definedName function="false" hidden="false" name="partners_y2" vbProcedure="false">'Scenario Parameters'!$B$64</definedName>
-    <definedName function="false" hidden="false" name="partners_y3" vbProcedure="false">'Scenario Parameters'!$B$65</definedName>
-    <definedName function="false" hidden="false" name="partners_y4" vbProcedure="false">'Scenario Parameters'!$B$66</definedName>
-    <definedName function="false" hidden="false" name="partners_y5" vbProcedure="false">'Scenario Parameters'!$B$67</definedName>
-    <definedName function="false" hidden="false" name="partners_y6" vbProcedure="false">'Scenario Parameters'!$B$68</definedName>
-    <definedName function="false" hidden="false" name="partners_y7" vbProcedure="false">'Scenario Parameters'!$B$69</definedName>
+    <definedName function="false" hidden="false" name="partners_y1" vbProcedure="false">'Scenario Parameters'!$B$61</definedName>
+    <definedName function="false" hidden="false" name="partners_y2" vbProcedure="false">'Scenario Parameters'!$B$62</definedName>
+    <definedName function="false" hidden="false" name="partners_y3" vbProcedure="false">'Scenario Parameters'!$B$63</definedName>
+    <definedName function="false" hidden="false" name="partners_y4" vbProcedure="false">'Scenario Parameters'!$B$64</definedName>
+    <definedName function="false" hidden="false" name="partners_y5" vbProcedure="false">'Scenario Parameters'!$B$65</definedName>
+    <definedName function="false" hidden="false" name="partners_y6" vbProcedure="false">'Scenario Parameters'!$B$66</definedName>
+    <definedName function="false" hidden="false" name="partners_y7" vbProcedure="false">'Scenario Parameters'!$B$67</definedName>
     <definedName function="false" hidden="false" name="persistency_m13" vbProcedure="false">'Scenario Parameters'!$B$10</definedName>
-    <definedName function="false" hidden="false" name="pm_share" vbProcedure="false">'Scenario Parameters'!$B$41</definedName>
+    <definedName function="false" hidden="false" name="pm_share" vbProcedure="false">'Scenario Parameters'!$B$40</definedName>
     <definedName function="false" hidden="false" name="ramp_y1" vbProcedure="false">Assumptions!$B$99</definedName>
     <definedName function="false" hidden="false" name="ramp_y2" vbProcedure="false">Assumptions!$B$100</definedName>
     <definedName function="false" hidden="false" name="ramp_y3" vbProcedure="false">Assumptions!$B$101</definedName>
@@ -117,7 +113,7 @@
     <definedName function="false" hidden="false" name="redemption_rate" vbProcedure="false">'Scenario Parameters'!$B$32</definedName>
     <definedName function="false" hidden="false" name="referral_conversion" vbProcedure="false">'Scenario Parameters'!$B$20</definedName>
     <definedName function="false" hidden="false" name="referral_rate" vbProcedure="false">'Scenario Parameters'!$B$19</definedName>
-    <definedName function="false" hidden="false" name="replacement_events" vbProcedure="false">'Scenario Parameters'!$B$47</definedName>
+    <definedName function="false" hidden="false" name="replacement_events" vbProcedure="false">'Scenario Parameters'!$B$45</definedName>
     <definedName function="false" hidden="false" name="replacement_fee" vbProcedure="false">Assumptions!$B$21</definedName>
     <definedName function="false" hidden="false" name="scenario_index" vbProcedure="false">'Scenario Parameters'!$C$6</definedName>
     <definedName function="false" hidden="false" name="seasonality_amplitude" vbProcedure="false">'Scenario Parameters'!$B$22</definedName>
@@ -133,12 +129,11 @@
     <definedName function="false" hidden="false" name="spot_attach" vbProcedure="false">'Scenario Parameters'!$B$34</definedName>
     <definedName function="false" hidden="false" name="spot_frequency" vbProcedure="false">'Scenario Parameters'!$B$36</definedName>
     <definedName function="false" hidden="false" name="spot_ticket_mult" vbProcedure="false">'Scenario Parameters'!$B$35</definedName>
-    <definedName function="false" hidden="false" name="spot_to_sip" vbProcedure="false">'Scenario Parameters'!$B$37</definedName>
-    <definedName function="false" hidden="false" name="sw_lapsed_keeps_card" vbProcedure="false">'Scenario Parameters'!$B$84</definedName>
-    <definedName function="false" hidden="false" name="sw_prepaid_vs_credit" vbProcedure="false">'Scenario Parameters'!$B$83</definedName>
-    <definedName function="false" hidden="false" name="ticket_gulf" vbProcedure="false">'Scenario Parameters'!$B$75</definedName>
-    <definedName function="false" hidden="false" name="ticket_india" vbProcedure="false">'Scenario Parameters'!$B$76</definedName>
-    <definedName function="false" hidden="false" name="ticket_uae" vbProcedure="false">'Scenario Parameters'!$B$74</definedName>
+    <definedName function="false" hidden="false" name="sw_lapsed_keeps_card" vbProcedure="false">'Scenario Parameters'!$B$79</definedName>
+    <definedName function="false" hidden="false" name="sw_prepaid_vs_credit" vbProcedure="false">'Scenario Parameters'!$B$78</definedName>
+    <definedName function="false" hidden="false" name="ticket_gulf" vbProcedure="false">'Scenario Parameters'!$B$73</definedName>
+    <definedName function="false" hidden="false" name="ticket_india" vbProcedure="false">'Scenario Parameters'!$B$74</definedName>
+    <definedName function="false" hidden="false" name="ticket_uae" vbProcedure="false">'Scenario Parameters'!$B$72</definedName>
     <definedName function="false" hidden="false" name="txn_fee" vbProcedure="false">Assumptions!$B$15</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -151,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="520">
   <si>
     <t xml:space="preserve">Aurumix Revenue Model</t>
   </si>
@@ -966,7 +961,7 @@
     <t xml:space="preserve">% of customers/yr</t>
   </si>
   <si>
-    <t xml:space="preserve">Load-bearing because it is MISSING, not because it is large. ASSUMPTION.</t>
+    <t xml:space="preserve">⚠ NO SOURCE. NOT DERIVED, NOT OBSERVED - CHOSEN. The v2.6 brief records it as a confirmed negative: 'S45, S46 and S47 are all Low confidence with no published source. There is no spot-attach benchmark for any comparable gold or savings product anywhere.' Load-bearing because it is MISSING, not because it is large. WHAT IT ASSERTS, in plain terms: 14% x 1.7 = 0.238 purchases per paying customer per year, i.e. the average customer makes a one-off gold purchase about once every four years. The only cross-check is Augmont's 0.85 transactions per REGISTERED user per year, which we sit at 28% of - but their average transaction is Rs 331, so they are counting micro-savings rather than lumps. It bounds this number; it does not confirm it. ⚠ KNOWN SIMPLIFICATION WITH A KNOWN DIRECTION: v2.6 applied a TENURE UPLIFT here - 'a 3-year account is ~2x as likely to buy spot as a 6-month account' - which the v3.0 simplification dropped. This rate is now flat from day one. If 14% was calibrated on a mature book, SPOT IS OVERSTATED IN THE EARLY YEARS, when nearly every account is young. Not rebuilt because spot is ~1.4% of Y7 revenue; restore the uplift in the Phase 5 simulation. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Spot ticket scenario multiplier</t>
@@ -987,15 +982,6 @@
     <t xml:space="preserve">⚠ PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
   </si>
   <si>
-    <t xml:space="preserve">Spot-to-SIP conversion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of spot buyers/yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO SOURCE EXISTS ANYWHERE - re-confirmed by search 2026-08-20, a CONFIRMED NEGATIVE rather than a gap in the searching. The mechanism design calls this arrow 'the growth funnel' and names spot 'the entry point for new investors'. THE STRATEGY QUESTION IN NUMERICAL FORM, and the one an experiment could answer.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Programme manager share of interchange</t>
   </si>
   <si>
@@ -1020,15 +1006,6 @@
     <t xml:space="preserve">RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
   </si>
   <si>
-    <t xml:space="preserve">Card transactions per active card per month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transactions/month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE INPUT IS FREQUENCY; AVERAGE TICKET IS DERIVED FROM IT. That inversion is deliberate. Monthly spend is already pinned by income (a multiple of the SIP ticket) and capped by the gold collateral, so specifying a ticket size would over-determine the card and let it drift away from what the customer actually saves - the exact problem an absolute AED 100 ticket created. Fixing frequency instead makes the average ticket fall out as spend / frequency, which means IT SCALES WITH THE SIP CONTRIBUTION AUTOMATICALLY: a customer on a smaller monthly savings amount gets a proportionally smaller basket, in every region, with no extra input. WHY FREQUENCY IS THE BETTER THING TO ANCHOR: it has a published number and ticket size does not. Visa scheme data gives ~175 transactions per card per year for the region, about 14-15/month, and UAE low-income cash dependency fell from 84% to 69% in two years, so card usage is rising. Base is set at 12, slightly BELOW the general anchor, because this is a secondary card earned on a savings product rather than someone's main salary card. ⚠ THE UAE-WIDE AVERAGE TICKET OF ~AED 313 IS DELIBERATELY NOT USED - it spans affluent expats and corporate cards, which is the same population mismatch that put card spend at AED 6,000. NO PUBLISHED TICKET SIZE OR FREQUENCY EXISTS FOR BLUE-COLLAR GCC WORKERS SPECIFICALLY - a confirmed negative, re-checked 2026-08-20. TRIANGULATED on frequency, DERIVED on ticket.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Foreign spend share (mean)</t>
   </si>
   <si>
@@ -1156,21 +1133,6 @@
   </si>
   <si>
     <t xml:space="preserve">Average monthly ticket - India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of new customers - UAE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of new</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DERIVED from market size: each region's share of acquisition equals its share of the addressable ceiling, so acquisition follows the opportunity. Previously these were four typed numbers with no basis, which sent 34% of acquisition to Oman and Bahrain - a market that is 16% of the opportunity - and only 8% to India, which is 26% of it. Because they are derived they sum to 1.000 by construction and cannot drift out of line with the ceilings. Shares are RENORMALISED on the Model for regions not yet open, so a region that opens later redistributes rather than vanishing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of new customers - Oman and Bahrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of new customers - India</t>
   </si>
   <si>
     <t xml:space="preserve">Prepaid instead of credit</t>
@@ -2648,7 +2610,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q169"/>
+  <dimension ref="A1:Q164"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
@@ -4484,26 +4446,26 @@
         <v>278</v>
       </c>
       <c r="B133" s="32" t="n">
-        <f aca="false">'Scenario Parameters'!$B$37</f>
-        <v>0.08</v>
+        <f aca="false">'Scenario Parameters'!$B$40</f>
+        <v>0.72</v>
       </c>
       <c r="C133" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D133" s="0" t="s">
         <v>279</v>
-      </c>
-      <c r="D133" s="0" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B134" s="32" t="n">
         <f aca="false">'Scenario Parameters'!$B$41</f>
-        <v>0.72</v>
+        <v>0.18</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="D134" s="0" t="s">
         <v>282</v>
@@ -4513,9 +4475,9 @@
       <c r="A135" s="0" t="s">
         <v>283</v>
       </c>
-      <c r="B135" s="32" t="n">
+      <c r="B135" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$42</f>
-        <v>0.18</v>
+        <v>4</v>
       </c>
       <c r="C135" s="0" t="s">
         <v>284</v>
@@ -4528,9 +4490,9 @@
       <c r="A136" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="B136" s="36" t="n">
+      <c r="B136" s="32" t="n">
         <f aca="false">'Scenario Parameters'!$B$43</f>
-        <v>4</v>
+        <v>0.34</v>
       </c>
       <c r="C136" s="0" t="s">
         <v>287</v>
@@ -4543,9 +4505,9 @@
       <c r="A137" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="B137" s="36" t="n">
+      <c r="B137" s="34" t="n">
         <f aca="false">'Scenario Parameters'!$B$44</f>
-        <v>12</v>
+        <v>1.06</v>
       </c>
       <c r="C137" s="0" t="s">
         <v>290</v>
@@ -4558,177 +4520,177 @@
       <c r="A138" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="B138" s="32" t="n">
+      <c r="B138" s="34" t="n">
         <f aca="false">'Scenario Parameters'!$B$45</f>
-        <v>0.34</v>
+        <v>0.11</v>
       </c>
       <c r="C138" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="D138" s="0" t="s">
         <v>293</v>
-      </c>
-      <c r="D138" s="0" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B139" s="32" t="n">
+        <f aca="false">'Scenario Parameters'!$B$46</f>
+        <v>0.6</v>
+      </c>
+      <c r="C139" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D139" s="0" t="s">
         <v>295</v>
-      </c>
-      <c r="B139" s="34" t="n">
-        <f aca="false">'Scenario Parameters'!$B$46</f>
-        <v>1.06</v>
-      </c>
-      <c r="C139" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="D139" s="0" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>298</v>
-      </c>
-      <c r="B140" s="34" t="n">
+        <v>296</v>
+      </c>
+      <c r="B140" s="32" t="n">
         <f aca="false">'Scenario Parameters'!$B$47</f>
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>296</v>
+        <v>226</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B141" s="32" t="n">
         <f aca="false">'Scenario Parameters'!$B$48</f>
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="C141" s="0" t="s">
         <v>226</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B142" s="32" t="n">
         <f aca="false">'Scenario Parameters'!$B$49</f>
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>226</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="B143" s="32" t="n">
+        <v>299</v>
+      </c>
+      <c r="B143" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$50</f>
-        <v>0.12</v>
+        <v>250</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="B144" s="32" t="n">
+        <v>301</v>
+      </c>
+      <c r="B144" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$51</f>
-        <v>0.03</v>
+        <v>1000</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B145" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$52</f>
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="C145" s="0" t="s">
         <v>63</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B146" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$53</f>
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C146" s="0" t="s">
         <v>63</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>308</v>
-      </c>
-      <c r="B147" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$54</f>
-        <v>2250</v>
+        <v>304</v>
+      </c>
+      <c r="B147" s="32" t="n">
+        <f aca="false">'Scenario Parameters'!$B$57</f>
+        <v>0.5</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>309</v>
-      </c>
-      <c r="B148" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$55</f>
-        <v>4000</v>
+        <v>306</v>
+      </c>
+      <c r="B148" s="34" t="n">
+        <f aca="false">'Scenario Parameters'!$B$58</f>
+        <v>0.42</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>63</v>
+        <v>307</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B149" s="34" t="n">
+        <f aca="false">'Scenario Parameters'!$B$59</f>
+        <v>2.1</v>
+      </c>
+      <c r="C149" s="0" t="s">
         <v>310</v>
-      </c>
-      <c r="B149" s="32" t="n">
-        <f aca="false">'Scenario Parameters'!$B$59</f>
-        <v>0.5</v>
-      </c>
-      <c r="C149" s="0" t="s">
-        <v>226</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>311</v>
@@ -4738,290 +4700,215 @@
       <c r="A150" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="B150" s="34" t="n">
+      <c r="B150" s="32" t="n">
         <f aca="false">'Scenario Parameters'!$B$60</f>
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="C150" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="D150" s="0" t="s">
         <v>313</v>
-      </c>
-      <c r="D150" s="0" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="B151" s="36" t="n">
+        <f aca="false">'Scenario Parameters'!$B$61</f>
+        <v>0</v>
+      </c>
+      <c r="C151" s="0" t="s">
         <v>315</v>
       </c>
-      <c r="B151" s="34" t="n">
-        <f aca="false">'Scenario Parameters'!$B$61</f>
-        <v>2.1</v>
-      </c>
-      <c r="C151" s="0" t="s">
+      <c r="D151" s="0" t="s">
         <v>316</v>
-      </c>
-      <c r="D151" s="0" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>318</v>
-      </c>
-      <c r="B152" s="32" t="n">
+        <v>317</v>
+      </c>
+      <c r="B152" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$62</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B153" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$63</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D153" s="0" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B154" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$64</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D154" s="0" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B155" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$65</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B156" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$66</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D156" s="0" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B157" s="36" t="n">
         <f aca="false">'Scenario Parameters'!$B$67</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D157" s="0" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="B158" s="36" t="n">
+        <v>323</v>
+      </c>
+      <c r="B158" s="35" t="n">
         <f aca="false">'Scenario Parameters'!$B$68</f>
-        <v>5</v>
+        <v>32000000</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>321</v>
+        <v>109</v>
       </c>
       <c r="D158" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="B159" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$69</f>
-        <v>6</v>
+        <v>325</v>
+      </c>
+      <c r="B159" s="35" t="n">
+        <f aca="false">'Scenario Parameters'!$B$72</f>
+        <v>33.6</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>321</v>
+        <v>103</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B160" s="35" t="n">
-        <f aca="false">'Scenario Parameters'!$B$70</f>
-        <v>32000000</v>
+        <f aca="false">'Scenario Parameters'!$B$73</f>
+        <v>26</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D160" s="0" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B161" s="35" t="n">
         <f aca="false">'Scenario Parameters'!$B$74</f>
-        <v>33.6</v>
+        <v>30</v>
       </c>
       <c r="C161" s="0" t="s">
         <v>103</v>
       </c>
       <c r="D161" s="0" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>333</v>
-      </c>
-      <c r="B162" s="35" t="n">
-        <f aca="false">'Scenario Parameters'!$B$75</f>
-        <v>26</v>
+        <v>329</v>
+      </c>
+      <c r="B162" s="36" t="n">
+        <f aca="false">'Scenario Parameters'!$B$78</f>
+        <v>0</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>103</v>
+        <v>330</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
+        <v>332</v>
+      </c>
+      <c r="B163" s="36" t="n">
+        <f aca="false">'Scenario Parameters'!$B$79</f>
+        <v>1</v>
+      </c>
+      <c r="C163" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="D163" s="0" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="9" t="s">
         <v>334</v>
-      </c>
-      <c r="B163" s="35" t="n">
-        <f aca="false">'Scenario Parameters'!$B$76</f>
-        <v>30</v>
-      </c>
-      <c r="C163" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="D163" s="0" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="B164" s="32" t="n">
-        <f aca="false">'Scenario Parameters'!$B$77</f>
-        <v>0.626084007279636</v>
-      </c>
-      <c r="C164" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="D164" s="0" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="B165" s="32" t="n">
-        <f aca="false">'Scenario Parameters'!$B$78</f>
-        <v>0.132405993819994</v>
-      </c>
-      <c r="C165" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="D165" s="0" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="s">
-        <v>339</v>
-      </c>
-      <c r="B166" s="32" t="n">
-        <f aca="false">'Scenario Parameters'!$B$79</f>
-        <v>0.24150999890037</v>
-      </c>
-      <c r="C166" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="D166" s="0" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="B167" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$83</f>
-        <v>0</v>
-      </c>
-      <c r="C167" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="D167" s="0" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="B168" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$84</f>
-        <v>1</v>
-      </c>
-      <c r="C168" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="D168" s="0" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="9" t="s">
-        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -5040,7 +4927,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -5058,12 +4945,12 @@
     </row>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5072,25 +4959,25 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">IF($B$6="Base",1,IF($B$6="Aggressive",2,3))</f>
         <v>1</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -5102,16 +4989,16 @@
         <v>30</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>32</v>
@@ -5422,7 +5309,7 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5434,16 +5321,16 @@
         <v>30</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>32</v>
@@ -5499,7 +5386,7 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -5511,16 +5398,16 @@
         <v>30</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>32</v>
@@ -5670,78 +5557,78 @@
         <v>277</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
         <v>278</v>
       </c>
-      <c r="B37" s="38" t="n">
-        <f aca="false">CHOOSE($C$6,C37,D37,E37)</f>
-        <v>0.08</v>
-      </c>
-      <c r="C37" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E37" s="19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F37" s="23" t="s">
+      <c r="B40" s="38" t="n">
+        <f aca="false">CHOOSE($C$6,C40,D40,E40)</f>
+        <v>0.72</v>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="G40" s="9" t="s">
         <v>279</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B41" s="38" t="n">
         <f aca="false">CHOOSE($C$6,C41,D41,E41)</f>
-        <v>0.72</v>
+        <v>0.18</v>
       </c>
       <c r="C41" s="19" t="n">
-        <v>0.72</v>
+        <v>0.18</v>
       </c>
       <c r="D41" s="19" t="n">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>0.55</v>
+        <v>0.08</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>282</v>
@@ -5751,18 +5638,18 @@
       <c r="A42" s="0" t="s">
         <v>283</v>
       </c>
-      <c r="B42" s="38" t="n">
+      <c r="B42" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C42,D42,E42)</f>
-        <v>0.18</v>
-      </c>
-      <c r="C42" s="19" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D42" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E42" s="19" t="n">
-        <v>0.08</v>
+        <v>4</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="F42" s="23" t="s">
         <v>284</v>
@@ -5775,18 +5662,18 @@
       <c r="A43" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="B43" s="31" t="n">
+      <c r="B43" s="38" t="n">
         <f aca="false">CHOOSE($C$6,C43,D43,E43)</f>
-        <v>4</v>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>2</v>
+        <v>0.34</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>0.24</v>
       </c>
       <c r="F43" s="23" t="s">
         <v>287</v>
@@ -5799,18 +5686,18 @@
       <c r="A44" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="40" t="n">
         <f aca="false">CHOOSE($C$6,C44,D44,E44)</f>
-        <v>12</v>
-      </c>
-      <c r="C44" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D44" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>8</v>
+        <v>1.06</v>
+      </c>
+      <c r="C44" s="15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>1.1</v>
       </c>
       <c r="F44" s="23" t="s">
         <v>290</v>
@@ -5823,314 +5710,314 @@
       <c r="A45" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="B45" s="38" t="n">
+      <c r="B45" s="40" t="n">
         <f aca="false">CHOOSE($C$6,C45,D45,E45)</f>
-        <v>0.34</v>
-      </c>
-      <c r="C45" s="19" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="D45" s="19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
+      </c>
+      <c r="C45" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.18</v>
       </c>
       <c r="F45" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="G45" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" s="38" t="n">
+        <f aca="false">CHOOSE($C$6,C46,D46,E46)</f>
+        <v>0.6</v>
+      </c>
+      <c r="C46" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="B46" s="40" t="n">
-        <f aca="false">CHOOSE($C$6,C46,D46,E46)</f>
-        <v>1.06</v>
-      </c>
-      <c r="C46" s="15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>298</v>
-      </c>
-      <c r="B47" s="40" t="n">
+        <v>296</v>
+      </c>
+      <c r="B47" s="38" t="n">
         <f aca="false">CHOOSE($C$6,C47,D47,E47)</f>
-        <v>0.11</v>
-      </c>
-      <c r="C47" s="15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D47" s="15" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="E47" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C47" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E47" s="19" t="n">
         <v>0.18</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>296</v>
+        <v>226</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B48" s="38" t="n">
         <f aca="false">CHOOSE($C$6,C48,D48,E48)</f>
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="C48" s="19" t="n">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="D48" s="19" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>0.74</v>
+        <v>0.06</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>226</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B49" s="38" t="n">
         <f aca="false">CHOOSE($C$6,C49,D49,E49)</f>
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="C49" s="19" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="D49" s="19" t="n">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="E49" s="19" t="n">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
       <c r="F49" s="23" t="s">
         <v>226</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>303</v>
-      </c>
-      <c r="B50" s="38" t="n">
+        <v>299</v>
+      </c>
+      <c r="B50" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C50,D50,E50)</f>
-        <v>0.12</v>
-      </c>
-      <c r="C50" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D50" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E50" s="19" t="n">
-        <v>0.06</v>
+        <v>250</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>200</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>304</v>
-      </c>
-      <c r="B51" s="38" t="n">
+        <v>301</v>
+      </c>
+      <c r="B51" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C51,D51,E51)</f>
-        <v>0.03</v>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D51" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>0.02</v>
+        <v>1000</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>900</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>226</v>
+        <v>63</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B52" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C52,D52,E52)</f>
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="D52" s="17" t="n">
-        <v>300</v>
+        <v>2400</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="F52" s="23" t="s">
         <v>63</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B53" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C53,D53,E53)</f>
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="D53" s="17" t="n">
-        <v>1100</v>
+        <v>4500</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>900</v>
+        <v>3600</v>
       </c>
       <c r="F53" s="23" t="s">
         <v>63</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="F56" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>304</v>
+      </c>
+      <c r="B57" s="38" t="n">
+        <f aca="false">CHOOSE($C$6,C57,D57,E57)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="B58" s="40" t="n">
+        <f aca="false">CHOOSE($C$6,C58,D58,E58)</f>
+        <v>0.42</v>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="G58" s="9" t="s">
         <v>308</v>
-      </c>
-      <c r="B54" s="31" t="n">
-        <f aca="false">CHOOSE($C$6,C54,D54,E54)</f>
-        <v>2250</v>
-      </c>
-      <c r="C54" s="17" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D54" s="17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>309</v>
-      </c>
-      <c r="B55" s="31" t="n">
-        <f aca="false">CHOOSE($C$6,C55,D55,E55)</f>
-        <v>4000</v>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D55" s="17" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F55" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E58" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="F58" s="14" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B59" s="40" t="n">
+        <f aca="false">CHOOSE($C$6,C59,D59,E59)</f>
+        <v>2.1</v>
+      </c>
+      <c r="C59" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D59" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F59" s="23" t="s">
         <v>310</v>
-      </c>
-      <c r="B59" s="38" t="n">
-        <f aca="false">CHOOSE($C$6,C59,D59,E59)</f>
-        <v>0.5</v>
-      </c>
-      <c r="C59" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D59" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E59" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F59" s="23" t="s">
-        <v>226</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>311</v>
@@ -6140,469 +6027,376 @@
       <c r="A60" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="B60" s="40" t="n">
+      <c r="B60" s="38" t="n">
         <f aca="false">CHOOSE($C$6,C60,D60,E60)</f>
-        <v>0.42</v>
-      </c>
-      <c r="C60" s="15" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D60" s="15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>0.1</v>
       </c>
       <c r="F60" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="G60" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="G60" s="9" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
+        <v>314</v>
+      </c>
+      <c r="B61" s="31" t="n">
+        <f aca="false">CHOOSE($C$6,C61,D61,E61)</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="B61" s="40" t="n">
-        <f aca="false">CHOOSE($C$6,C61,D61,E61)</f>
-        <v>2.1</v>
-      </c>
-      <c r="C61" s="15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D61" s="15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F61" s="23" t="s">
+      <c r="G61" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>318</v>
-      </c>
-      <c r="B62" s="38" t="n">
+        <v>317</v>
+      </c>
+      <c r="B62" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C62,D62,E62)</f>
-        <v>0.2</v>
-      </c>
-      <c r="C62" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D62" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E62" s="19" t="n">
-        <v>0.1</v>
+        <v>1</v>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="F62" s="23" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B63" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C63,D63,E63)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="23" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B64" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C64,D64,E64)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B65" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C65,D65,E65)</f>
+        <v>4</v>
+      </c>
+      <c r="C65" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E65" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="C65" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>1</v>
-      </c>
       <c r="F65" s="23" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B66" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C66,D66,E66)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D66" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="23" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B67" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C67,D67,E67)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D67" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E67" s="17" t="n">
         <v>2</v>
       </c>
       <c r="F67" s="23" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
+        <v>323</v>
+      </c>
+      <c r="B68" s="41" t="n">
+        <f aca="false">CHOOSE($C$6,C68,D68,E68)</f>
+        <v>32000000</v>
+      </c>
+      <c r="C68" s="20" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="D68" s="20" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="E68" s="20" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="F68" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="E71" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="0" t="s">
+        <v>325</v>
+      </c>
+      <c r="B72" s="41" t="n">
+        <f aca="false">CHOOSE($C$6,C72,D72,E72)</f>
+        <v>33.6</v>
+      </c>
+      <c r="C72" s="20" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="D72" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="E72" s="20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
         <v>327</v>
       </c>
-      <c r="B68" s="31" t="n">
-        <f aca="false">CHOOSE($C$6,C68,D68,E68)</f>
-        <v>5</v>
-      </c>
-      <c r="C68" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F68" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>328</v>
-      </c>
-      <c r="B69" s="31" t="n">
-        <f aca="false">CHOOSE($C$6,C69,D69,E69)</f>
-        <v>6</v>
-      </c>
-      <c r="C69" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D69" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>329</v>
-      </c>
-      <c r="B70" s="41" t="n">
-        <f aca="false">CHOOSE($C$6,C70,D70,E70)</f>
-        <v>32000000</v>
-      </c>
-      <c r="C70" s="20" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="D70" s="20" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E70" s="20" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="F73" s="14" t="s">
+      <c r="B73" s="41" t="n">
+        <f aca="false">CHOOSE($C$6,C73,D73,E73)</f>
+        <v>26</v>
+      </c>
+      <c r="C73" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="D73" s="20" t="n">
         <v>32</v>
+      </c>
+      <c r="E73" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B74" s="41" t="n">
         <f aca="false">CHOOSE($C$6,C74,D74,E74)</f>
-        <v>33.6</v>
+        <v>30</v>
       </c>
       <c r="C74" s="20" t="n">
-        <v>33.6</v>
+        <v>30</v>
       </c>
       <c r="D74" s="20" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E74" s="20" t="n">
-        <v>26.5</v>
+        <v>24</v>
       </c>
       <c r="F74" s="23" t="s">
         <v>103</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>333</v>
-      </c>
-      <c r="B75" s="41" t="n">
-        <f aca="false">CHOOSE($C$6,C75,D75,E75)</f>
-        <v>26</v>
-      </c>
-      <c r="C75" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="D75" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="E75" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="F75" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>334</v>
-      </c>
-      <c r="B76" s="41" t="n">
-        <f aca="false">CHOOSE($C$6,C76,D76,E76)</f>
-        <v>30</v>
-      </c>
-      <c r="C76" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="D76" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E76" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F76" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>332</v>
-      </c>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B76" s="13"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="13"/>
+      <c r="E76" s="13"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>335</v>
-      </c>
-      <c r="B77" s="38" t="n">
-        <f aca="false">Assumptions!$B$81/(Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)</f>
-        <v>0.626084007279636</v>
-      </c>
-      <c r="F77" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>337</v>
+      <c r="A77" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="D77" s="14" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>338</v>
-      </c>
-      <c r="B78" s="38" t="n">
-        <f aca="false">Assumptions!$B$82/(Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)</f>
-        <v>0.132405993819994</v>
-      </c>
-      <c r="F78" s="23" t="s">
-        <v>336</v>
+        <v>329</v>
+      </c>
+      <c r="B78" s="31" t="n">
+        <f aca="false">IF($C$78="Prepaid",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C78" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>356</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>339</v>
-      </c>
-      <c r="B79" s="38" t="n">
-        <f aca="false">Assumptions!$B$83/(Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)</f>
-        <v>0.24150999890037</v>
-      </c>
-      <c r="F79" s="23" t="s">
-        <v>336</v>
+        <v>332</v>
+      </c>
+      <c r="B79" s="31" t="n">
+        <f aca="false">IF($C$79="ON",1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="C79" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="D79" s="23" t="s">
+        <v>357</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>340</v>
-      </c>
-      <c r="B83" s="31" t="n">
-        <f aca="false">IF($C$83="Prepaid",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C83" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="D83" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>343</v>
-      </c>
-      <c r="B84" s="31" t="n">
-        <f aca="false">IF($C$84="ON",1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="C84" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="D84" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -6611,11 +6405,11 @@
       <formula1>"Base,Aggressive,Conservative"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C78" type="list">
       <formula1>"Credit,Prepaid"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C84" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C79" type="list">
       <formula1>"ON,OFF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6651,10 +6445,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C2" s="28" t="n">
         <v>1</v>
@@ -6746,200 +6540,200 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>365</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>366</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>367</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>368</v>
+      </c>
+      <c r="J3" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="K3" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="L3" s="42" t="s">
         <v>371</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="M3" s="42" t="s">
         <v>372</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="N3" s="42" t="s">
         <v>373</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="O3" s="42" t="s">
         <v>374</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="P3" s="42" t="s">
         <v>375</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="Q3" s="42" t="s">
         <v>376</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="R3" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="S3" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="I3" s="42" t="s">
+      <c r="T3" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="U3" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="V3" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="W3" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="X3" s="42" t="s">
         <v>383</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="Y3" s="42" t="s">
         <v>384</v>
       </c>
-      <c r="O3" s="42" t="s">
+      <c r="Z3" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="AA3" s="42" t="s">
         <v>386</v>
       </c>
-      <c r="Q3" s="42" t="s">
+      <c r="AB3" s="42" t="s">
         <v>387</v>
       </c>
-      <c r="R3" s="42" t="s">
+      <c r="AC3" s="42" t="s">
         <v>388</v>
       </c>
-      <c r="S3" s="42" t="s">
+      <c r="AD3" s="42" t="s">
         <v>389</v>
       </c>
-      <c r="T3" s="42" t="s">
+      <c r="AE3" s="42" t="s">
         <v>390</v>
-      </c>
-      <c r="U3" s="42" t="s">
-        <v>391</v>
-      </c>
-      <c r="V3" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="W3" s="42" t="s">
-        <v>393</v>
-      </c>
-      <c r="X3" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="Y3" s="42" t="s">
-        <v>395</v>
-      </c>
-      <c r="Z3" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="AA3" s="42" t="s">
-        <v>397</v>
-      </c>
-      <c r="AB3" s="42" t="s">
-        <v>398</v>
-      </c>
-      <c r="AC3" s="42" t="s">
-        <v>399</v>
-      </c>
-      <c r="AD3" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="AE3" s="42" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="F4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="H4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="J4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="K4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="L4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="M4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="N4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="O4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="P4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="Q4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="R4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="S4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="T4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="V4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="W4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="X4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="Y4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="Z4" s="43" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="AA4" s="43" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="AB4" s="43" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="AC4" s="43" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="AD4" s="43" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="AE4" s="43" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C5" s="44" t="n">
         <v>1</v>
@@ -7031,10 +6825,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C6" s="44" t="n">
         <v>1</v>
@@ -7126,7 +6920,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>259</v>
@@ -7221,10 +7015,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="C8" s="44" t="n">
         <v>0</v>
@@ -7316,7 +7110,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B10" s="46"/>
       <c r="C10" s="46"/>
@@ -7351,10 +7145,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C11" s="47" t="n">
         <f aca="false">(1+(Assumptions!$F$58-1)*Assumptions!$B$124)*12/SUMPRODUCT(1+(Assumptions!$F$58:$Q$58-1)*Assumptions!$B$124)</f>
@@ -7407,10 +7201,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C12" s="47" t="n">
         <f aca="false">(1+(Assumptions!$F$59-1)*Assumptions!$B$124)*12/SUMPRODUCT(1+(Assumptions!$F$59:$Q$59-1)*Assumptions!$B$124)</f>
@@ -7463,66 +7257,66 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C13" s="48" t="n">
-        <f aca="false">Assumptions!$F$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$F$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.256603773584906</v>
       </c>
       <c r="D13" s="48" t="n">
-        <f aca="false">Assumptions!$G$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$G$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.256603773584906</v>
       </c>
       <c r="E13" s="48" t="n">
-        <f aca="false">Assumptions!$H$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$H$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.256603773584906</v>
       </c>
       <c r="F13" s="48" t="n">
-        <f aca="false">Assumptions!$I$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$I$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.273710691823899</v>
       </c>
       <c r="G13" s="48" t="n">
-        <f aca="false">Assumptions!$J$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$J$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.290817610062893</v>
       </c>
       <c r="H13" s="48" t="n">
-        <f aca="false">Assumptions!$K$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$K$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.470440251572327</v>
       </c>
       <c r="I13" s="48" t="n">
-        <f aca="false">Assumptions!$L$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$L$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.513207547169811</v>
       </c>
       <c r="J13" s="48" t="n">
-        <f aca="false">Assumptions!$M$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$M$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.478993710691824</v>
       </c>
       <c r="K13" s="48" t="n">
-        <f aca="false">Assumptions!$N$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$N$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.307924528301887</v>
       </c>
       <c r="L13" s="48" t="n">
-        <f aca="false">Assumptions!$O$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$O$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.359245283018868</v>
       </c>
       <c r="M13" s="48" t="n">
-        <f aca="false">Assumptions!$P$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$P$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.342138364779874</v>
       </c>
       <c r="N13" s="48" t="n">
-        <f aca="false">Assumptions!$Q$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f aca="false">Assumptions!$Q$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v>0.273710691823899</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C14" s="49" t="n">
         <f aca="false">SUM($C$11:$N$11)</f>
@@ -7535,10 +7329,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="C15" s="50" t="n">
         <f aca="false">IF(C7=1,INDEX($C$11:$N$11,1,C6),1)</f>
@@ -7659,10 +7453,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="C16" s="50" t="n">
         <f aca="false">IF(C7=1,INDEX($C$12:$N$12,1,C6),1)</f>
@@ -7783,7 +7577,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>226</v>
@@ -7907,7 +7701,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="45" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="46"/>
@@ -7942,7 +7736,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>185</v>
@@ -8066,10 +7860,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C21" s="47" t="n">
         <f aca="false">Assumptions!$B$106*1+Assumptions!$B$107*IF(C2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(C2&gt;=Assumptions!$B$54,1,0)</f>
@@ -8190,7 +7984,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="45" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="B23" s="46"/>
       <c r="C23" s="46"/>
@@ -8225,7 +8019,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>185</v>
@@ -8349,7 +8143,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>185</v>
@@ -8472,7 +8266,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>185</v>
@@ -8596,10 +8390,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C27" s="50" t="n">
         <v>1</v>
@@ -8719,7 +8513,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>185</v>
@@ -8843,7 +8637,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B29" s="23" t="s">
         <v>185</v>
@@ -8967,7 +8761,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>185</v>
@@ -9091,7 +8885,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B31" s="23" t="s">
         <v>185</v>
@@ -9215,7 +9009,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>185</v>
@@ -9339,131 +9133,131 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C33" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$44,C29*Assumptions!$B$161*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$44,C29*Assumptions!$B$159*C7,0)</f>
         <v>1094.54304911931</v>
       </c>
       <c r="D33" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$44,D29*Assumptions!$B$161*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$44,D29*Assumptions!$B$159*D7,0)</f>
         <v>2081.40063983363</v>
       </c>
       <c r="E33" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$44,E29*Assumptions!$B$161*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$44,E29*Assumptions!$B$159*E7,0)</f>
         <v>2976.68339387234</v>
       </c>
       <c r="F33" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$44,F29*Assumptions!$B$161*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$44,F29*Assumptions!$B$159*F7,0)</f>
         <v>4077.2313601391</v>
       </c>
       <c r="G33" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$44,G29*Assumptions!$B$161*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$44,G29*Assumptions!$B$159*G7,0)</f>
         <v>5004.80887514993</v>
       </c>
       <c r="H33" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$44,H29*Assumptions!$B$161*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$44,H29*Assumptions!$B$159*H7,0)</f>
         <v>5713.82932010027</v>
       </c>
       <c r="I33" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$44,I29*Assumptions!$B$161*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$44,I29*Assumptions!$B$159*I7,0)</f>
         <v>6355.69296722831</v>
       </c>
       <c r="J33" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$44,J29*Assumptions!$B$161*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$44,J29*Assumptions!$B$159*J7,0)</f>
         <v>6966.13473645063</v>
       </c>
       <c r="K33" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$44,K29*Assumptions!$B$161*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$44,K29*Assumptions!$B$159*K7,0)</f>
         <v>7633.18480946622</v>
       </c>
       <c r="L33" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$44,L29*Assumptions!$B$161*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$44,L29*Assumptions!$B$159*L7,0)</f>
         <v>8613.46257029891</v>
       </c>
       <c r="M33" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$44,M29*Assumptions!$B$161*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$44,M29*Assumptions!$B$159*M7,0)</f>
         <v>9437.54716853707</v>
       </c>
       <c r="N33" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$44,N29*Assumptions!$B$161*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$44,N29*Assumptions!$B$159*N7,0)</f>
         <v>10069.9319266963</v>
       </c>
       <c r="O33" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$44,O29*Assumptions!$B$161*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$44,O29*Assumptions!$B$159*O7,0)</f>
         <v>13245.8236789219</v>
       </c>
       <c r="P33" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$44,P29*Assumptions!$B$161*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$44,P29*Assumptions!$B$159*P7,0)</f>
         <v>16151.3052685608</v>
       </c>
       <c r="Q33" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$44,Q29*Assumptions!$B$161*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$44,Q29*Assumptions!$B$159*Q7,0)</f>
         <v>18824.7265212321</v>
       </c>
       <c r="R33" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$44,R29*Assumptions!$B$161*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$44,R29*Assumptions!$B$159*R7,0)</f>
         <v>22298.0461483471</v>
       </c>
       <c r="S33" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$44,S29*Assumptions!$B$161*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$44,S29*Assumptions!$B$159*S7,0)</f>
         <v>25259.4117760345</v>
       </c>
       <c r="T33" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$44,T29*Assumptions!$B$161*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$44,T29*Assumptions!$B$159*T7,0)</f>
         <v>27509.3809284406</v>
       </c>
       <c r="U33" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$44,U29*Assumptions!$B$161*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$44,U29*Assumptions!$B$159*U7,0)</f>
         <v>29571.2367489937</v>
       </c>
       <c r="V33" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$44,V29*Assumptions!$B$161*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$44,V29*Assumptions!$B$159*V7,0)</f>
         <v>31569.0787173947</v>
       </c>
       <c r="W33" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$44,W29*Assumptions!$B$161*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$44,W29*Assumptions!$B$159*W7,0)</f>
         <v>33831.2643979833</v>
       </c>
       <c r="X33" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$44,X29*Assumptions!$B$161*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$44,X29*Assumptions!$B$159*X7,0)</f>
         <v>37347.8615367224</v>
       </c>
       <c r="Y33" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$44,Y29*Assumptions!$B$161*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$44,Y29*Assumptions!$B$159*Y7,0)</f>
         <v>40364.4635390667</v>
       </c>
       <c r="Z33" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$44,Z29*Assumptions!$B$161*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$44,Z29*Assumptions!$B$159*Z7,0)</f>
         <v>42708.7143964784</v>
       </c>
       <c r="AA33" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$44,AA29*Assumptions!$B$161*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$44,AA29*Assumptions!$B$159*AA7,0)</f>
         <v>1038433.44430093</v>
       </c>
       <c r="AB33" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$44,AB29*Assumptions!$B$161*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$44,AB29*Assumptions!$B$159*AB7,0)</f>
         <v>1772789.92056143</v>
       </c>
       <c r="AC33" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$44,AC29*Assumptions!$B$161*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$44,AC29*Assumptions!$B$159*AC7,0)</f>
         <v>2752302.66559791</v>
       </c>
       <c r="AD33" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$44,AD29*Assumptions!$B$161*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$44,AD29*Assumptions!$B$159*AD7,0)</f>
         <v>3811295.12674612</v>
       </c>
       <c r="AE33" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$44,AE29*Assumptions!$B$161*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$44,AE29*Assumptions!$B$159*AE7,0)</f>
         <v>4811926.62519251</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>109</v>
@@ -9587,7 +9381,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>47</v>
@@ -9711,10 +9505,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C36" s="55" t="n">
         <f aca="false">(Assumptions!$B$127+Assumptions!$B$128*IF(C29+C31=0,1,(C29+C31*Assumptions!$B$129)/(C29+C31)))*C7/12</f>
@@ -9835,7 +9629,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B37" s="23" t="s">
         <v>47</v>
@@ -9959,7 +9753,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>109</v>
@@ -10083,131 +9877,131 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B39" s="23" t="s">
         <v>185</v>
       </c>
       <c r="C39" s="53" t="n">
-        <f aca="false">C29+C31*Assumptions!$B$168</f>
+        <f aca="false">C29+C31*Assumptions!$B$163</f>
         <v>33.3973333333333</v>
       </c>
       <c r="D39" s="53" t="n">
-        <f aca="false">D29+D31*Assumptions!$B$168</f>
+        <f aca="false">D29+D31*Assumptions!$B$163</f>
         <v>65.1319857813291</v>
       </c>
       <c r="E39" s="53" t="n">
-        <f aca="false">E29+E31*Assumptions!$B$168</f>
+        <f aca="false">E29+E31*Assumptions!$B$163</f>
         <v>95.535848949433</v>
       </c>
       <c r="F39" s="53" t="n">
-        <f aca="false">F29+F31*Assumptions!$B$168</f>
+        <f aca="false">F29+F31*Assumptions!$B$163</f>
         <v>133.530483983591</v>
       </c>
       <c r="G39" s="53" t="n">
-        <f aca="false">G29+G31*Assumptions!$B$168</f>
+        <f aca="false">G29+G31*Assumptions!$B$163</f>
         <v>167.879329102143</v>
       </c>
       <c r="H39" s="53" t="n">
-        <f aca="false">H29+H31*Assumptions!$B$168</f>
+        <f aca="false">H29+H31*Assumptions!$B$163</f>
         <v>196.934923796119</v>
       </c>
       <c r="I39" s="53" t="n">
-        <f aca="false">I29+I31*Assumptions!$B$168</f>
+        <f aca="false">I29+I31*Assumptions!$B$163</f>
         <v>224.992786337787</v>
       </c>
       <c r="J39" s="53" t="n">
-        <f aca="false">J29+J31*Assumptions!$B$168</f>
+        <f aca="false">J29+J31*Assumptions!$B$163</f>
         <v>253.043695620966</v>
       </c>
       <c r="K39" s="53" t="n">
-        <f aca="false">K29+K31*Assumptions!$B$168</f>
+        <f aca="false">K29+K31*Assumptions!$B$163</f>
         <v>283.727084686245</v>
       </c>
       <c r="L39" s="53" t="n">
-        <f aca="false">L29+L31*Assumptions!$B$168</f>
+        <f aca="false">L29+L31*Assumptions!$B$163</f>
         <v>324.957016796835</v>
       </c>
       <c r="M39" s="53" t="n">
-        <f aca="false">M29+M31*Assumptions!$B$168</f>
+        <f aca="false">M29+M31*Assumptions!$B$163</f>
         <v>362.874730605935</v>
       </c>
       <c r="N39" s="53" t="n">
-        <f aca="false">N29+N31*Assumptions!$B$168</f>
+        <f aca="false">N29+N31*Assumptions!$B$163</f>
         <v>396.165209402494</v>
       </c>
       <c r="O39" s="53" t="n">
-        <f aca="false">O29+O31*Assumptions!$B$168</f>
+        <f aca="false">O29+O31*Assumptions!$B$163</f>
         <v>508.002404362146</v>
       </c>
       <c r="P39" s="53" t="n">
-        <f aca="false">P29+P31*Assumptions!$B$168</f>
+        <f aca="false">P29+P31*Assumptions!$B$163</f>
         <v>616.29816642807</v>
       </c>
       <c r="Q39" s="53" t="n">
-        <f aca="false">Q29+Q31*Assumptions!$B$168</f>
+        <f aca="false">Q29+Q31*Assumptions!$B$163</f>
         <v>721.821660853136</v>
       </c>
       <c r="R39" s="53" t="n">
-        <f aca="false">R29+R31*Assumptions!$B$168</f>
+        <f aca="false">R29+R31*Assumptions!$B$163</f>
         <v>855.716492742433</v>
       </c>
       <c r="S39" s="53" t="n">
-        <f aca="false">S29+S31*Assumptions!$B$168</f>
+        <f aca="false">S29+S31*Assumptions!$B$163</f>
         <v>979.140816912924</v>
       </c>
       <c r="T39" s="53" t="n">
-        <f aca="false">T29+T31*Assumptions!$B$168</f>
+        <f aca="false">T29+T31*Assumptions!$B$163</f>
         <v>1085.24996029053</v>
       </c>
       <c r="U39" s="53" t="n">
-        <f aca="false">U29+U31*Assumptions!$B$168</f>
+        <f aca="false">U29+U31*Assumptions!$B$163</f>
         <v>1188.95572367052</v>
       </c>
       <c r="V39" s="53" t="n">
-        <f aca="false">V29+V31*Assumptions!$B$168</f>
+        <f aca="false">V29+V31*Assumptions!$B$163</f>
         <v>1293.76575221657</v>
       </c>
       <c r="W39" s="53" t="n">
-        <f aca="false">W29+W31*Assumptions!$B$168</f>
+        <f aca="false">W29+W31*Assumptions!$B$163</f>
         <v>1409.60415755712</v>
       </c>
       <c r="X39" s="53" t="n">
-        <f aca="false">X29+X31*Assumptions!$B$168</f>
+        <f aca="false">X29+X31*Assumptions!$B$163</f>
         <v>1567.07245294755</v>
       </c>
       <c r="Y39" s="53" t="n">
-        <f aca="false">Y29+Y31*Assumptions!$B$168</f>
+        <f aca="false">Y29+Y31*Assumptions!$B$163</f>
         <v>1714.49931192451</v>
       </c>
       <c r="Z39" s="53" t="n">
-        <f aca="false">Z29+Z31*Assumptions!$B$168</f>
+        <f aca="false">Z29+Z31*Assumptions!$B$163</f>
         <v>1845.88427304582</v>
       </c>
       <c r="AA39" s="53" t="n">
-        <f aca="false">AA29+AA31*Assumptions!$B$168</f>
+        <f aca="false">AA29+AA31*Assumptions!$B$163</f>
         <v>4375.99292120623</v>
       </c>
       <c r="AB39" s="53" t="n">
-        <f aca="false">AB29+AB31*Assumptions!$B$168</f>
+        <f aca="false">AB29+AB31*Assumptions!$B$163</f>
         <v>8394.61044943059</v>
       </c>
       <c r="AC39" s="53" t="n">
-        <f aca="false">AC29+AC31*Assumptions!$B$168</f>
+        <f aca="false">AC29+AC31*Assumptions!$B$163</f>
         <v>14338.2313931956</v>
       </c>
       <c r="AD39" s="53" t="n">
-        <f aca="false">AD29+AD31*Assumptions!$B$168</f>
+        <f aca="false">AD29+AD31*Assumptions!$B$163</f>
         <v>22021.7309320211</v>
       </c>
       <c r="AE39" s="53" t="n">
-        <f aca="false">AE29+AE31*Assumptions!$B$168</f>
+        <f aca="false">AE29+AE31*Assumptions!$B$163</f>
         <v>31103.7458687549</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>185</v>
@@ -10331,131 +10125,131 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C41" s="28" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$48,C40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$48,C40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="D41" s="28" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$48,D40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$48,D40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="E41" s="28" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$48,E40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$48,E40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="F41" s="28" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$48,F40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$48,F40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="G41" s="28" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$48,G40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$48,G40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="H41" s="28" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$48,H40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$48,H40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="I41" s="28" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$48,I40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$48,I40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="J41" s="28" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$48,J40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$48,J40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="K41" s="28" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$48,K40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$48,K40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="L41" s="28" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$48,L40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$48,L40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="M41" s="28" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$48,M40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$48,M40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="N41" s="28" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$48,N40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$48,N40*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="O41" s="28" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$48,O40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$48,O40*Assumptions!$B$134,0)</f>
         <v>16.6200535811122</v>
       </c>
       <c r="P41" s="28" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$48,P40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$48,P40*Assumptions!$B$134,0)</f>
         <v>19.4965574558157</v>
       </c>
       <c r="Q41" s="28" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$48,Q40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$48,Q40*Assumptions!$B$134,0)</f>
         <v>22.2742858474409</v>
       </c>
       <c r="R41" s="28" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$48,R40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$48,R40*Assumptions!$B$134,0)</f>
         <v>25.0513258664756</v>
       </c>
       <c r="S41" s="28" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$48,S40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$48,S40*Assumptions!$B$134,0)</f>
         <v>28.0889813839383</v>
       </c>
       <c r="T41" s="28" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$48,T40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$48,T40*Assumptions!$B$134,0)</f>
         <v>32.1707446628867</v>
       </c>
       <c r="U41" s="28" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$48,U40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$48,U40*Assumptions!$B$134,0)</f>
         <v>35.9245983299876</v>
       </c>
       <c r="V41" s="28" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$48,V40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$48,V40*Assumptions!$B$134,0)</f>
         <v>39.2203557308469</v>
       </c>
       <c r="W41" s="28" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$48,W40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$48,W40*Assumptions!$B$134,0)</f>
         <v>50.2922380318524</v>
       </c>
       <c r="X41" s="28" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$48,X40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$48,X40*Assumptions!$B$134,0)</f>
         <v>61.0135184763789</v>
       </c>
       <c r="Y41" s="28" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$48,Y40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$48,Y40*Assumptions!$B$134,0)</f>
         <v>71.4603444244605</v>
       </c>
       <c r="Z41" s="28" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$48,Z40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$48,Z40*Assumptions!$B$134,0)</f>
         <v>84.7159327815008</v>
       </c>
       <c r="AA41" s="28" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$48,AA40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$48,AA40*Assumptions!$B$134,0)</f>
         <v>433.223299199416</v>
       </c>
       <c r="AB41" s="28" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$48,AB40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$48,AB40*Assumptions!$B$134,0)</f>
         <v>831.066434493629</v>
       </c>
       <c r="AC41" s="28" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$48,AC40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$48,AC40*Assumptions!$B$134,0)</f>
         <v>1419.48490792636</v>
       </c>
       <c r="AD41" s="28" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$48,AD40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$48,AD40*Assumptions!$B$134,0)</f>
         <v>2180.15136227009</v>
       </c>
       <c r="AE41" s="28" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$48,AE40*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$48,AE40*Assumptions!$B$134,0)</f>
         <v>3079.27084100673</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>109</v>
@@ -10579,131 +10373,131 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B43" s="23" t="s">
         <v>76</v>
       </c>
       <c r="C43" s="54" t="n">
-        <f aca="false">C42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">C42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>18.362025862069</v>
       </c>
       <c r="D43" s="54" t="n">
-        <f aca="false">D42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">D42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>27.8533253635403</v>
       </c>
       <c r="E43" s="54" t="n">
-        <f aca="false">E42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">E42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>37.5021152092164</v>
       </c>
       <c r="F43" s="54" t="n">
-        <f aca="false">F42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">F42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>45.2650619733683</v>
       </c>
       <c r="G43" s="54" t="n">
-        <f aca="false">G42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">G42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>54.5899307888715</v>
       </c>
       <c r="H43" s="54" t="n">
-        <f aca="false">H42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">H42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>65.3288293552581</v>
       </c>
       <c r="I43" s="54" t="n">
-        <f aca="false">I42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">I42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>76.0395854664234</v>
       </c>
       <c r="J43" s="54" t="n">
-        <f aca="false">J42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">J42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>86.4817229577577</v>
       </c>
       <c r="K43" s="54" t="n">
-        <f aca="false">K42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">K42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>95.8450234036076</v>
       </c>
       <c r="L43" s="54" t="n">
-        <f aca="false">L42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">L42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>101.740082099273</v>
       </c>
       <c r="M43" s="54" t="n">
-        <f aca="false">M42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">M42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>109.50272852474</v>
       </c>
       <c r="N43" s="54" t="n">
-        <f aca="false">N42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">N42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>119.077712247631</v>
       </c>
       <c r="O43" s="54" t="n">
-        <f aca="false">O42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">O42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>107.218017347765</v>
       </c>
       <c r="P43" s="54" t="n">
-        <f aca="false">P42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">P42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>104.672153432402</v>
       </c>
       <c r="Q43" s="54" t="n">
-        <f aca="false">Q42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Q42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>106.511417664459</v>
       </c>
       <c r="R43" s="54" t="n">
-        <f aca="false">R42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">R42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>106.622235326685</v>
       </c>
       <c r="S43" s="54" t="n">
-        <f aca="false">S42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">S42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>110.740517850552</v>
       </c>
       <c r="T43" s="54" t="n">
-        <f aca="false">T42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">T42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>118.150677941947</v>
       </c>
       <c r="U43" s="54" t="n">
-        <f aca="false">U42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">U42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>126.214346264411</v>
       </c>
       <c r="V43" s="54" t="n">
-        <f aca="false">V42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">V42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>134.359530364478</v>
       </c>
       <c r="W43" s="54" t="n">
-        <f aca="false">W42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">W42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>141.361229953599</v>
       </c>
       <c r="X43" s="54" t="n">
-        <f aca="false">X42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">X42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>143.981010391251</v>
       </c>
       <c r="Y43" s="54" t="n">
-        <f aca="false">Y42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Y42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>149.043399119671</v>
       </c>
       <c r="Z43" s="54" t="n">
-        <f aca="false">Z42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Z42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>156.5259241535</v>
       </c>
       <c r="AA43" s="54" t="n">
-        <f aca="false">AA42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AA42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>279.093907590975</v>
       </c>
       <c r="AB43" s="54" t="n">
-        <f aca="false">AB42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AB42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>343.656256693127</v>
       </c>
       <c r="AC43" s="54" t="n">
-        <f aca="false">AC42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AC42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>386.293444095649</v>
       </c>
       <c r="AD43" s="54" t="n">
-        <f aca="false">AD42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AD42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>428.226805545838</v>
       </c>
       <c r="AE43" s="54" t="n">
-        <f aca="false">AE42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AE42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>471.618998223509</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>109</v>
@@ -10827,10 +10621,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C45" s="44" t="n">
         <f aca="false">C41*C44*Assumptions!$B$7*C7</f>
@@ -10951,7 +10745,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>109</v>
@@ -11075,255 +10869,255 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,C42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,C42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>8.02792142600575</v>
       </c>
       <c r="D47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,D42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,D42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>12.1775401663812</v>
       </c>
       <c r="E47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,E42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,E42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>16.3960140602199</v>
       </c>
       <c r="F47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,F42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,F42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>19.7899928687137</v>
       </c>
       <c r="G47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,G42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,G42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>23.8668477169203</v>
       </c>
       <c r="H47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,H42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,H42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>28.5619197389506</v>
       </c>
       <c r="I47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,I42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,I42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>33.2446878125524</v>
       </c>
       <c r="J47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,J42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,J42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>37.8100151859959</v>
       </c>
       <c r="K47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,K42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,K42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>41.9036724344939</v>
       </c>
       <c r="L47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,L42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,L42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>44.4810061320928</v>
       </c>
       <c r="M47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,M42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,M42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>47.8748536317984</v>
       </c>
       <c r="N47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,N42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,N42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>52.0610593130269</v>
       </c>
       <c r="O47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,O42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,O42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>46.8759724654366</v>
       </c>
       <c r="P47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,P42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,P42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>45.7629147000593</v>
       </c>
       <c r="Q47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Q42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Q42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>46.5670454015148</v>
       </c>
       <c r="R47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,R42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,R42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>46.6154951472918</v>
       </c>
       <c r="S47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,S42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,S42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>48.4160180721609</v>
       </c>
       <c r="T47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,T42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,T42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>51.655757707357</v>
       </c>
       <c r="U47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,U42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,U42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>55.1812126971486</v>
       </c>
       <c r="V47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,V42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,V42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>58.7423065789936</v>
       </c>
       <c r="W47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,W42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,W42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>61.8034663100703</v>
       </c>
       <c r="X47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,X42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,X42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>62.9488405549843</v>
       </c>
       <c r="Y47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Y42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Y42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>65.1621289603561</v>
       </c>
       <c r="Z47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Z42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Z42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>68.4335067206819</v>
       </c>
       <c r="AA47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AA42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AA42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>122.020520908078</v>
       </c>
       <c r="AB47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AB42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AB42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>150.247333655418</v>
       </c>
       <c r="AC47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AC42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AC42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>168.888413504913</v>
       </c>
       <c r="AD47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AD42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AD42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>187.221778972273</v>
       </c>
       <c r="AE47" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AE42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AE42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>206.192948925695</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C48" s="44" t="n">
-        <f aca="false">C41*Assumptions!$B$151*Assumptions!$B$136*C7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">C41*Assumptions!$B$149*Assumptions!$B$135*C7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="D48" s="44" t="n">
-        <f aca="false">D41*Assumptions!$B$151*Assumptions!$B$136*D7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">D41*Assumptions!$B$149*Assumptions!$B$135*D7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="44" t="n">
-        <f aca="false">E41*Assumptions!$B$151*Assumptions!$B$136*E7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">E41*Assumptions!$B$149*Assumptions!$B$135*E7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="F48" s="44" t="n">
-        <f aca="false">F41*Assumptions!$B$151*Assumptions!$B$136*F7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">F41*Assumptions!$B$149*Assumptions!$B$135*F7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G48" s="44" t="n">
-        <f aca="false">G41*Assumptions!$B$151*Assumptions!$B$136*G7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">G41*Assumptions!$B$149*Assumptions!$B$135*G7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="H48" s="44" t="n">
-        <f aca="false">H41*Assumptions!$B$151*Assumptions!$B$136*H7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">H41*Assumptions!$B$149*Assumptions!$B$135*H7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="I48" s="44" t="n">
-        <f aca="false">I41*Assumptions!$B$151*Assumptions!$B$136*I7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">I41*Assumptions!$B$149*Assumptions!$B$135*I7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="J48" s="44" t="n">
-        <f aca="false">J41*Assumptions!$B$151*Assumptions!$B$136*J7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">J41*Assumptions!$B$149*Assumptions!$B$135*J7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="K48" s="44" t="n">
-        <f aca="false">K41*Assumptions!$B$151*Assumptions!$B$136*K7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">K41*Assumptions!$B$149*Assumptions!$B$135*K7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="L48" s="44" t="n">
-        <f aca="false">L41*Assumptions!$B$151*Assumptions!$B$136*L7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">L41*Assumptions!$B$149*Assumptions!$B$135*L7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="M48" s="44" t="n">
-        <f aca="false">M41*Assumptions!$B$151*Assumptions!$B$136*M7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">M41*Assumptions!$B$149*Assumptions!$B$135*M7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="N48" s="44" t="n">
-        <f aca="false">N41*Assumptions!$B$151*Assumptions!$B$136*N7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">N41*Assumptions!$B$149*Assumptions!$B$135*N7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="O48" s="44" t="n">
-        <f aca="false">O41*Assumptions!$B$151*Assumptions!$B$136*O7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">O41*Assumptions!$B$149*Assumptions!$B$135*O7/12*(1+Assumptions!$B$16)</f>
         <v>12.3320797571852</v>
       </c>
       <c r="P48" s="44" t="n">
-        <f aca="false">P41*Assumptions!$B$151*Assumptions!$B$136*P7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">P41*Assumptions!$B$149*Assumptions!$B$135*P7/12*(1+Assumptions!$B$16)</f>
         <v>14.4664456322153</v>
       </c>
       <c r="Q48" s="44" t="n">
-        <f aca="false">Q41*Assumptions!$B$151*Assumptions!$B$136*Q7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Q41*Assumptions!$B$149*Assumptions!$B$135*Q7/12*(1+Assumptions!$B$16)</f>
         <v>16.5275200988011</v>
       </c>
       <c r="R48" s="44" t="n">
-        <f aca="false">R41*Assumptions!$B$151*Assumptions!$B$136*R7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">R41*Assumptions!$B$149*Assumptions!$B$135*R7/12*(1+Assumptions!$B$16)</f>
         <v>18.5880837929249</v>
       </c>
       <c r="S48" s="44" t="n">
-        <f aca="false">S41*Assumptions!$B$151*Assumptions!$B$136*S7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">S41*Assumptions!$B$149*Assumptions!$B$135*S7/12*(1+Assumptions!$B$16)</f>
         <v>20.8420241868822</v>
       </c>
       <c r="T48" s="44" t="n">
-        <f aca="false">T41*Assumptions!$B$151*Assumptions!$B$136*T7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">T41*Assumptions!$B$149*Assumptions!$B$135*T7/12*(1+Assumptions!$B$16)</f>
         <v>23.8706925398619</v>
       </c>
       <c r="U48" s="44" t="n">
-        <f aca="false">U41*Assumptions!$B$151*Assumptions!$B$136*U7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">U41*Assumptions!$B$149*Assumptions!$B$135*U7/12*(1+Assumptions!$B$16)</f>
         <v>26.6560519608508</v>
       </c>
       <c r="V48" s="44" t="n">
-        <f aca="false">V41*Assumptions!$B$151*Assumptions!$B$136*V7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">V41*Assumptions!$B$149*Assumptions!$B$135*V7/12*(1+Assumptions!$B$16)</f>
         <v>29.1015039522884</v>
       </c>
       <c r="W48" s="44" t="n">
-        <f aca="false">W41*Assumptions!$B$151*Assumptions!$B$136*W7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">W41*Assumptions!$B$149*Assumptions!$B$135*W7/12*(1+Assumptions!$B$16)</f>
         <v>37.3168406196345</v>
       </c>
       <c r="X48" s="44" t="n">
-        <f aca="false">X41*Assumptions!$B$151*Assumptions!$B$136*X7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">X41*Assumptions!$B$149*Assumptions!$B$135*X7/12*(1+Assumptions!$B$16)</f>
         <v>45.2720307094732</v>
       </c>
       <c r="Y48" s="44" t="n">
-        <f aca="false">Y41*Assumptions!$B$151*Assumptions!$B$136*Y7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Y41*Assumptions!$B$149*Assumptions!$B$135*Y7/12*(1+Assumptions!$B$16)</f>
         <v>53.0235755629497</v>
       </c>
       <c r="Z48" s="44" t="n">
-        <f aca="false">Z41*Assumptions!$B$151*Assumptions!$B$136*Z7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Z41*Assumptions!$B$149*Assumptions!$B$135*Z7/12*(1+Assumptions!$B$16)</f>
         <v>62.8592221238736</v>
       </c>
       <c r="AA48" s="44" t="n">
-        <f aca="false">AA41*Assumptions!$B$151*Assumptions!$B$136*AA7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AA41*Assumptions!$B$149*Assumptions!$B$135*AA7/12*(1+Assumptions!$B$16)</f>
         <v>3857.4202560716</v>
       </c>
       <c r="AB48" s="44" t="n">
-        <f aca="false">AB41*Assumptions!$B$151*Assumptions!$B$136*AB7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AB41*Assumptions!$B$149*Assumptions!$B$135*AB7/12*(1+Assumptions!$B$16)</f>
         <v>7399.81553273127</v>
       </c>
       <c r="AC48" s="44" t="n">
-        <f aca="false">AC41*Assumptions!$B$151*Assumptions!$B$136*AC7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AC41*Assumptions!$B$149*Assumptions!$B$135*AC7/12*(1+Assumptions!$B$16)</f>
         <v>12639.0936201763</v>
       </c>
       <c r="AD48" s="44" t="n">
-        <f aca="false">AD41*Assumptions!$B$151*Assumptions!$B$136*AD7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AD41*Assumptions!$B$149*Assumptions!$B$135*AD7/12*(1+Assumptions!$B$16)</f>
         <v>19412.0677296529</v>
       </c>
       <c r="AE48" s="44" t="n">
-        <f aca="false">AE41*Assumptions!$B$151*Assumptions!$B$136*AE7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AE41*Assumptions!$B$149*Assumptions!$B$135*AE7/12*(1+Assumptions!$B$16)</f>
         <v>27417.8275683239</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>109</v>
@@ -11447,7 +11241,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>109</v>
@@ -11571,630 +11365,630 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C51" s="54" t="n">
-        <f aca="false">C46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">C46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="D51" s="54" t="n">
-        <f aca="false">D46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">D46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="E51" s="54" t="n">
-        <f aca="false">E46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">E46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="F51" s="54" t="n">
-        <f aca="false">F46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">F46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="G51" s="54" t="n">
-        <f aca="false">G46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">G46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="H51" s="54" t="n">
-        <f aca="false">H46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">H46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="I51" s="54" t="n">
-        <f aca="false">I46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">I46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="J51" s="54" t="n">
-        <f aca="false">J46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">J46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="K51" s="54" t="n">
-        <f aca="false">K46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">K46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="L51" s="54" t="n">
-        <f aca="false">L46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">L46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="M51" s="54" t="n">
-        <f aca="false">M46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">M46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="N51" s="54" t="n">
-        <f aca="false">N46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">N46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="O51" s="54" t="n">
-        <f aca="false">O46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">O46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0.823269767249377</v>
       </c>
       <c r="P51" s="54" t="n">
-        <f aca="false">P46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">P46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0.857113594435893</v>
       </c>
       <c r="Q51" s="54" t="n">
-        <f aca="false">Q46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Q46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0.976506908081388</v>
       </c>
       <c r="R51" s="54" t="n">
-        <f aca="false">R46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">R46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.09939527370899</v>
       </c>
       <c r="S51" s="54" t="n">
-        <f aca="false">S46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">S46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.30644710462777</v>
       </c>
       <c r="T51" s="54" t="n">
-        <f aca="false">T46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">T46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.51659712143511</v>
       </c>
       <c r="U51" s="54" t="n">
-        <f aca="false">U46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">U46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.67584020654423</v>
       </c>
       <c r="V51" s="54" t="n">
-        <f aca="false">V46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">V46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.99191960200181</v>
       </c>
       <c r="W51" s="54" t="n">
-        <f aca="false">W46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">W46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>2.98593650262676</v>
       </c>
       <c r="X51" s="54" t="n">
-        <f aca="false">X46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">X46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>3.76340319537393</v>
       </c>
       <c r="Y51" s="54" t="n">
-        <f aca="false">Y46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Y46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>4.69695545216025</v>
       </c>
       <c r="Z51" s="54" t="n">
-        <f aca="false">Z46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Z46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>6.34900275358911</v>
       </c>
       <c r="AA51" s="54" t="n">
-        <f aca="false">AA46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AA46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>609.386316502417</v>
       </c>
       <c r="AB51" s="54" t="n">
-        <f aca="false">AB46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AB46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1439.42994690458</v>
       </c>
       <c r="AC51" s="54" t="n">
-        <f aca="false">AC46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AC46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>2763.62207818033</v>
       </c>
       <c r="AD51" s="54" t="n">
-        <f aca="false">AD46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AD46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>4705.34023749549</v>
       </c>
       <c r="AE51" s="54" t="n">
-        <f aca="false">AE46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AE46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>7319.30285164406</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C52" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C29*Assumptions!$B$152*Assumptions!$B$25/12*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C29*Assumptions!$B$150*Assumptions!$B$25/12*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D52" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D29*Assumptions!$B$152*Assumptions!$B$25/12*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D29*Assumptions!$B$150*Assumptions!$B$25/12*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E52" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E29*Assumptions!$B$152*Assumptions!$B$25/12*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E29*Assumptions!$B$150*Assumptions!$B$25/12*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F52" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F29*Assumptions!$B$152*Assumptions!$B$25/12*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F29*Assumptions!$B$150*Assumptions!$B$25/12*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G52" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G29*Assumptions!$B$152*Assumptions!$B$25/12*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G29*Assumptions!$B$150*Assumptions!$B$25/12*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H52" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H29*Assumptions!$B$152*Assumptions!$B$25/12*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H29*Assumptions!$B$150*Assumptions!$B$25/12*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I52" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I29*Assumptions!$B$152*Assumptions!$B$25/12*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I29*Assumptions!$B$150*Assumptions!$B$25/12*I7,0)</f>
         <v>378.315057573114</v>
       </c>
       <c r="J52" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J29*Assumptions!$B$152*Assumptions!$B$25/12*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J29*Assumptions!$B$150*Assumptions!$B$25/12*J7,0)</f>
         <v>414.65087716968</v>
       </c>
       <c r="K52" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K29*Assumptions!$B$152*Assumptions!$B$25/12*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K29*Assumptions!$B$150*Assumptions!$B$25/12*K7,0)</f>
         <v>454.356238658703</v>
       </c>
       <c r="L52" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L29*Assumptions!$B$152*Assumptions!$B$25/12*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L29*Assumptions!$B$150*Assumptions!$B$25/12*L7,0)</f>
         <v>512.706105374935</v>
       </c>
       <c r="M52" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M29*Assumptions!$B$152*Assumptions!$B$25/12*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M29*Assumptions!$B$150*Assumptions!$B$25/12*M7,0)</f>
         <v>561.758760031968</v>
       </c>
       <c r="N52" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N29*Assumptions!$B$152*Assumptions!$B$25/12*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N29*Assumptions!$B$150*Assumptions!$B$25/12*N7,0)</f>
         <v>599.400709922397</v>
       </c>
       <c r="O52" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O29*Assumptions!$B$152*Assumptions!$B$25/12*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O29*Assumptions!$B$150*Assumptions!$B$25/12*O7,0)</f>
         <v>788.441885650116</v>
       </c>
       <c r="P52" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P29*Assumptions!$B$152*Assumptions!$B$25/12*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P29*Assumptions!$B$150*Assumptions!$B$25/12*P7,0)</f>
         <v>961.387218366717</v>
       </c>
       <c r="Q52" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q29*Assumptions!$B$152*Assumptions!$B$25/12*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q29*Assumptions!$B$150*Assumptions!$B$25/12*Q7,0)</f>
         <v>1120.51943578763</v>
       </c>
       <c r="R52" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R29*Assumptions!$B$152*Assumptions!$B$25/12*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R29*Assumptions!$B$150*Assumptions!$B$25/12*R7,0)</f>
         <v>1327.26465168733</v>
       </c>
       <c r="S52" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S29*Assumptions!$B$152*Assumptions!$B$25/12*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S29*Assumptions!$B$150*Assumptions!$B$25/12*S7,0)</f>
         <v>1503.53641524015</v>
       </c>
       <c r="T52" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T29*Assumptions!$B$152*Assumptions!$B$25/12*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T29*Assumptions!$B$150*Assumptions!$B$25/12*T7,0)</f>
         <v>1637.46315050242</v>
       </c>
       <c r="U52" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U29*Assumptions!$B$152*Assumptions!$B$25/12*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U29*Assumptions!$B$150*Assumptions!$B$25/12*U7,0)</f>
         <v>1760.19266363058</v>
       </c>
       <c r="V52" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V29*Assumptions!$B$152*Assumptions!$B$25/12*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V29*Assumptions!$B$150*Assumptions!$B$25/12*V7,0)</f>
         <v>1879.11182841635</v>
       </c>
       <c r="W52" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W29*Assumptions!$B$152*Assumptions!$B$25/12*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W29*Assumptions!$B$150*Assumptions!$B$25/12*W7,0)</f>
         <v>2013.76573797519</v>
       </c>
       <c r="X52" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X29*Assumptions!$B$152*Assumptions!$B$25/12*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X29*Assumptions!$B$150*Assumptions!$B$25/12*X7,0)</f>
         <v>2223.08699623348</v>
       </c>
       <c r="Y52" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y29*Assumptions!$B$152*Assumptions!$B$25/12*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y29*Assumptions!$B$150*Assumptions!$B$25/12*Y7,0)</f>
         <v>2402.64663923016</v>
       </c>
       <c r="Z52" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z29*Assumptions!$B$152*Assumptions!$B$25/12*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z29*Assumptions!$B$150*Assumptions!$B$25/12*Z7,0)</f>
         <v>2542.18538074276</v>
       </c>
       <c r="AA52" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA29*Assumptions!$B$152*Assumptions!$B$25/12*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA29*Assumptions!$B$150*Assumptions!$B$25/12*AA7,0)</f>
         <v>61811.514541722</v>
       </c>
       <c r="AB52" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB29*Assumptions!$B$152*Assumptions!$B$25/12*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB29*Assumptions!$B$150*Assumptions!$B$25/12*AB7,0)</f>
         <v>105523.209557228</v>
       </c>
       <c r="AC52" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC29*Assumptions!$B$152*Assumptions!$B$25/12*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC29*Assumptions!$B$150*Assumptions!$B$25/12*AC7,0)</f>
         <v>163827.539618923</v>
       </c>
       <c r="AD52" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD29*Assumptions!$B$152*Assumptions!$B$25/12*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD29*Assumptions!$B$150*Assumptions!$B$25/12*AD7,0)</f>
         <v>226862.805163459</v>
       </c>
       <c r="AE52" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE29*Assumptions!$B$152*Assumptions!$B$25/12*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE29*Assumptions!$B$150*Assumptions!$B$25/12*AE7,0)</f>
         <v>286424.203880507</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B53" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C53" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$49,C46*C17*Assumptions!$B$17+C41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$49,C46*C17*Assumptions!$B$17+C41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D53" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$49,D46*D17*Assumptions!$B$17+D41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$49,D46*D17*Assumptions!$B$17+D41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E53" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$49,E46*E17*Assumptions!$B$17+E41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$49,E46*E17*Assumptions!$B$17+E41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F53" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$49,F46*F17*Assumptions!$B$17+F41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$49,F46*F17*Assumptions!$B$17+F41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G53" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$49,G46*G17*Assumptions!$B$17+G41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$49,G46*G17*Assumptions!$B$17+G41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H53" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$49,H46*H17*Assumptions!$B$17+H41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$49,H46*H17*Assumptions!$B$17+H41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I53" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$49,I46*I17*Assumptions!$B$17+I41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$49,I46*I17*Assumptions!$B$17+I41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
         <v>0</v>
       </c>
       <c r="J53" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$49,J46*J17*Assumptions!$B$17+J41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$49,J46*J17*Assumptions!$B$17+J41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
         <v>0</v>
       </c>
       <c r="K53" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$49,K46*K17*Assumptions!$B$17+K41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$49,K46*K17*Assumptions!$B$17+K41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
         <v>0</v>
       </c>
       <c r="L53" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$49,L46*L17*Assumptions!$B$17+L41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$49,L46*L17*Assumptions!$B$17+L41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
         <v>0</v>
       </c>
       <c r="M53" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$49,M46*M17*Assumptions!$B$17+M41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$49,M46*M17*Assumptions!$B$17+M41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
         <v>0</v>
       </c>
       <c r="N53" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$49,N46*N17*Assumptions!$B$17+N41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$49,N46*N17*Assumptions!$B$17+N41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
         <v>0</v>
       </c>
       <c r="O53" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$49,O46*O17*Assumptions!$B$17+O41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$49,O46*O17*Assumptions!$B$17+O41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
         <v>56.6910428552007</v>
       </c>
       <c r="P53" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$49,P46*P17*Assumptions!$B$17+P41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$49,P46*P17*Assumptions!$B$17+P41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
         <v>66.3921767192706</v>
       </c>
       <c r="Q53" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$49,Q46*Q17*Assumptions!$B$17+Q41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$49,Q46*Q17*Assumptions!$B$17+Q41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
         <v>75.8484817603071</v>
       </c>
       <c r="R53" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$49,R46*R17*Assumptions!$B$17+R41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$49,R46*R17*Assumptions!$B$17+R41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
         <v>85.3806643891561</v>
       </c>
       <c r="S53" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$49,S46*S17*Assumptions!$B$17+S41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$49,S46*S17*Assumptions!$B$17+S41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
         <v>95.9024740544611</v>
       </c>
       <c r="T53" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$49,T46*T17*Assumptions!$B$17+T41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$49,T46*T17*Assumptions!$B$17+T41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
         <v>110.943029404407</v>
       </c>
       <c r="U53" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$49,U46*U17*Assumptions!$B$17+U41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$49,U46*U17*Assumptions!$B$17+U41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
         <v>124.139778707344</v>
       </c>
       <c r="V53" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$49,V46*V17*Assumptions!$B$17+V41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$49,V46*V17*Assumptions!$B$17+V41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
         <v>135.588644580425</v>
       </c>
       <c r="W53" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$49,W46*W17*Assumptions!$B$17+W41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$49,W46*W17*Assumptions!$B$17+W41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
         <v>172.658804983007</v>
       </c>
       <c r="X53" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$49,X46*X17*Assumptions!$B$17+X41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$49,X46*X17*Assumptions!$B$17+X41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
         <v>210.404776125054</v>
       </c>
       <c r="Y53" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$49,Y46*Y17*Assumptions!$B$17+Y41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$49,Y46*Y17*Assumptions!$B$17+Y41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
         <v>246.523989422082</v>
       </c>
       <c r="Z53" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$49,Z46*Z17*Assumptions!$B$17+Z41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$49,Z46*Z17*Assumptions!$B$17+Z41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
         <v>291.58919909234</v>
       </c>
       <c r="AA53" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$49,AA46*AA17*Assumptions!$B$17+AA41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$49,AA46*AA17*Assumptions!$B$17+AA41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
         <v>18292.6768217036</v>
       </c>
       <c r="AB53" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$49,AB46*AB17*Assumptions!$B$17+AB41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$49,AB46*AB17*Assumptions!$B$17+AB41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
         <v>35456.2987651961</v>
       </c>
       <c r="AC53" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$49,AC46*AC17*Assumptions!$B$17+AC41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$49,AC46*AC17*Assumptions!$B$17+AC41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
         <v>60971.9135721538</v>
       </c>
       <c r="AD53" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$49,AD46*AD17*Assumptions!$B$17+AD41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$49,AD46*AD17*Assumptions!$B$17+AD41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
         <v>94266.9001794799</v>
       </c>
       <c r="AE53" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$49,AE46*AE17*Assumptions!$B$17+AE41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$49,AE46*AE17*Assumptions!$B$17+AE41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
         <v>134052.244175485</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C54" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$50,C41*C42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$50,C41*C42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="D54" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$50,D41*D42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$50,D41*D42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="E54" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$50,E41*E42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$50,E41*E42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="F54" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$50,F41*F42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$50,F41*F42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="G54" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$50,G41*G42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$50,G41*G42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="H54" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$50,H41*H42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$50,H41*H42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="I54" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$50,I41*I42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$50,I41*I42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="J54" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$50,J41*J42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$50,J41*J42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="K54" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$50,K41*K42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$50,K41*K42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="L54" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$50,L41*L42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$50,L41*L42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="M54" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$50,M41*M42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$50,M41*M42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="N54" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$50,N41*N42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$50,N41*N42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="O54" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$50,O41*O42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$50,O41*O42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>356.393838636094</v>
       </c>
       <c r="P54" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$50,P41*P42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$50,P41*P42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>408.149330683759</v>
       </c>
       <c r="Q54" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,Q41*Q42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,Q41*Q42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>474.493152614863</v>
       </c>
       <c r="R54" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$50,R41*R42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$50,R41*R42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>534.205672356167</v>
       </c>
       <c r="S54" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$50,S41*S42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$50,S41*S42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>622.117668870368</v>
       </c>
       <c r="T54" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$50,T41*T42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$50,T41*T42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>760.199058363464</v>
       </c>
       <c r="U54" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$50,U41*U42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$50,U41*U42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>906.839938606184</v>
       </c>
       <c r="V54" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$50,V41*V42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$50,V41*V42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>1053.92571534487</v>
       </c>
       <c r="W54" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$50,W41*W42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$50,W41*W42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>1421.87452506036</v>
       </c>
       <c r="X54" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$50,X41*X42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$50,X41*X42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>1756.95760755085</v>
       </c>
       <c r="Y54" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,Y41*Y42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,Y41*Y42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>2130.1385270568</v>
       </c>
       <c r="Z54" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,Z41*Z42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,Z41*Z42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>2652.04793383004</v>
       </c>
       <c r="AA54" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,AA41*AA42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,AA41*AA42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>24181.9966866039</v>
       </c>
       <c r="AB54" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,AB41*AB42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,AB41*AB42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>57120.2359882768</v>
       </c>
       <c r="AC54" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,AC41*AC42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,AC41*AC42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>109667.542784934</v>
       </c>
       <c r="AD54" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,AD41*AD42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,AD41*AD42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>186719.850694265</v>
       </c>
       <c r="AE54" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,AE41*AE42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,AE41*AE42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>290448.525858891</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B55" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C55" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$50,(C54*Assumptions!$B$29*Assumptions!$B$30+C41*C43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$50,(C54*Assumptions!$B$29*Assumptions!$B$30+C41*C43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v>0</v>
       </c>
       <c r="D55" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$50,(D54*Assumptions!$B$29*Assumptions!$B$30+D41*D43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$50,(D54*Assumptions!$B$29*Assumptions!$B$30+D41*D43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v>0</v>
       </c>
       <c r="E55" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$50,(E54*Assumptions!$B$29*Assumptions!$B$30+E41*E43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$50,(E54*Assumptions!$B$29*Assumptions!$B$30+E41*E43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v>0</v>
       </c>
       <c r="F55" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$50,(F54*Assumptions!$B$29*Assumptions!$B$30+F41*F43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$50,(F54*Assumptions!$B$29*Assumptions!$B$30+F41*F43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v>0</v>
       </c>
       <c r="G55" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$50,(G54*Assumptions!$B$29*Assumptions!$B$30+G41*G43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$50,(G54*Assumptions!$B$29*Assumptions!$B$30+G41*G43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v>0</v>
       </c>
       <c r="H55" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$50,(H54*Assumptions!$B$29*Assumptions!$B$30+H41*H43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$50,(H54*Assumptions!$B$29*Assumptions!$B$30+H41*H43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v>0</v>
       </c>
       <c r="I55" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$50,(I54*Assumptions!$B$29*Assumptions!$B$30+I41*I43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$50,(I54*Assumptions!$B$29*Assumptions!$B$30+I41*I43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v>0</v>
       </c>
       <c r="J55" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$50,(J54*Assumptions!$B$29*Assumptions!$B$30+J41*J43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$50,(J54*Assumptions!$B$29*Assumptions!$B$30+J41*J43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v>0</v>
       </c>
       <c r="K55" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$50,(K54*Assumptions!$B$29*Assumptions!$B$30+K41*K43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$50,(K54*Assumptions!$B$29*Assumptions!$B$30+K41*K43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v>0</v>
       </c>
       <c r="L55" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$50,(L54*Assumptions!$B$29*Assumptions!$B$30+L41*L43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$50,(L54*Assumptions!$B$29*Assumptions!$B$30+L41*L43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v>0</v>
       </c>
       <c r="M55" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$50,(M54*Assumptions!$B$29*Assumptions!$B$30+M41*M43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$50,(M54*Assumptions!$B$29*Assumptions!$B$30+M41*M43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v>0</v>
       </c>
       <c r="N55" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$50,(N54*Assumptions!$B$29*Assumptions!$B$30+N41*N43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$50,(N54*Assumptions!$B$29*Assumptions!$B$30+N41*N43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v>0</v>
       </c>
       <c r="O55" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$50,(O54*Assumptions!$B$29*Assumptions!$B$30+O41*O43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$50,(O54*Assumptions!$B$29*Assumptions!$B$30+O41*O43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v>0.846435366760723</v>
       </c>
       <c r="P55" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$50,(P54*Assumptions!$B$29*Assumptions!$B$30+P41*P43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$50,(P54*Assumptions!$B$29*Assumptions!$B$30+P41*P43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v>0.969354660373927</v>
       </c>
       <c r="Q55" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,(Q54*Assumptions!$B$29*Assumptions!$B$30+Q41*Q43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,(Q54*Assumptions!$B$29*Assumptions!$B$30+Q41*Q43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v>1.1269212374603</v>
       </c>
       <c r="R55" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$50,(R54*Assumptions!$B$29*Assumptions!$B$30+R41*R43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$50,(R54*Assumptions!$B$29*Assumptions!$B$30+R41*R43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v>1.2687384718459</v>
       </c>
       <c r="S55" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$50,(S54*Assumptions!$B$29*Assumptions!$B$30+S41*S43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$50,(S54*Assumptions!$B$29*Assumptions!$B$30+S41*S43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v>1.47752946356712</v>
       </c>
       <c r="T55" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$50,(T54*Assumptions!$B$29*Assumptions!$B$30+T41*T43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$50,(T54*Assumptions!$B$29*Assumptions!$B$30+T41*T43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v>1.80547276361323</v>
       </c>
       <c r="U55" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$50,(U54*Assumptions!$B$29*Assumptions!$B$30+U41*U43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$50,(U54*Assumptions!$B$29*Assumptions!$B$30+U41*U43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v>2.15374485418969</v>
       </c>
       <c r="V55" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$50,(V54*Assumptions!$B$29*Assumptions!$B$30+V41*V43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$50,(V54*Assumptions!$B$29*Assumptions!$B$30+V41*V43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v>2.50307357394407</v>
       </c>
       <c r="W55" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$50,(W54*Assumptions!$B$29*Assumptions!$B$30+W41*W43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$50,(W54*Assumptions!$B$29*Assumptions!$B$30+W41*W43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v>3.37695199701836</v>
       </c>
       <c r="X55" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$50,(X54*Assumptions!$B$29*Assumptions!$B$30+X41*X43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$50,(X54*Assumptions!$B$29*Assumptions!$B$30+X41*X43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v>4.17277431793328</v>
       </c>
       <c r="Y55" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,(Y54*Assumptions!$B$29*Assumptions!$B$30+Y41*Y43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,(Y54*Assumptions!$B$29*Assumptions!$B$30+Y41*Y43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v>5.0590790017599</v>
       </c>
       <c r="Z55" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,(Z54*Assumptions!$B$29*Assumptions!$B$30+Z41*Z43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,(Z54*Assumptions!$B$29*Assumptions!$B$30+Z41*Z43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v>6.29861384284634</v>
       </c>
       <c r="AA55" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,(AA54*Assumptions!$B$29*Assumptions!$B$30+AA41*AA43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,(AA54*Assumptions!$B$29*Assumptions!$B$30+AA41*AA43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v>689.18690556821</v>
       </c>
       <c r="AB55" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,(AB54*Assumptions!$B$29*Assumptions!$B$30+AB41*AB43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,(AB54*Assumptions!$B$29*Assumptions!$B$30+AB41*AB43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v>1627.92672566589</v>
       </c>
       <c r="AC55" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,(AC54*Assumptions!$B$29*Assumptions!$B$30+AC41*AC43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,(AC54*Assumptions!$B$29*Assumptions!$B$30+AC41*AC43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v>3125.52496937061</v>
       </c>
       <c r="AD55" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,(AD54*Assumptions!$B$29*Assumptions!$B$30+AD41*AD43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,(AD54*Assumptions!$B$29*Assumptions!$B$30+AD41*AD43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v>5321.51574478657</v>
       </c>
       <c r="AE55" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,(AE54*Assumptions!$B$29*Assumptions!$B$30+AE41*AE43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,(AE54*Assumptions!$B$29*Assumptions!$B$30+AE41*AE43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v>8277.7829869784</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C56" s="44" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$46,(C29+C31*Assumptions!$B$129)*Assumptions!$B$128*C7/12,0)</f>
@@ -12315,7 +12109,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>109</v>
@@ -12439,7 +12233,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="45" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="B59" s="46"/>
       <c r="C59" s="46"/>
@@ -12474,7 +12268,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B60" s="23" t="s">
         <v>185</v>
@@ -12598,7 +12392,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B61" s="23" t="s">
         <v>185</v>
@@ -12721,7 +12515,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B62" s="23" t="s">
         <v>185</v>
@@ -12845,10 +12639,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C63" s="50" t="n">
         <v>1</v>
@@ -12968,7 +12762,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B64" s="23" t="s">
         <v>185</v>
@@ -13092,7 +12886,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B65" s="23" t="s">
         <v>185</v>
@@ -13216,7 +13010,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>185</v>
@@ -13340,7 +13134,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B67" s="23" t="s">
         <v>185</v>
@@ -13464,7 +13258,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="B68" s="23" t="s">
         <v>185</v>
@@ -13588,131 +13382,131 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C69" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$44,C65*Assumptions!$B$162*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$44,C65*Assumptions!$B$160*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$44,D65*Assumptions!$B$162*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$44,D65*Assumptions!$B$160*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E69" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$44,E65*Assumptions!$B$162*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$44,E65*Assumptions!$B$160*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F69" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$44,F65*Assumptions!$B$162*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$44,F65*Assumptions!$B$160*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G69" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$44,G65*Assumptions!$B$162*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$44,G65*Assumptions!$B$160*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H69" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$44,H65*Assumptions!$B$162*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$44,H65*Assumptions!$B$160*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I69" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$44,I65*Assumptions!$B$162*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$44,I65*Assumptions!$B$160*I7,0)</f>
         <v>0</v>
       </c>
       <c r="J69" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$44,J65*Assumptions!$B$162*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$44,J65*Assumptions!$B$160*J7,0)</f>
         <v>0</v>
       </c>
       <c r="K69" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$44,K65*Assumptions!$B$162*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$44,K65*Assumptions!$B$160*K7,0)</f>
         <v>0</v>
       </c>
       <c r="L69" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$44,L65*Assumptions!$B$162*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$44,L65*Assumptions!$B$160*L7,0)</f>
         <v>0</v>
       </c>
       <c r="M69" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$44,M65*Assumptions!$B$162*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$44,M65*Assumptions!$B$160*M7,0)</f>
         <v>0</v>
       </c>
       <c r="N69" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$44,N65*Assumptions!$B$162*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$44,N65*Assumptions!$B$160*N7,0)</f>
         <v>0</v>
       </c>
       <c r="O69" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$44,O65*Assumptions!$B$162*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$44,O65*Assumptions!$B$160*O7,0)</f>
         <v>819.134013610426</v>
       </c>
       <c r="P69" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$44,P65*Assumptions!$B$162*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$44,P65*Assumptions!$B$160*P7,0)</f>
         <v>1574.66844928915</v>
       </c>
       <c r="Q69" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$44,Q65*Assumptions!$B$162*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$44,Q65*Assumptions!$B$160*Q7,0)</f>
         <v>2275.06878088705</v>
       </c>
       <c r="R69" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$44,R65*Assumptions!$B$162*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$44,R65*Assumptions!$B$160*R7,0)</f>
         <v>3152.61294262461</v>
       </c>
       <c r="S69" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$44,S65*Assumptions!$B$162*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$44,S65*Assumptions!$B$160*S7,0)</f>
         <v>3912.11901968446</v>
       </c>
       <c r="T69" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$44,T65*Assumptions!$B$162*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$44,T65*Assumptions!$B$160*T7,0)</f>
         <v>4508.18021973141</v>
       </c>
       <c r="U69" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$44,U65*Assumptions!$B$162*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$44,U65*Assumptions!$B$160*U7,0)</f>
         <v>5058.8770350913</v>
       </c>
       <c r="V69" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$44,V65*Assumptions!$B$162*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$44,V65*Assumptions!$B$160*V7,0)</f>
         <v>5592.34143577003</v>
       </c>
       <c r="W69" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$44,W65*Assumptions!$B$162*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$44,W65*Assumptions!$B$160*W7,0)</f>
         <v>6183.25326812008</v>
       </c>
       <c r="X69" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$44,X65*Assumptions!$B$162*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$44,X65*Assumptions!$B$160*X7,0)</f>
         <v>7057.170454616</v>
       </c>
       <c r="Y69" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$44,Y65*Assumptions!$B$162*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$44,Y65*Assumptions!$B$160*Y7,0)</f>
         <v>7815.01740794317</v>
       </c>
       <c r="Z69" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$44,Z65*Assumptions!$B$162*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$44,Z65*Assumptions!$B$160*Z7,0)</f>
         <v>8417.32563867564</v>
       </c>
       <c r="AA69" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$44,AA65*Assumptions!$B$162*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$44,AA65*Assumptions!$B$160*AA7,0)</f>
         <v>221554.970910488</v>
       </c>
       <c r="AB69" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$44,AB65*Assumptions!$B$162*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$44,AB65*Assumptions!$B$160*AB7,0)</f>
         <v>386950.532569554</v>
       </c>
       <c r="AC69" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$44,AC65*Assumptions!$B$162*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$44,AC65*Assumptions!$B$160*AC7,0)</f>
         <v>600746.854649707</v>
       </c>
       <c r="AD69" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$44,AD65*Assumptions!$B$162*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$44,AD65*Assumptions!$B$160*AD7,0)</f>
         <v>826655.003342824</v>
       </c>
       <c r="AE69" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$44,AE65*Assumptions!$B$162*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$44,AE65*Assumptions!$B$160*AE7,0)</f>
         <v>1024752.60766016</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>109</v>
@@ -13836,7 +13630,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B71" s="23" t="s">
         <v>47</v>
@@ -13960,10 +13754,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C72" s="55" t="n">
         <f aca="false">(Assumptions!$B$127+Assumptions!$B$128*IF(C65+C67=0,1,(C65+C67*Assumptions!$B$129)/(C65+C67)))*C7/12</f>
@@ -14084,7 +13878,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B73" s="23" t="s">
         <v>47</v>
@@ -14208,7 +14002,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B74" s="23" t="s">
         <v>109</v>
@@ -14332,131 +14126,131 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B75" s="23" t="s">
         <v>185</v>
       </c>
       <c r="C75" s="53" t="n">
-        <f aca="false">C65+C67*Assumptions!$B$168</f>
+        <f aca="false">C65+C67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="D75" s="53" t="n">
-        <f aca="false">D65+D67*Assumptions!$B$168</f>
+        <f aca="false">D65+D67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="E75" s="53" t="n">
-        <f aca="false">E65+E67*Assumptions!$B$168</f>
+        <f aca="false">E65+E67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="F75" s="53" t="n">
-        <f aca="false">F65+F67*Assumptions!$B$168</f>
+        <f aca="false">F65+F67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="G75" s="53" t="n">
-        <f aca="false">G65+G67*Assumptions!$B$168</f>
+        <f aca="false">G65+G67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="H75" s="53" t="n">
-        <f aca="false">H65+H67*Assumptions!$B$168</f>
+        <f aca="false">H65+H67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="I75" s="53" t="n">
-        <f aca="false">I65+I67*Assumptions!$B$168</f>
+        <f aca="false">I65+I67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="J75" s="53" t="n">
-        <f aca="false">J65+J67*Assumptions!$B$168</f>
+        <f aca="false">J65+J67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="K75" s="53" t="n">
-        <f aca="false">K65+K67*Assumptions!$B$168</f>
+        <f aca="false">K65+K67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="L75" s="53" t="n">
-        <f aca="false">L65+L67*Assumptions!$B$168</f>
+        <f aca="false">L65+L67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="M75" s="53" t="n">
-        <f aca="false">M65+M67*Assumptions!$B$168</f>
+        <f aca="false">M65+M67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="N75" s="53" t="n">
-        <f aca="false">N65+N67*Assumptions!$B$168</f>
+        <f aca="false">N65+N67*Assumptions!$B$163</f>
         <v>0</v>
       </c>
       <c r="O75" s="53" t="n">
-        <f aca="false">O65+O67*Assumptions!$B$168</f>
+        <f aca="false">O65+O67*Assumptions!$B$163</f>
         <v>32.2998</v>
       </c>
       <c r="P75" s="53" t="n">
-        <f aca="false">P65+P67*Assumptions!$B$168</f>
+        <f aca="false">P65+P67*Assumptions!$B$163</f>
         <v>63.6615053901048</v>
       </c>
       <c r="Q75" s="53" t="n">
-        <f aca="false">Q65+Q67*Assumptions!$B$168</f>
+        <f aca="false">Q65+Q67*Assumptions!$B$163</f>
         <v>94.2970451452031</v>
       </c>
       <c r="R75" s="53" t="n">
-        <f aca="false">R65+R67*Assumptions!$B$168</f>
+        <f aca="false">R65+R67*Assumptions!$B$163</f>
         <v>133.259864024599</v>
       </c>
       <c r="S75" s="53" t="n">
-        <f aca="false">S65+S67*Assumptions!$B$168</f>
+        <f aca="false">S65+S67*Assumptions!$B$163</f>
         <v>169.249922373745</v>
       </c>
       <c r="T75" s="53" t="n">
-        <f aca="false">T65+T67*Assumptions!$B$168</f>
+        <f aca="false">T65+T67*Assumptions!$B$163</f>
         <v>200.25055438054</v>
       </c>
       <c r="U75" s="53" t="n">
-        <f aca="false">U65+U67*Assumptions!$B$168</f>
+        <f aca="false">U65+U67*Assumptions!$B$163</f>
         <v>230.604651516452</v>
       </c>
       <c r="V75" s="53" t="n">
-        <f aca="false">V65+V67*Assumptions!$B$168</f>
+        <f aca="false">V65+V67*Assumptions!$B$163</f>
         <v>261.334569885971</v>
       </c>
       <c r="W75" s="53" t="n">
-        <f aca="false">W65+W67*Assumptions!$B$168</f>
+        <f aca="false">W65+W67*Assumptions!$B$163</f>
         <v>295.352035323397</v>
       </c>
       <c r="X75" s="53" t="n">
-        <f aca="false">X65+X67*Assumptions!$B$168</f>
+        <f aca="false">X65+X67*Assumptions!$B$163</f>
         <v>341.661256254414</v>
       </c>
       <c r="Y75" s="53" t="n">
-        <f aca="false">Y65+Y67*Assumptions!$B$168</f>
+        <f aca="false">Y65+Y67*Assumptions!$B$163</f>
         <v>385.06836174693</v>
       </c>
       <c r="Z75" s="53" t="n">
-        <f aca="false">Z65+Z67*Assumptions!$B$168</f>
+        <f aca="false">Z65+Z67*Assumptions!$B$163</f>
         <v>423.794614106518</v>
       </c>
       <c r="AA75" s="53" t="n">
-        <f aca="false">AA65+AA67*Assumptions!$B$168</f>
+        <f aca="false">AA65+AA67*Assumptions!$B$163</f>
         <v>1141.21510330995</v>
       </c>
       <c r="AB75" s="53" t="n">
-        <f aca="false">AB65+AB67*Assumptions!$B$168</f>
+        <f aca="false">AB65+AB67*Assumptions!$B$163</f>
         <v>2286.90237148129</v>
       </c>
       <c r="AC75" s="53" t="n">
-        <f aca="false">AC65+AC67*Assumptions!$B$168</f>
+        <f aca="false">AC65+AC67*Assumptions!$B$163</f>
         <v>3963.43025012807</v>
       </c>
       <c r="AD75" s="53" t="n">
-        <f aca="false">AD65+AD67*Assumptions!$B$168</f>
+        <f aca="false">AD65+AD67*Assumptions!$B$163</f>
         <v>6108.09559518737</v>
       </c>
       <c r="AE75" s="53" t="n">
-        <f aca="false">AE65+AE67*Assumptions!$B$168</f>
+        <f aca="false">AE65+AE67*Assumptions!$B$163</f>
         <v>8571.91731240708</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B76" s="23" t="s">
         <v>185</v>
@@ -14580,131 +14374,131 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C77" s="28" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$48,C76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$48,C76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="D77" s="28" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$48,D76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$48,D76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="E77" s="28" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$48,E76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$48,E76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="F77" s="28" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$48,F76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$48,F76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="G77" s="28" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$48,G76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$48,G76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="H77" s="28" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$48,H76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$48,H76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="I77" s="28" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$48,I76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$48,I76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="J77" s="28" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$48,J76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$48,J76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="K77" s="28" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$48,K76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$48,K76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="L77" s="28" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$48,L76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$48,L76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="M77" s="28" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$48,M76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$48,M76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="N77" s="28" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$48,N76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$48,N76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="O77" s="28" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$48,O76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$48,O76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="P77" s="28" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$48,P76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$48,P76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="Q77" s="28" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$48,Q76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$48,Q76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="R77" s="28" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$48,R76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$48,R76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="S77" s="28" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$48,S76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$48,S76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="T77" s="28" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$48,T76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$48,T76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="U77" s="28" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$48,U76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$48,U76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="V77" s="28" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$48,V76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$48,V76*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="W77" s="28" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$48,W76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$48,W76*Assumptions!$B$134,0)</f>
         <v>3.1976802</v>
       </c>
       <c r="X77" s="28" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$48,X76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$48,X76*Assumptions!$B$134,0)</f>
         <v>6.30248903362037</v>
       </c>
       <c r="Y77" s="28" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$48,Y76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$48,Y76*Assumptions!$B$134,0)</f>
         <v>9.3354074693751</v>
       </c>
       <c r="Z77" s="28" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$48,Z76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$48,Z76*Assumptions!$B$134,0)</f>
         <v>13.1927265384353</v>
       </c>
       <c r="AA77" s="28" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$48,AA76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$48,AA76*Assumptions!$B$134,0)</f>
         <v>112.980295227685</v>
       </c>
       <c r="AB77" s="28" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$48,AB76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$48,AB76*Assumptions!$B$134,0)</f>
         <v>226.403334776647</v>
       </c>
       <c r="AC77" s="28" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$48,AC76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$48,AC76*Assumptions!$B$134,0)</f>
         <v>392.379594762679</v>
       </c>
       <c r="AD77" s="28" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$48,AD76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$48,AD76*Assumptions!$B$134,0)</f>
         <v>604.70146392355</v>
       </c>
       <c r="AE77" s="28" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$48,AE76*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$48,AE76*Assumptions!$B$134,0)</f>
         <v>848.619813928301</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B78" s="23" t="s">
         <v>109</v>
@@ -14828,131 +14622,131 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>76</v>
       </c>
       <c r="C79" s="54" t="n">
-        <f aca="false">C78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">C78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="D79" s="54" t="n">
-        <f aca="false">D78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">D78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="E79" s="54" t="n">
-        <f aca="false">E78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">E78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="F79" s="54" t="n">
-        <f aca="false">F78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">F78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="G79" s="54" t="n">
-        <f aca="false">G78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">G78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="H79" s="54" t="n">
-        <f aca="false">H78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">H78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="I79" s="54" t="n">
-        <f aca="false">I78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">I78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="J79" s="54" t="n">
-        <f aca="false">J78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">J78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="K79" s="54" t="n">
-        <f aca="false">K78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">K78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="L79" s="54" t="n">
-        <f aca="false">L78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">L78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="M79" s="54" t="n">
-        <f aca="false">M78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">M78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="N79" s="54" t="n">
-        <f aca="false">N78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">N78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>0</v>
       </c>
       <c r="O79" s="54" t="n">
-        <f aca="false">O78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">O78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>14.1889870689655</v>
       </c>
       <c r="P79" s="54" t="n">
-        <f aca="false">P78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">P78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>21.4441313018357</v>
       </c>
       <c r="Q79" s="54" t="n">
-        <f aca="false">Q78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Q78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>28.7754219636977</v>
       </c>
       <c r="R79" s="54" t="n">
-        <f aca="false">R78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">R78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>34.5935787584534</v>
       </c>
       <c r="S79" s="54" t="n">
-        <f aca="false">S78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">S78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>41.5771273298616</v>
       </c>
       <c r="T79" s="54" t="n">
-        <f aca="false">T78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">T78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>49.6288365368252</v>
       </c>
       <c r="U79" s="54" t="n">
-        <f aca="false">U78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">U78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>57.6229617010566</v>
       </c>
       <c r="V79" s="54" t="n">
-        <f aca="false">V78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">V78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>65.3726196897888</v>
       </c>
       <c r="W79" s="54" t="n">
-        <f aca="false">W78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">W78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>72.2366142060459</v>
       </c>
       <c r="X79" s="54" t="n">
-        <f aca="false">X78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">X78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>76.3213217593821</v>
       </c>
       <c r="Y79" s="54" t="n">
-        <f aca="false">Y78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Y78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>81.8395404253454</v>
       </c>
       <c r="Z79" s="54" t="n">
-        <f aca="false">Z78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Z78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>88.76253712836</v>
       </c>
       <c r="AA79" s="54" t="n">
-        <f aca="false">AA78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AA78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>201.174102066705</v>
       </c>
       <c r="AB79" s="54" t="n">
-        <f aca="false">AB78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AB78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>257.355336305867</v>
       </c>
       <c r="AC79" s="54" t="n">
-        <f aca="false">AC78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AC78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>294.698526734985</v>
       </c>
       <c r="AD79" s="54" t="n">
-        <f aca="false">AD78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AD78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>329.95711338001</v>
       </c>
       <c r="AE79" s="54" t="n">
-        <f aca="false">AE78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AE78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>367.443954335902</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="B80" s="23" t="s">
         <v>109</v>
@@ -15076,10 +14870,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C81" s="44" t="n">
         <f aca="false">C77*C80*Assumptions!$B$7*C7</f>
@@ -15200,7 +14994,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B82" s="23" t="s">
         <v>109</v>
@@ -15324,255 +15118,255 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,C78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,C78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="D83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,D78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,D78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="E83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,E78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,E78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="F83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,F78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,F78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="G83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,G78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,G78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="H83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,H78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,H78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="I83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,I78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,I78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="J83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,J78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,J78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="K83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,K78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,K78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="L83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,L78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,L78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="M83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,M78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,M78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="N83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,N78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,N78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>0</v>
       </c>
       <c r="O83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,O78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,O78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>6.20345892985427</v>
       </c>
       <c r="P83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,P78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,P78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>9.37542526261803</v>
       </c>
       <c r="Q83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Q78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Q78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>12.5806829954381</v>
       </c>
       <c r="R83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,R78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,R78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>15.1243949988595</v>
       </c>
       <c r="S83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,S78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,S78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>18.1776190617758</v>
       </c>
       <c r="T83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,T78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,T78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>21.6978454977965</v>
       </c>
       <c r="U83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,U78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,U78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>25.1928960532298</v>
       </c>
       <c r="V83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,V78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,V78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>28.5810649774702</v>
       </c>
       <c r="W83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,W78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,W78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>31.5820197228218</v>
       </c>
       <c r="X83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,X78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,X78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>33.3678635906346</v>
       </c>
       <c r="Y83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Y78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Y78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>35.7804419300096</v>
       </c>
       <c r="Z83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Z78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Z78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>38.8071925718931</v>
       </c>
       <c r="AA83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AA78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AA78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>87.9537964095206</v>
       </c>
       <c r="AB83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AB78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AB78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>112.516365783726</v>
       </c>
       <c r="AC83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AC78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AC78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>128.842897551694</v>
       </c>
       <c r="AD83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AD78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AD78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>144.258035581915</v>
       </c>
       <c r="AE83" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AE78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AE78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>160.647371702214</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C84" s="44" t="n">
-        <f aca="false">C77*Assumptions!$B$151*Assumptions!$B$136*C7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">C77*Assumptions!$B$149*Assumptions!$B$135*C7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="D84" s="44" t="n">
-        <f aca="false">D77*Assumptions!$B$151*Assumptions!$B$136*D7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">D77*Assumptions!$B$149*Assumptions!$B$135*D7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="E84" s="44" t="n">
-        <f aca="false">E77*Assumptions!$B$151*Assumptions!$B$136*E7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">E77*Assumptions!$B$149*Assumptions!$B$135*E7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="F84" s="44" t="n">
-        <f aca="false">F77*Assumptions!$B$151*Assumptions!$B$136*F7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">F77*Assumptions!$B$149*Assumptions!$B$135*F7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G84" s="44" t="n">
-        <f aca="false">G77*Assumptions!$B$151*Assumptions!$B$136*G7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">G77*Assumptions!$B$149*Assumptions!$B$135*G7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="H84" s="44" t="n">
-        <f aca="false">H77*Assumptions!$B$151*Assumptions!$B$136*H7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">H77*Assumptions!$B$149*Assumptions!$B$135*H7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="I84" s="44" t="n">
-        <f aca="false">I77*Assumptions!$B$151*Assumptions!$B$136*I7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">I77*Assumptions!$B$149*Assumptions!$B$135*I7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="J84" s="44" t="n">
-        <f aca="false">J77*Assumptions!$B$151*Assumptions!$B$136*J7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">J77*Assumptions!$B$149*Assumptions!$B$135*J7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="K84" s="44" t="n">
-        <f aca="false">K77*Assumptions!$B$151*Assumptions!$B$136*K7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">K77*Assumptions!$B$149*Assumptions!$B$135*K7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="L84" s="44" t="n">
-        <f aca="false">L77*Assumptions!$B$151*Assumptions!$B$136*L7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">L77*Assumptions!$B$149*Assumptions!$B$135*L7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="M84" s="44" t="n">
-        <f aca="false">M77*Assumptions!$B$151*Assumptions!$B$136*M7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">M77*Assumptions!$B$149*Assumptions!$B$135*M7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="N84" s="44" t="n">
-        <f aca="false">N77*Assumptions!$B$151*Assumptions!$B$136*N7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">N77*Assumptions!$B$149*Assumptions!$B$135*N7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="O84" s="44" t="n">
-        <f aca="false">O77*Assumptions!$B$151*Assumptions!$B$136*O7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">O77*Assumptions!$B$149*Assumptions!$B$135*O7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="P84" s="44" t="n">
-        <f aca="false">P77*Assumptions!$B$151*Assumptions!$B$136*P7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">P77*Assumptions!$B$149*Assumptions!$B$135*P7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="Q84" s="44" t="n">
-        <f aca="false">Q77*Assumptions!$B$151*Assumptions!$B$136*Q7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Q77*Assumptions!$B$149*Assumptions!$B$135*Q7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="R84" s="44" t="n">
-        <f aca="false">R77*Assumptions!$B$151*Assumptions!$B$136*R7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">R77*Assumptions!$B$149*Assumptions!$B$135*R7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="S84" s="44" t="n">
-        <f aca="false">S77*Assumptions!$B$151*Assumptions!$B$136*S7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">S77*Assumptions!$B$149*Assumptions!$B$135*S7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="T84" s="44" t="n">
-        <f aca="false">T77*Assumptions!$B$151*Assumptions!$B$136*T7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">T77*Assumptions!$B$149*Assumptions!$B$135*T7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="U84" s="44" t="n">
-        <f aca="false">U77*Assumptions!$B$151*Assumptions!$B$136*U7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">U77*Assumptions!$B$149*Assumptions!$B$135*U7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="V84" s="44" t="n">
-        <f aca="false">V77*Assumptions!$B$151*Assumptions!$B$136*V7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">V77*Assumptions!$B$149*Assumptions!$B$135*V7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="W84" s="44" t="n">
-        <f aca="false">W77*Assumptions!$B$151*Assumptions!$B$136*W7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">W77*Assumptions!$B$149*Assumptions!$B$135*W7/12*(1+Assumptions!$B$16)</f>
         <v>2.3726787084</v>
       </c>
       <c r="X84" s="44" t="n">
-        <f aca="false">X77*Assumptions!$B$151*Assumptions!$B$136*X7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">X77*Assumptions!$B$149*Assumptions!$B$135*X7/12*(1+Assumptions!$B$16)</f>
         <v>4.67644686294632</v>
       </c>
       <c r="Y84" s="44" t="n">
-        <f aca="false">Y77*Assumptions!$B$151*Assumptions!$B$136*Y7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Y77*Assumptions!$B$149*Assumptions!$B$135*Y7/12*(1+Assumptions!$B$16)</f>
         <v>6.92687234227633</v>
       </c>
       <c r="Z84" s="44" t="n">
-        <f aca="false">Z77*Assumptions!$B$151*Assumptions!$B$136*Z7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Z77*Assumptions!$B$149*Assumptions!$B$135*Z7/12*(1+Assumptions!$B$16)</f>
         <v>9.78900309151903</v>
       </c>
       <c r="AA84" s="44" t="n">
-        <f aca="false">AA77*Assumptions!$B$151*Assumptions!$B$136*AA7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AA77*Assumptions!$B$149*Assumptions!$B$135*AA7/12*(1+Assumptions!$B$16)</f>
         <v>1005.97654870731</v>
       </c>
       <c r="AB84" s="44" t="n">
-        <f aca="false">AB77*Assumptions!$B$151*Assumptions!$B$136*AB7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AB77*Assumptions!$B$149*Assumptions!$B$135*AB7/12*(1+Assumptions!$B$16)</f>
         <v>2015.89529285127</v>
       </c>
       <c r="AC84" s="44" t="n">
-        <f aca="false">AC77*Assumptions!$B$151*Assumptions!$B$136*AC7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AC77*Assumptions!$B$149*Assumptions!$B$135*AC7/12*(1+Assumptions!$B$16)</f>
         <v>3493.74791176689</v>
       </c>
       <c r="AD84" s="44" t="n">
-        <f aca="false">AD77*Assumptions!$B$151*Assumptions!$B$136*AD7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AD77*Assumptions!$B$149*Assumptions!$B$135*AD7/12*(1+Assumptions!$B$16)</f>
         <v>5384.26183477529</v>
       </c>
       <c r="AE84" s="44" t="n">
-        <f aca="false">AE77*Assumptions!$B$151*Assumptions!$B$136*AE7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AE77*Assumptions!$B$149*Assumptions!$B$135*AE7/12*(1+Assumptions!$B$16)</f>
         <v>7556.11082321759</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B85" s="23" t="s">
         <v>109</v>
@@ -15696,7 +15490,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="B86" s="23" t="s">
         <v>109</v>
@@ -15820,630 +15614,630 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B87" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C87" s="54" t="n">
-        <f aca="false">C82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">C82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="D87" s="54" t="n">
-        <f aca="false">D82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">D82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="E87" s="54" t="n">
-        <f aca="false">E82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">E82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="F87" s="54" t="n">
-        <f aca="false">F82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">F82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="G87" s="54" t="n">
-        <f aca="false">G82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">G82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="H87" s="54" t="n">
-        <f aca="false">H82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">H82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="I87" s="54" t="n">
-        <f aca="false">I82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">I82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="J87" s="54" t="n">
-        <f aca="false">J82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">J82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="K87" s="54" t="n">
-        <f aca="false">K82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">K82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="L87" s="54" t="n">
-        <f aca="false">L82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">L82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="M87" s="54" t="n">
-        <f aca="false">M82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">M82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="N87" s="54" t="n">
-        <f aca="false">N82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">N82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="O87" s="54" t="n">
-        <f aca="false">O82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">O82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="P87" s="54" t="n">
-        <f aca="false">P82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">P82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="Q87" s="54" t="n">
-        <f aca="false">Q82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Q82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="R87" s="54" t="n">
-        <f aca="false">R82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">R82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="S87" s="54" t="n">
-        <f aca="false">S82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">S82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="T87" s="54" t="n">
-        <f aca="false">T82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">T82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="U87" s="54" t="n">
-        <f aca="false">U82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">U82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="V87" s="54" t="n">
-        <f aca="false">V82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">V82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="W87" s="54" t="n">
-        <f aca="false">W82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">W82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0.0970156282039189</v>
       </c>
       <c r="X87" s="54" t="n">
-        <f aca="false">X82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">X82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0.206066523301093</v>
       </c>
       <c r="Y87" s="54" t="n">
-        <f aca="false">Y82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Y82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0.336926406526855</v>
       </c>
       <c r="Z87" s="54" t="n">
-        <f aca="false">Z82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Z82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0.56068431815721</v>
       </c>
       <c r="AA87" s="54" t="n">
-        <f aca="false">AA82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AA82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>114.552695596051</v>
       </c>
       <c r="AB87" s="54" t="n">
-        <f aca="false">AB82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AB82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>293.661176065557</v>
       </c>
       <c r="AC87" s="54" t="n">
-        <f aca="false">AC82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AC82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>582.793790027057</v>
       </c>
       <c r="AD87" s="54" t="n">
-        <f aca="false">AD82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AD82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1005.60876944412</v>
       </c>
       <c r="AE87" s="54" t="n">
-        <f aca="false">AE82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AE82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1571.57390959436</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="B88" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C88" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C65*Assumptions!$B$152*Assumptions!$B$25/12*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C65*Assumptions!$B$150*Assumptions!$B$25/12*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D88" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D65*Assumptions!$B$152*Assumptions!$B$25/12*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D65*Assumptions!$B$150*Assumptions!$B$25/12*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E88" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E65*Assumptions!$B$152*Assumptions!$B$25/12*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E65*Assumptions!$B$150*Assumptions!$B$25/12*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F88" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F65*Assumptions!$B$152*Assumptions!$B$25/12*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F65*Assumptions!$B$150*Assumptions!$B$25/12*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G88" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G65*Assumptions!$B$152*Assumptions!$B$25/12*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G65*Assumptions!$B$150*Assumptions!$B$25/12*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H88" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H65*Assumptions!$B$152*Assumptions!$B$25/12*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H65*Assumptions!$B$150*Assumptions!$B$25/12*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I88" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I65*Assumptions!$B$152*Assumptions!$B$25/12*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I65*Assumptions!$B$150*Assumptions!$B$25/12*I7,0)</f>
         <v>0</v>
       </c>
       <c r="J88" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J65*Assumptions!$B$152*Assumptions!$B$25/12*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J65*Assumptions!$B$150*Assumptions!$B$25/12*J7,0)</f>
         <v>0</v>
       </c>
       <c r="K88" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K65*Assumptions!$B$152*Assumptions!$B$25/12*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K65*Assumptions!$B$150*Assumptions!$B$25/12*K7,0)</f>
         <v>0</v>
       </c>
       <c r="L88" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L65*Assumptions!$B$152*Assumptions!$B$25/12*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L65*Assumptions!$B$150*Assumptions!$B$25/12*L7,0)</f>
         <v>0</v>
       </c>
       <c r="M88" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M65*Assumptions!$B$152*Assumptions!$B$25/12*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M65*Assumptions!$B$150*Assumptions!$B$25/12*M7,0)</f>
         <v>0</v>
       </c>
       <c r="N88" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N65*Assumptions!$B$152*Assumptions!$B$25/12*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N65*Assumptions!$B$150*Assumptions!$B$25/12*N7,0)</f>
         <v>0</v>
       </c>
       <c r="O88" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O65*Assumptions!$B$152*Assumptions!$B$25/12*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O65*Assumptions!$B$150*Assumptions!$B$25/12*O7,0)</f>
         <v>63.0103087392635</v>
       </c>
       <c r="P88" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P65*Assumptions!$B$152*Assumptions!$B$25/12*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P65*Assumptions!$B$150*Assumptions!$B$25/12*P7,0)</f>
         <v>121.128342253012</v>
       </c>
       <c r="Q88" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q65*Assumptions!$B$152*Assumptions!$B$25/12*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q65*Assumptions!$B$150*Assumptions!$B$25/12*Q7,0)</f>
         <v>175.005290837465</v>
       </c>
       <c r="R88" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R65*Assumptions!$B$152*Assumptions!$B$25/12*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R65*Assumptions!$B$150*Assumptions!$B$25/12*R7,0)</f>
         <v>242.508687894201</v>
       </c>
       <c r="S88" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S65*Assumptions!$B$152*Assumptions!$B$25/12*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S65*Assumptions!$B$150*Assumptions!$B$25/12*S7,0)</f>
         <v>300.93223228342</v>
       </c>
       <c r="T88" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T65*Assumptions!$B$152*Assumptions!$B$25/12*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T65*Assumptions!$B$150*Assumptions!$B$25/12*T7,0)</f>
         <v>346.783093825493</v>
       </c>
       <c r="U88" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U65*Assumptions!$B$152*Assumptions!$B$25/12*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U65*Assumptions!$B$150*Assumptions!$B$25/12*U7,0)</f>
         <v>389.144387314715</v>
       </c>
       <c r="V88" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V65*Assumptions!$B$152*Assumptions!$B$25/12*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V65*Assumptions!$B$150*Assumptions!$B$25/12*V7,0)</f>
         <v>430.180110443849</v>
       </c>
       <c r="W88" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W65*Assumptions!$B$152*Assumptions!$B$25/12*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W65*Assumptions!$B$150*Assumptions!$B$25/12*W7,0)</f>
         <v>475.634866778468</v>
       </c>
       <c r="X88" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X65*Assumptions!$B$152*Assumptions!$B$25/12*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X65*Assumptions!$B$150*Assumptions!$B$25/12*X7,0)</f>
         <v>542.859265739692</v>
       </c>
       <c r="Y88" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y65*Assumptions!$B$152*Assumptions!$B$25/12*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y65*Assumptions!$B$150*Assumptions!$B$25/12*Y7,0)</f>
         <v>601.155185226398</v>
       </c>
       <c r="Z88" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z65*Assumptions!$B$152*Assumptions!$B$25/12*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z65*Assumptions!$B$150*Assumptions!$B$25/12*Z7,0)</f>
         <v>647.486587590434</v>
       </c>
       <c r="AA88" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA65*Assumptions!$B$152*Assumptions!$B$25/12*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA65*Assumptions!$B$150*Assumptions!$B$25/12*AA7,0)</f>
         <v>17042.6900700375</v>
       </c>
       <c r="AB88" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB65*Assumptions!$B$152*Assumptions!$B$25/12*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB65*Assumptions!$B$150*Assumptions!$B$25/12*AB7,0)</f>
         <v>29765.4255822734</v>
       </c>
       <c r="AC88" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC65*Assumptions!$B$152*Assumptions!$B$25/12*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC65*Assumptions!$B$150*Assumptions!$B$25/12*AC7,0)</f>
         <v>46211.2965115159</v>
       </c>
       <c r="AD88" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD65*Assumptions!$B$152*Assumptions!$B$25/12*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD65*Assumptions!$B$150*Assumptions!$B$25/12*AD7,0)</f>
         <v>63588.8464109865</v>
       </c>
       <c r="AE88" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE65*Assumptions!$B$152*Assumptions!$B$25/12*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE65*Assumptions!$B$150*Assumptions!$B$25/12*AE7,0)</f>
         <v>78827.1236661663</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B89" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C89" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$49,C82*C17*Assumptions!$B$17+C77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$49,C82*C17*Assumptions!$B$17+C77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D89" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$49,D82*D17*Assumptions!$B$17+D77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$49,D82*D17*Assumptions!$B$17+D77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E89" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$49,E82*E17*Assumptions!$B$17+E77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$49,E82*E17*Assumptions!$B$17+E77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F89" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$49,F82*F17*Assumptions!$B$17+F77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$49,F82*F17*Assumptions!$B$17+F77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G89" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$49,G82*G17*Assumptions!$B$17+G77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$49,G82*G17*Assumptions!$B$17+G77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H89" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$49,H82*H17*Assumptions!$B$17+H77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$49,H82*H17*Assumptions!$B$17+H77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I89" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$49,I82*I17*Assumptions!$B$17+I77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$49,I82*I17*Assumptions!$B$17+I77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
         <v>0</v>
       </c>
       <c r="J89" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$49,J82*J17*Assumptions!$B$17+J77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$49,J82*J17*Assumptions!$B$17+J77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
         <v>0</v>
       </c>
       <c r="K89" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$49,K82*K17*Assumptions!$B$17+K77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$49,K82*K17*Assumptions!$B$17+K77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
         <v>0</v>
       </c>
       <c r="L89" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$49,L82*L17*Assumptions!$B$17+L77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$49,L82*L17*Assumptions!$B$17+L77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
         <v>0</v>
       </c>
       <c r="M89" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$49,M82*M17*Assumptions!$B$17+M77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$49,M82*M17*Assumptions!$B$17+M77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
         <v>0</v>
       </c>
       <c r="N89" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$49,N82*N17*Assumptions!$B$17+N77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$49,N82*N17*Assumptions!$B$17+N77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
         <v>0</v>
       </c>
       <c r="O89" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$49,O82*O17*Assumptions!$B$17+O77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$49,O82*O17*Assumptions!$B$17+O77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
         <v>0</v>
       </c>
       <c r="P89" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$49,P82*P17*Assumptions!$B$17+P77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$49,P82*P17*Assumptions!$B$17+P77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
         <v>0</v>
       </c>
       <c r="Q89" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$49,Q82*Q17*Assumptions!$B$17+Q77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$49,Q82*Q17*Assumptions!$B$17+Q77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
         <v>0</v>
       </c>
       <c r="R89" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$49,R82*R17*Assumptions!$B$17+R77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$49,R82*R17*Assumptions!$B$17+R77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
         <v>0</v>
       </c>
       <c r="S89" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$49,S82*S17*Assumptions!$B$17+S77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$49,S82*S17*Assumptions!$B$17+S77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
         <v>0</v>
       </c>
       <c r="T89" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$49,T82*T17*Assumptions!$B$17+T77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$49,T82*T17*Assumptions!$B$17+T77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
         <v>0</v>
       </c>
       <c r="U89" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$49,U82*U17*Assumptions!$B$17+U77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$49,U82*U17*Assumptions!$B$17+U77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
         <v>0</v>
       </c>
       <c r="V89" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$49,V82*V17*Assumptions!$B$17+V77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$49,V82*V17*Assumptions!$B$17+V77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
         <v>0</v>
       </c>
       <c r="W89" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$49,W82*W17*Assumptions!$B$17+W77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$49,W82*W17*Assumptions!$B$17+W77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
         <v>10.8645505394523</v>
       </c>
       <c r="X89" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$49,X82*X17*Assumptions!$B$17+X77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$49,X82*X17*Assumptions!$B$17+X77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
         <v>21.4736734196951</v>
       </c>
       <c r="Y89" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$49,Y82*Y17*Assumptions!$B$17+Y77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$49,Y82*Y17*Assumptions!$B$17+Y77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
         <v>31.8296647755427</v>
       </c>
       <c r="Z89" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$49,Z82*Z17*Assumptions!$B$17+Z77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$49,Z82*Z17*Assumptions!$B$17+Z77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
         <v>44.9439745149232</v>
       </c>
       <c r="AA89" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$49,AA82*AA17*Assumptions!$B$17+AA77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$49,AA82*AA17*Assumptions!$B$17+AA77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
         <v>4710.68367165603</v>
       </c>
       <c r="AB89" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$49,AB82*AB17*Assumptions!$B$17+AB77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$49,AB82*AB17*Assumptions!$B$17+AB77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
         <v>9526.32085898027</v>
       </c>
       <c r="AC89" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$49,AC82*AC17*Assumptions!$B$17+AC77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$49,AC82*AC17*Assumptions!$B$17+AC77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
         <v>16609.7040400814</v>
       </c>
       <c r="AD89" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$49,AD82*AD17*Assumptions!$B$17+AD77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$49,AD82*AD17*Assumptions!$B$17+AD77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
         <v>25742.4202463073</v>
       </c>
       <c r="AE89" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$49,AE82*AE17*Assumptions!$B$17+AE77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$49,AE82*AE17*Assumptions!$B$17+AE77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
         <v>36342.4590335677</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B90" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C90" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$50,C77*C78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$50,C77*C78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="D90" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$50,D77*D78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$50,D77*D78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="E90" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$50,E77*E78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$50,E77*E78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="F90" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$50,F77*F78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$50,F77*F78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="G90" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$50,G77*G78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$50,G77*G78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="H90" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$50,H77*H78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$50,H77*H78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="I90" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$50,I77*I78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$50,I77*I78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="J90" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$50,J77*J78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$50,J77*J78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="K90" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$50,K77*K78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$50,K77*K78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="L90" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$50,L77*L78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$50,L77*L78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="M90" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$50,M77*M78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$50,M77*M78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="N90" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$50,N77*N78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$50,N77*N78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="O90" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$50,O77*O78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$50,O77*O78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="P90" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$50,P77*P78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$50,P77*P78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="Q90" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,Q77*Q78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,Q77*Q78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="R90" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$50,R77*R78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$50,R77*R78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="S90" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$50,S77*S78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$50,S77*S78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="T90" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$50,T77*T78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$50,T77*T78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="U90" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$50,U77*U78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$50,U77*U78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="V90" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$50,V77*V78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$50,V77*V78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="W90" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$50,W77*W78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$50,W77*W78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>46.1979181923423</v>
       </c>
       <c r="X90" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$50,X77*X78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$50,X77*X78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>96.2028586839836</v>
       </c>
       <c r="Y90" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,Y77*Y78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,Y77*Y78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>152.801091395399</v>
       </c>
       <c r="Z90" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,Z77*Z78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,Z77*Z78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>234.203975838433</v>
       </c>
       <c r="AA90" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,AA77*AA78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,AA77*AA78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>4545.74188873216</v>
       </c>
       <c r="AB90" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,AB77*AB78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,AB77*AB78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>11653.2212724428</v>
       </c>
       <c r="AC90" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,AC77*AC78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,AC77*AC78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>23126.7376994864</v>
       </c>
       <c r="AD90" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,AD77*AD78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,AD77*AD78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>39905.1098985762</v>
       </c>
       <c r="AE90" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,AE77*AE78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,AE77*AE78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>62364.0440315224</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B91" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C91" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$50,(C90*Assumptions!$B$29*Assumptions!$B$30+C77*C79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$50,(C90*Assumptions!$B$29*Assumptions!$B$30+C77*C79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v>0</v>
       </c>
       <c r="D91" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$50,(D90*Assumptions!$B$29*Assumptions!$B$30+D77*D79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$50,(D90*Assumptions!$B$29*Assumptions!$B$30+D77*D79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v>0</v>
       </c>
       <c r="E91" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$50,(E90*Assumptions!$B$29*Assumptions!$B$30+E77*E79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$50,(E90*Assumptions!$B$29*Assumptions!$B$30+E77*E79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v>0</v>
       </c>
       <c r="F91" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$50,(F90*Assumptions!$B$29*Assumptions!$B$30+F77*F79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$50,(F90*Assumptions!$B$29*Assumptions!$B$30+F77*F79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v>0</v>
       </c>
       <c r="G91" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$50,(G90*Assumptions!$B$29*Assumptions!$B$30+G77*G79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$50,(G90*Assumptions!$B$29*Assumptions!$B$30+G77*G79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v>0</v>
       </c>
       <c r="H91" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$50,(H90*Assumptions!$B$29*Assumptions!$B$30+H77*H79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$50,(H90*Assumptions!$B$29*Assumptions!$B$30+H77*H79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v>0</v>
       </c>
       <c r="I91" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$50,(I90*Assumptions!$B$29*Assumptions!$B$30+I77*I79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$50,(I90*Assumptions!$B$29*Assumptions!$B$30+I77*I79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v>0</v>
       </c>
       <c r="J91" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$50,(J90*Assumptions!$B$29*Assumptions!$B$30+J77*J79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$50,(J90*Assumptions!$B$29*Assumptions!$B$30+J77*J79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v>0</v>
       </c>
       <c r="K91" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$50,(K90*Assumptions!$B$29*Assumptions!$B$30+K77*K79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$50,(K90*Assumptions!$B$29*Assumptions!$B$30+K77*K79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v>0</v>
       </c>
       <c r="L91" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$50,(L90*Assumptions!$B$29*Assumptions!$B$30+L77*L79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$50,(L90*Assumptions!$B$29*Assumptions!$B$30+L77*L79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v>0</v>
       </c>
       <c r="M91" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$50,(M90*Assumptions!$B$29*Assumptions!$B$30+M77*M79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$50,(M90*Assumptions!$B$29*Assumptions!$B$30+M77*M79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v>0</v>
       </c>
       <c r="N91" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$50,(N90*Assumptions!$B$29*Assumptions!$B$30+N77*N79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$50,(N90*Assumptions!$B$29*Assumptions!$B$30+N77*N79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v>0</v>
       </c>
       <c r="O91" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$50,(O90*Assumptions!$B$29*Assumptions!$B$30+O77*O79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$50,(O90*Assumptions!$B$29*Assumptions!$B$30+O77*O79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v>0</v>
       </c>
       <c r="P91" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$50,(P90*Assumptions!$B$29*Assumptions!$B$30+P77*P79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$50,(P90*Assumptions!$B$29*Assumptions!$B$30+P77*P79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v>0</v>
       </c>
       <c r="Q91" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,(Q90*Assumptions!$B$29*Assumptions!$B$30+Q77*Q79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,(Q90*Assumptions!$B$29*Assumptions!$B$30+Q77*Q79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v>0</v>
       </c>
       <c r="R91" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$50,(R90*Assumptions!$B$29*Assumptions!$B$30+R77*R79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$50,(R90*Assumptions!$B$29*Assumptions!$B$30+R77*R79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v>0</v>
       </c>
       <c r="S91" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$50,(S90*Assumptions!$B$29*Assumptions!$B$30+S77*S79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$50,(S90*Assumptions!$B$29*Assumptions!$B$30+S77*S79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v>0</v>
       </c>
       <c r="T91" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$50,(T90*Assumptions!$B$29*Assumptions!$B$30+T77*T79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$50,(T90*Assumptions!$B$29*Assumptions!$B$30+T77*T79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v>0</v>
       </c>
       <c r="U91" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$50,(U90*Assumptions!$B$29*Assumptions!$B$30+U77*U79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$50,(U90*Assumptions!$B$29*Assumptions!$B$30+U77*U79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v>0</v>
       </c>
       <c r="V91" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$50,(V90*Assumptions!$B$29*Assumptions!$B$30+V77*V79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$50,(V90*Assumptions!$B$29*Assumptions!$B$30+V77*V79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v>0</v>
       </c>
       <c r="W91" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$50,(W90*Assumptions!$B$29*Assumptions!$B$30+W77*W79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$50,(W90*Assumptions!$B$29*Assumptions!$B$30+W77*W79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v>0.109720055706813</v>
       </c>
       <c r="X91" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$50,(X90*Assumptions!$B$29*Assumptions!$B$30+X77*X79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$50,(X90*Assumptions!$B$29*Assumptions!$B$30+X77*X79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v>0.228481789374461</v>
       </c>
       <c r="Y91" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,(Y90*Assumptions!$B$29*Assumptions!$B$30+Y77*Y79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,(Y90*Assumptions!$B$29*Assumptions!$B$30+Y77*Y79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v>0.362902592064073</v>
       </c>
       <c r="Z91" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,(Z90*Assumptions!$B$29*Assumptions!$B$30+Z77*Z79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,(Z90*Assumptions!$B$29*Assumptions!$B$30+Z77*Z79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v>0.556234442616279</v>
       </c>
       <c r="AA91" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,(AA90*Assumptions!$B$29*Assumptions!$B$30+AA77*AA79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,(AA90*Assumptions!$B$29*Assumptions!$B$30+AA77*AA79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v>129.553643828867</v>
       </c>
       <c r="AB91" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,(AB90*Assumptions!$B$29*Assumptions!$B$30+AB77*AB79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,(AB90*Assumptions!$B$29*Assumptions!$B$30+AB77*AB79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v>332.116806264619</v>
       </c>
       <c r="AC91" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,(AC90*Assumptions!$B$29*Assumptions!$B$30+AC77*AC79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,(AC90*Assumptions!$B$29*Assumptions!$B$30+AC77*AC79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v>659.112024435362</v>
       </c>
       <c r="AD91" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,(AD90*Assumptions!$B$29*Assumptions!$B$30+AD77*AD79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,(AD90*Assumptions!$B$29*Assumptions!$B$30+AD77*AD79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v>1137.29563210942</v>
       </c>
       <c r="AE91" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,(AE90*Assumptions!$B$29*Assumptions!$B$30+AE77*AE79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,(AE90*Assumptions!$B$29*Assumptions!$B$30+AE77*AE79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v>1777.37525489839</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C92" s="44" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$46,(C65+C67*Assumptions!$B$129)*Assumptions!$B$128*C7/12,0)</f>
@@ -16564,7 +16358,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="B93" s="23" t="s">
         <v>109</v>
@@ -16688,7 +16482,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="45" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="B95" s="46"/>
       <c r="C95" s="46"/>
@@ -16723,7 +16517,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B96" s="23" t="s">
         <v>185</v>
@@ -16847,7 +16641,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B97" s="23" t="s">
         <v>185</v>
@@ -16970,7 +16764,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="B98" s="23" t="s">
         <v>185</v>
@@ -17094,10 +16888,10 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C99" s="50" t="n">
         <v>1</v>
@@ -17217,7 +17011,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="B100" s="23" t="s">
         <v>185</v>
@@ -17341,7 +17135,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B101" s="23" t="s">
         <v>185</v>
@@ -17465,7 +17259,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="B102" s="23" t="s">
         <v>185</v>
@@ -17589,7 +17383,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B103" s="23" t="s">
         <v>185</v>
@@ -17713,7 +17507,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="B104" s="23" t="s">
         <v>185</v>
@@ -17837,131 +17631,131 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B105" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C105" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$44,C101*Assumptions!$B$163*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$44,C101*Assumptions!$B$161*C7,0)</f>
         <v>2328.89884083207</v>
       </c>
       <c r="D105" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$44,D101*Assumptions!$B$163*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$44,D101*Assumptions!$B$161*D7,0)</f>
         <v>4425.29637752063</v>
       </c>
       <c r="E105" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$44,E101*Assumptions!$B$163*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$44,E101*Assumptions!$B$161*E7,0)</f>
         <v>6324.0836607316</v>
       </c>
       <c r="F105" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$44,F101*Assumptions!$B$163*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$44,F101*Assumptions!$B$161*F7,0)</f>
         <v>8654.67631287747</v>
       </c>
       <c r="G105" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$44,G101*Assumptions!$B$163*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$44,G101*Assumptions!$B$161*G7,0)</f>
         <v>10614.7384529907</v>
       </c>
       <c r="H105" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$44,H101*Assumptions!$B$163*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$44,H101*Assumptions!$B$161*H7,0)</f>
         <v>12109.512783455</v>
       </c>
       <c r="I105" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$44,I101*Assumptions!$B$163*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$44,I101*Assumptions!$B$161*I7,0)</f>
         <v>13460.0196090584</v>
       </c>
       <c r="J105" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$44,J101*Assumptions!$B$163*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$44,J101*Assumptions!$B$161*J7,0)</f>
         <v>14741.9244354845</v>
       </c>
       <c r="K105" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$44,K101*Assumptions!$B$163*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$44,K101*Assumptions!$B$161*K7,0)</f>
         <v>16140.5032752361</v>
       </c>
       <c r="L105" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$44,L101*Assumptions!$B$163*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$44,L101*Assumptions!$B$161*L7,0)</f>
         <v>18194.1005060361</v>
       </c>
       <c r="M105" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$44,M101*Assumptions!$B$163*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$44,M101*Assumptions!$B$161*M7,0)</f>
         <v>19914.9754501246</v>
       </c>
       <c r="N105" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$44,N101*Assumptions!$B$163*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$44,N101*Assumptions!$B$161*N7,0)</f>
         <v>21230.3367357236</v>
       </c>
       <c r="O105" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$44,O101*Assumptions!$B$163*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$44,O101*Assumptions!$B$161*O7,0)</f>
         <v>27654.7679342518</v>
       </c>
       <c r="P105" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$44,P101*Assumptions!$B$163*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$44,P101*Assumptions!$B$161*P7,0)</f>
         <v>33491.7366890793</v>
       </c>
       <c r="Q105" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$44,Q101*Assumptions!$B$163*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$44,Q101*Assumptions!$B$161*Q7,0)</f>
         <v>38823.9280063937</v>
       </c>
       <c r="R105" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$44,R101*Assumptions!$B$163*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$44,R101*Assumptions!$B$161*R7,0)</f>
         <v>45721.7821330174</v>
       </c>
       <c r="S105" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$44,S101*Assumptions!$B$163*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$44,S101*Assumptions!$B$161*S7,0)</f>
         <v>51542.7960219198</v>
       </c>
       <c r="T105" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$44,T101*Assumptions!$B$163*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$44,T101*Assumptions!$B$161*T7,0)</f>
         <v>55908.938139351</v>
       </c>
       <c r="U105" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$44,U101*Assumptions!$B$163*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$44,U101*Assumptions!$B$161*U7,0)</f>
         <v>59870.4808954726</v>
       </c>
       <c r="V105" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$44,V101*Assumptions!$B$163*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$44,V101*Assumptions!$B$161*V7,0)</f>
         <v>63674.186453339</v>
       </c>
       <c r="W105" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$44,W101*Assumptions!$B$163*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$44,W101*Assumptions!$B$161*W7,0)</f>
         <v>67958.6446663875</v>
       </c>
       <c r="X105" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$44,X101*Assumptions!$B$163*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$44,X101*Assumptions!$B$161*X7,0)</f>
         <v>74625.180861561</v>
       </c>
       <c r="Y105" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$44,Y101*Assumptions!$B$163*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$44,Y101*Assumptions!$B$161*Y7,0)</f>
         <v>80252.9551889773</v>
       </c>
       <c r="Z105" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$44,Z101*Assumptions!$B$163*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$44,Z101*Assumptions!$B$161*Z7,0)</f>
         <v>84534.2277569755</v>
       </c>
       <c r="AA105" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$44,AA101*Assumptions!$B$163*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$44,AA101*Assumptions!$B$161*AA7,0)</f>
         <v>1836962.31940587</v>
       </c>
       <c r="AB105" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$44,AB101*Assumptions!$B$163*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$44,AB101*Assumptions!$B$161*AB7,0)</f>
         <v>2826204.38794753</v>
       </c>
       <c r="AC105" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$44,AC101*Assumptions!$B$163*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$44,AC101*Assumptions!$B$161*AC7,0)</f>
         <v>3755689.39169232</v>
       </c>
       <c r="AD105" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$44,AD101*Assumptions!$B$163*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$44,AD101*Assumptions!$B$161*AD7,0)</f>
         <v>4187442.06517568</v>
       </c>
       <c r="AE105" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$44,AE101*Assumptions!$B$163*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$44,AE101*Assumptions!$B$161*AE7,0)</f>
         <v>3887615.65942124</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="B106" s="23" t="s">
         <v>109</v>
@@ -18085,7 +17879,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B107" s="23" t="s">
         <v>47</v>
@@ -18209,10 +18003,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="B108" s="23" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="C108" s="55" t="n">
         <f aca="false">(Assumptions!$B$127+Assumptions!$B$128*IF(C101+C103=0,1,(C101+C103*Assumptions!$B$129)/(C101+C103)))*C7/12</f>
@@ -18333,7 +18127,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B109" s="23" t="s">
         <v>47</v>
@@ -18457,7 +18251,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B110" s="23" t="s">
         <v>109</v>
@@ -18581,131 +18375,131 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B111" s="23" t="s">
         <v>185</v>
       </c>
       <c r="C111" s="53" t="n">
-        <f aca="false">C101+C103*Assumptions!$B$168</f>
+        <f aca="false">C101+C103*Assumptions!$B$163</f>
         <v>79.588</v>
       </c>
       <c r="D111" s="53" t="n">
-        <f aca="false">D101+D103*Assumptions!$B$168</f>
+        <f aca="false">D101+D103*Assumptions!$B$163</f>
         <v>155.098384616594</v>
       </c>
       <c r="E111" s="53" t="n">
-        <f aca="false">E101+E103*Assumptions!$B$168</f>
+        <f aca="false">E101+E103*Assumptions!$B$163</f>
         <v>227.337378616796</v>
       </c>
       <c r="F111" s="53" t="n">
-        <f aca="false">F101+F103*Assumptions!$B$168</f>
+        <f aca="false">F101+F103*Assumptions!$B$163</f>
         <v>317.48649145679</v>
       </c>
       <c r="G111" s="53" t="n">
-        <f aca="false">G101+G103*Assumptions!$B$168</f>
+        <f aca="false">G101+G103*Assumptions!$B$163</f>
         <v>398.843779389411</v>
       </c>
       <c r="H111" s="53" t="n">
-        <f aca="false">H101+H103*Assumptions!$B$168</f>
+        <f aca="false">H101+H103*Assumptions!$B$163</f>
         <v>467.555609719971</v>
       </c>
       <c r="I111" s="53" t="n">
-        <f aca="false">I101+I103*Assumptions!$B$168</f>
+        <f aca="false">I101+I103*Assumptions!$B$163</f>
         <v>533.819795440222</v>
       </c>
       <c r="J111" s="53" t="n">
-        <f aca="false">J101+J103*Assumptions!$B$168</f>
+        <f aca="false">J101+J103*Assumptions!$B$163</f>
         <v>599.982532585397</v>
       </c>
       <c r="K111" s="53" t="n">
-        <f aca="false">K101+K103*Assumptions!$B$168</f>
+        <f aca="false">K101+K103*Assumptions!$B$163</f>
         <v>672.261524130128</v>
       </c>
       <c r="L111" s="53" t="n">
-        <f aca="false">L101+L103*Assumptions!$B$168</f>
+        <f aca="false">L101+L103*Assumptions!$B$163</f>
         <v>769.24797532723</v>
       </c>
       <c r="M111" s="53" t="n">
-        <f aca="false">M101+M103*Assumptions!$B$168</f>
+        <f aca="false">M101+M103*Assumptions!$B$163</f>
         <v>858.274621006678</v>
       </c>
       <c r="N111" s="53" t="n">
-        <f aca="false">N101+N103*Assumptions!$B$168</f>
+        <f aca="false">N101+N103*Assumptions!$B$163</f>
         <v>936.301287051554</v>
       </c>
       <c r="O111" s="53" t="n">
-        <f aca="false">O101+O103*Assumptions!$B$168</f>
+        <f aca="false">O101+O103*Assumptions!$B$163</f>
         <v>1191.11036280643</v>
       </c>
       <c r="P111" s="53" t="n">
-        <f aca="false">P101+P103*Assumptions!$B$168</f>
+        <f aca="false">P101+P103*Assumptions!$B$163</f>
         <v>1436.51333237038</v>
       </c>
       <c r="Q111" s="53" t="n">
-        <f aca="false">Q101+Q103*Assumptions!$B$168</f>
+        <f aca="false">Q101+Q103*Assumptions!$B$163</f>
         <v>1674.36020533866</v>
       </c>
       <c r="R111" s="53" t="n">
-        <f aca="false">R101+R103*Assumptions!$B$168</f>
+        <f aca="false">R101+R103*Assumptions!$B$163</f>
         <v>1974.56804474914</v>
       </c>
       <c r="S111" s="53" t="n">
-        <f aca="false">S101+S103*Assumptions!$B$168</f>
+        <f aca="false">S101+S103*Assumptions!$B$163</f>
         <v>2249.43201193502</v>
       </c>
       <c r="T111" s="53" t="n">
-        <f aca="false">T101+T103*Assumptions!$B$168</f>
+        <f aca="false">T101+T103*Assumptions!$B$163</f>
         <v>2484.24477435057</v>
       </c>
       <c r="U111" s="53" t="n">
-        <f aca="false">U101+U103*Assumptions!$B$168</f>
+        <f aca="false">U101+U103*Assumptions!$B$163</f>
         <v>2712.48214170006</v>
       </c>
       <c r="V111" s="53" t="n">
-        <f aca="false">V101+V103*Assumptions!$B$168</f>
+        <f aca="false">V101+V103*Assumptions!$B$163</f>
         <v>2941.90501571195</v>
       </c>
       <c r="W111" s="53" t="n">
-        <f aca="false">W101+W103*Assumptions!$B$168</f>
+        <f aca="false">W101+W103*Assumptions!$B$163</f>
         <v>3194.07448313124</v>
       </c>
       <c r="X111" s="53" t="n">
-        <f aca="false">X101+X103*Assumptions!$B$168</f>
+        <f aca="false">X101+X103*Assumptions!$B$163</f>
         <v>3534.76505642459</v>
       </c>
       <c r="Y111" s="53" t="n">
-        <f aca="false">Y101+Y103*Assumptions!$B$168</f>
+        <f aca="false">Y101+Y103*Assumptions!$B$163</f>
         <v>3851.02887137982</v>
       </c>
       <c r="Z111" s="53" t="n">
-        <f aca="false">Z101+Z103*Assumptions!$B$168</f>
+        <f aca="false">Z101+Z103*Assumptions!$B$163</f>
         <v>4130.62399009909</v>
       </c>
       <c r="AA111" s="53" t="n">
-        <f aca="false">AA101+AA103*Assumptions!$B$168</f>
+        <f aca="false">AA101+AA103*Assumptions!$B$163</f>
         <v>8921.32496728877</v>
       </c>
       <c r="AB111" s="53" t="n">
-        <f aca="false">AB101+AB103*Assumptions!$B$168</f>
+        <f aca="false">AB101+AB103*Assumptions!$B$163</f>
         <v>15722.7846947652</v>
       </c>
       <c r="AC111" s="53" t="n">
-        <f aca="false">AC101+AC103*Assumptions!$B$168</f>
+        <f aca="false">AC101+AC103*Assumptions!$B$163</f>
         <v>23967.7882282521</v>
       </c>
       <c r="AD111" s="53" t="n">
-        <f aca="false">AD101+AD103*Assumptions!$B$168</f>
+        <f aca="false">AD101+AD103*Assumptions!$B$163</f>
         <v>31915.1547014785</v>
       </c>
       <c r="AE111" s="53" t="n">
-        <f aca="false">AE101+AE103*Assumptions!$B$168</f>
+        <f aca="false">AE101+AE103*Assumptions!$B$163</f>
         <v>37850.0706318335</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="B112" s="23" t="s">
         <v>185</v>
@@ -18829,131 +18623,131 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C113" s="28" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$48,C112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$48,C112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="D113" s="28" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$48,D112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$48,D112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="E113" s="28" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$48,E112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$48,E112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="F113" s="28" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$48,F112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$48,F112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="G113" s="28" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$48,G112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$48,G112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="H113" s="28" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$48,H112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$48,H112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="I113" s="28" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$48,I112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$48,I112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="J113" s="28" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$48,J112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$48,J112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="K113" s="28" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$48,K112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$48,K112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="L113" s="28" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$48,L112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$48,L112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="M113" s="28" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$48,M112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$48,M112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="N113" s="28" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$48,N112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$48,N112*Assumptions!$B$134,0)</f>
         <v>0</v>
       </c>
       <c r="O113" s="28" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$48,O112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$48,O112*Assumptions!$B$134,0)</f>
         <v>39.4855341595517</v>
       </c>
       <c r="P113" s="28" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$48,P112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$48,P112*Assumptions!$B$134,0)</f>
         <v>46.2880053622772</v>
       </c>
       <c r="Q113" s="28" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$48,Q112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$48,Q112*Assumptions!$B$134,0)</f>
         <v>52.8481597485819</v>
       </c>
       <c r="R113" s="28" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$48,R112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$48,R112*Assumptions!$B$134,0)</f>
         <v>59.3982707259543</v>
       </c>
       <c r="S113" s="28" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$48,S112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$48,S112*Assumptions!$B$134,0)</f>
         <v>66.5538908888827</v>
       </c>
       <c r="T113" s="28" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$48,T112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$48,T112*Assumptions!$B$134,0)</f>
         <v>76.1555495573957</v>
       </c>
       <c r="U113" s="28" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$48,U112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$48,U112*Assumptions!$B$134,0)</f>
         <v>84.9691874796611</v>
       </c>
       <c r="V113" s="28" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$48,V112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$48,V112*Assumptions!$B$134,0)</f>
         <v>92.6938274181038</v>
       </c>
       <c r="W113" s="28" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$48,W112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$48,W112*Assumptions!$B$134,0)</f>
         <v>117.919925917837</v>
       </c>
       <c r="X113" s="28" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$48,X112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$48,X112*Assumptions!$B$134,0)</f>
         <v>142.214819904667</v>
       </c>
       <c r="Y113" s="28" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$48,Y112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$48,Y112*Assumptions!$B$134,0)</f>
         <v>165.761660328528</v>
       </c>
       <c r="Z113" s="28" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$48,Z112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$48,Z112*Assumptions!$B$134,0)</f>
         <v>195.482236430164</v>
       </c>
       <c r="AA113" s="28" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$48,AA112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$48,AA112*Assumptions!$B$134,0)</f>
         <v>883.211171761589</v>
       </c>
       <c r="AB113" s="28" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$48,AB112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$48,AB112*Assumptions!$B$134,0)</f>
         <v>1556.55568478176</v>
       </c>
       <c r="AC113" s="28" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$48,AC112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$48,AC112*Assumptions!$B$134,0)</f>
         <v>2372.81103459696</v>
       </c>
       <c r="AD113" s="28" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$48,AD112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$48,AD112*Assumptions!$B$134,0)</f>
         <v>3159.60031544637</v>
       </c>
       <c r="AE113" s="28" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$48,AE112*Assumptions!$B$135,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$48,AE112*Assumptions!$B$134,0)</f>
         <v>3747.15699255152</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B114" s="23" t="s">
         <v>109</v>
@@ -19077,131 +18871,131 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B115" s="23" t="s">
         <v>76</v>
       </c>
       <c r="C115" s="54" t="n">
-        <f aca="false">C114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">C114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>15.1312068965517</v>
       </c>
       <c r="D115" s="54" t="n">
-        <f aca="false">D114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">D114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>22.9584655936423</v>
       </c>
       <c r="E115" s="54" t="n">
-        <f aca="false">E114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">E114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>30.919359730185</v>
       </c>
       <c r="F115" s="54" t="n">
-        <f aca="false">F114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">F114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>37.3313209289439</v>
       </c>
       <c r="G115" s="54" t="n">
-        <f aca="false">G114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">G114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>45.0343373532196</v>
       </c>
       <c r="H115" s="54" t="n">
-        <f aca="false">H114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">H114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>53.9055077488188</v>
       </c>
       <c r="I115" s="54" t="n">
-        <f aca="false">I114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">I114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>62.7579525496257</v>
       </c>
       <c r="J115" s="54" t="n">
-        <f aca="false">J114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">J114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>71.39397827595</v>
       </c>
       <c r="K115" s="54" t="n">
-        <f aca="false">K114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">K114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>79.1479125033387</v>
       </c>
       <c r="L115" s="54" t="n">
-        <f aca="false">L114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">L114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>84.0564659610508</v>
       </c>
       <c r="M115" s="54" t="n">
-        <f aca="false">M114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">M114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>90.5051971718634</v>
       </c>
       <c r="N115" s="54" t="n">
-        <f aca="false">N114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">N114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>98.4481979983085</v>
       </c>
       <c r="O115" s="54" t="n">
-        <f aca="false">O114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">O114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>89.3127511400015</v>
       </c>
       <c r="P115" s="54" t="n">
-        <f aca="false">P114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">P114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>87.5178593569937</v>
       </c>
       <c r="Q115" s="54" t="n">
-        <f aca="false">Q114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Q114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>89.2336521389829</v>
       </c>
       <c r="R115" s="54" t="n">
-        <f aca="false">R114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">R114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>89.501394035373</v>
       </c>
       <c r="S115" s="54" t="n">
-        <f aca="false">S114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">S114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>93.05145845571</v>
       </c>
       <c r="T115" s="54" t="n">
-        <f aca="false">T114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">T114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>99.3147312164927</v>
       </c>
       <c r="U115" s="54" t="n">
-        <f aca="false">U114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">U114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>106.132639990328</v>
       </c>
       <c r="V115" s="54" t="n">
-        <f aca="false">V114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">V114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>113.03822216734</v>
       </c>
       <c r="W115" s="54" t="n">
-        <f aca="false">W114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">W114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>119.031350342347</v>
       </c>
       <c r="X115" s="54" t="n">
-        <f aca="false">X114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">X114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>121.465503397614</v>
       </c>
       <c r="Y115" s="54" t="n">
-        <f aca="false">Y114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Y114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>125.92051328888</v>
       </c>
       <c r="Z115" s="54" t="n">
-        <f aca="false">Z114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">Z114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>132.378083591593</v>
       </c>
       <c r="AA115" s="54" t="n">
-        <f aca="false">AA114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AA114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>237.052265744479</v>
       </c>
       <c r="AB115" s="54" t="n">
-        <f aca="false">AB114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AB114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>297.430997948455</v>
       </c>
       <c r="AC115" s="54" t="n">
-        <f aca="false">AC114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AC114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>348.496772512984</v>
       </c>
       <c r="AD115" s="54" t="n">
-        <f aca="false">AD114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AD114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>412.555916229431</v>
       </c>
       <c r="AE115" s="54" t="n">
-        <f aca="false">AE114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f aca="false">AE114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v>506.58474671341</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="B116" s="23" t="s">
         <v>109</v>
@@ -19325,10 +19119,10 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C117" s="44" t="n">
         <f aca="false">C113*C116*Assumptions!$B$7*C7</f>
@@ -19449,7 +19243,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B118" s="23" t="s">
         <v>109</v>
@@ -19573,255 +19367,255 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,C114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,C114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>6.6153996818555</v>
       </c>
       <c r="D119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,D114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,D114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>10.0374958205537</v>
       </c>
       <c r="E119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,E114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,E114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>13.5180176915601</v>
       </c>
       <c r="F119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,F114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,F114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>16.3213423942317</v>
       </c>
       <c r="G119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,G114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,G114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>19.6891195154403</v>
       </c>
       <c r="H119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,H114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,H114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>23.5676163342306</v>
       </c>
       <c r="I119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,I114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,I114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>27.4379262783929</v>
       </c>
       <c r="J119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,J114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,J114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>31.2136172879079</v>
       </c>
       <c r="K119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,K114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,K114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>34.6036557938704</v>
       </c>
       <c r="L119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,L114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,L114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>36.7496870526142</v>
       </c>
       <c r="M119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,M114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,M114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>39.5690876921034</v>
       </c>
       <c r="N119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,N114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,N114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>43.0417865653319</v>
       </c>
       <c r="O119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,O114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,O114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>39.0477474478161</v>
       </c>
       <c r="P119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,P114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,P114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>38.2630164867333</v>
       </c>
       <c r="Q119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Q114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Q114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>39.0131651762398</v>
       </c>
       <c r="R119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,R114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,R114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>39.1302225708223</v>
       </c>
       <c r="S119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,S114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,S114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>40.682319187928</v>
       </c>
       <c r="T119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,T114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,T114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>43.4206369514964</v>
       </c>
       <c r="U119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,U114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,U114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>46.4014429005334</v>
       </c>
       <c r="V119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,V114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,V114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>49.4205798701852</v>
       </c>
       <c r="W119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,W114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,W114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>52.0407897776513</v>
       </c>
       <c r="X119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,X114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,X114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>53.1050072890162</v>
       </c>
       <c r="Y119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Y114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Y114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>55.0527482206442</v>
       </c>
       <c r="Z119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,Z114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,Z114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>57.8760133321579</v>
       </c>
       <c r="AA119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AA114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AA114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>103.639814993643</v>
       </c>
       <c r="AB119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AB114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AB114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>130.037540472107</v>
       </c>
       <c r="AC119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AC114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AC114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>152.363618696897</v>
       </c>
       <c r="AD119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AD114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AD114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>180.370428851498</v>
       </c>
       <c r="AE119" s="44" t="n">
-        <f aca="false">IF(Assumptions!$B$136=0,0,AE114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f aca="false">IF(Assumptions!$B$135=0,0,AE114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v>221.480057417262</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C120" s="44" t="n">
-        <f aca="false">C113*Assumptions!$B$151*Assumptions!$B$136*C7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">C113*Assumptions!$B$149*Assumptions!$B$135*C7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="D120" s="44" t="n">
-        <f aca="false">D113*Assumptions!$B$151*Assumptions!$B$136*D7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">D113*Assumptions!$B$149*Assumptions!$B$135*D7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="E120" s="44" t="n">
-        <f aca="false">E113*Assumptions!$B$151*Assumptions!$B$136*E7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">E113*Assumptions!$B$149*Assumptions!$B$135*E7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="F120" s="44" t="n">
-        <f aca="false">F113*Assumptions!$B$151*Assumptions!$B$136*F7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">F113*Assumptions!$B$149*Assumptions!$B$135*F7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="G120" s="44" t="n">
-        <f aca="false">G113*Assumptions!$B$151*Assumptions!$B$136*G7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">G113*Assumptions!$B$149*Assumptions!$B$135*G7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="H120" s="44" t="n">
-        <f aca="false">H113*Assumptions!$B$151*Assumptions!$B$136*H7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">H113*Assumptions!$B$149*Assumptions!$B$135*H7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="I120" s="44" t="n">
-        <f aca="false">I113*Assumptions!$B$151*Assumptions!$B$136*I7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">I113*Assumptions!$B$149*Assumptions!$B$135*I7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="J120" s="44" t="n">
-        <f aca="false">J113*Assumptions!$B$151*Assumptions!$B$136*J7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">J113*Assumptions!$B$149*Assumptions!$B$135*J7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="K120" s="44" t="n">
-        <f aca="false">K113*Assumptions!$B$151*Assumptions!$B$136*K7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">K113*Assumptions!$B$149*Assumptions!$B$135*K7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="L120" s="44" t="n">
-        <f aca="false">L113*Assumptions!$B$151*Assumptions!$B$136*L7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">L113*Assumptions!$B$149*Assumptions!$B$135*L7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="M120" s="44" t="n">
-        <f aca="false">M113*Assumptions!$B$151*Assumptions!$B$136*M7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">M113*Assumptions!$B$149*Assumptions!$B$135*M7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="N120" s="44" t="n">
-        <f aca="false">N113*Assumptions!$B$151*Assumptions!$B$136*N7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">N113*Assumptions!$B$149*Assumptions!$B$135*N7/12*(1+Assumptions!$B$16)</f>
         <v>0</v>
       </c>
       <c r="O120" s="44" t="n">
-        <f aca="false">O113*Assumptions!$B$151*Assumptions!$B$136*O7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">O113*Assumptions!$B$149*Assumptions!$B$135*O7/12*(1+Assumptions!$B$16)</f>
         <v>29.2982663463873</v>
       </c>
       <c r="P120" s="44" t="n">
-        <f aca="false">P113*Assumptions!$B$151*Assumptions!$B$136*P7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">P113*Assumptions!$B$149*Assumptions!$B$135*P7/12*(1+Assumptions!$B$16)</f>
         <v>34.3456999788097</v>
       </c>
       <c r="Q120" s="44" t="n">
-        <f aca="false">Q113*Assumptions!$B$151*Assumptions!$B$136*Q7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Q113*Assumptions!$B$149*Assumptions!$B$135*Q7/12*(1+Assumptions!$B$16)</f>
         <v>39.2133345334478</v>
       </c>
       <c r="R120" s="44" t="n">
-        <f aca="false">R113*Assumptions!$B$151*Assumptions!$B$136*R7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">R113*Assumptions!$B$149*Assumptions!$B$135*R7/12*(1+Assumptions!$B$16)</f>
         <v>44.0735168786581</v>
       </c>
       <c r="S120" s="44" t="n">
-        <f aca="false">S113*Assumptions!$B$151*Assumptions!$B$136*S7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">S113*Assumptions!$B$149*Assumptions!$B$135*S7/12*(1+Assumptions!$B$16)</f>
         <v>49.382987039551</v>
       </c>
       <c r="T120" s="44" t="n">
-        <f aca="false">T113*Assumptions!$B$151*Assumptions!$B$136*T7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">T113*Assumptions!$B$149*Assumptions!$B$135*T7/12*(1+Assumptions!$B$16)</f>
         <v>56.5074177715877</v>
       </c>
       <c r="U120" s="44" t="n">
-        <f aca="false">U113*Assumptions!$B$151*Assumptions!$B$136*U7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">U113*Assumptions!$B$149*Assumptions!$B$135*U7/12*(1+Assumptions!$B$16)</f>
         <v>63.0471371099085</v>
       </c>
       <c r="V120" s="44" t="n">
-        <f aca="false">V113*Assumptions!$B$151*Assumptions!$B$136*V7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">V113*Assumptions!$B$149*Assumptions!$B$135*V7/12*(1+Assumptions!$B$16)</f>
         <v>68.778819944233</v>
       </c>
       <c r="W120" s="44" t="n">
-        <f aca="false">W113*Assumptions!$B$151*Assumptions!$B$136*W7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">W113*Assumptions!$B$149*Assumptions!$B$135*W7/12*(1+Assumptions!$B$16)</f>
         <v>87.496585031035</v>
       </c>
       <c r="X120" s="44" t="n">
-        <f aca="false">X113*Assumptions!$B$151*Assumptions!$B$136*X7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">X113*Assumptions!$B$149*Assumptions!$B$135*X7/12*(1+Assumptions!$B$16)</f>
         <v>105.523396369263</v>
       </c>
       <c r="Y120" s="44" t="n">
-        <f aca="false">Y113*Assumptions!$B$151*Assumptions!$B$136*Y7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Y113*Assumptions!$B$149*Assumptions!$B$135*Y7/12*(1+Assumptions!$B$16)</f>
         <v>122.995151963767</v>
       </c>
       <c r="Z120" s="44" t="n">
-        <f aca="false">Z113*Assumptions!$B$151*Assumptions!$B$136*Z7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">Z113*Assumptions!$B$149*Assumptions!$B$135*Z7/12*(1+Assumptions!$B$16)</f>
         <v>145.047819431182</v>
       </c>
       <c r="AA120" s="44" t="n">
-        <f aca="false">AA113*Assumptions!$B$151*Assumptions!$B$136*AA7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AA113*Assumptions!$B$149*Assumptions!$B$135*AA7/12*(1+Assumptions!$B$16)</f>
         <v>7864.11227336519</v>
       </c>
       <c r="AB120" s="44" t="n">
-        <f aca="false">AB113*Assumptions!$B$151*Assumptions!$B$136*AB7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AB113*Assumptions!$B$149*Assumptions!$B$135*AB7/12*(1+Assumptions!$B$16)</f>
         <v>13859.5718172968</v>
       </c>
       <c r="AC120" s="44" t="n">
-        <f aca="false">AC113*Assumptions!$B$151*Assumptions!$B$136*AC7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AC113*Assumptions!$B$149*Assumptions!$B$135*AC7/12*(1+Assumptions!$B$16)</f>
         <v>21127.5094520513</v>
       </c>
       <c r="AD120" s="44" t="n">
-        <f aca="false">AD113*Assumptions!$B$151*Assumptions!$B$136*AD7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AD113*Assumptions!$B$149*Assumptions!$B$135*AD7/12*(1+Assumptions!$B$16)</f>
         <v>28133.0812087345</v>
       </c>
       <c r="AE120" s="44" t="n">
-        <f aca="false">AE113*Assumptions!$B$151*Assumptions!$B$136*AE7/12*(1+Assumptions!$B$16)</f>
+        <f aca="false">AE113*Assumptions!$B$149*Assumptions!$B$135*AE7/12*(1+Assumptions!$B$16)</f>
         <v>33364.6858616787</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B121" s="23" t="s">
         <v>109</v>
@@ -19945,7 +19739,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="B122" s="23" t="s">
         <v>109</v>
@@ -20069,630 +19863,630 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B123" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C123" s="54" t="n">
-        <f aca="false">C118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">C118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="D123" s="54" t="n">
-        <f aca="false">D118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">D118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="E123" s="54" t="n">
-        <f aca="false">E118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">E118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="F123" s="54" t="n">
-        <f aca="false">F118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">F118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="G123" s="54" t="n">
-        <f aca="false">G118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">G118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="H123" s="54" t="n">
-        <f aca="false">H118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">H118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="I123" s="54" t="n">
-        <f aca="false">I118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">I118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="J123" s="54" t="n">
-        <f aca="false">J118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">J118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="K123" s="54" t="n">
-        <f aca="false">K118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">K118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="L123" s="54" t="n">
-        <f aca="false">L118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">L118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="M123" s="54" t="n">
-        <f aca="false">M118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">M118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="N123" s="54" t="n">
-        <f aca="false">N118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">N118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>0</v>
       </c>
       <c r="O123" s="54" t="n">
-        <f aca="false">O118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">O118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.62927149894219</v>
       </c>
       <c r="P123" s="54" t="n">
-        <f aca="false">P118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">P118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.70143140014885</v>
       </c>
       <c r="Q123" s="54" t="n">
-        <f aca="false">Q118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Q118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1.94103739919315</v>
       </c>
       <c r="R123" s="54" t="n">
-        <f aca="false">R118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">R118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>2.18815945849121</v>
       </c>
       <c r="S123" s="54" t="n">
-        <f aca="false">S118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">S118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>2.60103337750735</v>
       </c>
       <c r="T123" s="54" t="n">
-        <f aca="false">T118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">T118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>3.01778380603988</v>
       </c>
       <c r="U123" s="54" t="n">
-        <f aca="false">U118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">U118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>3.33305434679432</v>
       </c>
       <c r="V123" s="54" t="n">
-        <f aca="false">V118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">V118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>3.96066338283244</v>
       </c>
       <c r="W123" s="54" t="n">
-        <f aca="false">W118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">W118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>5.89519056599328</v>
       </c>
       <c r="X123" s="54" t="n">
-        <f aca="false">X118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">X118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>7.40026500533368</v>
       </c>
       <c r="Y123" s="54" t="n">
-        <f aca="false">Y118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Y118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>9.20490186831365</v>
       </c>
       <c r="Z123" s="54" t="n">
-        <f aca="false">Z118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">Z118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>12.3901775641137</v>
       </c>
       <c r="AA123" s="54" t="n">
-        <f aca="false">AA118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AA118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>1055.21073536048</v>
       </c>
       <c r="AB123" s="54" t="n">
-        <f aca="false">AB118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AB118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>2333.35826986237</v>
       </c>
       <c r="AC123" s="54" t="n">
-        <f aca="false">AC118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AC118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>4167.66161619478</v>
       </c>
       <c r="AD123" s="54" t="n">
-        <f aca="false">AD118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AD118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>6569.69948741119</v>
       </c>
       <c r="AE123" s="54" t="n">
-        <f aca="false">AE118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f aca="false">AE118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v>9567.19298287415</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="B124" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C124" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C101*Assumptions!$B$152*Assumptions!$B$25/12*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C101*Assumptions!$B$150*Assumptions!$B$25/12*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D124" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D101*Assumptions!$B$152*Assumptions!$B$25/12*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D101*Assumptions!$B$150*Assumptions!$B$25/12*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E124" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E101*Assumptions!$B$152*Assumptions!$B$25/12*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E101*Assumptions!$B$150*Assumptions!$B$25/12*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F124" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F101*Assumptions!$B$152*Assumptions!$B$25/12*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F101*Assumptions!$B$150*Assumptions!$B$25/12*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G124" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G101*Assumptions!$B$152*Assumptions!$B$25/12*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G101*Assumptions!$B$150*Assumptions!$B$25/12*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H124" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H101*Assumptions!$B$152*Assumptions!$B$25/12*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H101*Assumptions!$B$150*Assumptions!$B$25/12*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I124" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I101*Assumptions!$B$152*Assumptions!$B$25/12*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I101*Assumptions!$B$150*Assumptions!$B$25/12*I7,0)</f>
         <v>897.334640603893</v>
       </c>
       <c r="J124" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J101*Assumptions!$B$152*Assumptions!$B$25/12*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J101*Assumptions!$B$150*Assumptions!$B$25/12*J7,0)</f>
         <v>982.794962365633</v>
       </c>
       <c r="K124" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K101*Assumptions!$B$152*Assumptions!$B$25/12*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K101*Assumptions!$B$150*Assumptions!$B$25/12*K7,0)</f>
         <v>1076.03355168241</v>
       </c>
       <c r="L124" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L101*Assumptions!$B$152*Assumptions!$B$25/12*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L101*Assumptions!$B$150*Assumptions!$B$25/12*L7,0)</f>
         <v>1212.94003373574</v>
       </c>
       <c r="M124" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M101*Assumptions!$B$152*Assumptions!$B$25/12*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M101*Assumptions!$B$150*Assumptions!$B$25/12*M7,0)</f>
         <v>1327.66503000831</v>
       </c>
       <c r="N124" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N101*Assumptions!$B$152*Assumptions!$B$25/12*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N101*Assumptions!$B$150*Assumptions!$B$25/12*N7,0)</f>
         <v>1415.35578238157</v>
       </c>
       <c r="O124" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O101*Assumptions!$B$152*Assumptions!$B$25/12*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O101*Assumptions!$B$150*Assumptions!$B$25/12*O7,0)</f>
         <v>1843.65119561679</v>
       </c>
       <c r="P124" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P101*Assumptions!$B$152*Assumptions!$B$25/12*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P101*Assumptions!$B$150*Assumptions!$B$25/12*P7,0)</f>
         <v>2232.78244593862</v>
       </c>
       <c r="Q124" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q101*Assumptions!$B$152*Assumptions!$B$25/12*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q101*Assumptions!$B$150*Assumptions!$B$25/12*Q7,0)</f>
         <v>2588.26186709291</v>
       </c>
       <c r="R124" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R101*Assumptions!$B$152*Assumptions!$B$25/12*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R101*Assumptions!$B$150*Assumptions!$B$25/12*R7,0)</f>
         <v>3048.11880886783</v>
       </c>
       <c r="S124" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S101*Assumptions!$B$152*Assumptions!$B$25/12*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S101*Assumptions!$B$150*Assumptions!$B$25/12*S7,0)</f>
         <v>3436.18640146132</v>
       </c>
       <c r="T124" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T101*Assumptions!$B$152*Assumptions!$B$25/12*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T101*Assumptions!$B$150*Assumptions!$B$25/12*T7,0)</f>
         <v>3727.2625426234</v>
       </c>
       <c r="U124" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U101*Assumptions!$B$152*Assumptions!$B$25/12*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U101*Assumptions!$B$150*Assumptions!$B$25/12*U7,0)</f>
         <v>3991.36539303151</v>
       </c>
       <c r="V124" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V101*Assumptions!$B$152*Assumptions!$B$25/12*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V101*Assumptions!$B$150*Assumptions!$B$25/12*V7,0)</f>
         <v>4244.94576355594</v>
       </c>
       <c r="W124" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W101*Assumptions!$B$152*Assumptions!$B$25/12*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W101*Assumptions!$B$150*Assumptions!$B$25/12*W7,0)</f>
         <v>4530.5763110925</v>
       </c>
       <c r="X124" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X101*Assumptions!$B$152*Assumptions!$B$25/12*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X101*Assumptions!$B$150*Assumptions!$B$25/12*X7,0)</f>
         <v>4975.0120574374</v>
       </c>
       <c r="Y124" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y101*Assumptions!$B$152*Assumptions!$B$25/12*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y101*Assumptions!$B$150*Assumptions!$B$25/12*Y7,0)</f>
         <v>5350.19701259849</v>
       </c>
       <c r="Z124" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z101*Assumptions!$B$152*Assumptions!$B$25/12*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z101*Assumptions!$B$150*Assumptions!$B$25/12*Z7,0)</f>
         <v>5635.61518379837</v>
       </c>
       <c r="AA124" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA101*Assumptions!$B$152*Assumptions!$B$25/12*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA101*Assumptions!$B$150*Assumptions!$B$25/12*AA7,0)</f>
         <v>122464.154627058</v>
       </c>
       <c r="AB124" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB101*Assumptions!$B$152*Assumptions!$B$25/12*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB101*Assumptions!$B$150*Assumptions!$B$25/12*AB7,0)</f>
         <v>188413.625863168</v>
       </c>
       <c r="AC124" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC101*Assumptions!$B$152*Assumptions!$B$25/12*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC101*Assumptions!$B$150*Assumptions!$B$25/12*AC7,0)</f>
         <v>250379.292779488</v>
       </c>
       <c r="AD124" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD101*Assumptions!$B$152*Assumptions!$B$25/12*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD101*Assumptions!$B$150*Assumptions!$B$25/12*AD7,0)</f>
         <v>279162.804345045</v>
       </c>
       <c r="AE124" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE101*Assumptions!$B$152*Assumptions!$B$25/12*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE101*Assumptions!$B$150*Assumptions!$B$25/12*AE7,0)</f>
         <v>259174.377294749</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B125" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C125" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$49,C118*C17*Assumptions!$B$17+C113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$49,C118*C17*Assumptions!$B$17+C113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D125" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$49,D118*D17*Assumptions!$B$17+D113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$49,D118*D17*Assumptions!$B$17+D113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E125" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$49,E118*E17*Assumptions!$B$17+E113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$49,E118*E17*Assumptions!$B$17+E113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F125" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$49,F118*F17*Assumptions!$B$17+F113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$49,F118*F17*Assumptions!$B$17+F113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G125" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$49,G118*G17*Assumptions!$B$17+G113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$49,G118*G17*Assumptions!$B$17+G113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H125" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$49,H118*H17*Assumptions!$B$17+H113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$49,H118*H17*Assumptions!$B$17+H113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I125" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$49,I118*I17*Assumptions!$B$17+I113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$49,I118*I17*Assumptions!$B$17+I113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
         <v>0</v>
       </c>
       <c r="J125" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$49,J118*J17*Assumptions!$B$17+J113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$49,J118*J17*Assumptions!$B$17+J113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
         <v>0</v>
       </c>
       <c r="K125" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$49,K118*K17*Assumptions!$B$17+K113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$49,K118*K17*Assumptions!$B$17+K113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
         <v>0</v>
       </c>
       <c r="L125" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$49,L118*L17*Assumptions!$B$17+L113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$49,L118*L17*Assumptions!$B$17+L113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
         <v>0</v>
       </c>
       <c r="M125" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$49,M118*M17*Assumptions!$B$17+M113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$49,M118*M17*Assumptions!$B$17+M113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
         <v>0</v>
       </c>
       <c r="N125" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$49,N118*N17*Assumptions!$B$17+N113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$49,N118*N17*Assumptions!$B$17+N113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
         <v>0</v>
       </c>
       <c r="O125" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$49,O118*O17*Assumptions!$B$17+O113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$49,O118*O17*Assumptions!$B$17+O113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
         <v>134.35265147553</v>
       </c>
       <c r="P125" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$49,P118*P17*Assumptions!$B$17+P113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$49,P118*P17*Assumptions!$B$17+P113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
         <v>157.286260933086</v>
       </c>
       <c r="Q125" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$49,Q118*Q17*Assumptions!$B$17+Q113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$49,Q118*Q17*Assumptions!$B$17+Q113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
         <v>179.576054686859</v>
       </c>
       <c r="R125" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$49,R118*R17*Assumptions!$B$17+R113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$49,R118*R17*Assumptions!$B$17+R113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
         <v>201.98829262674</v>
       </c>
       <c r="S125" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$49,S118*S17*Assumptions!$B$17+S113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$49,S118*S17*Assumptions!$B$17+S113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
         <v>226.66021770449</v>
       </c>
       <c r="T125" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$49,T118*T17*Assumptions!$B$17+T113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$49,T118*T17*Assumptions!$B$17+T113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
         <v>261.559180834006</v>
       </c>
       <c r="U125" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$49,U118*U17*Assumptions!$B$17+U113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$49,U118*U17*Assumptions!$B$17+U113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
         <v>292.332177037148</v>
       </c>
       <c r="V125" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$49,V118*V17*Assumptions!$B$17+V113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$49,V118*V17*Assumptions!$B$17+V113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
         <v>319.031727713127</v>
       </c>
       <c r="W125" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$49,W118*W17*Assumptions!$B$17+W113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$49,W118*W17*Assumptions!$B$17+W113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
         <v>403.480776830281</v>
       </c>
       <c r="X125" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$49,X118*X17*Assumptions!$B$17+X113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$49,X118*X17*Assumptions!$B$17+X113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
         <v>488.471469035738</v>
       </c>
       <c r="Y125" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$49,Y118*Y17*Assumptions!$B$17+Y113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$49,Y118*Y17*Assumptions!$B$17+Y113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
         <v>569.549880527215</v>
       </c>
       <c r="Z125" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$49,Z118*Z17*Assumptions!$B$17+Z113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$49,Z118*Z17*Assumptions!$B$17+Z113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
         <v>670.387955502782</v>
       </c>
       <c r="AA125" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$49,AA118*AA17*Assumptions!$B$17+AA113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$49,AA118*AA17*Assumptions!$B$17+AA113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
         <v>37040.7356999757</v>
       </c>
       <c r="AB125" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$49,AB118*AB17*Assumptions!$B$17+AB113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$49,AB118*AB17*Assumptions!$B$17+AB113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
         <v>65919.0182572536</v>
       </c>
       <c r="AC125" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$49,AC118*AC17*Assumptions!$B$17+AC113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$49,AC118*AC17*Assumptions!$B$17+AC113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
         <v>101310.799768184</v>
       </c>
       <c r="AD125" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$49,AD118*AD17*Assumptions!$B$17+AD113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$49,AD118*AD17*Assumptions!$B$17+AD113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
         <v>136280.301422837</v>
       </c>
       <c r="AE125" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$49,AE118*AE17*Assumptions!$B$17+AE113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$49,AE118*AE17*Assumptions!$B$17+AE113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
         <v>164018.791606945</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="B126" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C126" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$50,C113*C114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$50,C113*C114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="D126" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$50,D113*D114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$50,D113*D114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="E126" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$50,E113*E114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$50,E113*E114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="F126" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$50,F113*F114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$50,F113*F114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="G126" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$50,G113*G114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$50,G113*G114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="H126" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$50,H113*H114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$50,H113*H114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="I126" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$50,I113*I114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$50,I113*I114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="J126" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$50,J113*J114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$50,J113*J114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="K126" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$50,K113*K114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$50,K113*K114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="L126" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$50,L113*L114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$50,L113*L114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="M126" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$50,M113*M114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$50,M113*M114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="N126" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$50,N113*N114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$50,N113*N114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>0</v>
       </c>
       <c r="O126" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$50,O113*O114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$50,O113*O114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>705.312337204413</v>
       </c>
       <c r="P126" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$50,P113*P114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$50,P113*P114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>810.205428642309</v>
       </c>
       <c r="Q126" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,Q113*Q114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,Q113*Q114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>943.166860638072</v>
       </c>
       <c r="R126" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$50,R113*R114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$50,R113*R114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>1063.24560665268</v>
       </c>
       <c r="S126" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$50,S113*S114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$50,S113*S114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>1238.58732262255</v>
       </c>
       <c r="T126" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$50,T113*T114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$50,T113*T114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>1512.67358698741</v>
       </c>
       <c r="U126" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$50,U113*U114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$50,U113*U114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>1803.60083700991</v>
       </c>
       <c r="V126" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$50,V113*V114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$50,V113*V114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>2095.58909144573</v>
       </c>
       <c r="W126" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$50,W113*W114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$50,W113*W114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>2807.23360285394</v>
       </c>
       <c r="X126" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$50,X113*X114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$50,X113*X114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>3454.83893806427</v>
       </c>
       <c r="Y126" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,Y113*Y114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,Y113*Y114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>4174.55867043703</v>
       </c>
       <c r="Z126" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,Z113*Z114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,Z113*Z114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>5175.51276696478</v>
       </c>
       <c r="AA126" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,AA113*AA114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,AA113*AA114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>41873.4418793842</v>
       </c>
       <c r="AB126" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,AB113*AB114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,AB113*AB114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>92593.5821373955</v>
       </c>
       <c r="AC126" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,AC113*AC114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,AC113*AC114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>165383.397468047</v>
       </c>
       <c r="AD126" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,AD113*AD114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,AD113*AD114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>260702.360611555</v>
       </c>
       <c r="AE126" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,AE113*AE114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,AE113*AE114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v>379650.515193419</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B127" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C127" s="54" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$50,(C126*Assumptions!$B$29*Assumptions!$B$30+C113*C115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$50,(C126*Assumptions!$B$29*Assumptions!$B$30+C113*C115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v>0</v>
       </c>
       <c r="D127" s="54" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$50,(D126*Assumptions!$B$29*Assumptions!$B$30+D113*D115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$50,(D126*Assumptions!$B$29*Assumptions!$B$30+D113*D115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v>0</v>
       </c>
       <c r="E127" s="54" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$50,(E126*Assumptions!$B$29*Assumptions!$B$30+E113*E115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$50,(E126*Assumptions!$B$29*Assumptions!$B$30+E113*E115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v>0</v>
       </c>
       <c r="F127" s="54" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$50,(F126*Assumptions!$B$29*Assumptions!$B$30+F113*F115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$50,(F126*Assumptions!$B$29*Assumptions!$B$30+F113*F115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v>0</v>
       </c>
       <c r="G127" s="54" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$50,(G126*Assumptions!$B$29*Assumptions!$B$30+G113*G115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$50,(G126*Assumptions!$B$29*Assumptions!$B$30+G113*G115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v>0</v>
       </c>
       <c r="H127" s="54" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$50,(H126*Assumptions!$B$29*Assumptions!$B$30+H113*H115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$50,(H126*Assumptions!$B$29*Assumptions!$B$30+H113*H115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v>0</v>
       </c>
       <c r="I127" s="54" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$50,(I126*Assumptions!$B$29*Assumptions!$B$30+I113*I115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$50,(I126*Assumptions!$B$29*Assumptions!$B$30+I113*I115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v>0</v>
       </c>
       <c r="J127" s="54" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$50,(J126*Assumptions!$B$29*Assumptions!$B$30+J113*J115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$50,(J126*Assumptions!$B$29*Assumptions!$B$30+J113*J115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v>0</v>
       </c>
       <c r="K127" s="54" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$50,(K126*Assumptions!$B$29*Assumptions!$B$30+K113*K115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$50,(K126*Assumptions!$B$29*Assumptions!$B$30+K113*K115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v>0</v>
       </c>
       <c r="L127" s="54" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$50,(L126*Assumptions!$B$29*Assumptions!$B$30+L113*L115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$50,(L126*Assumptions!$B$29*Assumptions!$B$30+L113*L115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v>0</v>
       </c>
       <c r="M127" s="54" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$50,(M126*Assumptions!$B$29*Assumptions!$B$30+M113*M115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$50,(M126*Assumptions!$B$29*Assumptions!$B$30+M113*M115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v>0</v>
       </c>
       <c r="N127" s="54" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$50,(N126*Assumptions!$B$29*Assumptions!$B$30+N113*N115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$50,(N126*Assumptions!$B$29*Assumptions!$B$30+N113*N115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v>0</v>
       </c>
       <c r="O127" s="54" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$50,(O126*Assumptions!$B$29*Assumptions!$B$30+O113*O115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$50,(O126*Assumptions!$B$29*Assumptions!$B$30+O113*O115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v>1.67511680086048</v>
       </c>
       <c r="P127" s="54" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$50,(P126*Assumptions!$B$29*Assumptions!$B$30+P113*P115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$50,(P126*Assumptions!$B$29*Assumptions!$B$30+P113*P115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v>1.92423789302548</v>
       </c>
       <c r="Q127" s="54" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,(Q126*Assumptions!$B$29*Assumptions!$B$30+Q113*Q115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$50,(Q126*Assumptions!$B$29*Assumptions!$B$30+Q113*Q115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v>2.24002129401542</v>
       </c>
       <c r="R127" s="54" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$50,(R126*Assumptions!$B$29*Assumptions!$B$30+R113*R115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$50,(R126*Assumptions!$B$29*Assumptions!$B$30+R113*R115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v>2.52520831580011</v>
       </c>
       <c r="S127" s="54" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$50,(S126*Assumptions!$B$29*Assumptions!$B$30+S113*S115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$50,(S126*Assumptions!$B$29*Assumptions!$B$30+S113*S115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v>2.94164489122855</v>
       </c>
       <c r="T127" s="54" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$50,(T126*Assumptions!$B$29*Assumptions!$B$30+T113*T115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$50,(T126*Assumptions!$B$29*Assumptions!$B$30+T113*T115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v>3.5925997690951</v>
       </c>
       <c r="U127" s="54" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$50,(U126*Assumptions!$B$29*Assumptions!$B$30+U113*U115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$50,(U126*Assumptions!$B$29*Assumptions!$B$30+U113*U115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v>4.28355198789854</v>
       </c>
       <c r="V127" s="54" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$50,(V126*Assumptions!$B$29*Assumptions!$B$30+V113*V115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$50,(V126*Assumptions!$B$29*Assumptions!$B$30+V113*V115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v>4.97702409218362</v>
       </c>
       <c r="W127" s="54" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$50,(W126*Assumptions!$B$29*Assumptions!$B$30+W113*W115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$50,(W126*Assumptions!$B$29*Assumptions!$B$30+W113*W115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v>6.66717980677811</v>
       </c>
       <c r="X127" s="54" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$50,(X126*Assumptions!$B$29*Assumptions!$B$30+X113*X115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$50,(X126*Assumptions!$B$29*Assumptions!$B$30+X113*X115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v>8.20524247790265</v>
       </c>
       <c r="Y127" s="54" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,(Y126*Assumptions!$B$29*Assumptions!$B$30+Y113*Y115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$50,(Y126*Assumptions!$B$29*Assumptions!$B$30+Y113*Y115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v>9.91457684228794</v>
       </c>
       <c r="Z127" s="54" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,(Z126*Assumptions!$B$29*Assumptions!$B$30+Z113*Z115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$50,(Z126*Assumptions!$B$29*Assumptions!$B$30+Z113*Z115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v>12.2918428215414</v>
       </c>
       <c r="AA127" s="54" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,(AA126*Assumptions!$B$29*Assumptions!$B$30+AA113*AA115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$50,(AA126*Assumptions!$B$29*Assumptions!$B$30+AA113*AA115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v>1193.39309356245</v>
       </c>
       <c r="AB127" s="54" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,(AB126*Assumptions!$B$29*Assumptions!$B$30+AB113*AB115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$50,(AB126*Assumptions!$B$29*Assumptions!$B$30+AB113*AB115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v>2638.91709091577</v>
       </c>
       <c r="AC127" s="54" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,(AC126*Assumptions!$B$29*Assumptions!$B$30+AC113*AC115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$50,(AC126*Assumptions!$B$29*Assumptions!$B$30+AC113*AC115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v>4713.42682783933</v>
       </c>
       <c r="AD127" s="54" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,(AD126*Assumptions!$B$29*Assumptions!$B$30+AD113*AD115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$50,(AD126*Assumptions!$B$29*Assumptions!$B$30+AD113*AD115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v>7430.01727742932</v>
       </c>
       <c r="AE127" s="54" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,(AE126*Assumptions!$B$29*Assumptions!$B$30+AE113*AE115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$50,(AE126*Assumptions!$B$29*Assumptions!$B$30+AE113*AE115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v>10820.0396830124</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C128" s="44" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$46,(C101+C103*Assumptions!$B$129)*Assumptions!$B$128*C7/12,0)</f>
@@ -20813,7 +20607,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="B129" s="23" t="s">
         <v>109</v>
@@ -20937,7 +20731,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="45" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="B131" s="46"/>
       <c r="C131" s="46"/>
@@ -20972,125 +20766,125 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="B132" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C132" s="57" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,C5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,C5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="D132" s="57" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,D5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,D5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="E132" s="57" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,E5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,E5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="F132" s="57" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,F5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,F5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="G132" s="57" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,G5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,G5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="H132" s="57" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,H5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,H5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="I132" s="57" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,I5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,I5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="J132" s="57" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,J5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,J5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="K132" s="57" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,K5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,K5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="L132" s="57" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,L5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,L5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="M132" s="57" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,M5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,M5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="N132" s="57" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,N5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,N5)*Assumptions!$B$158,0)</f>
         <v>0</v>
       </c>
       <c r="O132" s="57" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,O5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,O5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="P132" s="57" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,P5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,P5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="Q132" s="57" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,Q5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,Q5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="R132" s="57" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,R5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,R5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="S132" s="57" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,S5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,S5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="T132" s="57" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,T5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,T5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="U132" s="57" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,U5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,U5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="V132" s="57" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,V5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,V5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="W132" s="57" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,W5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,W5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="X132" s="57" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,X5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,X5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="Y132" s="57" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,Y5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,Y5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="Z132" s="57" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,Z5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,Z5)*Assumptions!$B$158,0)</f>
         <v>32000000</v>
       </c>
       <c r="AA132" s="57" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AA5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AA5)*Assumptions!$B$158,0)</f>
         <v>64000000</v>
       </c>
       <c r="AB132" s="57" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AB5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AB5)*Assumptions!$B$158,0)</f>
         <v>96000000</v>
       </c>
       <c r="AC132" s="57" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AC5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AC5)*Assumptions!$B$158,0)</f>
         <v>128000000</v>
       </c>
       <c r="AD132" s="57" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AD5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AD5)*Assumptions!$B$158,0)</f>
         <v>160000000</v>
       </c>
       <c r="AE132" s="57" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AE5)*Assumptions!$B$160,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AE5)*Assumptions!$B$158,0)</f>
         <v>192000000</v>
       </c>
     </row>
@@ -21220,12 +21014,12 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="9" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="45" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="B136" s="46"/>
       <c r="C136" s="46"/>
@@ -21260,10 +21054,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B137" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C137" s="44" t="n">
         <f aca="false">C29+C65+C101</f>
@@ -21384,10 +21178,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B138" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C138" s="44" t="n">
         <f aca="false">C31+C67+C103</f>
@@ -21508,10 +21302,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="B139" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C139" s="44" t="n">
         <f aca="false">C32+C68+C104</f>
@@ -21632,10 +21426,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B140" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C140" s="44" t="n">
         <f aca="false">C28+C64+C100</f>
@@ -21756,10 +21550,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="B141" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C141" s="44" t="n">
         <f aca="false">C41+C77+C113</f>
@@ -21880,10 +21674,10 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B142" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C142" s="44" t="n">
         <f aca="false">C37+C73+C109</f>
@@ -22004,10 +21798,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="6" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C143" s="53" t="n">
         <f aca="false">C35+C71+C107</f>
@@ -22128,10 +21922,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C144" s="54" t="n">
         <f aca="false">C38+C74+C110</f>
@@ -22252,10 +22046,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B145" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C145" s="44" t="n">
         <f aca="false">C40+C76+C112</f>
@@ -22376,10 +22170,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C146" s="54" t="n">
         <f aca="false">C33+C69+C105</f>
@@ -22500,10 +22294,10 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B147" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C147" s="54" t="n">
         <f aca="false">C34+C70+C106</f>
@@ -22624,10 +22418,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="C148" s="54" t="n">
         <f aca="false">C46+C82+C118</f>
@@ -22748,10 +22542,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="B149" s="23" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="C149" s="58" t="n">
         <f aca="false">C137+C138-C139</f>
@@ -22872,7 +22666,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="B150" s="23" t="s">
         <v>109</v>
@@ -22996,7 +22790,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="6" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="B151" s="23" t="s">
         <v>109</v>
@@ -23120,10 +22914,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="B152" s="23" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="C152" s="59" t="n">
         <f aca="false">IF(C151=0,0,((C46+C82+C118)/C7)/C151)</f>
@@ -23988,10 +23782,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="B160" s="23" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C160" s="44" t="n">
         <f aca="false">C56+C92+C128</f>
@@ -24112,10 +23906,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="6" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C161" s="44" t="n">
         <f aca="false">C48+C84+C120</f>
@@ -24236,7 +24030,7 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B162" s="23" t="s">
         <v>109</v>
@@ -24360,7 +24154,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="6" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="B163" s="23" t="s">
         <v>109</v>
@@ -24484,10 +24278,10 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="B164" s="23" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="C164" s="58" t="n">
         <f aca="false">C162-(C154+C155+C156+C157+C158+C159+C133)</f>
@@ -24638,35 +24432,35 @@
     </row>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D4" s="60" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="E4" s="60" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="F4" s="60" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="G4" s="60" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="H4" s="60" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="I4" s="60" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="J4" s="60" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -24681,7 +24475,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="D7" s="35" t="n">
         <f aca="false">SUM(Model!C57:N57)</f>
@@ -24714,7 +24508,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="D8" s="35" t="n">
         <f aca="false">SUM(Model!C93:N93)</f>
@@ -24747,7 +24541,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="D9" s="35" t="n">
         <f aca="false">SUM(Model!C129:N129)</f>
@@ -24780,7 +24574,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="D10" s="35" t="n">
         <f aca="false">SUM(Model!C133:N133)</f>
@@ -24813,7 +24607,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="D11" s="61" t="n">
         <f aca="false">SUM(Model!C162:N162)</f>
@@ -24846,7 +24640,7 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -24861,7 +24655,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="D14" s="35" t="n">
         <f aca="false">SUM(Model!C154:N154)</f>
@@ -24894,7 +24688,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="D15" s="35" t="n">
         <f aca="false">SUM(Model!C155:N155)</f>
@@ -24927,7 +24721,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="D16" s="35" t="n">
         <f aca="false">SUM(Model!C156:N156)</f>
@@ -24960,7 +24754,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="D17" s="35" t="n">
         <f aca="false">SUM(Model!C157:N157)</f>
@@ -24993,7 +24787,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="D18" s="35" t="n">
         <f aca="false">SUM(Model!C158:N158)</f>
@@ -25026,7 +24820,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="D19" s="35" t="n">
         <f aca="false">SUM(Model!C159:N159)</f>
@@ -25059,7 +24853,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="D20" s="35" t="n">
         <f aca="false">SUM(Model!C133:N133)</f>
@@ -25092,7 +24886,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="D21" s="61" t="n">
         <f aca="false">SUM(Model!C162:N162)</f>
@@ -25125,7 +24919,7 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -25140,7 +24934,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="D24" s="62" t="n">
         <f aca="false">IF(D$11=0,0,D14/D$11)</f>
@@ -25173,7 +24967,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="D25" s="62" t="n">
         <f aca="false">IF(D$11=0,0,D15/D$11)</f>
@@ -25206,7 +25000,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D26" s="62" t="n">
         <f aca="false">IF(D$11=0,0,D16/D$11)</f>
@@ -25239,7 +25033,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D27" s="62" t="n">
         <f aca="false">IF(D$11=0,0,D17/D$11)</f>
@@ -25272,7 +25066,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="D28" s="62" t="n">
         <f aca="false">IF(D$11=0,0,D18/D$11)</f>
@@ -25305,7 +25099,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="D29" s="62" t="n">
         <f aca="false">IF(D$11=0,0,D19/D$11)</f>
@@ -25338,7 +25132,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="D30" s="62" t="n">
         <f aca="false">IF(D$11=0,0,D20/D$11)</f>
@@ -25371,7 +25165,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="D31" s="38" t="n">
         <f aca="false">SUM(D24:D30)</f>
@@ -25404,7 +25198,7 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -25419,7 +25213,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="D34" s="36" t="n">
         <f aca="false">SUM(Model!C140:N140)</f>
@@ -25452,7 +25246,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="D35" s="63" t="n">
         <f aca="false">Model!N137</f>
@@ -25485,7 +25279,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="D36" s="36" t="n">
         <f aca="false">Model!N138</f>
@@ -25518,7 +25312,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D37" s="36" t="n">
         <f aca="false">Model!N139</f>
@@ -25551,7 +25345,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="D38" s="36" t="n">
         <f aca="false">Model!N141</f>
@@ -25584,7 +25378,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D39" s="36" t="n">
         <f aca="false">Model!N142</f>
@@ -25617,7 +25411,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D40" s="61" t="n">
         <f aca="false">Model!N144</f>
@@ -25650,7 +25444,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="D41" s="35" t="n">
         <f aca="false">Model!N163</f>
@@ -25683,7 +25477,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
@@ -3158,7 +3158,7 @@
         <v>105</v>
       </c>
       <c r="B37" s="19" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>102</v>
@@ -18650,119 +18650,119 @@
       </c>
       <c r="C112" s="55" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$48,C107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*C7,0)</f>
-        <v>109.975778594848</v>
+        <v>153.966090032787</v>
       </c>
       <c r="D112" s="55" t="n">
         <f aca="false">IF(D2&gt;=Assumptions!$B$48,D107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*D7,0)</f>
-        <v>209.095932161433</v>
+        <v>292.734305026006</v>
       </c>
       <c r="E112" s="55" t="n">
         <f aca="false">IF(E2&gt;=Assumptions!$B$48,E107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*E7,0)</f>
-        <v>298.98564585667</v>
+        <v>418.579904199338</v>
       </c>
       <c r="F112" s="55" t="n">
         <f aca="false">IF(F2&gt;=Assumptions!$B$48,F107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*F7,0)</f>
-        <v>409.447163883113</v>
+        <v>573.226029436358</v>
       </c>
       <c r="G112" s="55" t="n">
         <f aca="false">IF(G2&gt;=Assumptions!$B$48,G107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*G7,0)</f>
-        <v>502.50265282002</v>
+        <v>703.503713948027</v>
       </c>
       <c r="H112" s="55" t="n">
         <f aca="false">IF(H2&gt;=Assumptions!$B$48,H107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*H7,0)</f>
-        <v>573.595489667497</v>
+        <v>803.033685534495</v>
       </c>
       <c r="I112" s="55" t="n">
         <f aca="false">IF(I2&gt;=Assumptions!$B$48,I107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*I7,0)</f>
-        <v>637.925938758195</v>
+        <v>893.096314261473</v>
       </c>
       <c r="J112" s="55" t="n">
         <f aca="false">IF(J2&gt;=Assumptions!$B$48,J107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*J7,0)</f>
-        <v>699.080577831729</v>
+        <v>978.71280896442</v>
       </c>
       <c r="K112" s="55" t="n">
         <f aca="false">IF(K2&gt;=Assumptions!$B$48,K107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*K7,0)</f>
-        <v>765.88275225382</v>
+        <v>1072.23585315535</v>
       </c>
       <c r="L112" s="55" t="n">
         <f aca="false">IF(L2&gt;=Assumptions!$B$48,L107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*L7,0)</f>
-        <v>864.034898403311</v>
+        <v>1209.64885776464</v>
       </c>
       <c r="M112" s="55" t="n">
         <f aca="false">IF(M2&gt;=Assumptions!$B$48,M107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*M7,0)</f>
-        <v>946.488929467386</v>
+        <v>1325.08450125434</v>
       </c>
       <c r="N112" s="55" t="n">
         <f aca="false">IF(N2&gt;=Assumptions!$B$48,N107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*N7,0)</f>
-        <v>1009.70666515587</v>
+        <v>1413.58933121821</v>
       </c>
       <c r="O112" s="55" t="n">
         <f aca="false">IF(O2&gt;=Assumptions!$B$48,O107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*O7,0)</f>
-        <v>1317.88501180474</v>
+        <v>1845.03901652663</v>
       </c>
       <c r="P112" s="55" t="n">
         <f aca="false">IF(P2&gt;=Assumptions!$B$48,P107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*P7,0)</f>
-        <v>1599.33777099481</v>
+        <v>2239.07287939273</v>
       </c>
       <c r="Q112" s="55" t="n">
         <f aca="false">IF(Q2&gt;=Assumptions!$B$48,Q107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*Q7,0)</f>
-        <v>1857.85159101555</v>
+        <v>2600.99222742177</v>
       </c>
       <c r="R112" s="55" t="n">
         <f aca="false">IF(R2&gt;=Assumptions!$B$48,R107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*R7,0)</f>
-        <v>2193.68471394563</v>
+        <v>3071.15859952388</v>
       </c>
       <c r="S112" s="55" t="n">
         <f aca="false">IF(S2&gt;=Assumptions!$B$48,S107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*S7,0)</f>
-        <v>2479.26705330481</v>
+        <v>3470.97387462674</v>
       </c>
       <c r="T112" s="55" t="n">
         <f aca="false">IF(T2&gt;=Assumptions!$B$48,T107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*T7,0)</f>
-        <v>2695.46212910878</v>
+        <v>3773.6469807523</v>
       </c>
       <c r="U112" s="55" t="n">
         <f aca="false">IF(U2&gt;=Assumptions!$B$48,U107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*U7,0)</f>
-        <v>2893.10978476021</v>
+        <v>4050.35369866429</v>
       </c>
       <c r="V112" s="55" t="n">
         <f aca="false">IF(V2&gt;=Assumptions!$B$48,V107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*V7,0)</f>
-        <v>3084.23926685855</v>
+        <v>4317.93497360197</v>
       </c>
       <c r="W112" s="55" t="n">
         <f aca="false">IF(W2&gt;=Assumptions!$B$48,W107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*W7,0)</f>
-        <v>3300.52302617667</v>
+        <v>4620.73223664734</v>
       </c>
       <c r="X112" s="55" t="n">
         <f aca="false">IF(X2&gt;=Assumptions!$B$48,X107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*X7,0)</f>
-        <v>3637.19274711402</v>
+        <v>5092.06984595962</v>
       </c>
       <c r="Y112" s="55" t="n">
         <f aca="false">IF(Y2&gt;=Assumptions!$B$48,Y107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*Y7,0)</f>
-        <v>3924.90850397063</v>
+        <v>5494.87190555888</v>
       </c>
       <c r="Z112" s="55" t="n">
         <f aca="false">IF(Z2&gt;=Assumptions!$B$48,Z107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*Z7,0)</f>
-        <v>4147.34714817492</v>
+        <v>5806.28600744489</v>
       </c>
       <c r="AA112" s="55" t="n">
         <f aca="false">IF(AA2&gt;=Assumptions!$B$48,AA107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*AA7,0)</f>
-        <v>92164.0866392288</v>
+        <v>129029.72129492</v>
       </c>
       <c r="AB112" s="55" t="n">
         <f aca="false">IF(AB2&gt;=Assumptions!$B$48,AB107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*AB7,0)</f>
-        <v>151335.24491909</v>
+        <v>211869.342886727</v>
       </c>
       <c r="AC112" s="55" t="n">
         <f aca="false">IF(AC2&gt;=Assumptions!$B$48,AC107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*AC7,0)</f>
-        <v>226107.492490286</v>
+        <v>316550.489486401</v>
       </c>
       <c r="AD112" s="55" t="n">
         <f aca="false">IF(AD2&gt;=Assumptions!$B$48,AD107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*AD7,0)</f>
-        <v>302805.223249116</v>
+        <v>423927.312548762</v>
       </c>
       <c r="AE112" s="55" t="n">
         <f aca="false">IF(AE2&gt;=Assumptions!$B$48,AE107*Assumptions!$B$37*Assumptions!$B$139*Assumptions!$B$141*Assumptions!$B$34*Assumptions!$B$140/12*AE7,0)</f>
-        <v>362552.27050258</v>
+        <v>507573.178703612</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18774,119 +18774,119 @@
       </c>
       <c r="C113" s="54" t="n">
         <f aca="false">(C111+C112)*(1-Assumptions!$B$8)/C21/(1+Assumptions!$B$9)</f>
-        <v>16.136650151973</v>
+        <v>16.4277090937062</v>
       </c>
       <c r="D113" s="54" t="n">
         <f aca="false">(D111+D112)*(1-Assumptions!$B$8)/D21/(1+Assumptions!$B$9)</f>
-        <v>30.6804639039654</v>
+        <v>31.2338515818088</v>
       </c>
       <c r="E113" s="54" t="n">
         <f aca="false">(E111+E112)*(1-Assumptions!$B$8)/E21/(1+Assumptions!$B$9)</f>
-        <v>43.8699032577416</v>
+        <v>44.6611906374568</v>
       </c>
       <c r="F113" s="54" t="n">
         <f aca="false">(F111+F112)*(1-Assumptions!$B$8)/F21/(1+Assumptions!$B$9)</f>
-        <v>60.0778255332023</v>
+        <v>61.1614573995837</v>
       </c>
       <c r="G113" s="54" t="n">
         <f aca="false">(G111+G112)*(1-Assumptions!$B$8)/G21/(1+Assumptions!$B$9)</f>
-        <v>73.7317763292916</v>
+        <v>75.0616863532682</v>
       </c>
       <c r="H113" s="54" t="n">
         <f aca="false">(H111+H112)*(1-Assumptions!$B$8)/H21/(1+Assumptions!$B$9)</f>
-        <v>84.1631663242225</v>
+        <v>85.6812287406806</v>
       </c>
       <c r="I113" s="54" t="n">
         <f aca="false">(I111+I112)*(1-Assumptions!$B$8)/I21/(1+Assumptions!$B$9)</f>
-        <v>93.6023170568597</v>
+        <v>95.2906347119967</v>
       </c>
       <c r="J113" s="54" t="n">
         <f aca="false">(J111+J112)*(1-Assumptions!$B$8)/J21/(1+Assumptions!$B$9)</f>
-        <v>102.575483953321</v>
+        <v>104.425651833646</v>
       </c>
       <c r="K113" s="54" t="n">
         <f aca="false">(K111+K112)*(1-Assumptions!$B$8)/K21/(1+Assumptions!$B$9)</f>
-        <v>112.377308789784</v>
+        <v>114.404273510661</v>
       </c>
       <c r="L113" s="54" t="n">
         <f aca="false">(L111+L112)*(1-Assumptions!$B$8)/L21/(1+Assumptions!$B$9)</f>
-        <v>126.779087657061</v>
+        <v>129.065819211618</v>
       </c>
       <c r="M113" s="54" t="n">
         <f aca="false">(M111+M112)*(1-Assumptions!$B$8)/M21/(1+Assumptions!$B$9)</f>
-        <v>138.877495778386</v>
+        <v>141.382447956882</v>
       </c>
       <c r="N113" s="54" t="n">
         <f aca="false">(N111+N112)*(1-Assumptions!$B$8)/N21/(1+Assumptions!$B$9)</f>
-        <v>148.153379043219</v>
+        <v>150.82564158299</v>
       </c>
       <c r="O113" s="54" t="n">
         <f aca="false">(O111+O112)*(1-Assumptions!$B$8)/O21/(1+Assumptions!$B$9)</f>
-        <v>178.882626528198</v>
+        <v>182.109156661863</v>
       </c>
       <c r="P113" s="54" t="n">
         <f aca="false">(P111+P112)*(1-Assumptions!$B$8)/P21/(1+Assumptions!$B$9)</f>
-        <v>217.085510965423</v>
+        <v>221.001111693712</v>
       </c>
       <c r="Q113" s="54" t="n">
         <f aca="false">(Q111+Q112)*(1-Assumptions!$B$8)/Q21/(1+Assumptions!$B$9)</f>
-        <v>252.174787119965</v>
+        <v>256.723297869079</v>
       </c>
       <c r="R113" s="54" t="n">
         <f aca="false">(R111+R112)*(1-Assumptions!$B$8)/R21/(1+Assumptions!$B$9)</f>
-        <v>297.758969781419</v>
+        <v>303.129688599758</v>
       </c>
       <c r="S113" s="54" t="n">
         <f aca="false">(S111+S112)*(1-Assumptions!$B$8)/S21/(1+Assumptions!$B$9)</f>
-        <v>336.522381230101</v>
+        <v>342.592280944597</v>
       </c>
       <c r="T113" s="54" t="n">
         <f aca="false">(T111+T112)*(1-Assumptions!$B$8)/T21/(1+Assumptions!$B$9)</f>
-        <v>365.86753855101</v>
+        <v>372.466740837872</v>
       </c>
       <c r="U113" s="54" t="n">
         <f aca="false">(U111+U112)*(1-Assumptions!$B$8)/U21/(1+Assumptions!$B$9)</f>
-        <v>392.695168771685</v>
+        <v>399.778264654039</v>
       </c>
       <c r="V113" s="54" t="n">
         <f aca="false">(V111+V112)*(1-Assumptions!$B$8)/V21/(1+Assumptions!$B$9)</f>
-        <v>418.638057156086</v>
+        <v>426.189088425745</v>
       </c>
       <c r="W113" s="54" t="n">
         <f aca="false">(W111+W112)*(1-Assumptions!$B$8)/W21/(1+Assumptions!$B$9)</f>
-        <v>447.995251900441</v>
+        <v>456.075802863101</v>
       </c>
       <c r="X113" s="54" t="n">
         <f aca="false">(X111+X112)*(1-Assumptions!$B$8)/X21/(1+Assumptions!$B$9)</f>
-        <v>493.692989877835</v>
+        <v>502.597797122316</v>
       </c>
       <c r="Y113" s="54" t="n">
         <f aca="false">(Y111+Y112)*(1-Assumptions!$B$8)/Y21/(1+Assumptions!$B$9)</f>
-        <v>532.745979948326</v>
+        <v>542.355191257738</v>
       </c>
       <c r="Z113" s="54" t="n">
         <f aca="false">(Z111+Z112)*(1-Assumptions!$B$8)/Z21/(1+Assumptions!$B$9)</f>
-        <v>562.938605678354</v>
+        <v>573.092405462473</v>
       </c>
       <c r="AA113" s="54" t="n">
         <f aca="false">(AA111+AA112)*(1-Assumptions!$B$8)/AA21/(1+Assumptions!$B$9)</f>
-        <v>11572.4862577021</v>
+        <v>11781.2207578411</v>
       </c>
       <c r="AB113" s="54" t="n">
         <f aca="false">(AB111+AB112)*(1-Assumptions!$B$8)/AB21/(1+Assumptions!$B$9)</f>
-        <v>17578.3998988877</v>
+        <v>17895.4638758437</v>
       </c>
       <c r="AC113" s="54" t="n">
         <f aca="false">(AC111+AC112)*(1-Assumptions!$B$8)/AC21/(1+Assumptions!$B$9)</f>
-        <v>24295.6496351307</v>
+        <v>24733.873554279</v>
       </c>
       <c r="AD113" s="54" t="n">
         <f aca="false">(AD111+AD112)*(1-Assumptions!$B$8)/AD21/(1+Assumptions!$B$9)</f>
-        <v>30098.9420369722</v>
+        <v>30641.8407262332</v>
       </c>
       <c r="AE113" s="54" t="n">
         <f aca="false">(AE111+AE112)*(1-Assumptions!$B$8)/AE21/(1+Assumptions!$B$9)</f>
-        <v>33337.4827259011</v>
+        <v>33938.7954116734</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19146,119 +19146,119 @@
       </c>
       <c r="C116" s="45" t="n">
         <f aca="false">C113</f>
-        <v>16.136650151973</v>
+        <v>16.4277090937062</v>
       </c>
       <c r="D116" s="45" t="n">
         <f aca="false">C116*(1-D114)+D113</f>
-        <v>46.5418555480957</v>
+        <v>47.3813372927298</v>
       </c>
       <c r="E116" s="45" t="n">
         <f aca="false">D116*(1-E114)+E113</f>
-        <v>89.6089939949684</v>
+        <v>91.2252835418272</v>
       </c>
       <c r="F116" s="45" t="n">
         <f aca="false">E116*(1-F114)+F113</f>
-        <v>148.127909669121</v>
+        <v>150.799712814346</v>
       </c>
       <c r="G116" s="45" t="n">
         <f aca="false">F116*(1-G114)+G113</f>
-        <v>219.257252482685</v>
+        <v>223.212025206511</v>
       </c>
       <c r="H116" s="45" t="n">
         <f aca="false">G116*(1-H114)+H113</f>
-        <v>299.526639639361</v>
+        <v>304.929242158055</v>
       </c>
       <c r="I116" s="45" t="n">
         <f aca="false">H116*(1-I114)+I113</f>
-        <v>387.755063827678</v>
+        <v>394.749054368867</v>
       </c>
       <c r="J116" s="45" t="n">
         <f aca="false">I116*(1-J114)+J113</f>
-        <v>483.307293620459</v>
+        <v>492.024772656584</v>
       </c>
       <c r="K116" s="45" t="n">
         <f aca="false">J116*(1-K114)+K113</f>
-        <v>586.85853348429</v>
+        <v>597.443780242097</v>
       </c>
       <c r="L116" s="45" t="n">
         <f aca="false">K116*(1-L114)+L113</f>
-        <v>702.864963204835</v>
+        <v>715.542633628689</v>
       </c>
       <c r="M116" s="45" t="n">
         <f aca="false">L116*(1-M114)+M113</f>
-        <v>828.756741589967</v>
+        <v>843.705139051006</v>
       </c>
       <c r="N116" s="45" t="n">
         <f aca="false">M116*(1-N114)+N113</f>
-        <v>961.482100699935</v>
+        <v>978.824483418131</v>
       </c>
       <c r="O116" s="45" t="n">
         <f aca="false">N116*(1-O114)+O113</f>
-        <v>1122.60678361447</v>
+        <v>1142.8553940351</v>
       </c>
       <c r="P116" s="45" t="n">
         <f aca="false">O116*(1-P114)+P113</f>
-        <v>1318.98930688065</v>
+        <v>1342.78009543977</v>
       </c>
       <c r="Q116" s="45" t="n">
         <f aca="false">P116*(1-Q114)+Q113</f>
-        <v>1546.7967414557</v>
+        <v>1574.69652352971</v>
       </c>
       <c r="R116" s="45" t="n">
         <f aca="false">Q116*(1-R114)+R113</f>
-        <v>1815.96963408504</v>
+        <v>1848.7245240367</v>
       </c>
       <c r="S116" s="45" t="n">
         <f aca="false">R116*(1-S114)+S113</f>
-        <v>2118.81782786311</v>
+        <v>2157.0352316548</v>
       </c>
       <c r="T116" s="45" t="n">
         <f aca="false">S116*(1-T114)+T113</f>
-        <v>2445.16831923479</v>
+        <v>2489.27215098757</v>
       </c>
       <c r="U116" s="45" t="n">
         <f aca="false">T116*(1-U114)+U113</f>
-        <v>2791.98180759093</v>
+        <v>2842.3411611496</v>
       </c>
       <c r="V116" s="45" t="n">
         <f aca="false">U116*(1-V114)+V113</f>
-        <v>3157.91706898289</v>
+        <v>3214.87684635446</v>
       </c>
       <c r="W116" s="45" t="n">
         <f aca="false">V116*(1-W114)+W113</f>
-        <v>3545.99995176769</v>
+        <v>3609.95963259533</v>
       </c>
       <c r="X116" s="45" t="n">
         <f aca="false">W116*(1-X114)+X113</f>
-        <v>3972.2740592977</v>
+        <v>4043.92250386859</v>
       </c>
       <c r="Y116" s="45" t="n">
         <f aca="false">X116*(1-Y114)+Y113</f>
-        <v>4429.22053649321</v>
+        <v>4509.11098648831</v>
       </c>
       <c r="Z116" s="45" t="n">
         <f aca="false">Y116*(1-Z114)+Z113</f>
-        <v>4907.21073701492</v>
+        <v>4995.72276091864</v>
       </c>
       <c r="AA116" s="45" t="n">
         <f aca="false">Z116*(1-AA114)+AA113</f>
-        <v>15298.6614397925</v>
+        <v>15574.6054657623</v>
       </c>
       <c r="AB116" s="45" t="n">
         <f aca="false">AA116*(1-AB114)+AB113</f>
-        <v>29100.4853292198</v>
+        <v>29625.3747197734</v>
       </c>
       <c r="AC116" s="45" t="n">
         <f aca="false">AB116*(1-AC114)+AC113</f>
-        <v>46076.0470282005</v>
+        <v>46907.1269215473</v>
       </c>
       <c r="AD116" s="45" t="n">
         <f aca="false">AC116*(1-AD114)+AD113</f>
-        <v>64374.0524080039</v>
+        <v>65535.1758997133</v>
       </c>
       <c r="AE116" s="45" t="n">
         <f aca="false">AD116*(1-AE114)+AE113</f>
-        <v>80912.7085805939</v>
+        <v>82372.1420510131</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19270,119 +19270,119 @@
       </c>
       <c r="C117" s="45" t="n">
         <f aca="false">C113</f>
-        <v>16.136650151973</v>
+        <v>16.4277090937062</v>
       </c>
       <c r="D117" s="45" t="n">
         <f aca="false">C117*(1-D115)+D113</f>
-        <v>46.7032220496154</v>
+        <v>47.5456143836668</v>
       </c>
       <c r="E117" s="45" t="n">
         <f aca="false">D117*(1-E115)+E113</f>
-        <v>90.2346094298216</v>
+        <v>91.8621832869112</v>
       </c>
       <c r="F117" s="45" t="n">
         <f aca="false">E117*(1-F115)+F113</f>
-        <v>149.644987490891</v>
+        <v>152.344154374016</v>
       </c>
       <c r="G117" s="45" t="n">
         <f aca="false">F117*(1-G115)+G113</f>
-        <v>222.244126902625</v>
+        <v>226.252774284423</v>
       </c>
       <c r="H117" s="45" t="n">
         <f aca="false">G117*(1-H115)+H113</f>
-        <v>304.682911566896</v>
+        <v>310.17851845988</v>
       </c>
       <c r="I117" s="45" t="n">
         <f aca="false">H117*(1-I115)+I113</f>
-        <v>395.865654725631</v>
+        <v>403.005937092035</v>
       </c>
       <c r="J117" s="45" t="n">
         <f aca="false">I117*(1-J115)+J113</f>
-        <v>495.229637139499</v>
+        <v>504.162161098514</v>
       </c>
       <c r="K117" s="45" t="n">
         <f aca="false">J117*(1-K115)+K113</f>
-        <v>603.515449729651</v>
+        <v>614.401139539098</v>
       </c>
       <c r="L117" s="45" t="n">
         <f aca="false">K117*(1-L115)+L113</f>
-        <v>725.251271569083</v>
+        <v>738.332726865289</v>
       </c>
       <c r="M117" s="45" t="n">
         <f aca="false">L117*(1-M115)+M113</f>
-        <v>857.981966475594</v>
+        <v>873.45750327144</v>
       </c>
       <c r="N117" s="45" t="n">
         <f aca="false">M117*(1-N115)+N113</f>
-        <v>998.743092539236</v>
+        <v>1016.75755680785</v>
       </c>
       <c r="O117" s="45" t="n">
         <f aca="false">N117*(1-O115)+O113</f>
-        <v>1169.16702030519</v>
+        <v>1190.25544401362</v>
       </c>
       <c r="P117" s="45" t="n">
         <f aca="false">O117*(1-P115)+P113</f>
-        <v>1376.38255514029</v>
+        <v>1401.20855348235</v>
       </c>
       <c r="Q117" s="45" t="n">
         <f aca="false">P117*(1-Q115)+Q113</f>
-        <v>1616.89351742602</v>
+        <v>1646.05764453079</v>
       </c>
       <c r="R117" s="45" t="n">
         <f aca="false">Q117*(1-R115)+R113</f>
-        <v>1900.93989910389</v>
+        <v>1935.22740922035</v>
       </c>
       <c r="S117" s="45" t="n">
         <f aca="false">R117*(1-S115)+S113</f>
-        <v>2221.22185724873</v>
+        <v>2261.28633637152</v>
       </c>
       <c r="T117" s="45" t="n">
         <f aca="false">S117*(1-T115)+T113</f>
-        <v>2567.87467913769</v>
+        <v>2614.19178210357</v>
       </c>
       <c r="U117" s="45" t="n">
         <f aca="false">T117*(1-U115)+U113</f>
-        <v>2938.06442494501</v>
+        <v>2991.05869043474</v>
       </c>
       <c r="V117" s="45" t="n">
         <f aca="false">U117*(1-V115)+V113</f>
-        <v>3330.62280461467</v>
+        <v>3390.69769870321</v>
       </c>
       <c r="W117" s="45" t="n">
         <f aca="false">V117*(1-W115)+W113</f>
-        <v>3748.73532218635</v>
+        <v>3816.35176831597</v>
       </c>
       <c r="X117" s="45" t="n">
         <f aca="false">W117*(1-X115)+X113</f>
-        <v>4208.64224479048</v>
+        <v>4284.55409429863</v>
       </c>
       <c r="Y117" s="45" t="n">
         <f aca="false">X117*(1-Y115)+Y113</f>
-        <v>4703.16473285113</v>
+        <v>4787.99635137471</v>
       </c>
       <c r="Z117" s="45" t="n">
         <f aca="false">Y117*(1-Z115)+Z113</f>
-        <v>5222.93258117914</v>
+        <v>5317.13932269643</v>
       </c>
       <c r="AA117" s="45" t="n">
         <f aca="false">Z117*(1-AA115)+AA113</f>
-        <v>16165.1493142634</v>
+        <v>16456.7222992421</v>
       </c>
       <c r="AB117" s="45" t="n">
         <f aca="false">AA117*(1-AB115)+AB113</f>
-        <v>31692.892844609</v>
+        <v>32264.5418402147</v>
       </c>
       <c r="AC117" s="45" t="n">
         <f aca="false">AB117*(1-AC115)+AC113</f>
-        <v>51819.4939704391</v>
+        <v>52754.1691932481</v>
       </c>
       <c r="AD117" s="45" t="n">
         <f aca="false">AC117*(1-AD115)+AD113</f>
-        <v>74864.834538222</v>
+        <v>76215.1816863915</v>
       </c>
       <c r="AE117" s="45" t="n">
         <f aca="false">AD117*(1-AE115)+AE113</f>
-        <v>97649.6332075908</v>
+        <v>99410.9528516534</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19394,119 +19394,119 @@
       </c>
       <c r="C118" s="57" t="n">
         <f aca="false">C116*C21</f>
-        <v>2282.6905304981</v>
+        <v>2323.86372839568</v>
       </c>
       <c r="D118" s="57" t="n">
         <f aca="false">D116*D21</f>
-        <v>6583.81088583362</v>
+        <v>6702.56397342956</v>
       </c>
       <c r="E118" s="57" t="n">
         <f aca="false">E116*E21</f>
-        <v>12676.0882905282</v>
+        <v>12904.7286098269</v>
       </c>
       <c r="F118" s="57" t="n">
         <f aca="false">F116*F21</f>
-        <v>20954.1741017938</v>
+        <v>21332.1273747174</v>
       </c>
       <c r="G118" s="57" t="n">
         <f aca="false">G116*G21</f>
-        <v>31016.1309362007</v>
+        <v>31575.5730857131</v>
       </c>
       <c r="H118" s="57" t="n">
         <f aca="false">H116*H21</f>
-        <v>42371.0384433839</v>
+        <v>43135.2905956784</v>
       </c>
       <c r="I118" s="57" t="n">
         <f aca="false">I116*I21</f>
-        <v>54851.8313290633</v>
+        <v>55841.2012310199</v>
       </c>
       <c r="J118" s="57" t="n">
         <f aca="false">J116*J21</f>
-        <v>68368.6497555502</v>
+        <v>69601.8243400004</v>
       </c>
       <c r="K118" s="57" t="n">
         <f aca="false">K116*K21</f>
-        <v>83017.0081466876</v>
+        <v>84514.397153047</v>
       </c>
       <c r="L118" s="57" t="n">
         <f aca="false">L116*L21</f>
-        <v>99427.277694956</v>
+        <v>101220.660953114</v>
       </c>
       <c r="M118" s="57" t="n">
         <f aca="false">M116*M21</f>
-        <v>117235.928665317</v>
+        <v>119350.528970155</v>
       </c>
       <c r="N118" s="57" t="n">
         <f aca="false">N116*N21</f>
-        <v>136011.257965013</v>
+        <v>138464.511424329</v>
       </c>
       <c r="O118" s="57" t="n">
         <f aca="false">O116*O21</f>
-        <v>171667.076014521</v>
+        <v>174763.458287462</v>
       </c>
       <c r="P118" s="57" t="n">
         <f aca="false">P116*P21</f>
-        <v>201697.549766794</v>
+        <v>205335.595757283</v>
       </c>
       <c r="Q118" s="57" t="n">
         <f aca="false">Q116*Q21</f>
-        <v>236533.466277076</v>
+        <v>240799.852406212</v>
       </c>
       <c r="R118" s="57" t="n">
         <f aca="false">R116*R21</f>
-        <v>277694.916657121</v>
+        <v>282703.737435021</v>
       </c>
       <c r="S118" s="57" t="n">
         <f aca="false">S116*S21</f>
-        <v>324005.935493806</v>
+        <v>329850.07438335</v>
       </c>
       <c r="T118" s="57" t="n">
         <f aca="false">T116*T21</f>
-        <v>373910.884784509</v>
+        <v>380655.165995476</v>
       </c>
       <c r="U118" s="57" t="n">
         <f aca="false">U116*U21</f>
-        <v>426944.99996846</v>
+        <v>434645.864689376</v>
       </c>
       <c r="V118" s="57" t="n">
         <f aca="false">V116*V21</f>
-        <v>482903.183413163</v>
+        <v>491613.373458812</v>
       </c>
       <c r="W118" s="57" t="n">
         <f aca="false">W116*W21</f>
-        <v>542248.1425844</v>
+        <v>552028.745686718</v>
       </c>
       <c r="X118" s="57" t="n">
         <f aca="false">X116*X21</f>
-        <v>607433.237390942</v>
+        <v>618389.592866428</v>
       </c>
       <c r="Y118" s="57" t="n">
         <f aca="false">Y116*Y21</f>
-        <v>677308.697596808</v>
+        <v>689525.406200676</v>
       </c>
       <c r="Z118" s="57" t="n">
         <f aca="false">Z116*Z21</f>
-        <v>750402.127357639</v>
+        <v>763937.232042074</v>
       </c>
       <c r="AA118" s="57" t="n">
         <f aca="false">AA116*AA21</f>
-        <v>2528939.70740605</v>
+        <v>2574554.53501974</v>
       </c>
       <c r="AB118" s="57" t="n">
         <f aca="false">AB116*AB21</f>
-        <v>5200091.28694672</v>
+        <v>5293886.03695001</v>
       </c>
       <c r="AC118" s="57" t="n">
         <f aca="false">AC116*AC21</f>
-        <v>8900443.39342943</v>
+        <v>9060981.89495548</v>
       </c>
       <c r="AD118" s="57" t="n">
         <f aca="false">AD116*AD21</f>
-        <v>13442281.0934829</v>
+        <v>13684741.3360179</v>
       </c>
       <c r="AE118" s="57" t="n">
         <f aca="false">AE116*AE21</f>
-        <v>18264364.1341435</v>
+        <v>18593800.9408071</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19890,119 +19890,119 @@
       </c>
       <c r="C122" s="55" t="n">
         <f aca="false">IF(C107=0,0,C118/C107*Assumptions!$B$31)</f>
-        <v>14.702380952381</v>
+        <v>14.9675697865353</v>
       </c>
       <c r="D122" s="55" t="n">
         <f aca="false">IF(D107=0,0,D118/D107*Assumptions!$B$31)</f>
-        <v>22.3033162940651</v>
+        <v>22.7056042272206</v>
       </c>
       <c r="E122" s="55" t="n">
         <f aca="false">IF(E107=0,0,E118/E107*Assumptions!$B$31)</f>
-        <v>30.0311937943732</v>
+        <v>30.5728704994176</v>
       </c>
       <c r="F122" s="55" t="n">
         <f aca="false">IF(F107=0,0,F118/F107*Assumptions!$B$31)</f>
-        <v>36.2501961132347</v>
+        <v>36.9040458044018</v>
       </c>
       <c r="G122" s="55" t="n">
         <f aca="false">IF(G107=0,0,G118/G107*Assumptions!$B$31)</f>
-        <v>43.7206834428614</v>
+        <v>44.5092793245894</v>
       </c>
       <c r="H122" s="55" t="n">
         <f aca="false">IF(H107=0,0,H118/H107*Assumptions!$B$31)</f>
-        <v>52.3240148118927</v>
+        <v>53.2677901453698</v>
       </c>
       <c r="I122" s="55" t="n">
         <f aca="false">IF(I107=0,0,I118/I107*Assumptions!$B$31)</f>
-        <v>60.9057857098369</v>
+        <v>62.0043516059295</v>
       </c>
       <c r="J122" s="55" t="n">
         <f aca="false">IF(J107=0,0,J118/J107*Assumptions!$B$31)</f>
-        <v>69.2735503066784</v>
+        <v>70.5230467047829</v>
       </c>
       <c r="K122" s="55" t="n">
         <f aca="false">IF(K107=0,0,K118/K107*Assumptions!$B$31)</f>
-        <v>76.7790029620823</v>
+        <v>78.1638762250588</v>
       </c>
       <c r="L122" s="55" t="n">
         <f aca="false">IF(L107=0,0,L118/L107*Assumptions!$B$31)</f>
-        <v>81.5101972895697</v>
+        <v>82.9804077446601</v>
       </c>
       <c r="M122" s="55" t="n">
         <f aca="false">IF(M107=0,0,M118/M107*Assumptions!$B$31)</f>
-        <v>87.7370178905977</v>
+        <v>89.3195423512239</v>
       </c>
       <c r="N122" s="55" t="n">
         <f aca="false">IF(N107=0,0,N118/N107*Assumptions!$B$31)</f>
-        <v>95.4151448632314</v>
+        <v>97.1361607387486</v>
       </c>
       <c r="O122" s="55" t="n">
         <f aca="false">IF(O107=0,0,O118/O107*Assumptions!$B$31)</f>
-        <v>92.2671637417246</v>
+        <v>93.931399055899</v>
       </c>
       <c r="P122" s="55" t="n">
         <f aca="false">IF(P107=0,0,P118/P107*Assumptions!$B$31)</f>
-        <v>89.3301592337265</v>
+        <v>90.9414194002765</v>
       </c>
       <c r="Q122" s="55" t="n">
         <f aca="false">IF(Q107=0,0,Q118/Q107*Assumptions!$B$31)</f>
-        <v>90.1818742805742</v>
+        <v>91.8084969466429</v>
       </c>
       <c r="R122" s="55" t="n">
         <f aca="false">IF(R107=0,0,R118/R107*Assumptions!$B$31)</f>
-        <v>89.6667441382992</v>
+        <v>91.2840753323057</v>
       </c>
       <c r="S122" s="55" t="n">
         <f aca="false">IF(S107=0,0,S118/S107*Assumptions!$B$31)</f>
-        <v>92.569376099355</v>
+        <v>94.2390624587067</v>
       </c>
       <c r="T122" s="55" t="n">
         <f aca="false">IF(T107=0,0,T118/T107*Assumptions!$B$31)</f>
-        <v>98.2590482458742</v>
+        <v>100.031359991423</v>
       </c>
       <c r="U122" s="55" t="n">
         <f aca="false">IF(U107=0,0,U118/U107*Assumptions!$B$31)</f>
-        <v>104.530901858854</v>
+        <v>106.416339876467</v>
       </c>
       <c r="V122" s="55" t="n">
         <f aca="false">IF(V107=0,0,V118/V107*Assumptions!$B$31)</f>
-        <v>110.904632224829</v>
+        <v>112.905034079282</v>
       </c>
       <c r="W122" s="55" t="n">
         <f aca="false">IF(W107=0,0,W118/W107*Assumptions!$B$31)</f>
-        <v>116.373202454385</v>
+        <v>118.472241649848</v>
       </c>
       <c r="X122" s="55" t="n">
         <f aca="false">IF(X107=0,0,X118/X107*Assumptions!$B$31)</f>
-        <v>118.295960575635</v>
+        <v>120.429680819439</v>
       </c>
       <c r="Y122" s="55" t="n">
         <f aca="false">IF(Y107=0,0,Y118/Y107*Assumptions!$B$31)</f>
-        <v>122.234779990172</v>
+        <v>124.439545252595</v>
       </c>
       <c r="Z122" s="55" t="n">
         <f aca="false">IF(Z107=0,0,Z118/Z107*Assumptions!$B$31)</f>
-        <v>128.162611235852</v>
+        <v>130.474297592361</v>
       </c>
       <c r="AA122" s="55" t="n">
         <f aca="false">IF(AA107=0,0,AA118/AA107*Assumptions!$B$31)</f>
-        <v>233.236049927953</v>
+        <v>237.44296011233</v>
       </c>
       <c r="AB122" s="55" t="n">
         <f aca="false">IF(AB107=0,0,AB118/AB107*Assumptions!$B$31)</f>
-        <v>292.071922589339</v>
+        <v>297.340063368138</v>
       </c>
       <c r="AC122" s="55" t="n">
         <f aca="false">IF(AC107=0,0,AC118/AC107*Assumptions!$B$31)</f>
-        <v>334.592047397104</v>
+        <v>340.627129419121</v>
       </c>
       <c r="AD122" s="55" t="n">
         <f aca="false">IF(AD107=0,0,AD118/AD107*Assumptions!$B$31)</f>
-        <v>377.336256186718</v>
+        <v>384.142321285046</v>
       </c>
       <c r="AE122" s="55" t="n">
         <f aca="false">IF(AE107=0,0,AE118/AE107*Assumptions!$B$31)</f>
-        <v>428.206103701989</v>
+        <v>435.929715121548</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20014,119 +20014,119 @@
       </c>
       <c r="C123" s="55" t="n">
         <f aca="false">C122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>15.4375</v>
+        <v>15.7159482758621</v>
       </c>
       <c r="D123" s="55" t="n">
         <f aca="false">D122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>23.4184821087683</v>
+        <v>23.8408844385817</v>
       </c>
       <c r="E123" s="55" t="n">
         <f aca="false">E122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>31.5327534840919</v>
+        <v>32.1015140243885</v>
       </c>
       <c r="F123" s="55" t="n">
         <f aca="false">F122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>38.0627059188965</v>
+        <v>38.7492480946219</v>
       </c>
       <c r="G123" s="55" t="n">
         <f aca="false">G122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>45.9067176150045</v>
+        <v>46.7347432908189</v>
       </c>
       <c r="H123" s="55" t="n">
         <f aca="false">H122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>54.9402155524874</v>
+        <v>55.9311796526383</v>
       </c>
       <c r="I123" s="55" t="n">
         <f aca="false">I122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>63.9510749953288</v>
+        <v>65.104569186226</v>
       </c>
       <c r="J123" s="55" t="n">
         <f aca="false">J122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>72.7372278220123</v>
+        <v>74.049199040022</v>
       </c>
       <c r="K123" s="55" t="n">
         <f aca="false">K122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>80.6179531101864</v>
+        <v>82.0720700363118</v>
       </c>
       <c r="L123" s="55" t="n">
         <f aca="false">L122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>85.5857071540482</v>
+        <v>87.1294281318931</v>
       </c>
       <c r="M123" s="55" t="n">
         <f aca="false">M122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>92.1238687851276</v>
+        <v>93.7855194687851</v>
       </c>
       <c r="N123" s="55" t="n">
         <f aca="false">N122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>100.185902106393</v>
+        <v>101.992968775686</v>
       </c>
       <c r="O123" s="55" t="n">
         <f aca="false">O122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>96.8805219288109</v>
+        <v>98.627969008694</v>
       </c>
       <c r="P123" s="55" t="n">
         <f aca="false">P122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>93.7966671954128</v>
+        <v>95.4884903702903</v>
       </c>
       <c r="Q123" s="55" t="n">
         <f aca="false">Q122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>94.6909679946029</v>
+        <v>96.398921793975</v>
       </c>
       <c r="R123" s="55" t="n">
         <f aca="false">R122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>94.1500813452142</v>
+        <v>95.8482790989209</v>
       </c>
       <c r="S123" s="55" t="n">
         <f aca="false">S122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>97.1978449043227</v>
+        <v>98.9510155816421</v>
       </c>
       <c r="T123" s="55" t="n">
         <f aca="false">T122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>103.172000658168</v>
+        <v>105.032927990994</v>
       </c>
       <c r="U123" s="55" t="n">
         <f aca="false">U122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>109.757446951796</v>
+        <v>111.73715687029</v>
       </c>
       <c r="V123" s="55" t="n">
         <f aca="false">V122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>116.449863836071</v>
+        <v>118.550285783246</v>
       </c>
       <c r="W123" s="55" t="n">
         <f aca="false">W122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>122.191862577104</v>
+        <v>124.395853732341</v>
       </c>
       <c r="X123" s="55" t="n">
         <f aca="false">X122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>124.210758604416</v>
+        <v>126.451164860411</v>
       </c>
       <c r="Y123" s="55" t="n">
         <f aca="false">Y122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>128.346518989681</v>
+        <v>130.661522515224</v>
       </c>
       <c r="Z123" s="55" t="n">
         <f aca="false">Z122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>134.570741797645</v>
+        <v>136.998012471979</v>
       </c>
       <c r="AA123" s="55" t="n">
         <f aca="false">AA122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>244.897852424351</v>
+        <v>249.315108117947</v>
       </c>
       <c r="AB123" s="55" t="n">
         <f aca="false">AB122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>306.675518718805</v>
+        <v>312.207066536545</v>
       </c>
       <c r="AC123" s="55" t="n">
         <f aca="false">AC122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>351.321649766959</v>
+        <v>357.658485890077</v>
       </c>
       <c r="AD123" s="55" t="n">
         <f aca="false">AD122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>396.203068996054</v>
+        <v>403.349437349299</v>
       </c>
       <c r="AE123" s="55" t="n">
         <f aca="false">AE122*Assumptions!$B$156*Assumptions!$B$158</f>
-        <v>449.616408887089</v>
+        <v>457.726200877625</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20138,119 +20138,119 @@
       </c>
       <c r="C124" s="55" t="n">
         <f aca="false">C123/12*C16</f>
-        <v>1.41510416666667</v>
+        <v>1.44062859195402</v>
       </c>
       <c r="D124" s="55" t="n">
         <f aca="false">D123/12*D16</f>
-        <v>1.9515401757307</v>
+        <v>1.98674036988181</v>
       </c>
       <c r="E124" s="55" t="n">
         <f aca="false">E123/12*E16</f>
-        <v>2.57517486786751</v>
+        <v>2.62162364532506</v>
       </c>
       <c r="F124" s="55" t="n">
         <f aca="false">F123/12*F16</f>
-        <v>3.10845431670988</v>
+        <v>3.16452192772746</v>
       </c>
       <c r="G124" s="55" t="n">
         <f aca="false">G123/12*G16</f>
-        <v>3.82555980125037</v>
+        <v>3.89456194090157</v>
       </c>
       <c r="H124" s="55" t="n">
         <f aca="false">H123/12*H16</f>
-        <v>4.34943373123858</v>
+        <v>4.42788505583387</v>
       </c>
       <c r="I124" s="55" t="n">
         <f aca="false">I123/12*I16</f>
-        <v>4.68974549965745</v>
+        <v>4.77433507365657</v>
       </c>
       <c r="J124" s="55" t="n">
         <f aca="false">J123/12*J16</f>
-        <v>5.45529208665092</v>
+        <v>5.55368992800165</v>
       </c>
       <c r="K124" s="55" t="n">
         <f aca="false">K123/12*K16</f>
-        <v>6.7181627591822</v>
+        <v>6.83933916969265</v>
       </c>
       <c r="L124" s="55" t="n">
         <f aca="false">L123/12*L16</f>
-        <v>7.27478510809409</v>
+        <v>7.40600139121091</v>
       </c>
       <c r="M124" s="55" t="n">
         <f aca="false">M123/12*M16</f>
-        <v>8.06083851869867</v>
+        <v>8.20623295351869</v>
       </c>
       <c r="N124" s="55" t="n">
         <f aca="false">N123/12*N16</f>
-        <v>9.51766070010734</v>
+        <v>9.68933203369018</v>
       </c>
       <c r="O124" s="55" t="n">
         <f aca="false">O123/12*O16</f>
-        <v>8.880714510141</v>
+        <v>9.04089715913028</v>
       </c>
       <c r="P124" s="55" t="n">
         <f aca="false">P123/12*P16</f>
-        <v>7.81638893295107</v>
+        <v>7.95737419752419</v>
       </c>
       <c r="Q124" s="55" t="n">
         <f aca="false">Q123/12*Q16</f>
-        <v>7.73309571955924</v>
+        <v>7.87257861317463</v>
       </c>
       <c r="R124" s="55" t="n">
         <f aca="false">R123/12*R16</f>
-        <v>7.68892330985916</v>
+        <v>7.82760945974521</v>
       </c>
       <c r="S124" s="55" t="n">
         <f aca="false">S123/12*S16</f>
-        <v>8.09982040869356</v>
+        <v>8.24591796513684</v>
       </c>
       <c r="T124" s="55" t="n">
         <f aca="false">T123/12*T16</f>
-        <v>8.1677833854383</v>
+        <v>8.31510679928705</v>
       </c>
       <c r="U124" s="55" t="n">
         <f aca="false">U123/12*U16</f>
-        <v>8.04887944313174</v>
+        <v>8.19405817048796</v>
       </c>
       <c r="V124" s="55" t="n">
         <f aca="false">V123/12*V16</f>
-        <v>8.73373978770529</v>
+        <v>8.89127143374348</v>
       </c>
       <c r="W124" s="55" t="n">
         <f aca="false">W123/12*W16</f>
-        <v>10.1826552147587</v>
+        <v>10.3663211443617</v>
       </c>
       <c r="X124" s="55" t="n">
         <f aca="false">X123/12*X16</f>
-        <v>10.5579144813754</v>
+        <v>10.7483490131349</v>
       </c>
       <c r="Y124" s="55" t="n">
         <f aca="false">Y123/12*Y16</f>
-        <v>11.2303204115971</v>
+        <v>11.4328832200821</v>
       </c>
       <c r="Z124" s="55" t="n">
         <f aca="false">Z123/12*Z16</f>
-        <v>12.7842204707762</v>
+        <v>13.014811184838</v>
       </c>
       <c r="AA124" s="55" t="n">
         <f aca="false">AA123/12*AA16</f>
-        <v>20.4081543686959</v>
+        <v>20.7762590098289</v>
       </c>
       <c r="AB124" s="55" t="n">
         <f aca="false">AB123/12*AB16</f>
-        <v>25.5562932265671</v>
+        <v>26.0172555447121</v>
       </c>
       <c r="AC124" s="55" t="n">
         <f aca="false">AC123/12*AC16</f>
-        <v>29.2768041472466</v>
+        <v>29.8048738241731</v>
       </c>
       <c r="AD124" s="55" t="n">
         <f aca="false">AD123/12*AD16</f>
-        <v>33.0169224163379</v>
+        <v>33.6124531124416</v>
       </c>
       <c r="AE124" s="55" t="n">
         <f aca="false">AE123/12*AE16</f>
-        <v>37.4680340739241</v>
+        <v>38.1438500731354</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20310,71 +20310,71 @@
       </c>
       <c r="O125" s="45" t="n">
         <f aca="false">O121*O124*Assumptions!$B$7*O7</f>
-        <v>1290.86061701442</v>
+        <v>1314.14404458921</v>
       </c>
       <c r="P125" s="45" t="n">
         <f aca="false">P121*P124*Assumptions!$B$7*P7</f>
-        <v>1332.59092408035</v>
+        <v>1356.62704684891</v>
       </c>
       <c r="Q125" s="45" t="n">
         <f aca="false">Q121*Q124*Assumptions!$B$7*Q7</f>
-        <v>1506.00368875973</v>
+        <v>1533.16768102383</v>
       </c>
       <c r="R125" s="45" t="n">
         <f aca="false">R121*R124*Assumptions!$B$7*R7</f>
-        <v>1683.84273700911</v>
+        <v>1714.21443624429</v>
       </c>
       <c r="S125" s="45" t="n">
         <f aca="false">S121*S124*Assumptions!$B$7*S7</f>
-        <v>1988.60253892586</v>
+        <v>2024.47123193566</v>
       </c>
       <c r="T125" s="45" t="n">
         <f aca="false">T121*T124*Assumptions!$B$7*T7</f>
-        <v>2296.21588633291</v>
+        <v>2337.63304290337</v>
       </c>
       <c r="U125" s="45" t="n">
         <f aca="false">U121*U124*Assumptions!$B$7*U7</f>
-        <v>2526.33748356013</v>
+        <v>2571.90537451028</v>
       </c>
       <c r="V125" s="45" t="n">
         <f aca="false">V121*V124*Assumptions!$B$7*V7</f>
-        <v>2992.27528275978</v>
+        <v>3046.24735682547</v>
       </c>
       <c r="W125" s="45" t="n">
         <f aca="false">W121*W124*Assumptions!$B$7*W7</f>
-        <v>4445.83925209261</v>
+        <v>4526.02945610914</v>
       </c>
       <c r="X125" s="45" t="n">
         <f aca="false">X121*X124*Assumptions!$B$7*X7</f>
-        <v>5569.46753140187</v>
+        <v>5669.92477069505</v>
       </c>
       <c r="Y125" s="45" t="n">
         <f aca="false">Y121*Y124*Assumptions!$B$7*Y7</f>
-        <v>6917.7214147467</v>
+        <v>7042.49729172357</v>
       </c>
       <c r="Z125" s="45" t="n">
         <f aca="false">Z121*Z124*Assumptions!$B$7*Z7</f>
-        <v>9308.26733031334</v>
+        <v>9476.16180735878</v>
       </c>
       <c r="AA125" s="45" t="n">
         <f aca="false">AA121*AA124*Assumptions!$B$7*AA7</f>
-        <v>837592.477532582</v>
+        <v>852700.246358104</v>
       </c>
       <c r="AB125" s="45" t="n">
         <f aca="false">AB121*AB124*Assumptions!$B$7*AB7</f>
-        <v>1938981.07395398</v>
+        <v>1973954.73788737</v>
       </c>
       <c r="AC125" s="45" t="n">
         <f aca="false">AC121*AC124*Assumptions!$B$7*AC7</f>
-        <v>3668771.77692431</v>
+        <v>3734945.90977069</v>
       </c>
       <c r="AD125" s="45" t="n">
         <f aca="false">AD121*AD124*Assumptions!$B$7*AD7</f>
-        <v>6176338.04522465</v>
+        <v>6287741.49007221</v>
       </c>
       <c r="AE125" s="45" t="n">
         <f aca="false">AE121*AE124*Assumptions!$B$7*AE7</f>
-        <v>9550463.58400505</v>
+        <v>9722726.58764228</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20434,71 +20434,71 @@
       </c>
       <c r="O126" s="55" t="n">
         <f aca="false">O125/Assumptions!$B$7</f>
-        <v>351.493701025028</v>
+        <v>357.833640459962</v>
       </c>
       <c r="P126" s="55" t="n">
         <f aca="false">P125/Assumptions!$B$7</f>
-        <v>362.85661649567</v>
+        <v>369.401510374107</v>
       </c>
       <c r="Q126" s="55" t="n">
         <f aca="false">Q125/Assumptions!$B$7</f>
-        <v>410.075885298769</v>
+        <v>417.472479516359</v>
       </c>
       <c r="R126" s="55" t="n">
         <f aca="false">R125/Assumptions!$B$7</f>
-        <v>458.500404903775</v>
+        <v>466.770438732278</v>
       </c>
       <c r="S126" s="55" t="n">
         <f aca="false">S125/Assumptions!$B$7</f>
-        <v>541.484694057415</v>
+        <v>551.251526735373</v>
       </c>
       <c r="T126" s="55" t="n">
         <f aca="false">T125/Assumptions!$B$7</f>
-        <v>625.245986748239</v>
+        <v>636.523633193565</v>
       </c>
       <c r="U126" s="55" t="n">
         <f aca="false">U125/Assumptions!$B$7</f>
-        <v>687.90673480194</v>
+        <v>700.314601636564</v>
       </c>
       <c r="V126" s="55" t="n">
         <f aca="false">V125/Assumptions!$B$7</f>
-        <v>814.778838055761</v>
+        <v>829.475114179843</v>
       </c>
       <c r="W126" s="55" t="n">
         <f aca="false">W125/Assumptions!$B$7</f>
-        <v>1210.57569832338</v>
+        <v>1232.41101595892</v>
       </c>
       <c r="X126" s="55" t="n">
         <f aca="false">X125/Assumptions!$B$7</f>
-        <v>1516.53302420745</v>
+        <v>1543.88693551942</v>
       </c>
       <c r="Y126" s="55" t="n">
         <f aca="false">Y125/Assumptions!$B$7</f>
-        <v>1883.65457174859</v>
+        <v>1917.63030407721</v>
       </c>
       <c r="Z126" s="55" t="n">
         <f aca="false">Z125/Assumptions!$B$7</f>
-        <v>2534.58606679737</v>
+        <v>2580.30273855923</v>
       </c>
       <c r="AA126" s="55" t="n">
         <f aca="false">AA125/Assumptions!$B$7</f>
-        <v>228071.471077626</v>
+        <v>232185.227054623</v>
       </c>
       <c r="AB126" s="55" t="n">
         <f aca="false">AB125/Assumptions!$B$7</f>
-        <v>527973.063023548</v>
+        <v>537496.184584715</v>
       </c>
       <c r="AC126" s="55" t="n">
         <f aca="false">AC125/Assumptions!$B$7</f>
-        <v>998984.826936504</v>
+        <v>1017003.65140114</v>
       </c>
       <c r="AD126" s="55" t="n">
         <f aca="false">AD125/Assumptions!$B$7</f>
-        <v>1681780.27099378</v>
+        <v>1712114.76925043</v>
       </c>
       <c r="AE126" s="55" t="n">
         <f aca="false">AE125/Assumptions!$B$7</f>
-        <v>2600534.67229545</v>
+        <v>2647440.86797611</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20510,119 +20510,119 @@
       </c>
       <c r="C127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,C122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>6.74931175595238</v>
+        <v>6.87105000513137</v>
       </c>
       <c r="D127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,D122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>10.2386161362443</v>
+        <v>10.4232914405585</v>
       </c>
       <c r="E127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,E122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>13.7861949012295</v>
+        <v>14.0348583636389</v>
       </c>
       <c r="F127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,F122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>16.6411056532318</v>
+        <v>16.9412635270832</v>
       </c>
       <c r="G127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,G122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>20.0705262429886</v>
+        <v>20.4325410399443</v>
       </c>
       <c r="H127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,H122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>24.0199930495845</v>
+        <v>24.4532449136088</v>
       </c>
       <c r="I127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,I122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>27.959562252422</v>
+        <v>28.463872659097</v>
       </c>
       <c r="J127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,J122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>31.8008891876595</v>
+        <v>32.3744861279144</v>
       </c>
       <c r="K127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,K122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>35.2463610472809</v>
+        <v>35.8821044295661</v>
       </c>
       <c r="L127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,L122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>37.4182749432431</v>
+        <v>38.093193430283</v>
       </c>
       <c r="M127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,M122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>40.2767747754025</v>
+        <v>41.0032524106087</v>
       </c>
       <c r="N127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,N122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>43.8015149387772</v>
+        <v>44.5915687891318</v>
       </c>
       <c r="O127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,O122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>42.3563948551855</v>
+        <v>43.1203828790986</v>
       </c>
       <c r="P127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,P122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>41.0081262232326</v>
+        <v>41.7477953434394</v>
       </c>
       <c r="Q127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,Q122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>41.3991166619261</v>
+        <v>42.1458381295683</v>
       </c>
       <c r="R127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,R122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>41.162639730988</v>
+        <v>41.9050958322366</v>
       </c>
       <c r="S127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,S122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>42.4951292156102</v>
+        <v>43.26161960995</v>
       </c>
       <c r="T127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,T122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>45.1070443353716</v>
+        <v>45.9206461960627</v>
       </c>
       <c r="U127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,U122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>47.98621713458</v>
+        <v>48.8517510245406</v>
       </c>
       <c r="V127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,V122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>50.9121577307106</v>
+        <v>51.8304672070205</v>
       </c>
       <c r="W127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,W122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>53.422573251716</v>
+        <v>54.3861634323835</v>
       </c>
       <c r="X127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,X122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>54.3052394017522</v>
+        <v>55.2847503511737</v>
       </c>
       <c r="Y127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,Y122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>56.1134036892385</v>
+        <v>57.1255287425192</v>
       </c>
       <c r="Z127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,Z122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>58.8346487204583</v>
+        <v>59.895857238493</v>
       </c>
       <c r="AA127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,AA122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>107.069924170051</v>
+        <v>109.001158876567</v>
       </c>
       <c r="AB127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,AB122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>134.079266963668</v>
+        <v>136.497672839936</v>
       </c>
       <c r="AC127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,AC122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>153.598661758233</v>
+        <v>156.369141598965</v>
       </c>
       <c r="AD127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,AD122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>173.220925105715</v>
+        <v>176.345334364917</v>
       </c>
       <c r="AE127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,AE122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
-        <v>196.573364480694</v>
+        <v>200.118984847985</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20882,119 +20882,119 @@
       </c>
       <c r="C130" s="55" t="n">
         <f aca="false">C112*Assumptions!$B$8</f>
-        <v>5.49878892974238</v>
+        <v>7.69830450163933</v>
       </c>
       <c r="D130" s="55" t="n">
         <f aca="false">D112*Assumptions!$B$8</f>
-        <v>10.4547966080716</v>
+        <v>14.6367152513003</v>
       </c>
       <c r="E130" s="55" t="n">
         <f aca="false">E112*Assumptions!$B$8</f>
-        <v>14.9492822928335</v>
+        <v>20.9289952099669</v>
       </c>
       <c r="F130" s="55" t="n">
         <f aca="false">F112*Assumptions!$B$8</f>
-        <v>20.4723581941557</v>
+        <v>28.6613014718179</v>
       </c>
       <c r="G130" s="55" t="n">
         <f aca="false">G112*Assumptions!$B$8</f>
-        <v>25.125132641001</v>
+        <v>35.1751856974014</v>
       </c>
       <c r="H130" s="55" t="n">
         <f aca="false">H112*Assumptions!$B$8</f>
-        <v>28.6797744833748</v>
+        <v>40.1516842767248</v>
       </c>
       <c r="I130" s="55" t="n">
         <f aca="false">I112*Assumptions!$B$8</f>
-        <v>31.8962969379098</v>
+        <v>44.6548157130737</v>
       </c>
       <c r="J130" s="55" t="n">
         <f aca="false">J112*Assumptions!$B$8</f>
-        <v>34.9540288915865</v>
+        <v>48.935640448221</v>
       </c>
       <c r="K130" s="55" t="n">
         <f aca="false">K112*Assumptions!$B$8</f>
-        <v>38.294137612691</v>
+        <v>53.6117926577674</v>
       </c>
       <c r="L130" s="55" t="n">
         <f aca="false">L112*Assumptions!$B$8</f>
-        <v>43.2017449201656</v>
+        <v>60.4824428882318</v>
       </c>
       <c r="M130" s="55" t="n">
         <f aca="false">M112*Assumptions!$B$8</f>
-        <v>47.3244464733693</v>
+        <v>66.254225062717</v>
       </c>
       <c r="N130" s="55" t="n">
         <f aca="false">N112*Assumptions!$B$8</f>
-        <v>50.4853332577934</v>
+        <v>70.6794665609107</v>
       </c>
       <c r="O130" s="55" t="n">
         <f aca="false">O112*Assumptions!$B$8</f>
-        <v>65.8942505902369</v>
+        <v>92.2519508263317</v>
       </c>
       <c r="P130" s="55" t="n">
         <f aca="false">P112*Assumptions!$B$8</f>
-        <v>79.9668885497403</v>
+        <v>111.953643969636</v>
       </c>
       <c r="Q130" s="55" t="n">
         <f aca="false">Q112*Assumptions!$B$8</f>
-        <v>92.8925795507775</v>
+        <v>130.049611371088</v>
       </c>
       <c r="R130" s="55" t="n">
         <f aca="false">R112*Assumptions!$B$8</f>
-        <v>109.684235697281</v>
+        <v>153.557929976194</v>
       </c>
       <c r="S130" s="55" t="n">
         <f aca="false">S112*Assumptions!$B$8</f>
-        <v>123.963352665241</v>
+        <v>173.548693731337</v>
       </c>
       <c r="T130" s="55" t="n">
         <f aca="false">T112*Assumptions!$B$8</f>
-        <v>134.773106455439</v>
+        <v>188.682349037615</v>
       </c>
       <c r="U130" s="55" t="n">
         <f aca="false">U112*Assumptions!$B$8</f>
-        <v>144.65548923801</v>
+        <v>202.517684933215</v>
       </c>
       <c r="V130" s="55" t="n">
         <f aca="false">V112*Assumptions!$B$8</f>
-        <v>154.211963342927</v>
+        <v>215.896748680098</v>
       </c>
       <c r="W130" s="55" t="n">
         <f aca="false">W112*Assumptions!$B$8</f>
-        <v>165.026151308834</v>
+        <v>231.036611832367</v>
       </c>
       <c r="X130" s="55" t="n">
         <f aca="false">X112*Assumptions!$B$8</f>
-        <v>181.859637355701</v>
+        <v>254.603492297981</v>
       </c>
       <c r="Y130" s="55" t="n">
         <f aca="false">Y112*Assumptions!$B$8</f>
-        <v>196.245425198531</v>
+        <v>274.743595277944</v>
       </c>
       <c r="Z130" s="55" t="n">
         <f aca="false">Z112*Assumptions!$B$8</f>
-        <v>207.367357408746</v>
+        <v>290.314300372244</v>
       </c>
       <c r="AA130" s="55" t="n">
         <f aca="false">AA112*Assumptions!$B$8</f>
-        <v>4608.20433196144</v>
+        <v>6451.48606474602</v>
       </c>
       <c r="AB130" s="55" t="n">
         <f aca="false">AB112*Assumptions!$B$8</f>
-        <v>7566.76224595452</v>
+        <v>10593.4671443363</v>
       </c>
       <c r="AC130" s="55" t="n">
         <f aca="false">AC112*Assumptions!$B$8</f>
-        <v>11305.3746245143</v>
+        <v>15827.52447432</v>
       </c>
       <c r="AD130" s="55" t="n">
         <f aca="false">AD112*Assumptions!$B$8</f>
-        <v>15140.2611624558</v>
+        <v>21196.3656274381</v>
       </c>
       <c r="AE130" s="55" t="n">
         <f aca="false">AE112*Assumptions!$B$8</f>
-        <v>18127.613525129</v>
+        <v>25378.6589351806</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21054,71 +21054,71 @@
       </c>
       <c r="O131" s="55" t="n">
         <f aca="false">O126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1.77152825316614</v>
+        <v>1.80348154791821</v>
       </c>
       <c r="P131" s="55" t="n">
         <f aca="false">P126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1.82879734713818</v>
+        <v>1.8617836122855</v>
       </c>
       <c r="Q131" s="55" t="n">
         <f aca="false">Q126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>2.0667824619058</v>
+        <v>2.10406129676245</v>
       </c>
       <c r="R131" s="55" t="n">
         <f aca="false">R126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>2.31084204071503</v>
+        <v>2.35252301121068</v>
       </c>
       <c r="S131" s="55" t="n">
         <f aca="false">S126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>2.72908285804937</v>
+        <v>2.77830769474628</v>
       </c>
       <c r="T131" s="55" t="n">
         <f aca="false">T126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3.15123977321112</v>
+        <v>3.20807911129557</v>
       </c>
       <c r="U131" s="55" t="n">
         <f aca="false">U126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3.46704994340178</v>
+        <v>3.52958559224828</v>
       </c>
       <c r="V131" s="55" t="n">
         <f aca="false">V126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>4.10648534380103</v>
+        <v>4.18055457546641</v>
       </c>
       <c r="W131" s="55" t="n">
         <f aca="false">W126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>6.10130151954983</v>
+        <v>6.21135152043296</v>
       </c>
       <c r="X131" s="55" t="n">
         <f aca="false">X126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>7.64332644200556</v>
+        <v>7.78119015501786</v>
       </c>
       <c r="Y131" s="55" t="n">
         <f aca="false">Y126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>9.4936190416129</v>
+        <v>9.66485673254916</v>
       </c>
       <c r="Z131" s="55" t="n">
         <f aca="false">Z126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>12.7743137766587</v>
+        <v>13.0047258023385</v>
       </c>
       <c r="AA131" s="55" t="n">
         <f aca="false">AA126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1149.48021423124</v>
+        <v>1170.2135443553</v>
       </c>
       <c r="AB131" s="55" t="n">
         <f aca="false">AB126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>2660.98423763868</v>
+        <v>2708.98077030696</v>
       </c>
       <c r="AC131" s="55" t="n">
         <f aca="false">AC126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>5034.88352775998</v>
+        <v>5125.69840306175</v>
       </c>
       <c r="AD131" s="55" t="n">
         <f aca="false">AD126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>8476.17256580865</v>
+        <v>8629.05843702217</v>
       </c>
       <c r="AE131" s="55" t="n">
         <f aca="false">AE126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>13106.6947483691</v>
+        <v>13343.1019745996</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21302,71 +21302,71 @@
       </c>
       <c r="O133" s="55" t="n">
         <f aca="false">IF(O2&gt;=Assumptions!$B$52,O126*O17*Assumptions!$B$17+O121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
-        <v>134.813081275744</v>
+        <v>134.84561832341</v>
       </c>
       <c r="P133" s="55" t="n">
         <f aca="false">IF(P2&gt;=Assumptions!$B$52,P126*P17*Assumptions!$B$17+P121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
-        <v>157.868060910983</v>
+        <v>157.901649800321</v>
       </c>
       <c r="Q133" s="55" t="n">
         <f aca="false">IF(Q2&gt;=Assumptions!$B$52,Q126*Q17*Assumptions!$B$17+Q121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
-        <v>180.310758333176</v>
+        <v>180.348718212934</v>
       </c>
       <c r="R133" s="55" t="n">
         <f aca="false">IF(R2&gt;=Assumptions!$B$52,R126*R17*Assumptions!$B$17+R121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
-        <v>202.90461592888</v>
+        <v>202.949887862492</v>
       </c>
       <c r="S133" s="55" t="n">
         <f aca="false">IF(S2&gt;=Assumptions!$B$52,S126*S17*Assumptions!$B$17+S121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
-        <v>227.807939078724</v>
+        <v>227.86474641747</v>
       </c>
       <c r="T133" s="55" t="n">
         <f aca="false">IF(T2&gt;=Assumptions!$B$52,T126*T17*Assumptions!$B$17+T121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
-        <v>263.134787665251</v>
+        <v>263.240896841869</v>
       </c>
       <c r="U133" s="55" t="n">
         <f aca="false">IF(U2&gt;=Assumptions!$B$52,U126*U17*Assumptions!$B$17+U121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
-        <v>294.275136616193</v>
+        <v>294.402492834269</v>
       </c>
       <c r="V133" s="55" t="n">
         <f aca="false">IF(V2&gt;=Assumptions!$B$52,V126*V17*Assumptions!$B$17+V121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
-        <v>321.315552581625</v>
+        <v>321.456341058305</v>
       </c>
       <c r="W133" s="55" t="n">
         <f aca="false">IF(W2&gt;=Assumptions!$B$52,W126*W17*Assumptions!$B$17+W121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
-        <v>406.979362723077</v>
+        <v>407.113835320742</v>
       </c>
       <c r="X133" s="55" t="n">
         <f aca="false">IF(X2&gt;=Assumptions!$B$52,X126*X17*Assumptions!$B$17+X121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
-        <v>493.605528925367</v>
+        <v>493.802064197585</v>
       </c>
       <c r="Y133" s="55" t="n">
         <f aca="false">IF(Y2&gt;=Assumptions!$B$52,Y126*Y17*Assumptions!$B$17+Y121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
-        <v>576.554482569666</v>
+        <v>576.786970599688</v>
       </c>
       <c r="Z133" s="55" t="n">
         <f aca="false">IF(Z2&gt;=Assumptions!$B$52,Z126*Z17*Assumptions!$B$17+Z121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
-        <v>680.136490722126</v>
+        <v>680.386753559243</v>
       </c>
       <c r="AA133" s="55" t="n">
         <f aca="false">IF(AA2&gt;=Assumptions!$B$52,AA126*AA17*Assumptions!$B$17+AA121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
-        <v>39106.8782877433</v>
+        <v>39134.8518283869</v>
       </c>
       <c r="AB133" s="55" t="n">
         <f aca="false">IF(AB2&gt;=Assumptions!$B$52,AB126*AB17*Assumptions!$B$17+AB121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
-        <v>73016.81904228</v>
+        <v>73081.5762688959</v>
       </c>
       <c r="AC133" s="55" t="n">
         <f aca="false">IF(AC2&gt;=Assumptions!$B$52,AC126*AC17*Assumptions!$B$17+AC121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
-        <v>121462.415627096</v>
+        <v>121584.943633455</v>
       </c>
       <c r="AD133" s="55" t="n">
         <f aca="false">IF(AD2&gt;=Assumptions!$B$52,AD126*AD17*Assumptions!$B$17+AD121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
-        <v>182612.814747992</v>
+        <v>182819.089336138</v>
       </c>
       <c r="AE133" s="55" t="n">
         <f aca="false">IF(AE2&gt;=Assumptions!$B$52,AE126*AE17*Assumptions!$B$17+AE121*(Assumptions!$B$148*MAX(0,Assumptions!$B$152-Assumptions!$B$18)+Assumptions!$B$149*MAX(0,Assumptions!$B$153-Assumptions!$B$18)+Assumptions!$B$150*MAX(0,Assumptions!$B$154-Assumptions!$B$18)+Assumptions!$B$151*MAX(0,Assumptions!$B$155-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE121*(Assumptions!$B$146*Assumptions!$B$20+Assumptions!$B$147*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
-        <v>250929.391590982</v>
+        <v>251248.353721611</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21426,71 +21426,71 @@
       </c>
       <c r="O134" s="55" t="n">
         <f aca="false">IF(O2&gt;=Assumptions!$B$53,O121*O122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>766.89534769097</v>
+        <v>780.727942821736</v>
       </c>
       <c r="P134" s="55" t="n">
         <f aca="false">IF(P2&gt;=Assumptions!$B$53,P121*P122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>870.855879589608</v>
+        <v>886.563624897856</v>
       </c>
       <c r="Q134" s="55" t="n">
         <f aca="false">IF(Q2&gt;=Assumptions!$B$53,Q121*Q122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>1004.26747420107</v>
+        <v>1022.38158248904</v>
       </c>
       <c r="R134" s="55" t="n">
         <f aca="false">IF(R2&gt;=Assumptions!$B$53,R121*R122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>1122.85813445822</v>
+        <v>1143.11127852803</v>
       </c>
       <c r="S134" s="55" t="n">
         <f aca="false">IF(S2&gt;=Assumptions!$B$53,S121*S122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>1299.5632657378</v>
+        <v>1323.0036641649</v>
       </c>
       <c r="T134" s="55" t="n">
         <f aca="false">IF(T2&gt;=Assumptions!$B$53,T121*T122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>1579.56880862713</v>
+        <v>1608.05970491006</v>
       </c>
       <c r="U134" s="55" t="n">
         <f aca="false">IF(U2&gt;=Assumptions!$B$53,U121*U122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>1876.10927673256</v>
+        <v>1909.94891355427</v>
       </c>
       <c r="V134" s="55" t="n">
         <f aca="false">IF(V2&gt;=Assumptions!$B$53,V121*V122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>2172.74356814869</v>
+        <v>2211.93363781291</v>
       </c>
       <c r="W134" s="55" t="n">
         <f aca="false">IF(W2&gt;=Assumptions!$B$53,W121*W122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>2905.38167597611</v>
+        <v>2957.78643830141</v>
       </c>
       <c r="X134" s="55" t="n">
         <f aca="false">IF(X2&gt;=Assumptions!$B$53,X121*X122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>3568.31299813518</v>
+        <v>3632.67514239862</v>
       </c>
       <c r="Y134" s="55" t="n">
         <f aca="false">IF(Y2&gt;=Assumptions!$B$53,Y121*Y122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>4305.49616399678</v>
+        <v>4383.15498074792</v>
       </c>
       <c r="Z134" s="55" t="n">
         <f aca="false">IF(Z2&gt;=Assumptions!$B$53,Z121*Z122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>5335.97066694183</v>
+        <v>5432.21629170365</v>
       </c>
       <c r="AA134" s="55" t="n">
         <f aca="false">IF(AA2&gt;=Assumptions!$B$53,AA121*AA122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>45614.2942155252</v>
+        <v>46437.0454109246</v>
       </c>
       <c r="AB134" s="55" t="n">
         <f aca="false">IF(AB2&gt;=Assumptions!$B$53,AB121*AB122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>105594.61260471</v>
+        <v>107499.236916943</v>
       </c>
       <c r="AC134" s="55" t="n">
         <f aca="false">IF(AC2&gt;=Assumptions!$B$53,AC121*AC122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>199796.965387301</v>
+        <v>203400.730280228</v>
       </c>
       <c r="AD134" s="55" t="n">
         <f aca="false">IF(AD2&gt;=Assumptions!$B$53,AD121*AD122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>336356.054198756</v>
+        <v>342422.953850086</v>
       </c>
       <c r="AE134" s="55" t="n">
         <f aca="false">IF(AE2&gt;=Assumptions!$B$53,AE121*AE122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
-        <v>520106.93445909</v>
+        <v>529488.173595223</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21550,71 +21550,71 @@
       </c>
       <c r="O135" s="55" t="n">
         <f aca="false">IF(O2&gt;=Assumptions!$B$53,(O134*Assumptions!$B$29*Assumptions!$B$30+O121*O123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
-        <v>1.82137645076605</v>
+        <v>1.85422886420162</v>
       </c>
       <c r="P135" s="55" t="n">
         <f aca="false">IF(P2&gt;=Assumptions!$B$53,(P134*Assumptions!$B$29*Assumptions!$B$30+P121*P123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
-        <v>2.06828271402532</v>
+        <v>2.10558860913241</v>
       </c>
       <c r="Q135" s="55" t="n">
         <f aca="false">IF(Q2&gt;=Assumptions!$B$53,(Q134*Assumptions!$B$29*Assumptions!$B$30+Q121*Q123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
-        <v>2.38513525122753</v>
+        <v>2.42815625841148</v>
       </c>
       <c r="R135" s="55" t="n">
         <f aca="false">IF(R2&gt;=Assumptions!$B$53,(R134*Assumptions!$B$29*Assumptions!$B$30+R121*R123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
-        <v>2.66678806933828</v>
+        <v>2.71488928650407</v>
       </c>
       <c r="S135" s="55" t="n">
         <f aca="false">IF(S2&gt;=Assumptions!$B$53,(S134*Assumptions!$B$29*Assumptions!$B$30+S121*S123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
-        <v>3.08646275612727</v>
+        <v>3.14213370239163</v>
       </c>
       <c r="T135" s="55" t="n">
         <f aca="false">IF(T2&gt;=Assumptions!$B$53,(T134*Assumptions!$B$29*Assumptions!$B$30+T121*T123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
-        <v>3.75147592048943</v>
+        <v>3.81914179916139</v>
       </c>
       <c r="U135" s="55" t="n">
         <f aca="false">IF(U2&gt;=Assumptions!$B$53,(U134*Assumptions!$B$29*Assumptions!$B$30+U121*U123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
-        <v>4.45575953223984</v>
+        <v>4.53612866969138</v>
       </c>
       <c r="V135" s="55" t="n">
         <f aca="false">IF(V2&gt;=Assumptions!$B$53,(V134*Assumptions!$B$29*Assumptions!$B$30+V121*V123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
-        <v>5.16026597435315</v>
+        <v>5.25334238980567</v>
       </c>
       <c r="W135" s="55" t="n">
         <f aca="false">IF(W2&gt;=Assumptions!$B$53,(W134*Assumptions!$B$29*Assumptions!$B$30+W121*W123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
-        <v>6.90028148044326</v>
+        <v>7.02474279096585</v>
       </c>
       <c r="X135" s="55" t="n">
         <f aca="false">IF(X2&gt;=Assumptions!$B$53,(X134*Assumptions!$B$29*Assumptions!$B$30+X121*X123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
-        <v>8.47474337057105</v>
+        <v>8.62760346319673</v>
       </c>
       <c r="Y135" s="55" t="n">
         <f aca="false">IF(Y2&gt;=Assumptions!$B$53,(Y134*Assumptions!$B$29*Assumptions!$B$30+Y121*Y123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
-        <v>10.2255533894924</v>
+        <v>10.4099930792763</v>
       </c>
       <c r="Z135" s="55" t="n">
         <f aca="false">IF(Z2&gt;=Assumptions!$B$53,(Z134*Assumptions!$B$29*Assumptions!$B$30+Z121*Z123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
-        <v>12.6729303339869</v>
+        <v>12.9015136927962</v>
       </c>
       <c r="AA135" s="55" t="n">
         <f aca="false">IF(AA2&gt;=Assumptions!$B$53,(AA134*Assumptions!$B$29*Assumptions!$B$30+AA121*AA123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
-        <v>1300.00738514247</v>
+        <v>1323.45579421135</v>
       </c>
       <c r="AB135" s="55" t="n">
         <f aca="false">IF(AB2&gt;=Assumptions!$B$53,(AB134*Assumptions!$B$29*Assumptions!$B$30+AB121*AB123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
-        <v>3009.44645923422</v>
+        <v>3063.72825213288</v>
       </c>
       <c r="AC135" s="55" t="n">
         <f aca="false">IF(AC2&gt;=Assumptions!$B$53,(AC134*Assumptions!$B$29*Assumptions!$B$30+AC121*AC123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
-        <v>5694.21351353807</v>
+        <v>5796.92081298651</v>
       </c>
       <c r="AD135" s="55" t="n">
         <f aca="false">IF(AD2&gt;=Assumptions!$B$53,(AD134*Assumptions!$B$29*Assumptions!$B$30+AD121*AD123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
-        <v>9586.14754466454</v>
+        <v>9759.05418472745</v>
       </c>
       <c r="AE135" s="55" t="n">
         <f aca="false">IF(AE2&gt;=Assumptions!$B$53,(AE134*Assumptions!$B$29*Assumptions!$B$30+AE121*AE123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
-        <v>14823.0476320841</v>
+        <v>15090.4129474638</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21750,119 +21750,119 @@
       </c>
       <c r="C137" s="57" t="n">
         <f aca="false">C129+C130+C131+C132+C133+C135</f>
-        <v>121.943730971346</v>
+        <v>124.143246543243</v>
       </c>
       <c r="D137" s="57" t="n">
         <f aca="false">D129+D130+D131+D132+D133+D135</f>
-        <v>231.850489484883</v>
+        <v>236.032408128112</v>
       </c>
       <c r="E137" s="57" t="n">
         <f aca="false">E129+E130+E131+E132+E133+E135</f>
-        <v>331.522319082249</v>
+        <v>337.502031999382</v>
       </c>
       <c r="F137" s="57" t="n">
         <f aca="false">F129+F130+F131+F132+F133+F135</f>
-        <v>454.004649364511</v>
+        <v>462.193592642173</v>
       </c>
       <c r="G137" s="57" t="n">
         <f aca="false">G129+G130+G131+G132+G133+G135</f>
-        <v>557.186765038669</v>
+        <v>567.236818095069</v>
       </c>
       <c r="H137" s="57" t="n">
         <f aca="false">H129+H130+H131+H132+H133+H135</f>
-        <v>636.016175307783</v>
+        <v>647.488085101133</v>
       </c>
       <c r="I137" s="57" t="n">
         <f aca="false">I129+I130+I131+I132+I133+I135</f>
-        <v>1607.94861622286</v>
+        <v>1620.70713499803</v>
       </c>
       <c r="J137" s="57" t="n">
         <f aca="false">J129+J130+J131+J132+J133+J135</f>
-        <v>1762.09428000527</v>
+        <v>1776.0758915619</v>
       </c>
       <c r="K137" s="57" t="n">
         <f aca="false">K129+K130+K131+K132+K133+K135</f>
-        <v>1930.47505494566</v>
+        <v>1945.79270999073</v>
       </c>
       <c r="L137" s="57" t="n">
         <f aca="false">L129+L130+L131+L132+L133+L135</f>
-        <v>2177.87619979893</v>
+        <v>2195.156897767</v>
       </c>
       <c r="M137" s="57" t="n">
         <f aca="false">M129+M130+M131+M132+M133+M135</f>
-        <v>2385.70886045162</v>
+        <v>2404.63863904096</v>
       </c>
       <c r="N137" s="57" t="n">
         <f aca="false">N129+N130+N131+N132+N133+N135</f>
-        <v>2545.05474128994</v>
+        <v>2565.24887459305</v>
       </c>
       <c r="O137" s="57" t="n">
         <f aca="false">O129+O130+O131+O132+O133+O135</f>
-        <v>3460.25144220515</v>
+        <v>3486.7064851971</v>
       </c>
       <c r="P137" s="57" t="n">
         <f aca="false">P129+P130+P131+P132+P133+P135</f>
-        <v>4193.03711080317</v>
+        <v>4225.12774727266</v>
       </c>
       <c r="Q137" s="57" t="n">
         <f aca="false">Q129+Q130+Q131+Q132+Q133+Q135</f>
-        <v>4867.64153928256</v>
+        <v>4904.91683082467</v>
       </c>
       <c r="R137" s="57" t="n">
         <f aca="false">R129+R130+R131+R132+R133+R135</f>
-        <v>5737.25812795482</v>
+        <v>5781.26687635501</v>
       </c>
       <c r="S137" s="57" t="n">
         <f aca="false">S129+S130+S131+S132+S133+S135</f>
-        <v>6482.83485140532</v>
+        <v>6532.58189559313</v>
       </c>
       <c r="T137" s="57" t="n">
         <f aca="false">T129+T130+T131+T132+T133+T135</f>
-        <v>7064.18763467139</v>
+        <v>7118.32749164694</v>
       </c>
       <c r="U137" s="57" t="n">
         <f aca="false">U129+U130+U131+U132+U133+U135</f>
-        <v>7594.53643297271</v>
+        <v>7652.66888967229</v>
       </c>
       <c r="V137" s="57" t="n">
         <f aca="false">V129+V130+V131+V132+V133+V135</f>
-        <v>8104.67951477559</v>
+        <v>8166.67223423656</v>
       </c>
       <c r="W137" s="57" t="n">
         <f aca="false">W129+W130+W131+W132+W133+W135</f>
-        <v>8739.24045582133</v>
+        <v>8805.61990025393</v>
       </c>
       <c r="X137" s="57" t="n">
         <f aca="false">X129+X130+X131+X132+X133+X135</f>
-        <v>9677.58884661063</v>
+        <v>9750.81996063076</v>
       </c>
       <c r="Y137" s="57" t="n">
         <f aca="false">Y129+Y130+Y131+Y132+Y133+Y135</f>
-        <v>10489.351854715</v>
+        <v>10568.4381902051</v>
       </c>
       <c r="Z137" s="57" t="n">
         <f aca="false">Z129+Z130+Z131+Z132+Z133+Z135</f>
-        <v>11159.3381642031</v>
+        <v>11242.9943653882</v>
       </c>
       <c r="AA137" s="57" t="n">
         <f aca="false">AA129+AA130+AA131+AA132+AA133+AA135</f>
-        <v>273864.078386585</v>
+        <v>275779.515399206</v>
       </c>
       <c r="AB137" s="57" t="n">
         <f aca="false">AB129+AB130+AB131+AB132+AB133+AB135</f>
-        <v>460141.087667566</v>
+        <v>463334.828118131</v>
       </c>
       <c r="AC137" s="57" t="n">
         <f aca="false">AC129+AC130+AC131+AC132+AC133+AC135</f>
-        <v>702115.398151262</v>
+        <v>706953.598182178</v>
       </c>
       <c r="AD137" s="57" t="n">
         <f aca="false">AD129+AD130+AD131+AD132+AD133+AD135</f>
-        <v>963922.418165796</v>
+        <v>970510.5897302</v>
       </c>
       <c r="AE137" s="57" t="n">
         <f aca="false">AE129+AE130+AE131+AE132+AE133+AE135</f>
-        <v>1192704.12167941</v>
+        <v>1200777.9017617</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22817,119 +22817,119 @@
       </c>
       <c r="C150" s="45" t="n">
         <f aca="false">C40+C78+C116</f>
-        <v>24.0747982689045</v>
+        <v>24.3658572106377</v>
       </c>
       <c r="D150" s="45" t="n">
         <f aca="false">D40+D78+D116</f>
-        <v>69.4403603660965</v>
+        <v>70.2798421107306</v>
       </c>
       <c r="E150" s="45" t="n">
         <f aca="false">E40+E78+E116</f>
-        <v>133.702153253851</v>
+        <v>135.318442800709</v>
       </c>
       <c r="F150" s="45" t="n">
         <f aca="false">F40+F78+F116</f>
-        <v>221.026803651932</v>
+        <v>223.698606797158</v>
       </c>
       <c r="G150" s="45" t="n">
         <f aca="false">G40+G78+G116</f>
-        <v>327.177295839109</v>
+        <v>331.132068562935</v>
       </c>
       <c r="H150" s="45" t="n">
         <f aca="false">H40+H78+H116</f>
-        <v>446.976081240084</v>
+        <v>452.378683758779</v>
       </c>
       <c r="I150" s="45" t="n">
         <f aca="false">I40+I78+I116</f>
-        <v>578.662212389927</v>
+        <v>585.656202931115</v>
       </c>
       <c r="J150" s="45" t="n">
         <f aca="false">J40+J78+J116</f>
-        <v>721.289316691805</v>
+        <v>730.00679572793</v>
       </c>
       <c r="K150" s="45" t="n">
         <f aca="false">K40+K78+K116</f>
-        <v>875.867918229026</v>
+        <v>886.453164986833</v>
       </c>
       <c r="L150" s="45" t="n">
         <f aca="false">L40+L78+L116</f>
-        <v>1049.05641251019</v>
+        <v>1061.73408293405</v>
       </c>
       <c r="M150" s="45" t="n">
         <f aca="false">M40+M78+M116</f>
-        <v>1237.02063289191</v>
+        <v>1251.96903035295</v>
       </c>
       <c r="N150" s="45" t="n">
         <f aca="false">N40+N78+N116</f>
-        <v>1435.20489652243</v>
+        <v>1452.54727924063</v>
       </c>
       <c r="O150" s="45" t="n">
         <f aca="false">O40+O78+O116</f>
-        <v>1681.90364909594</v>
+        <v>1702.15225951658</v>
       </c>
       <c r="P150" s="45" t="n">
         <f aca="false">P40+P78+P116</f>
-        <v>1986.81170610076</v>
+        <v>2010.60249465988</v>
       </c>
       <c r="Q150" s="45" t="n">
         <f aca="false">Q40+Q78+Q116</f>
-        <v>2343.72674647053</v>
+        <v>2371.62652854453</v>
       </c>
       <c r="R150" s="45" t="n">
         <f aca="false">R40+R78+R116</f>
-        <v>2768.77712837287</v>
+        <v>2801.53201832454</v>
       </c>
       <c r="S150" s="45" t="n">
         <f aca="false">S40+S78+S116</f>
-        <v>3249.51632430253</v>
+        <v>3287.73372809423</v>
       </c>
       <c r="T150" s="45" t="n">
         <f aca="false">T40+T78+T116</f>
-        <v>3769.44011068024</v>
+        <v>3813.54394243302</v>
       </c>
       <c r="U150" s="45" t="n">
         <f aca="false">U40+U78+U116</f>
-        <v>4323.6112969102</v>
+        <v>4373.97065046887</v>
       </c>
       <c r="V150" s="45" t="n">
         <f aca="false">V40+V78+V116</f>
-        <v>4909.84958594167</v>
+        <v>4966.80936331324</v>
       </c>
       <c r="W150" s="45" t="n">
         <f aca="false">W40+W78+W116</f>
-        <v>5533.08417106017</v>
+        <v>5597.04385188781</v>
       </c>
       <c r="X150" s="45" t="n">
         <f aca="false">X40+X78+X116</f>
-        <v>6219.46943995685</v>
+        <v>6291.11788452774</v>
       </c>
       <c r="Y150" s="45" t="n">
         <f aca="false">Y40+Y78+Y116</f>
-        <v>6956.81016218823</v>
+        <v>7036.70061218333</v>
       </c>
       <c r="Z150" s="45" t="n">
         <f aca="false">Z40+Z78+Z116</f>
-        <v>7729.43986038715</v>
+        <v>7817.95188429086</v>
       </c>
       <c r="AA150" s="45" t="n">
         <f aca="false">AA40+AA78+AA116</f>
-        <v>25272.7485111844</v>
+        <v>25548.6925371541</v>
       </c>
       <c r="AB150" s="45" t="n">
         <f aca="false">AB40+AB78+AB116</f>
-        <v>49092.720090644</v>
+        <v>49617.6094811976</v>
       </c>
       <c r="AC150" s="45" t="n">
         <f aca="false">AC40+AC78+AC116</f>
-        <v>79119.3497704202</v>
+        <v>79950.4296637671</v>
       </c>
       <c r="AD150" s="45" t="n">
         <f aca="false">AD40+AD78+AD116</f>
-        <v>112404.241501835</v>
+        <v>113565.364993544</v>
       </c>
       <c r="AE150" s="45" t="n">
         <f aca="false">AE40+AE78+AE116</f>
-        <v>144257.963038907</v>
+        <v>145717.396509327</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22941,119 +22941,119 @@
       </c>
       <c r="C151" s="45" t="n">
         <f aca="false">C41+C79+C117</f>
-        <v>24.0747982689045</v>
+        <v>24.3658572106377</v>
       </c>
       <c r="D151" s="45" t="n">
         <f aca="false">D41+D79+D117</f>
-        <v>69.6811083487855</v>
+        <v>70.5235006828369</v>
       </c>
       <c r="E151" s="45" t="n">
         <f aca="false">E41+E79+E117</f>
-        <v>134.635559850201</v>
+        <v>136.263133707291</v>
       </c>
       <c r="F151" s="45" t="n">
         <f aca="false">F41+F79+F117</f>
-        <v>223.290327613928</v>
+        <v>225.989494497053</v>
       </c>
       <c r="G151" s="45" t="n">
         <f aca="false">G41+G79+G117</f>
-        <v>331.633955829641</v>
+        <v>335.642603211439</v>
       </c>
       <c r="H151" s="45" t="n">
         <f aca="false">H41+H79+H117</f>
-        <v>454.669935749417</v>
+        <v>460.165542642401</v>
       </c>
       <c r="I151" s="45" t="n">
         <f aca="false">I41+I79+I117</f>
-        <v>590.764729917641</v>
+        <v>597.905012284045</v>
       </c>
       <c r="J151" s="45" t="n">
         <f aca="false">J41+J79+J117</f>
-        <v>739.080275991002</v>
+        <v>748.012799950017</v>
       </c>
       <c r="K151" s="45" t="n">
         <f aca="false">K41+K79+K117</f>
-        <v>900.724789814295</v>
+        <v>911.610479623743</v>
       </c>
       <c r="L151" s="45" t="n">
         <f aca="false">L41+L79+L117</f>
-        <v>1082.46425576019</v>
+        <v>1095.5457110564</v>
       </c>
       <c r="M151" s="45" t="n">
         <f aca="false">M41+M79+M117</f>
-        <v>1280.63590886118</v>
+        <v>1296.11144565703</v>
       </c>
       <c r="N151" s="45" t="n">
         <f aca="false">N41+N79+N117</f>
-        <v>1490.81461636238</v>
+        <v>1508.82908063099</v>
       </c>
       <c r="O151" s="45" t="n">
         <f aca="false">O41+O79+O117</f>
-        <v>1751.39464475643</v>
+        <v>1772.48306846485</v>
       </c>
       <c r="P151" s="45" t="n">
         <f aca="false">P41+P79+P117</f>
-        <v>2072.53545534729</v>
+        <v>2097.36145368935</v>
       </c>
       <c r="Q151" s="45" t="n">
         <f aca="false">Q41+Q79+Q117</f>
-        <v>2448.59272766643</v>
+        <v>2477.7568547712</v>
       </c>
       <c r="R151" s="45" t="n">
         <f aca="false">R41+R79+R117</f>
-        <v>2896.19191277428</v>
+        <v>2930.47942289074</v>
       </c>
       <c r="S151" s="45" t="n">
         <f aca="false">S41+S79+S117</f>
-        <v>3403.53166083096</v>
+        <v>3443.59613995374</v>
       </c>
       <c r="T151" s="45" t="n">
         <f aca="false">T41+T79+T117</f>
-        <v>3954.62023523261</v>
+        <v>4000.93733819849</v>
       </c>
       <c r="U151" s="45" t="n">
         <f aca="false">U41+U79+U117</f>
-        <v>4544.86558963965</v>
+        <v>4597.85985512937</v>
       </c>
       <c r="V151" s="45" t="n">
         <f aca="false">V41+V79+V117</f>
-        <v>5172.3797393605</v>
+        <v>5232.45463344904</v>
       </c>
       <c r="W151" s="45" t="n">
         <f aca="false">W41+W79+W117</f>
-        <v>5842.36225471787</v>
+        <v>5909.97870084749</v>
       </c>
       <c r="X151" s="45" t="n">
         <f aca="false">X41+X79+X117</f>
-        <v>6581.29721577193</v>
+        <v>6657.20906528008</v>
       </c>
       <c r="Y151" s="45" t="n">
         <f aca="false">Y41+Y79+Y117</f>
-        <v>7377.55427751002</v>
+        <v>7462.3858960336</v>
       </c>
       <c r="Z151" s="45" t="n">
         <f aca="false">Z41+Z79+Z117</f>
-        <v>8215.89958372056</v>
+        <v>8310.10632523785</v>
       </c>
       <c r="AA151" s="45" t="n">
         <f aca="false">AA41+AA79+AA117</f>
-        <v>26628.2849358229</v>
+        <v>26919.8579208016</v>
       </c>
       <c r="AB151" s="45" t="n">
         <f aca="false">AB41+AB79+AB117</f>
-        <v>53309.7139526035</v>
+        <v>53881.3629482092</v>
       </c>
       <c r="AC151" s="45" t="n">
         <f aca="false">AC41+AC79+AC117</f>
-        <v>88675.2704971467</v>
+        <v>89609.9457199556</v>
       </c>
       <c r="AD151" s="45" t="n">
         <f aca="false">AD41+AD79+AD117</f>
-        <v>130160.282221264</v>
+        <v>131510.629369433</v>
       </c>
       <c r="AE151" s="45" t="n">
         <f aca="false">AE41+AE79+AE117</f>
-        <v>173016.451947087</v>
+        <v>174777.77159115</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23065,119 +23065,119 @@
       </c>
       <c r="C152" s="54" t="n">
         <f aca="false">C37+C75+C113</f>
-        <v>24.0747982689045</v>
+        <v>24.3658572106377</v>
       </c>
       <c r="D152" s="54" t="n">
         <f aca="false">D37+D75+D113</f>
-        <v>45.776229001286</v>
+        <v>46.3296166791294</v>
       </c>
       <c r="E152" s="54" t="n">
         <f aca="false">E37+E75+E113</f>
-        <v>65.4595142471515</v>
+        <v>66.2508016268667</v>
       </c>
       <c r="F152" s="54" t="n">
         <f aca="false">F37+F75+F113</f>
-        <v>89.6506321360029</v>
+        <v>90.7342640023843</v>
       </c>
       <c r="G152" s="54" t="n">
         <f aca="false">G37+G75+G113</f>
-        <v>110.033653032223</v>
+        <v>111.3635630562</v>
       </c>
       <c r="H152" s="54" t="n">
         <f aca="false">H37+H75+H113</f>
-        <v>125.609069340984</v>
+        <v>127.127131757442</v>
       </c>
       <c r="I152" s="54" t="n">
         <f aca="false">I37+I75+I113</f>
-        <v>139.705381025132</v>
+        <v>141.393698680269</v>
       </c>
       <c r="J152" s="54" t="n">
         <f aca="false">J37+J75+J113</f>
-        <v>153.108060435352</v>
+        <v>154.958228315677</v>
       </c>
       <c r="K152" s="54" t="n">
         <f aca="false">K37+K75+K113</f>
-        <v>167.750461646431</v>
+        <v>169.777426367308</v>
       </c>
       <c r="L152" s="54" t="n">
         <f aca="false">L37+L75+L113</f>
-        <v>189.266048991755</v>
+        <v>191.552780546312</v>
       </c>
       <c r="M152" s="54" t="n">
         <f aca="false">M37+M75+M113</f>
-        <v>207.345535416465</v>
+        <v>209.850487594961</v>
       </c>
       <c r="N152" s="54" t="n">
         <f aca="false">N37+N75+N113</f>
-        <v>221.211880587311</v>
+        <v>223.884143127082</v>
       </c>
       <c r="O152" s="54" t="n">
         <f aca="false">O37+O75+O113</f>
-        <v>273.200760563703</v>
+        <v>276.427290697368</v>
       </c>
       <c r="P152" s="54" t="n">
         <f aca="false">P37+P75+P113</f>
-        <v>335.90952794506</v>
+        <v>339.825128673349</v>
       </c>
       <c r="Q152" s="54" t="n">
         <f aca="false">Q37+Q75+Q113</f>
-        <v>393.589177833201</v>
+        <v>398.137688582314</v>
       </c>
       <c r="R152" s="54" t="n">
         <f aca="false">R37+R75+R113</f>
-        <v>468.316521612576</v>
+        <v>473.687240430915</v>
       </c>
       <c r="S152" s="54" t="n">
         <f aca="false">S37+S75+S113</f>
-        <v>532.013693924959</v>
+        <v>538.083593639454</v>
       </c>
       <c r="T152" s="54" t="n">
         <f aca="false">T37+T75+T113</f>
-        <v>580.438863367243</v>
+        <v>587.038065654105</v>
       </c>
       <c r="U152" s="54" t="n">
         <f aca="false">U37+U75+U113</f>
-        <v>624.78872983574</v>
+        <v>631.871825718094</v>
       </c>
       <c r="V152" s="54" t="n">
         <f aca="false">V37+V75+V113</f>
-        <v>667.716254218379</v>
+        <v>675.267285488038</v>
       </c>
       <c r="W152" s="54" t="n">
         <f aca="false">W37+W75+W113</f>
-        <v>716.224255719475</v>
+        <v>724.304806682135</v>
       </c>
       <c r="X152" s="54" t="n">
         <f aca="false">X37+X75+X113</f>
-        <v>791.398904963463</v>
+        <v>800.303712207944</v>
       </c>
       <c r="Y152" s="54" t="n">
         <f aca="false">Y37+Y75+Y113</f>
-        <v>855.810700058484</v>
+        <v>865.419911367897</v>
       </c>
       <c r="Z152" s="54" t="n">
         <f aca="false">Z37+Z75+Z113</f>
-        <v>905.817400519671</v>
+        <v>915.97120030379</v>
       </c>
       <c r="AA152" s="54" t="n">
         <f aca="false">AA37+AA75+AA113</f>
-        <v>19399.0779594369</v>
+        <v>19607.8124595759</v>
       </c>
       <c r="AB152" s="54" t="n">
         <f aca="false">AB37+AB75+AB113</f>
-        <v>30043.7290159337</v>
+        <v>30360.7929928897</v>
       </c>
       <c r="AC152" s="54" t="n">
         <f aca="false">AC37+AC75+AC113</f>
-        <v>42344.0749148424</v>
+        <v>42782.2988339907</v>
       </c>
       <c r="AD152" s="54" t="n">
         <f aca="false">AD37+AD75+AD113</f>
-        <v>53491.8712533548</v>
+        <v>54034.7699426158</v>
       </c>
       <c r="AE152" s="54" t="n">
         <f aca="false">AE37+AE75+AE113</f>
-        <v>61075.3118846435</v>
+        <v>61676.6245704157</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23189,119 +23189,119 @@
       </c>
       <c r="C153" s="55" t="n">
         <f aca="false">C42+C80+C118</f>
-        <v>3405.62096311923</v>
+        <v>3446.79416101681</v>
       </c>
       <c r="D153" s="55" t="n">
         <f aca="false">D42+D80+D118</f>
-        <v>9823.03337738801</v>
+        <v>9941.78646498395</v>
       </c>
       <c r="E153" s="55" t="n">
         <f aca="false">E42+E80+E118</f>
-        <v>18913.5065992897</v>
+        <v>19142.1469185884</v>
       </c>
       <c r="F153" s="55" t="n">
         <f aca="false">F42+F80+F118</f>
-        <v>31266.4516446023</v>
+        <v>31644.4049175259</v>
       </c>
       <c r="G153" s="55" t="n">
         <f aca="false">G42+G80+G118</f>
-        <v>46282.5002694004</v>
+        <v>46841.9424189127</v>
       </c>
       <c r="H153" s="55" t="n">
         <f aca="false">H42+H80+H118</f>
-        <v>63229.2364522224</v>
+        <v>63993.4886045168</v>
       </c>
       <c r="I153" s="55" t="n">
         <f aca="false">I42+I80+I118</f>
-        <v>81857.556564679</v>
+        <v>82846.9264666356</v>
       </c>
       <c r="J153" s="55" t="n">
         <f aca="false">J42+J80+J118</f>
-        <v>102033.586739223</v>
+        <v>103266.761323673</v>
       </c>
       <c r="K153" s="55" t="n">
         <f aca="false">K42+K80+K118</f>
-        <v>123900.275712678</v>
+        <v>125397.664719037</v>
       </c>
       <c r="L153" s="55" t="n">
         <f aca="false">L42+L80+L118</f>
-        <v>148399.520113692</v>
+        <v>150192.90337185</v>
       </c>
       <c r="M153" s="55" t="n">
         <f aca="false">M42+M80+M118</f>
-        <v>174988.93872889</v>
+        <v>177103.539033728</v>
       </c>
       <c r="N153" s="55" t="n">
         <f aca="false">N42+N80+N118</f>
-        <v>203024.084662064</v>
+        <v>205477.33812138</v>
       </c>
       <c r="O153" s="55" t="n">
         <f aca="false">O42+O80+O118</f>
-        <v>257193.779507402</v>
+        <v>260290.161780343</v>
       </c>
       <c r="P153" s="55" t="n">
         <f aca="false">P42+P80+P118</f>
-        <v>303819.78904456</v>
+        <v>307457.835035048</v>
       </c>
       <c r="Q153" s="55" t="n">
         <f aca="false">Q42+Q80+Q118</f>
-        <v>358398.615985734</v>
+        <v>362665.00211487</v>
       </c>
       <c r="R153" s="55" t="n">
         <f aca="false">R42+R80+R118</f>
-        <v>423396.580798576</v>
+        <v>428405.401576476</v>
       </c>
       <c r="S153" s="55" t="n">
         <f aca="false">S42+S80+S118</f>
-        <v>496910.382153939</v>
+        <v>502754.521043482</v>
       </c>
       <c r="T153" s="55" t="n">
         <f aca="false">T42+T80+T118</f>
-        <v>576416.22289943</v>
+        <v>583160.504110397</v>
       </c>
       <c r="U153" s="55" t="n">
         <f aca="false">U42+U80+U118</f>
-        <v>661159.116439852</v>
+        <v>668859.981160768</v>
       </c>
       <c r="V153" s="55" t="n">
         <f aca="false">V42+V80+V118</f>
-        <v>750805.65554392</v>
+        <v>759515.845589568</v>
       </c>
       <c r="W153" s="55" t="n">
         <f aca="false">W42+W80+W118</f>
-        <v>846109.603872063</v>
+        <v>855890.206974381</v>
       </c>
       <c r="X153" s="55" t="n">
         <f aca="false">X42+X80+X118</f>
-        <v>951070.444881376</v>
+        <v>962026.800356863</v>
       </c>
       <c r="Y153" s="55" t="n">
         <f aca="false">Y42+Y80+Y118</f>
-        <v>1063823.30515214</v>
+        <v>1076040.01375601</v>
       </c>
       <c r="Z153" s="55" t="n">
         <f aca="false">Z42+Z80+Z118</f>
-        <v>1181972.49422505</v>
+        <v>1195507.59890948</v>
       </c>
       <c r="AA153" s="55" t="n">
         <f aca="false">AA42+AA80+AA118</f>
-        <v>4177702.57069549</v>
+        <v>4223317.39830918</v>
       </c>
       <c r="AB153" s="55" t="n">
         <f aca="false">AB42+AB80+AB118</f>
-        <v>8772589.97943718</v>
+        <v>8866384.72944046</v>
       </c>
       <c r="AC153" s="55" t="n">
         <f aca="false">AC42+AC80+AC118</f>
-        <v>15283370.4142539</v>
+        <v>15443908.9157799</v>
       </c>
       <c r="AD153" s="55" t="n">
         <f aca="false">AD42+AD80+AD118</f>
-        <v>23471714.9821616</v>
+        <v>23714175.2246966</v>
       </c>
       <c r="AE153" s="55" t="n">
         <f aca="false">AE42+AE80+AE118</f>
-        <v>32563240.2179197</v>
+        <v>32892677.0245833</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23561,119 +23561,119 @@
       </c>
       <c r="C156" s="55" t="n">
         <f aca="false">C36+C74+C112</f>
-        <v>215.195244328639</v>
+        <v>259.185555766578</v>
       </c>
       <c r="D156" s="55" t="n">
         <f aca="false">D36+D74+D112</f>
-        <v>409.188991019204</v>
+        <v>492.827363883777</v>
       </c>
       <c r="E156" s="55" t="n">
         <f aca="false">E36+E74+E112</f>
-        <v>585.154069554993</v>
+        <v>704.74832789766</v>
       </c>
       <c r="F156" s="55" t="n">
         <f aca="false">F36+F74+F112</f>
-        <v>801.432153979041</v>
+        <v>965.211019532286</v>
       </c>
       <c r="G156" s="55" t="n">
         <f aca="false">G36+G74+G112</f>
-        <v>983.680884260344</v>
+        <v>1184.68194538835</v>
       </c>
       <c r="H156" s="55" t="n">
         <f aca="false">H36+H74+H112</f>
-        <v>1122.95734435205</v>
+        <v>1352.39554021905</v>
       </c>
       <c r="I156" s="55" t="n">
         <f aca="false">I36+I74+I112</f>
-        <v>1249.01805847888</v>
+        <v>1504.18843398216</v>
       </c>
       <c r="J156" s="55" t="n">
         <f aca="false">J36+J74+J112</f>
-        <v>1368.88550226373</v>
+        <v>1648.51773339642</v>
       </c>
       <c r="K156" s="55" t="n">
         <f aca="false">K36+K74+K112</f>
-        <v>1499.84909726883</v>
+        <v>1806.20219817035</v>
       </c>
       <c r="L156" s="55" t="n">
         <f aca="false">L36+L74+L112</f>
-        <v>1692.29415863819</v>
+        <v>2037.90811799951</v>
       </c>
       <c r="M156" s="55" t="n">
         <f aca="false">M36+M74+M112</f>
-        <v>1854.02686456747</v>
+        <v>2232.62243635443</v>
       </c>
       <c r="N156" s="55" t="n">
         <f aca="false">N36+N74+N112</f>
-        <v>1978.0907752211</v>
+        <v>2381.97344128345</v>
       </c>
       <c r="O156" s="55" t="n">
         <f aca="false">O36+O74+O112</f>
-        <v>2656.5310859145</v>
+        <v>3183.68509063639</v>
       </c>
       <c r="P156" s="55" t="n">
         <f aca="false">P36+P74+P112</f>
-        <v>3277.30880816867</v>
+        <v>3917.04391656659</v>
       </c>
       <c r="Q156" s="55" t="n">
         <f aca="false">Q36+Q74+Q112</f>
-        <v>3848.55742225404</v>
+        <v>4591.69805866026</v>
       </c>
       <c r="R156" s="55" t="n">
         <f aca="false">R36+R74+R112</f>
-        <v>4588.24056907423</v>
+        <v>5465.71445465248</v>
       </c>
       <c r="S156" s="55" t="n">
         <f aca="false">S36+S74+S112</f>
-        <v>5219.19667303486</v>
+        <v>6210.90349435678</v>
       </c>
       <c r="T156" s="55" t="n">
         <f aca="false">T36+T74+T112</f>
-        <v>5699.44151400433</v>
+        <v>6777.62636564784</v>
       </c>
       <c r="U156" s="55" t="n">
         <f aca="false">U36+U74+U112</f>
-        <v>6139.52317725317</v>
+        <v>7296.76709115726</v>
       </c>
       <c r="V156" s="55" t="n">
         <f aca="false">V36+V74+V112</f>
-        <v>6565.64814596845</v>
+        <v>7799.34385271187</v>
       </c>
       <c r="W156" s="55" t="n">
         <f aca="false">W36+W74+W112</f>
-        <v>7047.0587538427</v>
+        <v>8367.26796431337</v>
       </c>
       <c r="X156" s="55" t="n">
         <f aca="false">X36+X74+X112</f>
-        <v>7792.36540510938</v>
+        <v>9247.24250395499</v>
       </c>
       <c r="Y156" s="55" t="n">
         <f aca="false">Y36+Y74+Y112</f>
-        <v>8431.52047312888</v>
+        <v>10001.4838747171</v>
       </c>
       <c r="Z156" s="55" t="n">
         <f aca="false">Z36+Z74+Z112</f>
-        <v>8928.38264893218</v>
+        <v>10587.3215082021</v>
       </c>
       <c r="AA156" s="55" t="n">
         <f aca="false">AA36+AA74+AA112</f>
-        <v>209910.956585175</v>
+        <v>246776.591240867</v>
       </c>
       <c r="AB156" s="55" t="n">
         <f aca="false">AB36+AB74+AB112</f>
-        <v>353924.243670005</v>
+        <v>414458.341637642</v>
       </c>
       <c r="AC156" s="55" t="n">
         <f aca="false">AC36+AC74+AC112</f>
-        <v>543129.876754848</v>
+        <v>633572.873750963</v>
       </c>
       <c r="AD156" s="55" t="n">
         <f aca="false">AD36+AD74+AD112</f>
-        <v>746913.460029849</v>
+        <v>868035.549329495</v>
       </c>
       <c r="AE156" s="55" t="n">
         <f aca="false">AE36+AE74+AE112</f>
-        <v>931795.439525834</v>
+        <v>1076816.34772687</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23733,71 +23733,71 @@
       </c>
       <c r="O157" s="55" t="n">
         <f aca="false">O50+O88+O126</f>
-        <v>523.282015876023</v>
+        <v>529.621955310957</v>
       </c>
       <c r="P157" s="55" t="n">
         <f aca="false">P50+P88+P126</f>
-        <v>539.728049334241</v>
+        <v>546.272943212677</v>
       </c>
       <c r="Q157" s="55" t="n">
         <f aca="false">Q50+Q88+Q126</f>
-        <v>609.758233708532</v>
+        <v>617.154827926123</v>
       </c>
       <c r="R157" s="55" t="n">
         <f aca="false">R50+R88+R126</f>
-        <v>681.607312165526</v>
+        <v>689.877345994029</v>
       </c>
       <c r="S157" s="55" t="n">
         <f aca="false">S50+S88+S126</f>
-        <v>804.997200572758</v>
+        <v>814.764033250717</v>
       </c>
       <c r="T157" s="55" t="n">
         <f aca="false">T50+T88+T126</f>
-        <v>929.68763334103</v>
+        <v>940.965279786356</v>
       </c>
       <c r="U157" s="55" t="n">
         <f aca="false">U50+U88+U126</f>
-        <v>1023.03972453413</v>
+        <v>1035.44759136875</v>
       </c>
       <c r="V157" s="55" t="n">
         <f aca="false">V50+V88+V126</f>
-        <v>1211.90143936292</v>
+        <v>1226.597715487</v>
       </c>
       <c r="W157" s="55" t="n">
         <f aca="false">W50+W88+W126</f>
-        <v>1823.08768868596</v>
+        <v>1844.92300632151</v>
       </c>
       <c r="X157" s="55" t="n">
         <f aca="false">X50+X88+X126</f>
-        <v>2303.06482341516</v>
+        <v>2330.41873472712</v>
       </c>
       <c r="Y157" s="55" t="n">
         <f aca="false">Y50+Y88+Y126</f>
-        <v>2878.98493214912</v>
+        <v>2912.96066447774</v>
       </c>
       <c r="Z157" s="55" t="n">
         <f aca="false">Z50+Z88+Z126</f>
-        <v>3898.45889167722</v>
+        <v>3944.17556343908</v>
       </c>
       <c r="AA157" s="55" t="n">
         <f aca="false">AA50+AA88+AA126</f>
-        <v>372332.790467257</v>
+        <v>376446.546444254</v>
       </c>
       <c r="AB157" s="55" t="n">
         <f aca="false">AB50+AB88+AB126</f>
-        <v>879878.03765354</v>
+        <v>889401.159214707</v>
       </c>
       <c r="AC157" s="55" t="n">
         <f aca="false">AC50+AC88+AC126</f>
-        <v>1690805.52948428</v>
+        <v>1708824.35394891</v>
       </c>
       <c r="AD157" s="55" t="n">
         <f aca="false">AD50+AD88+AD126</f>
-        <v>2884595.80123393</v>
+        <v>2914930.29949058</v>
       </c>
       <c r="AE157" s="55" t="n">
         <f aca="false">AE50+AE88+AE126</f>
-        <v>4510489.08935746</v>
+        <v>4557395.28503812</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23809,119 +23809,119 @@
       </c>
       <c r="C158" s="57" t="n">
         <f aca="false">C151*C21</f>
-        <v>3405.62096311923</v>
+        <v>3446.79416101681</v>
       </c>
       <c r="D158" s="57" t="n">
         <f aca="false">D151*D21</f>
-        <v>9857.0895870192</v>
+        <v>9976.25440659411</v>
       </c>
       <c r="E158" s="57" t="n">
         <f aca="false">E151*E21</f>
-        <v>19045.5462964095</v>
+        <v>19275.7828942334</v>
       </c>
       <c r="F158" s="57" t="n">
         <f aca="false">F151*F21</f>
-        <v>31586.6497442662</v>
+        <v>31968.4738915531</v>
       </c>
       <c r="G158" s="57" t="n">
         <f aca="false">G151*G21</f>
-        <v>46912.939391661</v>
+        <v>47480.0026502901</v>
       </c>
       <c r="H158" s="57" t="n">
         <f aca="false">H151*H21</f>
-        <v>64317.6091111125</v>
+        <v>65095.017662194</v>
       </c>
       <c r="I158" s="57" t="n">
         <f aca="false">I151*I21</f>
-        <v>83569.5786941495</v>
+        <v>84579.6430377011</v>
       </c>
       <c r="J158" s="57" t="n">
         <f aca="false">J151*J21</f>
-        <v>104550.295841687</v>
+        <v>105813.890680929</v>
       </c>
       <c r="K158" s="57" t="n">
         <f aca="false">K151*K21</f>
-        <v>127416.52876713</v>
+        <v>128956.418447575</v>
       </c>
       <c r="L158" s="57" t="n">
         <f aca="false">L151*L21</f>
-        <v>153125.393619837</v>
+        <v>154975.896286038</v>
       </c>
       <c r="M158" s="57" t="n">
         <f aca="false">M151*M21</f>
-        <v>181158.755667503</v>
+        <v>183347.925102643</v>
       </c>
       <c r="N158" s="57" t="n">
         <f aca="false">N151*N21</f>
-        <v>210890.635630622</v>
+        <v>213438.96174606</v>
       </c>
       <c r="O158" s="57" t="n">
         <f aca="false">O151*O21</f>
-        <v>267820.221649471</v>
+        <v>271045.026709106</v>
       </c>
       <c r="P158" s="57" t="n">
         <f aca="false">P151*P21</f>
-        <v>316928.515620016</v>
+        <v>320724.864089245</v>
       </c>
       <c r="Q158" s="57" t="n">
         <f aca="false">Q151*Q21</f>
-        <v>374434.539363404</v>
+        <v>378894.266934684</v>
       </c>
       <c r="R158" s="57" t="n">
         <f aca="false">R151*R21</f>
-        <v>442880.627927514</v>
+        <v>448123.814314256</v>
       </c>
       <c r="S158" s="57" t="n">
         <f aca="false">S151*S21</f>
-        <v>520462.13942918</v>
+        <v>526588.729864443</v>
       </c>
       <c r="T158" s="57" t="n">
         <f aca="false">T151*T21</f>
-        <v>604733.645332562</v>
+        <v>611816.376126345</v>
       </c>
       <c r="U158" s="57" t="n">
         <f aca="false">U151*U21</f>
-        <v>694992.93790157</v>
+        <v>703096.728770236</v>
       </c>
       <c r="V158" s="57" t="n">
         <f aca="false">V151*V21</f>
-        <v>790951.309802262</v>
+        <v>800137.858075965</v>
       </c>
       <c r="W158" s="57" t="n">
         <f aca="false">W151*W21</f>
-        <v>893403.870281133</v>
+        <v>903743.659570659</v>
       </c>
       <c r="X158" s="57" t="n">
         <f aca="false">X151*X21</f>
-        <v>1006400.51877869</v>
+        <v>1018008.82671886</v>
       </c>
       <c r="Y158" s="57" t="n">
         <f aca="false">Y151*Y21</f>
-        <v>1128162.76317239</v>
+        <v>1141135.06667</v>
       </c>
       <c r="Z158" s="57" t="n">
         <f aca="false">Z151*Z21</f>
-        <v>1256361.06867727</v>
+        <v>1270766.99967037</v>
       </c>
       <c r="AA158" s="57" t="n">
         <f aca="false">AA151*AA21</f>
-        <v>4401779.03010304</v>
+        <v>4449977.39714459</v>
       </c>
       <c r="AB158" s="57" t="n">
         <f aca="false">AB151*AB21</f>
-        <v>9526142.80821646</v>
+        <v>9628293.23380596</v>
       </c>
       <c r="AC158" s="57" t="n">
         <f aca="false">AC151*AC21</f>
-        <v>17129273.806276</v>
+        <v>17309823.667829</v>
       </c>
       <c r="AD158" s="57" t="n">
         <f aca="false">AD151*AD21</f>
-        <v>27179446.3044826</v>
+        <v>27461419.3240532</v>
       </c>
       <c r="AE158" s="57" t="n">
         <f aca="false">AE151*AE21</f>
-        <v>39054872.0342436</v>
+        <v>39452453.3771514</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23938,119 +23938,119 @@
       </c>
       <c r="C160" s="55" t="n">
         <f aca="false">C151*Assumptions!$B$6</f>
-        <v>3405.62096311923</v>
+        <v>3446.79416101681</v>
       </c>
       <c r="D160" s="55" t="n">
         <f aca="false">D151*Assumptions!$B$6</f>
-        <v>9857.0895870192</v>
+        <v>9976.25440659411</v>
       </c>
       <c r="E160" s="55" t="n">
         <f aca="false">E151*Assumptions!$B$6</f>
-        <v>19045.5462964095</v>
+        <v>19275.7828942334</v>
       </c>
       <c r="F160" s="55" t="n">
         <f aca="false">F151*Assumptions!$B$6</f>
-        <v>31586.6497442662</v>
+        <v>31968.4738915531</v>
       </c>
       <c r="G160" s="55" t="n">
         <f aca="false">G151*Assumptions!$B$6</f>
-        <v>46912.939391661</v>
+        <v>47480.0026502901</v>
       </c>
       <c r="H160" s="55" t="n">
         <f aca="false">H151*Assumptions!$B$6</f>
-        <v>64317.6091111125</v>
+        <v>65095.017662194</v>
       </c>
       <c r="I160" s="55" t="n">
         <f aca="false">I151*Assumptions!$B$6</f>
-        <v>83569.5786941495</v>
+        <v>84579.6430377011</v>
       </c>
       <c r="J160" s="55" t="n">
         <f aca="false">J151*Assumptions!$B$6</f>
-        <v>104550.295841687</v>
+        <v>105813.890680929</v>
       </c>
       <c r="K160" s="55" t="n">
         <f aca="false">K151*Assumptions!$B$6</f>
-        <v>127416.52876713</v>
+        <v>128956.418447575</v>
       </c>
       <c r="L160" s="55" t="n">
         <f aca="false">L151*Assumptions!$B$6</f>
-        <v>153125.393619837</v>
+        <v>154975.896286038</v>
       </c>
       <c r="M160" s="55" t="n">
         <f aca="false">M151*Assumptions!$B$6</f>
-        <v>181158.755667503</v>
+        <v>183347.925102643</v>
       </c>
       <c r="N160" s="55" t="n">
         <f aca="false">N151*Assumptions!$B$6</f>
-        <v>210890.635630622</v>
+        <v>213438.96174606</v>
       </c>
       <c r="O160" s="55" t="n">
         <f aca="false">O151*Assumptions!$B$6</f>
-        <v>247752.286447245</v>
+        <v>250735.454865038</v>
       </c>
       <c r="P160" s="55" t="n">
         <f aca="false">P151*Assumptions!$B$6</f>
-        <v>293180.865513428</v>
+        <v>296692.751238895</v>
       </c>
       <c r="Q160" s="55" t="n">
         <f aca="false">Q151*Assumptions!$B$6</f>
-        <v>346377.927255693</v>
+        <v>350503.484675933</v>
       </c>
       <c r="R160" s="55" t="n">
         <f aca="false">R151*Assumptions!$B$6</f>
-        <v>409695.307981049</v>
+        <v>414545.619162124</v>
       </c>
       <c r="S160" s="55" t="n">
         <f aca="false">S151*Assumptions!$B$6</f>
-        <v>481463.588741147</v>
+        <v>487131.109957857</v>
       </c>
       <c r="T160" s="55" t="n">
         <f aca="false">T151*Assumptions!$B$6</f>
-        <v>559420.578476005</v>
+        <v>565972.595861558</v>
       </c>
       <c r="U160" s="55" t="n">
         <f aca="false">U151*Assumptions!$B$6</f>
-        <v>642916.686310425</v>
+        <v>650413.255106601</v>
       </c>
       <c r="V160" s="55" t="n">
         <f aca="false">V151*Assumptions!$B$6</f>
-        <v>731684.837929937</v>
+        <v>740183.032447702</v>
       </c>
       <c r="W160" s="55" t="n">
         <f aca="false">W151*Assumptions!$B$6</f>
-        <v>826460.56455239</v>
+        <v>836025.587021886</v>
       </c>
       <c r="X160" s="55" t="n">
         <f aca="false">X151*Assumptions!$B$6</f>
-        <v>930990.304143097</v>
+        <v>941728.79437452</v>
       </c>
       <c r="Y160" s="55" t="n">
         <f aca="false">Y151*Assumptions!$B$6</f>
-        <v>1043628.82809657</v>
+        <v>1055629.10885291</v>
       </c>
       <c r="Z160" s="55" t="n">
         <f aca="false">Z151*Assumptions!$B$6</f>
-        <v>1162221.15511311</v>
+        <v>1175547.64076815</v>
       </c>
       <c r="AA160" s="55" t="n">
         <f aca="false">AA151*Assumptions!$B$6</f>
-        <v>3766837.1870215</v>
+        <v>3808083.1014766</v>
       </c>
       <c r="AB160" s="55" t="n">
         <f aca="false">AB151*Assumptions!$B$6</f>
-        <v>7541192.1357353</v>
+        <v>7622057.60265368</v>
       </c>
       <c r="AC160" s="55" t="n">
         <f aca="false">AC151*Assumptions!$B$6</f>
-        <v>12544003.7645264</v>
+        <v>12676222.9215449</v>
       </c>
       <c r="AD160" s="55" t="n">
         <f aca="false">AD151*Assumptions!$B$6</f>
-        <v>18412473.52302</v>
+        <v>18603493.6306</v>
       </c>
       <c r="AE160" s="55" t="n">
         <f aca="false">AE151*Assumptions!$B$6</f>
-        <v>24474907.292435</v>
+        <v>24724063.5692841</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24110,71 +24110,71 @@
       </c>
       <c r="O161" s="55" t="n">
         <f aca="false">O158-O160</f>
-        <v>20067.9352022268</v>
+        <v>20309.5718440681</v>
       </c>
       <c r="P161" s="55" t="n">
         <f aca="false">P158-P160</f>
-        <v>23747.6501065877</v>
+        <v>24032.1128503505</v>
       </c>
       <c r="Q161" s="55" t="n">
         <f aca="false">Q158-Q160</f>
-        <v>28056.6121077111</v>
+        <v>28390.7822587506</v>
       </c>
       <c r="R161" s="55" t="n">
         <f aca="false">R158-R160</f>
-        <v>33185.319946465</v>
+        <v>33578.195152132</v>
       </c>
       <c r="S161" s="55" t="n">
         <f aca="false">S158-S160</f>
-        <v>38998.5506880329</v>
+        <v>39457.6199065864</v>
       </c>
       <c r="T161" s="55" t="n">
         <f aca="false">T158-T160</f>
-        <v>45313.0668565563</v>
+        <v>45843.7802647862</v>
       </c>
       <c r="U161" s="55" t="n">
         <f aca="false">U158-U160</f>
-        <v>52076.2515911444</v>
+        <v>52683.4736636346</v>
       </c>
       <c r="V161" s="55" t="n">
         <f aca="false">V158-V160</f>
-        <v>59266.4718723248</v>
+        <v>59954.8256282639</v>
       </c>
       <c r="W161" s="55" t="n">
         <f aca="false">W158-W160</f>
-        <v>66943.3057287436</v>
+        <v>67718.0725487727</v>
       </c>
       <c r="X161" s="55" t="n">
         <f aca="false">X158-X160</f>
-        <v>75410.2146355908</v>
+        <v>76280.032344336</v>
       </c>
       <c r="Y161" s="55" t="n">
         <f aca="false">Y158-Y160</f>
-        <v>84533.9350758219</v>
+        <v>85505.9578170858</v>
       </c>
       <c r="Z161" s="55" t="n">
         <f aca="false">Z158-Z160</f>
-        <v>94139.9135641619</v>
+        <v>95219.3589022197</v>
       </c>
       <c r="AA161" s="55" t="n">
         <f aca="false">AA158-AA160</f>
-        <v>634941.843081532</v>
+        <v>641894.295667996</v>
       </c>
       <c r="AB161" s="55" t="n">
         <f aca="false">AB158-AB160</f>
-        <v>1984950.67248116</v>
+        <v>2006235.63115229</v>
       </c>
       <c r="AC161" s="55" t="n">
         <f aca="false">AC158-AC160</f>
-        <v>4585270.04174965</v>
+        <v>4633600.74628412</v>
       </c>
       <c r="AD161" s="55" t="n">
         <f aca="false">AD158-AD160</f>
-        <v>8766972.78146268</v>
+        <v>8857925.69345317</v>
       </c>
       <c r="AE161" s="55" t="n">
         <f aca="false">AE158-AE160</f>
-        <v>14579964.7418086</v>
+        <v>14728389.8078673</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24319,115 +24319,115 @@
       </c>
       <c r="D164" s="59" t="n">
         <f aca="false">D151-D150</f>
-        <v>0.240747982689044</v>
+        <v>0.243658572106369</v>
       </c>
       <c r="E164" s="59" t="n">
         <f aca="false">E151-E150</f>
-        <v>0.933406596350608</v>
+        <v>0.9446909065814</v>
       </c>
       <c r="F164" s="59" t="n">
         <f aca="false">F151-F150</f>
-        <v>2.26352396199582</v>
+        <v>2.29088769989517</v>
       </c>
       <c r="G164" s="59" t="n">
         <f aca="false">G151-G150</f>
-        <v>4.45665999053176</v>
+        <v>4.51053464850418</v>
       </c>
       <c r="H164" s="59" t="n">
         <f aca="false">H151-H150</f>
-        <v>7.69385450933248</v>
+        <v>7.78685888362236</v>
       </c>
       <c r="I164" s="59" t="n">
         <f aca="false">I151-I150</f>
-        <v>12.1025175277148</v>
+        <v>12.24880935293</v>
       </c>
       <c r="J164" s="59" t="n">
         <f aca="false">J151-J150</f>
-        <v>17.7909592991969</v>
+        <v>18.0060042220867</v>
       </c>
       <c r="K164" s="59" t="n">
         <f aca="false">K151-K150</f>
-        <v>24.8568715852692</v>
+        <v>25.1573146369095</v>
       </c>
       <c r="L164" s="59" t="n">
         <f aca="false">L151-L150</f>
-        <v>33.407843249998</v>
+        <v>33.8116281223506</v>
       </c>
       <c r="M164" s="59" t="n">
         <f aca="false">M151-M150</f>
-        <v>43.6152759692704</v>
+        <v>44.1424153040775</v>
       </c>
       <c r="N164" s="59" t="n">
         <f aca="false">N151-N150</f>
-        <v>55.609719839943</v>
+        <v>56.2818013903598</v>
       </c>
       <c r="O164" s="59" t="n">
         <f aca="false">O151-O150</f>
-        <v>69.4909956604861</v>
+        <v>70.3308089482759</v>
       </c>
       <c r="P164" s="59" t="n">
         <f aca="false">P151-P150</f>
-        <v>85.7237492465315</v>
+        <v>86.7589590294638</v>
       </c>
       <c r="Q164" s="59" t="n">
         <f aca="false">Q151-Q150</f>
-        <v>104.865981195902</v>
+        <v>106.130326226666</v>
       </c>
       <c r="R164" s="59" t="n">
         <f aca="false">R151-R150</f>
-        <v>127.414784401406</v>
+        <v>128.947404566202</v>
       </c>
       <c r="S164" s="59" t="n">
         <f aca="false">S151-S150</f>
-        <v>154.015336528424</v>
+        <v>155.862411859518</v>
       </c>
       <c r="T164" s="59" t="n">
         <f aca="false">T151-T150</f>
-        <v>185.180124552369</v>
+        <v>187.393395765472</v>
       </c>
       <c r="U164" s="59" t="n">
         <f aca="false">U151-U150</f>
-        <v>221.254292729451</v>
+        <v>223.889204660504</v>
       </c>
       <c r="V164" s="59" t="n">
         <f aca="false">V151-V150</f>
-        <v>262.530153418838</v>
+        <v>265.645270135803</v>
       </c>
       <c r="W164" s="59" t="n">
         <f aca="false">W151-W150</f>
-        <v>309.2780836577</v>
+        <v>312.934848959681</v>
       </c>
       <c r="X164" s="59" t="n">
         <f aca="false">X151-X150</f>
-        <v>361.827775815073</v>
+        <v>366.091180752343</v>
       </c>
       <c r="Y164" s="59" t="n">
         <f aca="false">Y151-Y150</f>
-        <v>420.744115321793</v>
+        <v>425.685283850264</v>
       </c>
       <c r="Z164" s="59" t="n">
         <f aca="false">Z151-Z150</f>
-        <v>486.459723333417</v>
+        <v>492.154440946986</v>
       </c>
       <c r="AA164" s="59" t="n">
         <f aca="false">AA151-AA150</f>
-        <v>1355.53642463848</v>
+        <v>1371.1653836475</v>
       </c>
       <c r="AB164" s="59" t="n">
         <f aca="false">AB151-AB150</f>
-        <v>4216.99386195952</v>
+        <v>4263.75346701163</v>
       </c>
       <c r="AC164" s="59" t="n">
         <f aca="false">AC151-AC150</f>
-        <v>9555.92072672644</v>
+        <v>9659.51605618856</v>
       </c>
       <c r="AD164" s="59" t="n">
         <f aca="false">AD151-AD150</f>
-        <v>17756.0407194289</v>
+        <v>17945.264375889</v>
       </c>
       <c r="AE164" s="59" t="n">
         <f aca="false">AE151-AE150</f>
-        <v>28758.4889081799</v>
+        <v>29060.3750818234</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24439,119 +24439,119 @@
       </c>
       <c r="C165" s="55" t="n">
         <f aca="false">IF(C145=0,0,C153/C145)</f>
-        <v>30.9024178443726</v>
+        <v>31.2760211840274</v>
       </c>
       <c r="D165" s="55" t="n">
         <f aca="false">IF(D145=0,0,D153/D145)</f>
-        <v>46.8778189061104</v>
+        <v>47.4445364892633</v>
       </c>
       <c r="E165" s="55" t="n">
         <f aca="false">IF(E145=0,0,E153/E145)</f>
-        <v>63.1195606455668</v>
+        <v>63.8825961209945</v>
       </c>
       <c r="F165" s="55" t="n">
         <f aca="false">IF(F145=0,0,F153/F145)</f>
-        <v>76.1891892625267</v>
+        <v>77.1101749173903</v>
       </c>
       <c r="G165" s="55" t="n">
         <f aca="false">IF(G145=0,0,G153/G145)</f>
-        <v>91.8888194568526</v>
+        <v>92.9995303815837</v>
       </c>
       <c r="H165" s="55" t="n">
         <f aca="false">IF(H145=0,0,H153/H145)</f>
-        <v>109.969243847369</v>
+        <v>111.298442743516</v>
       </c>
       <c r="I165" s="55" t="n">
         <f aca="false">IF(I145=0,0,I153/I145)</f>
-        <v>128.003781250676</v>
+        <v>129.5508966768</v>
       </c>
       <c r="J165" s="55" t="n">
         <f aca="false">IF(J145=0,0,J153/J145)</f>
-        <v>145.587854845476</v>
+        <v>147.347424886456</v>
       </c>
       <c r="K165" s="55" t="n">
         <f aca="false">IF(K145=0,0,K153/K145)</f>
-        <v>161.358469408852</v>
+        <v>163.308557064315</v>
       </c>
       <c r="L165" s="55" t="n">
         <f aca="false">IF(L145=0,0,L153/L145)</f>
-        <v>171.29596628772</v>
+        <v>173.366049249545</v>
       </c>
       <c r="M165" s="55" t="n">
         <f aca="false">IF(M145=0,0,M153/M145)</f>
-        <v>184.377179583795</v>
+        <v>186.60522921359</v>
       </c>
       <c r="N165" s="55" t="n">
         <f aca="false">IF(N145=0,0,N153/N145)</f>
-        <v>200.509012182568</v>
+        <v>202.93187461576</v>
       </c>
       <c r="O165" s="55" t="n">
         <f aca="false">IF(O145=0,0,O153/O145)</f>
-        <v>189.645438075899</v>
+        <v>191.92859894288</v>
       </c>
       <c r="P165" s="55" t="n">
         <f aca="false">IF(P145=0,0,P153/P145)</f>
-        <v>181.874383527136</v>
+        <v>184.052211949189</v>
       </c>
       <c r="Q165" s="55" t="n">
         <f aca="false">IF(Q145=0,0,Q153/Q145)</f>
-        <v>182.892754729887</v>
+        <v>185.069914677207</v>
       </c>
       <c r="R165" s="55" t="n">
         <f aca="false">IF(R145=0,0,R153/R145)</f>
-        <v>181.403451836255</v>
+        <v>183.549471478233</v>
       </c>
       <c r="S165" s="55" t="n">
         <f aca="false">IF(S145=0,0,S153/S145)</f>
-        <v>187.288848729272</v>
+        <v>189.491543790084</v>
       </c>
       <c r="T165" s="55" t="n">
         <f aca="false">IF(T145=0,0,T153/T145)</f>
-        <v>199.045342873022</v>
+        <v>201.374246385342</v>
       </c>
       <c r="U165" s="55" t="n">
         <f aca="false">IF(U145=0,0,U153/U145)</f>
-        <v>212.031253827609</v>
+        <v>214.500892318151</v>
       </c>
       <c r="V165" s="55" t="n">
         <f aca="false">IF(V145=0,0,V153/V145)</f>
-        <v>225.238165662585</v>
+        <v>227.851181712702</v>
       </c>
       <c r="W165" s="55" t="n">
         <f aca="false">IF(W145=0,0,W153/W145)</f>
-        <v>236.577861949892</v>
+        <v>239.312583503622</v>
       </c>
       <c r="X165" s="55" t="n">
         <f aca="false">IF(X145=0,0,X153/X145)</f>
-        <v>240.599734670122</v>
+        <v>243.371449672455</v>
       </c>
       <c r="Y165" s="55" t="n">
         <f aca="false">IF(Y145=0,0,Y153/Y145)</f>
-        <v>248.818860307078</v>
+        <v>251.67624037837</v>
       </c>
       <c r="Z165" s="55" t="n">
         <f aca="false">IF(Z145=0,0,Z153/Z145)</f>
-        <v>261.153477372951</v>
+        <v>264.144020445837</v>
       </c>
       <c r="AA165" s="55" t="n">
         <f aca="false">IF(AA145=0,0,AA153/AA145)</f>
-        <v>479.137851371719</v>
+        <v>484.369384762062</v>
       </c>
       <c r="AB165" s="55" t="n">
         <f aca="false">IF(AB145=0,0,AB153/AB145)</f>
-        <v>601.418742581821</v>
+        <v>607.848989605787</v>
       </c>
       <c r="AC165" s="55" t="n">
         <f aca="false">IF(AC145=0,0,AC153/AC145)</f>
-        <v>688.420581898936</v>
+        <v>695.651840819068</v>
       </c>
       <c r="AD165" s="55" t="n">
         <f aca="false">IF(AD145=0,0,AD153/AD145)</f>
-        <v>775.007681422905</v>
+        <v>783.013425807031</v>
       </c>
       <c r="AE165" s="55" t="n">
         <f aca="false">IF(AE145=0,0,AE153/AE145)</f>
-        <v>872.647599127451</v>
+        <v>881.476027639949</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24611,71 +24611,71 @@
       </c>
       <c r="O166" s="55" t="n">
         <f aca="false">O45*O46+O83*O84+O121*O122</f>
-        <v>5436.69626884179</v>
+        <v>5502.56576946449</v>
       </c>
       <c r="P166" s="55" t="n">
         <f aca="false">P45*P46+P83*P84+P121*P122</f>
-        <v>6168.32056381989</v>
+        <v>6243.11935100202</v>
       </c>
       <c r="Q166" s="55" t="n">
         <f aca="false">Q45*Q46+Q83*Q84+Q121*Q122</f>
-        <v>7110.88319193624</v>
+        <v>7197.14085045041</v>
       </c>
       <c r="R166" s="55" t="n">
         <f aca="false">R45*R46+R83*R84+R121*R122</f>
-        <v>7948.77331971459</v>
+        <v>8045.21686290413</v>
       </c>
       <c r="S166" s="55" t="n">
         <f aca="false">S45*S46+S83*S84+S121*S122</f>
-        <v>9199.96800654581</v>
+        <v>9311.58895143676</v>
       </c>
       <c r="T166" s="55" t="n">
         <f aca="false">T45*T46+T83*T84+T121*T122</f>
-        <v>11184.2121304184</v>
+        <v>11319.883065099</v>
       </c>
       <c r="U166" s="55" t="n">
         <f aca="false">U45*U46+U83*U84+U121*U122</f>
-        <v>13286.2301887549</v>
+        <v>13447.3713164773</v>
       </c>
       <c r="V166" s="55" t="n">
         <f aca="false">V45*V46+V83*V84+V121*V122</f>
-        <v>15389.2246268307</v>
+        <v>15575.8440061841</v>
       </c>
       <c r="W166" s="55" t="n">
         <f aca="false">W45*W46+W83*W84+W121*W122</f>
-        <v>20835.2878706967</v>
+        <v>21084.8343579601</v>
       </c>
       <c r="X166" s="55" t="n">
         <f aca="false">X45*X46+X83*X84+X121*X122</f>
-        <v>25804.6478814023</v>
+        <v>26111.1342826568</v>
       </c>
       <c r="Y166" s="55" t="n">
         <f aca="false">Y45*Y46+Y83*Y84+Y121*Y122</f>
-        <v>31335.8904179496</v>
+        <v>31705.6943072407</v>
       </c>
       <c r="Z166" s="55" t="n">
         <f aca="false">Z45*Z46+Z83*Z84+Z121*Z122</f>
-        <v>39082.2946534057</v>
+        <v>39540.6071522715</v>
       </c>
       <c r="AA166" s="55" t="n">
         <f aca="false">AA45*AA46+AA83*AA84+AA121*AA122</f>
-        <v>354602.657587864</v>
+        <v>358520.520423099</v>
       </c>
       <c r="AB166" s="55" t="n">
         <f aca="false">AB45*AB46+AB83*AB84+AB121*AB122</f>
-        <v>837979.083479562</v>
+        <v>847048.723061626</v>
       </c>
       <c r="AC166" s="55" t="n">
         <f aca="false">AC45*AC46+AC83*AC84+AC121*AC122</f>
-        <v>1610290.98046122</v>
+        <v>1627451.76566563</v>
       </c>
       <c r="AD166" s="55" t="n">
         <f aca="false">AD45*AD46+AD83*AD84+AD121*AD122</f>
-        <v>2747234.09641327</v>
+        <v>2776124.09475294</v>
       </c>
       <c r="AE166" s="55" t="n">
         <f aca="false">AE45*AE46+AE83*AE84+AE121*AE122</f>
-        <v>4295703.89462616</v>
+        <v>4340376.46194107</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24935,119 +24935,119 @@
       </c>
       <c r="C170" s="55" t="n">
         <f aca="false">C54+C92+C130</f>
-        <v>10.7597622164319</v>
+        <v>12.9592777883289</v>
       </c>
       <c r="D170" s="55" t="n">
         <f aca="false">D54+D92+D130</f>
-        <v>20.4594495509602</v>
+        <v>24.6413681941888</v>
       </c>
       <c r="E170" s="55" t="n">
         <f aca="false">E54+E92+E130</f>
-        <v>29.2577034777496</v>
+        <v>35.237416394883</v>
       </c>
       <c r="F170" s="55" t="n">
         <f aca="false">F54+F92+F130</f>
-        <v>40.071607698952</v>
+        <v>48.2605509766143</v>
       </c>
       <c r="G170" s="55" t="n">
         <f aca="false">G54+G92+G130</f>
-        <v>49.1840442130172</v>
+        <v>59.2340972694176</v>
       </c>
       <c r="H170" s="55" t="n">
         <f aca="false">H54+H92+H130</f>
-        <v>56.1478672176024</v>
+        <v>67.6197770109523</v>
       </c>
       <c r="I170" s="55" t="n">
         <f aca="false">I54+I92+I130</f>
-        <v>62.4509029239439</v>
+        <v>75.2094216991079</v>
       </c>
       <c r="J170" s="55" t="n">
         <f aca="false">J54+J92+J130</f>
-        <v>68.4442751131864</v>
+        <v>82.4258866698209</v>
       </c>
       <c r="K170" s="55" t="n">
         <f aca="false">K54+K92+K130</f>
-        <v>74.9924548634414</v>
+        <v>90.3101099085178</v>
       </c>
       <c r="L170" s="55" t="n">
         <f aca="false">L54+L92+L130</f>
-        <v>84.6147079319093</v>
+        <v>101.895405899976</v>
       </c>
       <c r="M170" s="55" t="n">
         <f aca="false">M54+M92+M130</f>
-        <v>92.7013432283737</v>
+        <v>111.631121817721</v>
       </c>
       <c r="N170" s="55" t="n">
         <f aca="false">N54+N92+N130</f>
-        <v>98.904538761055</v>
+        <v>119.098672064172</v>
       </c>
       <c r="O170" s="55" t="n">
         <f aca="false">O54+O92+O130</f>
-        <v>132.826554295725</v>
+        <v>159.18425453182</v>
       </c>
       <c r="P170" s="55" t="n">
         <f aca="false">P54+P92+P130</f>
-        <v>163.865440408434</v>
+        <v>195.85219582833</v>
       </c>
       <c r="Q170" s="55" t="n">
         <f aca="false">Q54+Q92+Q130</f>
-        <v>192.427871112702</v>
+        <v>229.584902933013</v>
       </c>
       <c r="R170" s="55" t="n">
         <f aca="false">R54+R92+R130</f>
-        <v>229.412028453712</v>
+        <v>273.285722732624</v>
       </c>
       <c r="S170" s="55" t="n">
         <f aca="false">S54+S92+S130</f>
-        <v>260.959833651743</v>
+        <v>310.545174717839</v>
       </c>
       <c r="T170" s="55" t="n">
         <f aca="false">T54+T92+T130</f>
-        <v>284.972075700216</v>
+        <v>338.881318282392</v>
       </c>
       <c r="U170" s="55" t="n">
         <f aca="false">U54+U92+U130</f>
-        <v>306.976158862659</v>
+        <v>364.838354557863</v>
       </c>
       <c r="V170" s="55" t="n">
         <f aca="false">V54+V92+V130</f>
-        <v>328.282407298422</v>
+        <v>389.967192635593</v>
       </c>
       <c r="W170" s="55" t="n">
         <f aca="false">W54+W92+W130</f>
-        <v>352.352937692135</v>
+        <v>418.363398215669</v>
       </c>
       <c r="X170" s="55" t="n">
         <f aca="false">X54+X92+X130</f>
-        <v>389.618270255469</v>
+        <v>462.362125197749</v>
       </c>
       <c r="Y170" s="55" t="n">
         <f aca="false">Y54+Y92+Y130</f>
-        <v>421.576023656444</v>
+        <v>500.074193735856</v>
       </c>
       <c r="Z170" s="55" t="n">
         <f aca="false">Z54+Z92+Z130</f>
-        <v>446.419132446609</v>
+        <v>529.366075410107</v>
       </c>
       <c r="AA170" s="55" t="n">
         <f aca="false">AA54+AA92+AA130</f>
-        <v>10495.5478292588</v>
+        <v>12338.8295620433</v>
       </c>
       <c r="AB170" s="55" t="n">
         <f aca="false">AB54+AB92+AB130</f>
-        <v>17696.2121835003</v>
+        <v>20722.9170818821</v>
       </c>
       <c r="AC170" s="55" t="n">
         <f aca="false">AC54+AC92+AC130</f>
-        <v>27156.4938377424</v>
+        <v>31678.6436875481</v>
       </c>
       <c r="AD170" s="55" t="n">
         <f aca="false">AD54+AD92+AD130</f>
-        <v>37345.6730014924</v>
+        <v>43401.7774664748</v>
       </c>
       <c r="AE170" s="55" t="n">
         <f aca="false">AE54+AE92+AE130</f>
-        <v>46589.7719762917</v>
+        <v>53840.8173863433</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25107,71 +25107,71 @@
       </c>
       <c r="O171" s="55" t="n">
         <f aca="false">O55+O93+O131</f>
-        <v>2.63734136001515</v>
+        <v>2.66929465476722</v>
       </c>
       <c r="P171" s="55" t="n">
         <f aca="false">P55+P93+P131</f>
-        <v>2.72022936864457</v>
+        <v>2.75321563379189</v>
       </c>
       <c r="Q171" s="55" t="n">
         <f aca="false">Q55+Q93+Q131</f>
-        <v>3.073181497891</v>
+        <v>3.11046033274766</v>
       </c>
       <c r="R171" s="55" t="n">
         <f aca="false">R55+R93+R131</f>
-        <v>3.43530085331425</v>
+        <v>3.47698182380991</v>
       </c>
       <c r="S171" s="55" t="n">
         <f aca="false">S55+S93+S131</f>
-        <v>4.0571858908867</v>
+        <v>4.10641072758361</v>
       </c>
       <c r="T171" s="55" t="n">
         <f aca="false">T55+T93+T131</f>
-        <v>4.68562567203879</v>
+        <v>4.74246501012323</v>
       </c>
       <c r="U171" s="55" t="n">
         <f aca="false">U55+U93+U131</f>
-        <v>5.15612021165199</v>
+        <v>5.2186558604985</v>
       </c>
       <c r="V171" s="55" t="n">
         <f aca="false">V55+V93+V131</f>
-        <v>6.10798325438911</v>
+        <v>6.18205248605448</v>
       </c>
       <c r="W171" s="55" t="n">
         <f aca="false">W55+W93+W131</f>
-        <v>9.18836195097726</v>
+        <v>9.29841195186039</v>
       </c>
       <c r="X171" s="55" t="n">
         <f aca="false">X55+X93+X131</f>
-        <v>11.6074467100124</v>
+        <v>11.7453104230247</v>
       </c>
       <c r="Y171" s="55" t="n">
         <f aca="false">Y55+Y93+Y131</f>
-        <v>14.5100840580316</v>
+        <v>14.6813217489678</v>
       </c>
       <c r="Z171" s="55" t="n">
         <f aca="false">Z55+Z93+Z131</f>
-        <v>19.6482328140532</v>
+        <v>19.878644839733</v>
       </c>
       <c r="AA171" s="55" t="n">
         <f aca="false">AA55+AA93+AA131</f>
-        <v>1876.55726395498</v>
+        <v>1897.29059407904</v>
       </c>
       <c r="AB171" s="55" t="n">
         <f aca="false">AB55+AB93+AB131</f>
-        <v>4434.58530977384</v>
+        <v>4482.58184244213</v>
       </c>
       <c r="AC171" s="55" t="n">
         <f aca="false">AC55+AC93+AC131</f>
-        <v>8521.65986860076</v>
+        <v>8612.47474390253</v>
       </c>
       <c r="AD171" s="55" t="n">
         <f aca="false">AD55+AD93+AD131</f>
-        <v>14538.362838219</v>
+        <v>14691.2487094325</v>
       </c>
       <c r="AE171" s="55" t="n">
         <f aca="false">AE55+AE93+AE131</f>
-        <v>22732.8650103616</v>
+        <v>22969.2722365921</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25355,71 +25355,71 @@
       </c>
       <c r="O173" s="55" t="n">
         <f aca="false">O57+O95+O133</f>
-        <v>191.55421353577</v>
+        <v>191.586750583436</v>
       </c>
       <c r="P173" s="55" t="n">
         <f aca="false">P57+P95+P133</f>
-        <v>224.304886086925</v>
+        <v>224.338474976264</v>
       </c>
       <c r="Q173" s="55" t="n">
         <f aca="false">Q57+Q95+Q133</f>
-        <v>256.202705760453</v>
+        <v>256.240665640211</v>
       </c>
       <c r="R173" s="55" t="n">
         <f aca="false">R57+R95+R133</f>
-        <v>288.329328234243</v>
+        <v>288.374600167855</v>
       </c>
       <c r="S173" s="55" t="n">
         <f aca="false">S57+S95+S133</f>
-        <v>323.756902572175</v>
+        <v>323.813709910921</v>
       </c>
       <c r="T173" s="55" t="n">
         <f aca="false">T57+T95+T133</f>
-        <v>374.139564466567</v>
+        <v>374.245673643184</v>
       </c>
       <c r="U173" s="55" t="n">
         <f aca="false">U57+U95+U133</f>
-        <v>418.47781584636</v>
+        <v>418.605172064436</v>
       </c>
       <c r="V173" s="55" t="n">
         <f aca="false">V57+V95+V133</f>
-        <v>456.965634651823</v>
+        <v>457.106423128504</v>
       </c>
       <c r="W173" s="55" t="n">
         <f aca="false">W57+W95+W133</f>
-        <v>590.578502891373</v>
+        <v>590.712975489038</v>
       </c>
       <c r="X173" s="55" t="n">
         <f aca="false">X57+X95+X133</f>
-        <v>725.586326198301</v>
+        <v>725.78286147052</v>
       </c>
       <c r="Y173" s="55" t="n">
         <f aca="false">Y57+Y95+Y133</f>
-        <v>855.04477533579</v>
+        <v>855.277263365812</v>
       </c>
       <c r="Z173" s="55" t="n">
         <f aca="false">Z57+Z95+Z133</f>
-        <v>1016.87020369037</v>
+        <v>1017.12046652749</v>
       </c>
       <c r="AA173" s="55" t="n">
         <f aca="false">AA57+AA95+AA133</f>
-        <v>62187.1008993788</v>
+        <v>62215.0744400224</v>
       </c>
       <c r="AB173" s="55" t="n">
         <f aca="false">AB57+AB95+AB133</f>
-        <v>118345.732448815</v>
+        <v>118410.489675431</v>
       </c>
       <c r="AC173" s="55" t="n">
         <f aca="false">AC57+AC95+AC133</f>
-        <v>200184.523532975</v>
+        <v>200307.051539335</v>
       </c>
       <c r="AD173" s="55" t="n">
         <f aca="false">AD57+AD95+AD133</f>
-        <v>305607.467843289</v>
+        <v>305813.742431434</v>
       </c>
       <c r="AE173" s="55" t="n">
         <f aca="false">AE57+AE95+AE133</f>
-        <v>427872.837499663</v>
+        <v>428191.799630292</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25479,71 +25479,71 @@
       </c>
       <c r="O174" s="55" t="n">
         <f aca="false">O59+O97+O135</f>
-        <v>2.71155226408484</v>
+        <v>2.74440467752041</v>
       </c>
       <c r="P174" s="55" t="n">
         <f aca="false">P59+P97+P135</f>
-        <v>3.07644988120517</v>
+        <v>3.11375577631226</v>
       </c>
       <c r="Q174" s="55" t="n">
         <f aca="false">Q59+Q97+Q135</f>
-        <v>3.5465529919782</v>
+        <v>3.58957399916214</v>
       </c>
       <c r="R174" s="55" t="n">
         <f aca="false">R59+R97+R135</f>
-        <v>3.96445069320765</v>
+        <v>4.01255191037344</v>
       </c>
       <c r="S174" s="55" t="n">
         <f aca="false">S59+S97+S135</f>
-        <v>4.58848404326472</v>
+        <v>4.64415498952909</v>
       </c>
       <c r="T174" s="55" t="n">
         <f aca="false">T59+T97+T135</f>
-        <v>5.57812580004618</v>
+        <v>5.64579167871814</v>
       </c>
       <c r="U174" s="55" t="n">
         <f aca="false">U59+U97+U135</f>
-        <v>6.6265073066415</v>
+        <v>6.70687644409304</v>
       </c>
       <c r="V174" s="55" t="n">
         <f aca="false">V59+V97+V135</f>
-        <v>7.67537578263181</v>
+        <v>7.76845219808434</v>
       </c>
       <c r="W174" s="55" t="n">
         <f aca="false">W59+W97+W135</f>
-        <v>10.39159982551</v>
+        <v>10.5160611360326</v>
       </c>
       <c r="X174" s="55" t="n">
         <f aca="false">X59+X97+X135</f>
-        <v>12.8700681308494</v>
+        <v>13.0229282234751</v>
       </c>
       <c r="Y174" s="55" t="n">
         <f aca="false">Y59+Y97+Y135</f>
-        <v>15.6287753459523</v>
+        <v>15.8132150357363</v>
       </c>
       <c r="Z174" s="55" t="n">
         <f aca="false">Z59+Z97+Z135</f>
-        <v>19.4922944583861</v>
+        <v>19.7208778171954</v>
       </c>
       <c r="AA174" s="55" t="n">
         <f aca="false">AA59+AA97+AA135</f>
-        <v>2122.29690566337</v>
+        <v>2145.74531473225</v>
       </c>
       <c r="AB174" s="55" t="n">
         <f aca="false">AB59+AB97+AB135</f>
-        <v>5015.30481462518</v>
+        <v>5069.58660752383</v>
       </c>
       <c r="AC174" s="55" t="n">
         <f aca="false">AC59+AC97+AC135</f>
-        <v>9637.59151806038</v>
+        <v>9740.29881750881</v>
       </c>
       <c r="AD174" s="55" t="n">
         <f aca="false">AD59+AD97+AD135</f>
-        <v>16442.1960670334</v>
+        <v>16615.1027070963</v>
       </c>
       <c r="AE174" s="55" t="n">
         <f aca="false">AE59+AE97+AE135</f>
-        <v>25709.7878093375</v>
+        <v>25977.1531247173</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25803,119 +25803,119 @@
       </c>
       <c r="C177" s="57" t="n">
         <f aca="false">C61+C99+C137+C141</f>
-        <v>181.931856714001</v>
+        <v>184.131372285898</v>
       </c>
       <c r="D177" s="57" t="n">
         <f aca="false">D61+D99+D137+D141</f>
-        <v>345.928312359987</v>
+        <v>350.110231003215</v>
       </c>
       <c r="E177" s="57" t="n">
         <f aca="false">E61+E99+E137+E141</f>
-        <v>494.673759404373</v>
+        <v>500.653472321506</v>
       </c>
       <c r="F177" s="57" t="n">
         <f aca="false">F61+F99+F137+F141</f>
-        <v>677.484636752019</v>
+        <v>685.673580029681</v>
       </c>
       <c r="G177" s="57" t="n">
         <f aca="false">G61+G99+G137+G141</f>
-        <v>831.517945595126</v>
+        <v>841.567998651527</v>
       </c>
       <c r="H177" s="57" t="n">
         <f aca="false">H61+H99+H137+H141</f>
-        <v>949.220464905802</v>
+        <v>960.692374699152</v>
       </c>
       <c r="I177" s="57" t="n">
         <f aca="false">I61+I99+I137+I141</f>
-        <v>2334.73201495568</v>
+        <v>2347.49053373085</v>
       </c>
       <c r="J177" s="57" t="n">
         <f aca="false">J61+J99+J137+J141</f>
-        <v>2558.70592619893</v>
+        <v>2572.68753775556</v>
       </c>
       <c r="K177" s="57" t="n">
         <f aca="false">K61+K99+K137+K141</f>
-        <v>2803.39509035592</v>
+        <v>2818.712745401</v>
       </c>
       <c r="L177" s="57" t="n">
         <f aca="false">L61+L99+L137+L141</f>
-        <v>3162.94058004422</v>
+        <v>3180.22127801229</v>
       </c>
       <c r="M177" s="57" t="n">
         <f aca="false">M61+M99+M137+M141</f>
-        <v>3465.06086592747</v>
+        <v>3483.99064451681</v>
       </c>
       <c r="N177" s="57" t="n">
         <f aca="false">N61+N99+N137+N141</f>
-        <v>3696.77225175916</v>
+        <v>3716.96638506228</v>
       </c>
       <c r="O177" s="57" t="n">
         <f aca="false">O61+O99+O137+O141</f>
-        <v>21807.7261806775</v>
+        <v>21834.1812236695</v>
       </c>
       <c r="P177" s="57" t="n">
         <f aca="false">P61+P99+P137+P141</f>
-        <v>22981.8163942083</v>
+        <v>23013.9070306778</v>
       </c>
       <c r="Q177" s="57" t="n">
         <f aca="false">Q61+Q99+Q137+Q141</f>
-        <v>24063.9621025226</v>
+        <v>24101.2373940647</v>
       </c>
       <c r="R177" s="57" t="n">
         <f aca="false">R61+R99+R137+R141</f>
-        <v>25456.1090848967</v>
+        <v>25500.1178332969</v>
       </c>
       <c r="S177" s="57" t="n">
         <f aca="false">S61+S99+S137+S141</f>
-        <v>26651.4711615074</v>
+        <v>26701.2182056952</v>
       </c>
       <c r="T177" s="57" t="n">
         <f aca="false">T61+T99+T137+T141</f>
-        <v>27584.5148262894</v>
+        <v>27638.6546832649</v>
       </c>
       <c r="U177" s="57" t="n">
         <f aca="false">U61+U99+U137+U141</f>
-        <v>28437.290999733</v>
+        <v>28495.4234564326</v>
       </c>
       <c r="V177" s="57" t="n">
         <f aca="false">V61+V99+V137+V141</f>
-        <v>29258.797253652</v>
+        <v>29320.7899731129</v>
       </c>
       <c r="W177" s="57" t="n">
         <f aca="false">W61+W99+W137+W141</f>
-        <v>30280.6060482521</v>
+        <v>30346.9854926847</v>
       </c>
       <c r="X177" s="57" t="n">
         <f aca="false">X61+X99+X137+X141</f>
-        <v>31787.5424298412</v>
+        <v>31860.7735438614</v>
       </c>
       <c r="Y177" s="57" t="n">
         <f aca="false">Y61+Y99+Y137+Y141</f>
-        <v>33094.0005572953</v>
+        <v>33173.0868927854</v>
       </c>
       <c r="Z177" s="57" t="n">
         <f aca="false">Z61+Z99+Z137+Z141</f>
-        <v>34174.2866609941</v>
+        <v>34257.9428621792</v>
       </c>
       <c r="AA177" s="57" t="n">
         <f aca="false">AA61+AA99+AA137+AA141</f>
-        <v>846755.311730761</v>
+        <v>848670.748743382</v>
       </c>
       <c r="AB177" s="57" t="n">
         <f aca="false">AB61+AB99+AB137+AB141</f>
-        <v>1364670.03340966</v>
+        <v>1367863.77386022</v>
       </c>
       <c r="AC177" s="57" t="n">
         <f aca="false">AC61+AC99+AC137+AC141</f>
-        <v>1988118.72403506</v>
+        <v>1992956.92406598</v>
       </c>
       <c r="AD177" s="57" t="n">
         <f aca="false">AD61+AD99+AD137+AD141</f>
-        <v>2660155.51500354</v>
+        <v>2666743.68656794</v>
       </c>
       <c r="AE177" s="57" t="n">
         <f aca="false">AE61+AE99+AE137+AE141</f>
-        <v>3308374.82531893</v>
+        <v>3316448.60540122</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25927,119 +25927,119 @@
       </c>
       <c r="C178" s="55" t="n">
         <f aca="false">IF(C145=0,0,C177/C145/C7*12)</f>
-        <v>19.8100762812873</v>
+        <v>20.0495756853397</v>
       </c>
       <c r="D178" s="55" t="n">
         <f aca="false">IF(D145=0,0,D177/D145/D7*12)</f>
-        <v>19.8102123752977</v>
+        <v>20.0496975330559</v>
       </c>
       <c r="E178" s="55" t="n">
         <f aca="false">IF(E145=0,0,E177/E145/E7*12)</f>
-        <v>19.8103446503151</v>
+        <v>20.0498159615506</v>
       </c>
       <c r="F178" s="55" t="n">
         <f aca="false">IF(F145=0,0,F177/F145/F7*12)</f>
-        <v>19.8105007112432</v>
+        <v>20.0499556860515</v>
       </c>
       <c r="G178" s="55" t="n">
         <f aca="false">IF(G145=0,0,G177/G145/G7*12)</f>
-        <v>19.8106503148725</v>
+        <v>20.0500896292023</v>
       </c>
       <c r="H178" s="55" t="n">
         <f aca="false">IF(H145=0,0,H177/H145/H7*12)</f>
-        <v>19.8107829783486</v>
+        <v>20.0502084054919</v>
       </c>
       <c r="I178" s="55" t="n">
         <f aca="false">IF(I145=0,0,I177/I145/I7*12)</f>
-        <v>43.8109132981804</v>
+        <v>44.0503250834694</v>
       </c>
       <c r="J178" s="55" t="n">
         <f aca="false">IF(J145=0,0,J177/J145/J7*12)</f>
-        <v>43.8110452309536</v>
+        <v>44.0504432055459</v>
       </c>
       <c r="K178" s="55" t="n">
         <f aca="false">IF(K145=0,0,K177/K145/K7*12)</f>
-        <v>43.8111897646247</v>
+        <v>44.0505726094608</v>
       </c>
       <c r="L178" s="55" t="n">
         <f aca="false">IF(L145=0,0,L177/L145/L7*12)</f>
-        <v>43.8113785721867</v>
+        <v>44.0507416526844</v>
       </c>
       <c r="M178" s="55" t="n">
         <f aca="false">IF(M145=0,0,M177/M145/M7*12)</f>
-        <v>43.8115566060345</v>
+        <v>44.0509010499841</v>
       </c>
       <c r="N178" s="55" t="n">
         <f aca="false">IF(N145=0,0,N177/N145/N7*12)</f>
-        <v>43.8117174342908</v>
+        <v>44.0510450427702</v>
       </c>
       <c r="O178" s="55" t="n">
         <f aca="false">IF(O145=0,0,O177/O145/O7*12)</f>
-        <v>192.962790603797</v>
+        <v>193.196874564636</v>
       </c>
       <c r="P178" s="55" t="n">
         <f aca="false">IF(P145=0,0,P177/P145/P7*12)</f>
-        <v>165.090116170837</v>
+        <v>165.32063959039</v>
       </c>
       <c r="Q178" s="55" t="n">
         <f aca="false">IF(Q145=0,0,Q177/Q145/Q7*12)</f>
-        <v>147.359642219862</v>
+        <v>147.587903617627</v>
       </c>
       <c r="R178" s="55" t="n">
         <f aca="false">IF(R145=0,0,R177/R145/R7*12)</f>
-        <v>130.87945253438</v>
+        <v>131.105718099087</v>
       </c>
       <c r="S178" s="55" t="n">
         <f aca="false">IF(S145=0,0,S177/S145/S7*12)</f>
-        <v>120.541414227899</v>
+        <v>120.766414154684</v>
       </c>
       <c r="T178" s="55" t="n">
         <f aca="false">IF(T145=0,0,T177/T145/T7*12)</f>
-        <v>114.304261263848</v>
+        <v>114.528605117473</v>
       </c>
       <c r="U178" s="55" t="n">
         <f aca="false">IF(U145=0,0,U177/U145/U7*12)</f>
-        <v>109.43679334442</v>
+        <v>109.660507679604</v>
       </c>
       <c r="V178" s="55" t="n">
         <f aca="false">IF(V145=0,0,V177/V145/V7*12)</f>
-        <v>105.330018881626</v>
+        <v>105.553189173102</v>
       </c>
       <c r="W178" s="55" t="n">
         <f aca="false">IF(W145=0,0,W177/W145/W7*12)</f>
-        <v>101.599901544562</v>
+        <v>101.822623144261</v>
       </c>
       <c r="X178" s="55" t="n">
         <f aca="false">IF(X145=0,0,X177/X145/X7*12)</f>
-        <v>96.4985209951169</v>
+        <v>96.720831172425</v>
       </c>
       <c r="Y178" s="55" t="n">
         <f aca="false">IF(Y145=0,0,Y177/Y145/Y7*12)</f>
-        <v>92.8847277000425</v>
+        <v>93.1066988311567</v>
       </c>
       <c r="Z178" s="55" t="n">
         <f aca="false">IF(Z145=0,0,Z177/Z145/Z7*12)</f>
-        <v>90.6085430095575</v>
+        <v>90.8303462202079</v>
       </c>
       <c r="AA178" s="55" t="n">
         <f aca="false">IF(AA145=0,0,AA177/AA145/AA7*12)</f>
-        <v>97.1137877421288</v>
+        <v>97.3334679034458</v>
       </c>
       <c r="AB178" s="55" t="n">
         <f aca="false">IF(AB145=0,0,AB177/AB145/AB7*12)</f>
-        <v>93.5571065621584</v>
+        <v>93.7760584760645</v>
       </c>
       <c r="AC178" s="55" t="n">
         <f aca="false">IF(AC145=0,0,AC177/AC145/AC7*12)</f>
-        <v>89.5523573522711</v>
+        <v>89.7702881090575</v>
       </c>
       <c r="AD178" s="55" t="n">
         <f aca="false">IF(AD145=0,0,AD177/AD145/AD7*12)</f>
-        <v>87.8351223791735</v>
+        <v>88.0526558475556</v>
       </c>
       <c r="AE178" s="55" t="n">
         <f aca="false">IF(AE145=0,0,AE177/AE145/AE7*12)</f>
-        <v>88.6596459384133</v>
+        <v>88.8760115321793</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26311,31 +26311,31 @@
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">SUM(Model!C137:N137)</f>
-        <v>14741.6818819637</v>
+        <v>14882.2163304608</v>
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">SUM(Model!O137:Z137)</f>
-        <v>87569.9459754207</v>
+        <v>88236.1408672764</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">Model!AA137</f>
-        <v>273864.078386585</v>
+        <v>275779.515399206</v>
       </c>
       <c r="G9" s="36" t="n">
         <f aca="false">Model!AB137</f>
-        <v>460141.087667566</v>
+        <v>463334.828118131</v>
       </c>
       <c r="H9" s="36" t="n">
         <f aca="false">Model!AC137</f>
-        <v>702115.398151262</v>
+        <v>706953.598182178</v>
       </c>
       <c r="I9" s="36" t="n">
         <f aca="false">Model!AD137</f>
-        <v>963922.418165796</v>
+        <v>970510.5897302</v>
       </c>
       <c r="J9" s="36" t="n">
         <f aca="false">Model!AE137</f>
-        <v>1192704.12167941</v>
+        <v>1200777.9017617</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26377,31 +26377,31 @@
       </c>
       <c r="D11" s="62" t="n">
         <f aca="false">SUM(Model!C177:N177)</f>
-        <v>21502.3637049727</v>
+        <v>21642.8981534698</v>
       </c>
       <c r="E11" s="62" t="n">
         <f aca="false">SUM(Model!O177:Z177)</f>
-        <v>335578.12369987</v>
+        <v>336244.318591725</v>
       </c>
       <c r="F11" s="62" t="n">
         <f aca="false">Model!AA177</f>
-        <v>846755.311730761</v>
+        <v>848670.748743382</v>
       </c>
       <c r="G11" s="62" t="n">
         <f aca="false">Model!AB177</f>
-        <v>1364670.03340966</v>
+        <v>1367863.77386022</v>
       </c>
       <c r="H11" s="62" t="n">
         <f aca="false">Model!AC177</f>
-        <v>1988118.72403506</v>
+        <v>1992956.92406598</v>
       </c>
       <c r="I11" s="62" t="n">
         <f aca="false">Model!AD177</f>
-        <v>2660155.51500354</v>
+        <v>2666743.68656794</v>
       </c>
       <c r="J11" s="62" t="n">
         <f aca="false">Model!AE177</f>
-        <v>3308374.82531893</v>
+        <v>3316448.60540122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26458,31 +26458,31 @@
       </c>
       <c r="D15" s="36" t="n">
         <f aca="false">SUM(Model!C170:N170)</f>
-        <v>687.988657196623</v>
+        <v>828.523105693701</v>
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">SUM(Model!O170:Z170)</f>
-        <v>3509.68873383427</v>
+        <v>4172.30490877886</v>
       </c>
       <c r="F15" s="36" t="n">
         <f aca="false">Model!AA170</f>
-        <v>10495.5478292588</v>
+        <v>12338.8295620433</v>
       </c>
       <c r="G15" s="36" t="n">
         <f aca="false">Model!AB170</f>
-        <v>17696.2121835003</v>
+        <v>20722.9170818821</v>
       </c>
       <c r="H15" s="36" t="n">
         <f aca="false">Model!AC170</f>
-        <v>27156.4938377424</v>
+        <v>31678.6436875481</v>
       </c>
       <c r="I15" s="36" t="n">
         <f aca="false">Model!AD170</f>
-        <v>37345.6730014924</v>
+        <v>43401.7774664748</v>
       </c>
       <c r="J15" s="36" t="n">
         <f aca="false">Model!AE170</f>
-        <v>46589.7719762917</v>
+        <v>53840.8173863433</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26495,27 +26495,27 @@
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">SUM(Model!O171:Z171)</f>
-        <v>86.827093641906</v>
+        <v>87.8632254929623</v>
       </c>
       <c r="F16" s="36" t="n">
         <f aca="false">Model!AA171</f>
-        <v>1876.55726395498</v>
+        <v>1897.29059407904</v>
       </c>
       <c r="G16" s="36" t="n">
         <f aca="false">Model!AB171</f>
-        <v>4434.58530977384</v>
+        <v>4482.58184244213</v>
       </c>
       <c r="H16" s="36" t="n">
         <f aca="false">Model!AC171</f>
-        <v>8521.65986860076</v>
+        <v>8612.47474390253</v>
       </c>
       <c r="I16" s="36" t="n">
         <f aca="false">Model!AD171</f>
-        <v>14538.362838219</v>
+        <v>14691.2487094325</v>
       </c>
       <c r="J16" s="36" t="n">
         <f aca="false">Model!AE171</f>
-        <v>22732.8650103616</v>
+        <v>22969.2722365921</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26561,27 +26561,27 @@
       </c>
       <c r="E18" s="36" t="n">
         <f aca="false">SUM(Model!O173:Z173)</f>
-        <v>5721.81085927016</v>
+        <v>5723.20503696767</v>
       </c>
       <c r="F18" s="36" t="n">
         <f aca="false">Model!AA173</f>
-        <v>62187.1008993788</v>
+        <v>62215.0744400224</v>
       </c>
       <c r="G18" s="36" t="n">
         <f aca="false">Model!AB173</f>
-        <v>118345.732448815</v>
+        <v>118410.489675431</v>
       </c>
       <c r="H18" s="36" t="n">
         <f aca="false">Model!AC173</f>
-        <v>200184.523532975</v>
+        <v>200307.051539335</v>
       </c>
       <c r="I18" s="36" t="n">
         <f aca="false">Model!AD173</f>
-        <v>305607.467843289</v>
+        <v>305813.742431434</v>
       </c>
       <c r="J18" s="36" t="n">
         <f aca="false">Model!AE173</f>
-        <v>427872.837499663</v>
+        <v>428191.799630292</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26594,27 +26594,27 @@
       </c>
       <c r="E19" s="36" t="n">
         <f aca="false">SUM(Model!O174:Z174)</f>
-        <v>96.1502365237579</v>
+        <v>97.2986438862322</v>
       </c>
       <c r="F19" s="36" t="n">
         <f aca="false">Model!AA174</f>
-        <v>2122.29690566337</v>
+        <v>2145.74531473225</v>
       </c>
       <c r="G19" s="36" t="n">
         <f aca="false">Model!AB174</f>
-        <v>5015.30481462518</v>
+        <v>5069.58660752383</v>
       </c>
       <c r="H19" s="36" t="n">
         <f aca="false">Model!AC174</f>
-        <v>9637.59151806038</v>
+        <v>9740.29881750881</v>
       </c>
       <c r="I19" s="36" t="n">
         <f aca="false">Model!AD174</f>
-        <v>16442.1960670334</v>
+        <v>16615.1027070963</v>
       </c>
       <c r="J19" s="36" t="n">
         <f aca="false">Model!AE174</f>
-        <v>25709.7878093375</v>
+        <v>25977.1531247173</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26656,31 +26656,31 @@
       </c>
       <c r="D21" s="62" t="n">
         <f aca="false">SUM(Model!C177:N177)</f>
-        <v>21502.3637049727</v>
+        <v>21642.8981534698</v>
       </c>
       <c r="E21" s="62" t="n">
         <f aca="false">SUM(Model!O177:Z177)</f>
-        <v>335578.12369987</v>
+        <v>336244.318591725</v>
       </c>
       <c r="F21" s="62" t="n">
         <f aca="false">Model!AA177</f>
-        <v>846755.311730761</v>
+        <v>848670.748743382</v>
       </c>
       <c r="G21" s="62" t="n">
         <f aca="false">Model!AB177</f>
-        <v>1364670.03340966</v>
+        <v>1367863.77386022</v>
       </c>
       <c r="H21" s="62" t="n">
         <f aca="false">Model!AC177</f>
-        <v>1988118.72403506</v>
+        <v>1992956.92406598</v>
       </c>
       <c r="I21" s="62" t="n">
         <f aca="false">Model!AD177</f>
-        <v>2660155.51500354</v>
+        <v>2666743.68656794</v>
       </c>
       <c r="J21" s="62" t="n">
         <f aca="false">Model!AE177</f>
-        <v>3308374.82531893</v>
+        <v>3316448.60540122</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26704,31 +26704,31 @@
       </c>
       <c r="D24" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D14/D$11)</f>
-        <v>0.508877971578608</v>
+        <v>0.505573659716999</v>
       </c>
       <c r="E24" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E14/E$11)</f>
-        <v>0.163479194616331</v>
+        <v>0.163155296193797</v>
       </c>
       <c r="F24" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F14/F$11)</f>
-        <v>0.189916514736274</v>
+        <v>0.189487876041972</v>
       </c>
       <c r="G24" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G14/G$11)</f>
-        <v>0.197192267734051</v>
+        <v>0.196731855714934</v>
       </c>
       <c r="H24" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H14/H$11)</f>
-        <v>0.206126192367241</v>
+        <v>0.205625790307246</v>
       </c>
       <c r="I24" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I14/I$11)</f>
-        <v>0.210274551250356</v>
+        <v>0.209755069447045</v>
       </c>
       <c r="J24" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J14/J$11)</f>
-        <v>0.208530996155099</v>
+        <v>0.208023334616019</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26737,31 +26737,31 @@
       </c>
       <c r="D25" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D15/D$11)</f>
-        <v>0.0319959547999608</v>
+        <v>0.0382815231037287</v>
       </c>
       <c r="E25" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E15/E$11)</f>
-        <v>0.0104586338797616</v>
+        <v>0.0124085513957634</v>
       </c>
       <c r="F25" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F15/F$11)</f>
-        <v>0.0123950185890254</v>
+        <v>0.014539006535</v>
       </c>
       <c r="G25" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G15/G$11)</f>
-        <v>0.0129673926665525</v>
+        <v>0.015149839829006</v>
       </c>
       <c r="H25" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H15/H$11)</f>
-        <v>0.0136593924243246</v>
+        <v>0.0158952977382563</v>
       </c>
       <c r="I25" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I15/I$11)</f>
-        <v>0.014038905917665</v>
+        <v>0.0162751964821682</v>
       </c>
       <c r="J25" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J15/J$11)</f>
-        <v>0.0140823741069909</v>
+        <v>0.0162344796474932</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26774,27 +26774,27 @@
       </c>
       <c r="E26" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E16/E$11)</f>
-        <v>0.000258738837575602</v>
+        <v>0.000261307687995905</v>
       </c>
       <c r="F26" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F16/F$11)</f>
-        <v>0.00221617418628211</v>
+        <v>0.0022356026726364</v>
       </c>
       <c r="G26" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G16/G$11)</f>
-        <v>0.00324956597654155</v>
+        <v>0.00327706744494879</v>
       </c>
       <c r="H26" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H16/H$11)</f>
-        <v>0.00428629325079002</v>
+        <v>0.00432145554171416</v>
       </c>
       <c r="I26" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I16/I$11)</f>
-        <v>0.00546523041838014</v>
+        <v>0.00550905915084024</v>
       </c>
       <c r="J26" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J16/J$11)</f>
-        <v>0.00687130878774298</v>
+        <v>0.00692586407013334</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26803,31 +26803,31 @@
       </c>
       <c r="D27" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D17/D$11)</f>
-        <v>0.459126073621431</v>
+        <v>0.456144817179273</v>
       </c>
       <c r="E27" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E17/E$11)</f>
-        <v>0.212479897667754</v>
+        <v>0.212058915023226</v>
       </c>
       <c r="F27" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F17/F$11)</f>
-        <v>0.247132776488221</v>
+        <v>0.24657500155864</v>
       </c>
       <c r="G27" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G17/G$11)</f>
-        <v>0.256527813673402</v>
+        <v>0.255928862761126</v>
       </c>
       <c r="H27" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H17/H$11)</f>
-        <v>0.267999645230906</v>
+        <v>0.267349036140372</v>
       </c>
       <c r="I27" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I17/I$11)</f>
-        <v>0.273239216271538</v>
+        <v>0.272564180705133</v>
       </c>
       <c r="J27" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J17/J$11)</f>
-        <v>0.270698125917076</v>
+        <v>0.270039120638423</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26840,27 +26840,27 @@
       </c>
       <c r="E28" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E18/E$11)</f>
-        <v>0.0170506074597031</v>
+        <v>0.0170209717176423</v>
       </c>
       <c r="F28" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F18/F$11)</f>
-        <v>0.0734416425121312</v>
+        <v>0.0733088474324626</v>
       </c>
       <c r="G28" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G18/G$11)</f>
-        <v>0.0867211337184024</v>
+        <v>0.0865659957798776</v>
       </c>
       <c r="H28" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H18/H$11)</f>
-        <v>0.100690427142441</v>
+        <v>0.100507466629371</v>
       </c>
       <c r="I28" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I18/I$11)</f>
-        <v>0.114883308934246</v>
+        <v>0.114676841262166</v>
       </c>
       <c r="J28" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J18/J$11)</f>
-        <v>0.129330218034898</v>
+        <v>0.129111543876462</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26873,27 +26873,27 @@
       </c>
       <c r="E29" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E19/E$11)</f>
-        <v>0.00028652116968671</v>
+        <v>0.000289368885974767</v>
       </c>
       <c r="F29" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F19/F$11)</f>
-        <v>0.00250638747258096</v>
+        <v>0.00252836016548165</v>
       </c>
       <c r="G29" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G19/G$11)</f>
-        <v>0.00367510437823151</v>
+        <v>0.00370620722940637</v>
       </c>
       <c r="H29" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H19/H$11)</f>
-        <v>0.00484759355744109</v>
+        <v>0.00488736043408149</v>
       </c>
       <c r="I29" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I19/I$11)</f>
-        <v>0.00618091535412039</v>
+        <v>0.00623048356345027</v>
       </c>
       <c r="J29" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J19/J$11)</f>
-        <v>0.00777112303375694</v>
+        <v>0.00783282246026985</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26906,27 +26906,27 @@
       </c>
       <c r="E30" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E20/E$11)</f>
-        <v>0.595986406369188</v>
+        <v>0.594805589095601</v>
       </c>
       <c r="F30" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F20/F$11)</f>
-        <v>0.472391486015486</v>
+        <v>0.471325305593808</v>
       </c>
       <c r="G30" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G20/G$11)</f>
-        <v>0.439666721852818</v>
+        <v>0.438640171240702</v>
       </c>
       <c r="H30" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H20/H$11)</f>
-        <v>0.402390456026856</v>
+        <v>0.40141359320896</v>
       </c>
       <c r="I30" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I20/I$11)</f>
-        <v>0.375917871853695</v>
+        <v>0.374989169389198</v>
       </c>
       <c r="J30" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J20/J$11)</f>
-        <v>0.362715853964437</v>
+        <v>0.3618328346912</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27148,31 +27148,31 @@
       </c>
       <c r="D39" s="37" t="n">
         <f aca="false">Model!N151</f>
-        <v>1490.81461636238</v>
+        <v>1508.82908063099</v>
       </c>
       <c r="E39" s="37" t="n">
         <f aca="false">Model!Z151</f>
-        <v>8215.89958372056</v>
+        <v>8310.10632523785</v>
       </c>
       <c r="F39" s="37" t="n">
         <f aca="false">Model!AA151</f>
-        <v>26628.2849358229</v>
+        <v>26919.8579208016</v>
       </c>
       <c r="G39" s="37" t="n">
         <f aca="false">Model!AB151</f>
-        <v>53309.7139526035</v>
+        <v>53881.3629482092</v>
       </c>
       <c r="H39" s="37" t="n">
         <f aca="false">Model!AC151</f>
-        <v>88675.2704971467</v>
+        <v>89609.9457199556</v>
       </c>
       <c r="I39" s="37" t="n">
         <f aca="false">Model!AD151</f>
-        <v>130160.282221264</v>
+        <v>131510.629369433</v>
       </c>
       <c r="J39" s="37" t="n">
         <f aca="false">Model!AE151</f>
-        <v>173016.451947087</v>
+        <v>174777.77159115</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27181,31 +27181,31 @@
       </c>
       <c r="D40" s="62" t="n">
         <f aca="false">Model!N158</f>
-        <v>210890.635630622</v>
+        <v>213438.96174606</v>
       </c>
       <c r="E40" s="62" t="n">
         <f aca="false">Model!Z158</f>
-        <v>1256361.06867727</v>
+        <v>1270766.99967037</v>
       </c>
       <c r="F40" s="62" t="n">
         <f aca="false">Model!AA158</f>
-        <v>4401779.03010304</v>
+        <v>4449977.39714459</v>
       </c>
       <c r="G40" s="62" t="n">
         <f aca="false">Model!AB158</f>
-        <v>9526142.80821646</v>
+        <v>9628293.23380596</v>
       </c>
       <c r="H40" s="62" t="n">
         <f aca="false">Model!AC158</f>
-        <v>17129273.806276</v>
+        <v>17309823.667829</v>
       </c>
       <c r="I40" s="62" t="n">
         <f aca="false">Model!AD158</f>
-        <v>27179446.3044826</v>
+        <v>27461419.3240532</v>
       </c>
       <c r="J40" s="62" t="n">
         <f aca="false">Model!AE158</f>
-        <v>39054872.0342436</v>
+        <v>39452453.3771514</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27214,31 +27214,31 @@
       </c>
       <c r="D41" s="37" t="n">
         <f aca="false">Model!N150</f>
-        <v>1435.20489652243</v>
+        <v>1452.54727924063</v>
       </c>
       <c r="E41" s="37" t="n">
         <f aca="false">Model!Z150</f>
-        <v>7729.43986038715</v>
+        <v>7817.95188429086</v>
       </c>
       <c r="F41" s="37" t="n">
         <f aca="false">Model!AA150</f>
-        <v>25272.7485111844</v>
+        <v>25548.6925371541</v>
       </c>
       <c r="G41" s="37" t="n">
         <f aca="false">Model!AB150</f>
-        <v>49092.720090644</v>
+        <v>49617.6094811976</v>
       </c>
       <c r="H41" s="37" t="n">
         <f aca="false">Model!AC150</f>
-        <v>79119.3497704202</v>
+        <v>79950.4296637671</v>
       </c>
       <c r="I41" s="37" t="n">
         <f aca="false">Model!AD150</f>
-        <v>112404.241501835</v>
+        <v>113565.364993544</v>
       </c>
       <c r="J41" s="37" t="n">
         <f aca="false">Model!AE150</f>
-        <v>144257.963038907</v>
+        <v>145717.396509327</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27247,31 +27247,31 @@
       </c>
       <c r="D42" s="62" t="n">
         <f aca="false">Model!N153</f>
-        <v>203024.084662064</v>
+        <v>205477.33812138</v>
       </c>
       <c r="E42" s="62" t="n">
         <f aca="false">Model!Z153</f>
-        <v>1181972.49422505</v>
+        <v>1195507.59890948</v>
       </c>
       <c r="F42" s="62" t="n">
         <f aca="false">Model!AA153</f>
-        <v>4177702.57069549</v>
+        <v>4223317.39830918</v>
       </c>
       <c r="G42" s="62" t="n">
         <f aca="false">Model!AB153</f>
-        <v>8772589.97943718</v>
+        <v>8866384.72944046</v>
       </c>
       <c r="H42" s="62" t="n">
         <f aca="false">Model!AC153</f>
-        <v>15283370.4142539</v>
+        <v>15443908.9157799</v>
       </c>
       <c r="I42" s="62" t="n">
         <f aca="false">Model!AD153</f>
-        <v>23471714.9821616</v>
+        <v>23714175.2246966</v>
       </c>
       <c r="J42" s="62" t="n">
         <f aca="false">Model!AE153</f>
-        <v>32563240.2179197</v>
+        <v>32892677.0245833</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27280,31 +27280,31 @@
       </c>
       <c r="D43" s="36" t="n">
         <f aca="false">Model!N178</f>
-        <v>43.8117174342908</v>
+        <v>44.0510450427702</v>
       </c>
       <c r="E43" s="36" t="n">
         <f aca="false">Model!Z178</f>
-        <v>90.6085430095575</v>
+        <v>90.8303462202079</v>
       </c>
       <c r="F43" s="36" t="n">
         <f aca="false">Model!AA178</f>
-        <v>97.1137877421288</v>
+        <v>97.3334679034458</v>
       </c>
       <c r="G43" s="36" t="n">
         <f aca="false">Model!AB178</f>
-        <v>93.5571065621584</v>
+        <v>93.7760584760645</v>
       </c>
       <c r="H43" s="36" t="n">
         <f aca="false">Model!AC178</f>
-        <v>89.5523573522711</v>
+        <v>89.7702881090575</v>
       </c>
       <c r="I43" s="36" t="n">
         <f aca="false">Model!AD178</f>
-        <v>87.8351223791735</v>
+        <v>88.0526558475556</v>
       </c>
       <c r="J43" s="36" t="n">
         <f aca="false">Model!AE178</f>
-        <v>88.6596459384133</v>
+        <v>88.8760115321793</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
@@ -48,7 +48,8 @@
     <definedName function="false" hidden="false" name="atm_a500" vbProcedure="false">'Scenario Parameters'!$B$50</definedName>
     <definedName function="false" hidden="false" name="atm_allowance" vbProcedure="false">Assumptions!$B$18</definedName>
     <definedName function="false" hidden="false" name="atm_fee" vbProcedure="false">Assumptions!$B$19</definedName>
-    <definedName function="false" hidden="false" name="aum_per_partner" vbProcedure="false">'Scenario Parameters'!$B$72</definedName>
+    <definedName function="false" hidden="false" name="aum_per_partner" vbProcedure="false">'Scenario Parameters'!$B$75</definedName>
+    <definedName function="false" hidden="false" name="aum_per_partner_user" vbProcedure="false">'Scenario Parameters'!$B$74</definedName>
     <definedName function="false" hidden="false" name="b2b_fee" vbProcedure="false">Assumptions!$B$26</definedName>
     <definedName function="false" hidden="false" name="bar_grams" vbProcedure="false">Assumptions!$B$10</definedName>
     <definedName function="false" hidden="false" name="cac_gulf" vbProcedure="false">'Scenario Parameters'!$B$18</definedName>
@@ -101,6 +102,8 @@
     <definedName function="false" hidden="false" name="partners_y5" vbProcedure="false">'Scenario Parameters'!$B$69</definedName>
     <definedName function="false" hidden="false" name="partners_y6" vbProcedure="false">'Scenario Parameters'!$B$70</definedName>
     <definedName function="false" hidden="false" name="partners_y7" vbProcedure="false">'Scenario Parameters'!$B$71</definedName>
+    <definedName function="false" hidden="false" name="partner_adoption" vbProcedure="false">'Scenario Parameters'!$B$73</definedName>
+    <definedName function="false" hidden="false" name="partner_users" vbProcedure="false">'Scenario Parameters'!$B$72</definedName>
     <definedName function="false" hidden="false" name="persistency_m13" vbProcedure="false">'Scenario Parameters'!$B$14</definedName>
     <definedName function="false" hidden="false" name="pm_share" vbProcedure="false">'Scenario Parameters'!$B$44</definedName>
     <definedName function="false" hidden="false" name="ramp_y1" vbProcedure="false">Assumptions!$B$107</definedName>
@@ -133,11 +136,11 @@
     <definedName function="false" hidden="false" name="spot_attach_mult" vbProcedure="false">'Scenario Parameters'!$B$38</definedName>
     <definedName function="false" hidden="false" name="spot_frequency" vbProcedure="false">'Scenario Parameters'!$B$40</definedName>
     <definedName function="false" hidden="false" name="spot_ticket_mult" vbProcedure="false">'Scenario Parameters'!$B$39</definedName>
-    <definedName function="false" hidden="false" name="sw_lapsed_keeps_card" vbProcedure="false">'Scenario Parameters'!$B$83</definedName>
-    <definedName function="false" hidden="false" name="sw_prepaid_vs_credit" vbProcedure="false">'Scenario Parameters'!$B$82</definedName>
-    <definedName function="false" hidden="false" name="ticket_gulf" vbProcedure="false">'Scenario Parameters'!$B$77</definedName>
-    <definedName function="false" hidden="false" name="ticket_india" vbProcedure="false">'Scenario Parameters'!$B$78</definedName>
-    <definedName function="false" hidden="false" name="ticket_uae" vbProcedure="false">'Scenario Parameters'!$B$76</definedName>
+    <definedName function="false" hidden="false" name="sw_lapsed_keeps_card" vbProcedure="false">'Scenario Parameters'!$B$86</definedName>
+    <definedName function="false" hidden="false" name="sw_prepaid_vs_credit" vbProcedure="false">'Scenario Parameters'!$B$85</definedName>
+    <definedName function="false" hidden="false" name="ticket_gulf" vbProcedure="false">'Scenario Parameters'!$B$80</definedName>
+    <definedName function="false" hidden="false" name="ticket_india" vbProcedure="false">'Scenario Parameters'!$B$81</definedName>
+    <definedName function="false" hidden="false" name="ticket_uae" vbProcedure="false">'Scenario Parameters'!$B$79</definedName>
     <definedName function="false" hidden="false" name="txn_fee" vbProcedure="false">Assumptions!$B$15</definedName>
     <definedName function="false" hidden="false" name="xchk_uae_obs" vbProcedure="false">Assumptions!$B$89</definedName>
   </definedNames>
@@ -151,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="560">
   <si>
     <t xml:space="preserve">Aurumix Revenue Model</t>
   </si>
@@ -1158,7 +1161,7 @@
     <t xml:space="preserve">partners</t>
   </si>
   <si>
-    <t xml:space="preserve">Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+    <t xml:space="preserve">RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
   </si>
   <si>
     <t xml:space="preserve">B2B partners - Y2</t>
@@ -1179,10 +1182,34 @@
     <t xml:space="preserve">B2B partners - Y7</t>
   </si>
   <si>
-    <t xml:space="preserve">AUM per partner (mature)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires a signed partner. Partner AUM earns NO tier and consumes NO benefits - structurally the highest-margin book. DERIVED.</t>
+    <t xml:space="preserve">Average partner user base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. ⚠ USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner users adopting gold (mature)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of partner users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. ⚠ THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUM per adopting partner user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DERIVED FROM BOTIM'S OWN DISCLOSURES AND CROSS-CHECKED AGAINST OUR OWN BOOK - two independent routes to nearly the same number, which is why this is the firmest input in the B2B block. Botim: AED 100m+ of gold across 128,000 trades since Aug 2025, against 75,000 active O Gold users, implies ~USD 363 per active user. Aurumix's own direct book runs at ~USD 302 of gold per customer. A partner's users are buying the same product with the same wallets. DERIVED.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUM per partner (derived)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO LONGER A TYPED NUMBER. Was a flat USD 32m asserted as 'mature AUM per partner' with no derivation. Now users x adoption x AUM per adopting user, every term of which has an external anchor. THE POINT OF THE CHANGE: the only remaining argument is the PARTNER COUNT, which rests on a nameable candidate list and is the argument that can actually be won. DERIVED.</t>
   </si>
   <si>
     <t xml:space="preserve">Average monthly ticket - UAE</t>
@@ -2715,7 +2742,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q173"/>
+  <dimension ref="A1:Q176"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
@@ -4957,7 +4984,7 @@
       </c>
       <c r="B162" s="37" t="n">
         <f aca="false">'Scenario Parameters'!$B$67</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C162" s="0" t="s">
         <v>334</v>
@@ -4972,7 +4999,7 @@
       </c>
       <c r="B163" s="37" t="n">
         <f aca="false">'Scenario Parameters'!$B$68</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C163" s="0" t="s">
         <v>334</v>
@@ -4987,7 +5014,7 @@
       </c>
       <c r="B164" s="37" t="n">
         <f aca="false">'Scenario Parameters'!$B$69</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C164" s="0" t="s">
         <v>334</v>
@@ -5002,7 +5029,7 @@
       </c>
       <c r="B165" s="37" t="n">
         <f aca="false">'Scenario Parameters'!$B$70</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C165" s="0" t="s">
         <v>334</v>
@@ -5017,7 +5044,7 @@
       </c>
       <c r="B166" s="37" t="n">
         <f aca="false">'Scenario Parameters'!$B$71</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C166" s="0" t="s">
         <v>334</v>
@@ -5030,95 +5057,140 @@
       <c r="A167" s="0" t="s">
         <v>342</v>
       </c>
-      <c r="B167" s="36" t="n">
+      <c r="B167" s="37" t="n">
         <f aca="false">'Scenario Parameters'!$B$72</f>
-        <v>32000000</v>
+        <v>900000</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>114</v>
+        <v>343</v>
       </c>
       <c r="D167" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="B168" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$76</f>
-        <v>33.6</v>
+        <v>345</v>
+      </c>
+      <c r="B168" s="34" t="n">
+        <f aca="false">'Scenario Parameters'!$B$73</f>
+        <v>0.06</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>108</v>
+        <v>346</v>
       </c>
       <c r="D168" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B169" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$77</f>
-        <v>26</v>
+        <f aca="false">'Scenario Parameters'!$B$74</f>
+        <v>350</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D169" s="0" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B170" s="36" t="n">
-        <f aca="false">'Scenario Parameters'!$B$78</f>
-        <v>30</v>
+        <f aca="false">'Scenario Parameters'!$B$75</f>
+        <v>18900000</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D170" s="0" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="B171" s="37" t="n">
-        <f aca="false">'Scenario Parameters'!$B$82</f>
-        <v>0</v>
+        <v>352</v>
+      </c>
+      <c r="B171" s="36" t="n">
+        <f aca="false">'Scenario Parameters'!$B$79</f>
+        <v>33.6</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="D171" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
-        <v>351</v>
-      </c>
-      <c r="B172" s="37" t="n">
-        <f aca="false">'Scenario Parameters'!$B$83</f>
+        <v>354</v>
+      </c>
+      <c r="B172" s="36" t="n">
+        <f aca="false">'Scenario Parameters'!$B$80</f>
+        <v>26</v>
+      </c>
+      <c r="C172" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D172" s="0" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="B173" s="36" t="n">
+        <f aca="false">'Scenario Parameters'!$B$81</f>
+        <v>30</v>
+      </c>
+      <c r="C173" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D173" s="0" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="B174" s="37" t="n">
+        <f aca="false">'Scenario Parameters'!$B$85</f>
+        <v>0</v>
+      </c>
+      <c r="C174" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="D174" s="0" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="B175" s="37" t="n">
+        <f aca="false">'Scenario Parameters'!$B$86</f>
         <v>1</v>
       </c>
-      <c r="C172" s="0" t="s">
-        <v>349</v>
-      </c>
-      <c r="D172" s="0" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="9" t="s">
-        <v>353</v>
+      <c r="C175" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="D175" s="0" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="9" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -5137,7 +5209,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -5155,12 +5227,12 @@
     </row>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5169,25 +5241,25 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">IF($B$6="Base",1,IF($B$6="Aggressive",2,3))</f>
         <v>1</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -5199,16 +5271,16 @@
         <v>30</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>32</v>
@@ -5240,7 +5312,7 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5252,16 +5324,16 @@
         <v>30</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>32</v>
@@ -5572,7 +5644,7 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -5584,16 +5656,16 @@
         <v>30</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>32</v>
@@ -5649,7 +5721,7 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -5661,16 +5733,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>32</v>
@@ -5822,7 +5894,7 @@
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -5834,16 +5906,16 @@
         <v>30</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F43" s="14" t="s">
         <v>32</v>
@@ -6187,7 +6259,7 @@
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
@@ -6199,16 +6271,16 @@
         <v>30</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="F60" s="14" t="s">
         <v>32</v>
@@ -6346,7 +6418,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="17" t="n">
         <v>1</v>
@@ -6364,13 +6436,13 @@
       </c>
       <c r="B67" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C67,D67,E67)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E67" s="17" t="n">
         <v>1</v>
@@ -6388,16 +6460,16 @@
       </c>
       <c r="B68" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C68,D68,E68)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C68" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D68" s="17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="23" t="s">
         <v>334</v>
@@ -6412,16 +6484,16 @@
       </c>
       <c r="B69" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C69,D69,E69)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D69" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="23" t="s">
         <v>334</v>
@@ -6436,16 +6508,16 @@
       </c>
       <c r="B70" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C70,D70,E70)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D70" s="17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" s="23" t="s">
         <v>334</v>
@@ -6460,16 +6532,16 @@
       </c>
       <c r="B71" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C71,D71,E71)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C71" s="17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D71" s="17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F71" s="23" t="s">
         <v>334</v>
@@ -6482,184 +6554,247 @@
       <c r="A72" s="0" t="s">
         <v>342</v>
       </c>
-      <c r="B72" s="42" t="n">
+      <c r="B72" s="31" t="n">
         <f aca="false">CHOOSE($C$6,C72,D72,E72)</f>
-        <v>32000000</v>
-      </c>
-      <c r="C72" s="20" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="D72" s="20" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E72" s="20" t="n">
-        <v>22000000</v>
+        <v>900000</v>
+      </c>
+      <c r="C72" s="17" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D72" s="17" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>500000</v>
       </c>
       <c r="F72" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="B73" s="40" t="n">
+        <f aca="false">CHOOSE($C$6,C73,D73,E73)</f>
+        <v>0.06</v>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E73" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="B74" s="42" t="n">
+        <f aca="false">CHOOSE($C$6,C74,D74,E74)</f>
+        <v>350</v>
+      </c>
+      <c r="C74" s="20" t="n">
+        <v>350</v>
+      </c>
+      <c r="D74" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="E74" s="20" t="n">
+        <v>220</v>
+      </c>
+      <c r="F74" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="G72" s="9" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
+      <c r="G74" s="9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="B75" s="42" t="n">
+        <f aca="false">'Scenario Parameters'!$B$72*'Scenario Parameters'!$B$73*'Scenario Parameters'!$B$74</f>
+        <v>18900000</v>
+      </c>
+      <c r="F75" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="14" t="s">
+      <c r="C78" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="D78" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="E78" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="F78" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="B79" s="42" t="n">
+        <f aca="false">CHOOSE($C$6,C79,D79,E79)</f>
+        <v>33.6</v>
+      </c>
+      <c r="C79" s="20" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="D79" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="E79" s="20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F79" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="B80" s="42" t="n">
+        <f aca="false">CHOOSE($C$6,C80,D80,E80)</f>
+        <v>26</v>
+      </c>
+      <c r="C80" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="D80" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E80" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="F80" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="B81" s="42" t="n">
+        <f aca="false">CHOOSE($C$6,C81,D81,E81)</f>
         <v>30</v>
       </c>
-      <c r="B75" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>357</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>362</v>
-      </c>
-      <c r="E75" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="F75" s="14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>344</v>
-      </c>
-      <c r="B76" s="42" t="n">
-        <f aca="false">CHOOSE($C$6,C76,D76,E76)</f>
-        <v>33.6</v>
-      </c>
-      <c r="C76" s="20" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="D76" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="E76" s="20" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F76" s="23" t="s">
+      <c r="C81" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="D81" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="E81" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="G76" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>346</v>
-      </c>
-      <c r="B77" s="42" t="n">
-        <f aca="false">CHOOSE($C$6,C77,D77,E77)</f>
-        <v>26</v>
-      </c>
-      <c r="C77" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="D77" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="E77" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="F77" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="B78" s="42" t="n">
-        <f aca="false">CHOOSE($C$6,C78,D78,E78)</f>
-        <v>30</v>
-      </c>
-      <c r="C78" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="D78" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E78" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F78" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>372</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>373</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
-        <v>348</v>
-      </c>
-      <c r="B82" s="31" t="n">
-        <f aca="false">IF($C$82="Prepaid",1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="C82" s="38" t="s">
-        <v>375</v>
-      </c>
-      <c r="D82" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>351</v>
-      </c>
-      <c r="B83" s="31" t="n">
-        <f aca="false">IF($C$83="ON",1,0)</f>
+      <c r="G81" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B83" s="13"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>380</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="D84" s="14" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="B85" s="31" t="n">
+        <f aca="false">IF($C$85="Prepaid",1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C85" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="B86" s="31" t="n">
+        <f aca="false">IF($C$86="ON",1,0)</f>
         <v>1</v>
       </c>
-      <c r="C83" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="D83" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>352</v>
+      <c r="C86" s="38" t="s">
+        <v>385</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -6668,11 +6803,11 @@
       <formula1>"Base,Aggressive,Conservative"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C82" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C85" type="list">
       <formula1>"Credit,Prepaid"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C83" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C86" type="list">
       <formula1>"ON,OFF"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6708,10 +6843,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C2" s="28" t="n">
         <v>1</v>
@@ -6803,200 +6938,200 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>207</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="E3" s="43" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F3" s="43" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="H3" s="43" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="I3" s="43" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="J3" s="43" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="K3" s="43" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="L3" s="43" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="M3" s="43" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="N3" s="43" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="O3" s="43" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="P3" s="43" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="Q3" s="43" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="R3" s="43" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="S3" s="43" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="T3" s="43" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="U3" s="43" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="V3" s="43" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="W3" s="43" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="X3" s="43" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="Y3" s="43" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="Z3" s="43" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AA3" s="43" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AB3" s="43" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AC3" s="43" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AD3" s="43" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AE3" s="43" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>207</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="E4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="H4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="I4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="L4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="M4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="N4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="O4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="P4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="R4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="S4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="T4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="U4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="V4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="W4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="X4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="Y4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="Z4" s="44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AA4" s="44" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AB4" s="44" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AC4" s="44" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AD4" s="44" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AE4" s="44" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C5" s="45" t="n">
         <v>1</v>
@@ -7088,10 +7223,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C6" s="45" t="n">
         <v>1</v>
@@ -7183,7 +7318,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B7" s="23" t="s">
         <v>278</v>
@@ -7278,10 +7413,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C8" s="45" t="n">
         <v>0</v>
@@ -7373,7 +7508,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B10" s="47"/>
       <c r="C10" s="47"/>
@@ -7408,10 +7543,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C11" s="48" t="n">
         <f aca="false">(1+(Assumptions!$F$61-1)*Assumptions!$B$133)*12/SUMPRODUCT(1+(Assumptions!$F$61:$Q$61-1)*Assumptions!$B$133)</f>
@@ -7464,10 +7599,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C12" s="48" t="n">
         <f aca="false">(1+(Assumptions!$F$62-1)*Assumptions!$B$133)*12/SUMPRODUCT(1+(Assumptions!$F$62:$Q$62-1)*Assumptions!$B$133)</f>
@@ -7520,10 +7655,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C13" s="49" t="n">
         <f aca="false">Assumptions!$F$63/AVERAGE(Assumptions!$F$63:$Q$63)*Assumptions!$B$145</f>
@@ -7576,10 +7711,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C14" s="50" t="n">
         <f aca="false">SUM($C$11:$N$11)</f>
@@ -7592,10 +7727,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C15" s="51" t="n">
         <f aca="false">IF(C7=1,INDEX($C$11:$N$11,1,C6),1)</f>
@@ -7716,10 +7851,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C16" s="51" t="n">
         <f aca="false">IF(C7=1,INDEX($C$12:$N$12,1,C6),1)</f>
@@ -7840,7 +7975,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>245</v>
@@ -7964,7 +8099,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
@@ -7999,7 +8134,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>190</v>
@@ -8123,7 +8258,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>35</v>
@@ -8247,15 +8382,15 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C23" s="48" t="n">
         <f aca="false">Assumptions!$B$114*1+Assumptions!$B$115*IF(C2&gt;=Assumptions!$B$56,1,0)+Assumptions!$B$116*IF(C2&gt;=Assumptions!$B$57,1,0)</f>
@@ -8376,7 +8511,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="46" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
@@ -8411,7 +8546,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>190</v>
@@ -8535,7 +8670,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>190</v>
@@ -8658,7 +8793,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>190</v>
@@ -8782,10 +8917,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C29" s="51" t="n">
         <v>1</v>
@@ -8905,7 +9040,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>190</v>
@@ -9029,7 +9164,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B31" s="23" t="s">
         <v>190</v>
@@ -9153,7 +9288,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>190</v>
@@ -9277,7 +9412,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B33" s="23" t="s">
         <v>190</v>
@@ -9401,7 +9536,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>190</v>
@@ -9525,131 +9660,131 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C35" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C31*Assumptions!$B$168*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C31*Assumptions!$B$171*C7,0)</f>
         <v>2594.15269984878</v>
       </c>
       <c r="D35" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D31*Assumptions!$B$168*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D31*Assumptions!$B$171*D7,0)</f>
         <v>4932.44018770634</v>
       </c>
       <c r="E35" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E31*Assumptions!$B$168*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E31*Assumptions!$B$171*E7,0)</f>
         <v>7053.1615978088</v>
       </c>
       <c r="F35" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F31*Assumptions!$B$168*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F31*Assumptions!$B$171*F7,0)</f>
         <v>9659.43478775547</v>
       </c>
       <c r="G35" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G31*Assumptions!$B$168*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G31*Assumptions!$B$171*G7,0)</f>
         <v>11855.2772079364</v>
       </c>
       <c r="H35" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H31*Assumptions!$B$168*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H31*Assumptions!$B$171*H7,0)</f>
         <v>13533.0715479916</v>
       </c>
       <c r="I35" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I31*Assumptions!$B$168*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I31*Assumptions!$B$171*I7,0)</f>
         <v>15051.4347298052</v>
       </c>
       <c r="J35" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J31*Assumptions!$B$168*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J31*Assumptions!$B$171*J7,0)</f>
         <v>16494.9905516247</v>
       </c>
       <c r="K35" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K31*Assumptions!$B$168*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K31*Assumptions!$B$171*K7,0)</f>
         <v>18071.9892908717</v>
       </c>
       <c r="L35" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L31*Assumptions!$B$168*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L31*Assumptions!$B$171*L7,0)</f>
         <v>20389.1705835684</v>
       </c>
       <c r="M35" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M31*Assumptions!$B$168*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M31*Assumptions!$B$171*M7,0)</f>
         <v>22336.0827718177</v>
       </c>
       <c r="N35" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N31*Assumptions!$B$168*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N31*Assumptions!$B$171*N7,0)</f>
         <v>23829.1003464687</v>
       </c>
       <c r="O35" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O31*Assumptions!$B$168*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O31*Assumptions!$B$171*O7,0)</f>
         <v>31440.4665464351</v>
       </c>
       <c r="P35" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P31*Assumptions!$B$168*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P31*Assumptions!$B$171*P7,0)</f>
         <v>38451.1312267871</v>
       </c>
       <c r="Q35" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q31*Assumptions!$B$168*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q31*Assumptions!$B$171*Q7,0)</f>
         <v>44943.2541967184</v>
       </c>
       <c r="R35" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R31*Assumptions!$B$168*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R31*Assumptions!$B$171*R7,0)</f>
         <v>53414.2097516778</v>
       </c>
       <c r="S35" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S31*Assumptions!$B$168*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S31*Assumptions!$B$171*S7,0)</f>
         <v>60694.6274468072</v>
       </c>
       <c r="T35" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T31*Assumptions!$B$168*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T31*Assumptions!$B$171*T7,0)</f>
         <v>66274.41547091</v>
       </c>
       <c r="U35" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U31*Assumptions!$B$168*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U31*Assumptions!$B$171*U7,0)</f>
         <v>71417.7572032574</v>
       </c>
       <c r="V35" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V31*Assumptions!$B$168*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V31*Assumptions!$B$171*V7,0)</f>
         <v>76425.4323599577</v>
       </c>
       <c r="W35" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W31*Assumptions!$B$168*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W31*Assumptions!$B$171*W7,0)</f>
         <v>82108.2850750478</v>
       </c>
       <c r="X35" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X31*Assumptions!$B$168*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X31*Assumptions!$B$171*X7,0)</f>
         <v>90932.0559966629</v>
       </c>
       <c r="Y35" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y31*Assumptions!$B$168*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y31*Assumptions!$B$171*Y7,0)</f>
         <v>98567.4157619095</v>
       </c>
       <c r="Z35" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z31*Assumptions!$B$168*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z31*Assumptions!$B$171*Z7,0)</f>
         <v>104562.511915754</v>
       </c>
       <c r="AA35" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA31*Assumptions!$B$168*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA31*Assumptions!$B$171*AA7,0)</f>
         <v>2514618.47665027</v>
       </c>
       <c r="AB35" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB31*Assumptions!$B$168*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB31*Assumptions!$B$171*AB7,0)</f>
         <v>4248983.84795424</v>
       </c>
       <c r="AC35" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC31*Assumptions!$B$168*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC31*Assumptions!$B$171*AC7,0)</f>
         <v>6436797.47723466</v>
       </c>
       <c r="AD35" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD31*Assumptions!$B$168*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD31*Assumptions!$B$171*AD7,0)</f>
         <v>8547635.08408199</v>
       </c>
       <c r="AE35" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE31*Assumptions!$B$168*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE31*Assumptions!$B$171*AE7,0)</f>
         <v>10098674.95331</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>114</v>
@@ -9773,7 +9908,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B37" s="23" t="s">
         <v>47</v>
@@ -9897,10 +10032,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C38" s="56" t="n">
         <f aca="false">(Assumptions!$B$136+Assumptions!$B$137*IF(C31+C33=0,1,(C31+C33*Assumptions!$B$138)/(C31+C33)))*C7/12</f>
@@ -10021,10 +10156,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C39" s="56" t="n">
         <f aca="false">Assumptions!$B$137*IF(C31+C33=0,1,(C31+C33*Assumptions!$B$138)/(C31+C33))*C7/12</f>
@@ -10145,7 +10280,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>47</v>
@@ -10269,7 +10404,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B41" s="23" t="s">
         <v>47</v>
@@ -10393,7 +10528,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>114</v>
@@ -10517,131 +10652,131 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B43" s="23" t="s">
         <v>190</v>
       </c>
       <c r="C43" s="54" t="n">
-        <f aca="false">C31+C33*Assumptions!$B$172</f>
+        <f aca="false">C31+C33*Assumptions!$B$175</f>
         <v>79.1542941176471</v>
       </c>
       <c r="D43" s="54" t="n">
-        <f aca="false">D31+D33*Assumptions!$B$172</f>
+        <f aca="false">D31+D33*Assumptions!$B$175</f>
         <v>154.348307789801</v>
       </c>
       <c r="E43" s="54" t="n">
-        <f aca="false">E31+E33*Assumptions!$B$172</f>
+        <f aca="false">E31+E33*Assumptions!$B$175</f>
         <v>226.371228018938</v>
       </c>
       <c r="F43" s="54" t="n">
-        <f aca="false">F31+F33*Assumptions!$B$172</f>
+        <f aca="false">F31+F33*Assumptions!$B$175</f>
         <v>316.354370060513</v>
       </c>
       <c r="G43" s="54" t="n">
-        <f aca="false">G31+G33*Assumptions!$B$172</f>
+        <f aca="false">G31+G33*Assumptions!$B$175</f>
         <v>397.679010851702</v>
       </c>
       <c r="H43" s="54" t="n">
-        <f aca="false">H31+H33*Assumptions!$B$172</f>
+        <f aca="false">H31+H33*Assumptions!$B$175</f>
         <v>466.452847282075</v>
       </c>
       <c r="I43" s="54" t="n">
-        <f aca="false">I31+I33*Assumptions!$B$172</f>
+        <f aca="false">I31+I33*Assumptions!$B$175</f>
         <v>532.850001982533</v>
       </c>
       <c r="J43" s="54" t="n">
-        <f aca="false">J31+J33*Assumptions!$B$172</f>
+        <f aca="false">J31+J33*Assumptions!$B$175</f>
         <v>599.21614752925</v>
       </c>
       <c r="K43" s="54" t="n">
-        <f aca="false">K31+K33*Assumptions!$B$172</f>
+        <f aca="false">K31+K33*Assumptions!$B$175</f>
         <v>671.794606721936</v>
       </c>
       <c r="L43" s="54" t="n">
-        <f aca="false">L31+L33*Assumptions!$B$172</f>
+        <f aca="false">L31+L33*Assumptions!$B$175</f>
         <v>769.296452156441</v>
       </c>
       <c r="M43" s="54" t="n">
-        <f aca="false">M31+M33*Assumptions!$B$172</f>
+        <f aca="false">M31+M33*Assumptions!$B$175</f>
         <v>858.936542653387</v>
       </c>
       <c r="N43" s="54" t="n">
-        <f aca="false">N31+N33*Assumptions!$B$172</f>
+        <f aca="false">N31+N33*Assumptions!$B$175</f>
         <v>937.614181968588</v>
       </c>
       <c r="O43" s="54" t="n">
-        <f aca="false">O31+O33*Assumptions!$B$172</f>
+        <f aca="false">O31+O33*Assumptions!$B$175</f>
         <v>1205.19240055455</v>
       </c>
       <c r="P43" s="54" t="n">
-        <f aca="false">P31+P33*Assumptions!$B$172</f>
+        <f aca="false">P31+P33*Assumptions!$B$175</f>
         <v>1465.72843859039</v>
       </c>
       <c r="Q43" s="54" t="n">
-        <f aca="false">Q31+Q33*Assumptions!$B$172</f>
+        <f aca="false">Q31+Q33*Assumptions!$B$175</f>
         <v>1720.83843322797</v>
       </c>
       <c r="R43" s="54" t="n">
-        <f aca="false">R31+R33*Assumptions!$B$172</f>
+        <f aca="false">R31+R33*Assumptions!$B$175</f>
         <v>2045.95478248527</v>
       </c>
       <c r="S43" s="54" t="n">
-        <f aca="false">S31+S33*Assumptions!$B$172</f>
+        <f aca="false">S31+S33*Assumptions!$B$175</f>
         <v>2347.30619344651</v>
       </c>
       <c r="T43" s="54" t="n">
-        <f aca="false">T31+T33*Assumptions!$B$172</f>
+        <f aca="false">T31+T33*Assumptions!$B$175</f>
         <v>2607.56301891197</v>
       </c>
       <c r="U43" s="54" t="n">
-        <f aca="false">U31+U33*Assumptions!$B$172</f>
+        <f aca="false">U31+U33*Assumptions!$B$175</f>
         <v>2862.77691998179</v>
       </c>
       <c r="V43" s="54" t="n">
-        <f aca="false">V31+V33*Assumptions!$B$172</f>
+        <f aca="false">V31+V33*Assumptions!$B$175</f>
         <v>3121.47826285308</v>
       </c>
       <c r="W43" s="54" t="n">
-        <f aca="false">W31+W33*Assumptions!$B$172</f>
+        <f aca="false">W31+W33*Assumptions!$B$175</f>
         <v>3408.20681696739</v>
       </c>
       <c r="X43" s="54" t="n">
-        <f aca="false">X31+X33*Assumptions!$B$172</f>
+        <f aca="false">X31+X33*Assumptions!$B$175</f>
         <v>3799.19990332518</v>
       </c>
       <c r="Y43" s="54" t="n">
-        <f aca="false">Y31+Y33*Assumptions!$B$172</f>
+        <f aca="false">Y31+Y33*Assumptions!$B$175</f>
         <v>4167.01612686082</v>
       </c>
       <c r="Z43" s="54" t="n">
-        <f aca="false">Z31+Z33*Assumptions!$B$172</f>
+        <f aca="false">Z31+Z33*Assumptions!$B$175</f>
         <v>4496.10602709555</v>
       </c>
       <c r="AA43" s="54" t="n">
-        <f aca="false">AA31+AA33*Assumptions!$B$172</f>
+        <f aca="false">AA31+AA33*Assumptions!$B$175</f>
         <v>10597.701391675</v>
       </c>
       <c r="AB43" s="54" t="n">
-        <f aca="false">AB31+AB33*Assumptions!$B$172</f>
+        <f aca="false">AB31+AB33*Assumptions!$B$175</f>
         <v>20182.1202348866</v>
       </c>
       <c r="AC43" s="54" t="n">
-        <f aca="false">AC31+AC33*Assumptions!$B$172</f>
+        <f aca="false">AC31+AC33*Assumptions!$B$175</f>
         <v>33893.0458033923</v>
       </c>
       <c r="AD43" s="54" t="n">
-        <f aca="false">AD31+AD33*Assumptions!$B$172</f>
+        <f aca="false">AD31+AD33*Assumptions!$B$175</f>
         <v>50639.0081667535</v>
       </c>
       <c r="AE43" s="54" t="n">
-        <f aca="false">AE31+AE33*Assumptions!$B$172</f>
+        <f aca="false">AE31+AE33*Assumptions!$B$175</f>
         <v>68689.4910320406</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>190</v>
@@ -10765,10 +10900,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C45" s="28" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$51,C44*Assumptions!$B$143,0)</f>
@@ -10889,7 +11024,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>114</v>
@@ -11013,7 +11148,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>76</v>
@@ -11137,7 +11272,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>114</v>
@@ -11261,10 +11396,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C49" s="45" t="n">
         <f aca="false">C45*C48*Assumptions!$B$7*C7</f>
@@ -11385,7 +11520,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>114</v>
@@ -11509,10 +11644,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C51" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,C46*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
@@ -11633,10 +11768,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C52" s="45" t="n">
         <f aca="false">C45*Assumptions!$B$158*Assumptions!$B$144*C7/12*(1+Assumptions!$B$16)</f>
@@ -11757,7 +11892,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B53" s="23" t="s">
         <v>114</v>
@@ -11881,7 +12016,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>114</v>
@@ -12005,131 +12140,131 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B55" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C55" s="55" t="n">
-        <f aca="false">C50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">C50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="D55" s="55" t="n">
-        <f aca="false">D50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">D50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="E55" s="55" t="n">
-        <f aca="false">E50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">E50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="F55" s="55" t="n">
-        <f aca="false">F50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">F50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="G55" s="55" t="n">
-        <f aca="false">G50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">G50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="H55" s="55" t="n">
-        <f aca="false">H50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">H50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="I55" s="55" t="n">
-        <f aca="false">I50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">I50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="J55" s="55" t="n">
-        <f aca="false">J50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">J50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="K55" s="55" t="n">
-        <f aca="false">K50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">K50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="L55" s="55" t="n">
-        <f aca="false">L50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">L50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="M55" s="55" t="n">
-        <f aca="false">M50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">M50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="N55" s="55" t="n">
-        <f aca="false">N50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">N50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="O55" s="55" t="n">
-        <f aca="false">O50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">O50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>2.11158547345258</v>
       </c>
       <c r="P55" s="55" t="n">
-        <f aca="false">P50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">P50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>2.17245396505516</v>
       </c>
       <c r="Q55" s="55" t="n">
-        <f aca="false">Q50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Q50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>2.45149272765391</v>
       </c>
       <c r="R55" s="55" t="n">
-        <f aca="false">R50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">R50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>2.73676047953534</v>
       </c>
       <c r="S55" s="55" t="n">
-        <f aca="false">S50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">S50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>3.23137231978959</v>
       </c>
       <c r="T55" s="55" t="n">
-        <f aca="false">T50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">T50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>3.73477971854553</v>
       </c>
       <c r="U55" s="55" t="n">
-        <f aca="false">U50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">U50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>4.11468953800432</v>
       </c>
       <c r="V55" s="55" t="n">
-        <f aca="false">V50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">V50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>4.88125125078498</v>
       </c>
       <c r="W55" s="55" t="n">
-        <f aca="false">W50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">W50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>7.32541263246647</v>
       </c>
       <c r="X55" s="55" t="n">
-        <f aca="false">X50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">X50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>9.24126848033657</v>
       </c>
       <c r="Y55" s="55" t="n">
-        <f aca="false">Y50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Y50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>11.5511266363492</v>
       </c>
       <c r="Z55" s="55" t="n">
-        <f aca="false">Z50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Z50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>15.6572931740687</v>
       </c>
       <c r="AA55" s="55" t="n">
-        <f aca="false">AA50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AA50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>1546.76661607075</v>
       </c>
       <c r="AB55" s="55" t="n">
-        <f aca="false">AB50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AB50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>3812.84596323652</v>
       </c>
       <c r="AC55" s="55" t="n">
-        <f aca="false">AC50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AC50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>7606.44885584735</v>
       </c>
       <c r="AD55" s="55" t="n">
-        <f aca="false">AD50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AD50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>13434.7844850062</v>
       </c>
       <c r="AE55" s="55" t="n">
-        <f aca="false">AE50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AE50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>21734.973438346</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B56" s="23" t="s">
         <v>114</v>
@@ -12253,7 +12388,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>114</v>
@@ -12377,258 +12512,258 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B58" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C58" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$53,C45*C46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$53,C45*C46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="D58" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$53,D45*D46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$53,D45*D46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="E58" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$53,E45*E46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$53,E45*E46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="F58" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$53,F45*F46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$53,F45*F46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="G58" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$53,G45*G46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$53,G45*G46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="H58" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$53,H45*H46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$53,H45*H46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="I58" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$53,I45*I46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$53,I45*I46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="J58" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$53,J45*J46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$53,J45*J46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="K58" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$53,K45*K46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$53,K45*K46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="L58" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$53,L45*L46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$53,L45*L46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="M58" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$53,M45*M46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$53,M45*M46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="N58" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$53,N45*N46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$53,N45*N46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="O58" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$53,O45*O46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$53,O45*O46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>914.106265563888</v>
       </c>
       <c r="P58" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$53,P45*P46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$53,P45*P46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>1034.50188812151</v>
       </c>
       <c r="Q58" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,Q45*Q46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,Q45*Q46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>1191.20151975408</v>
       </c>
       <c r="R58" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$53,R45*R46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$53,R45*R46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>1329.81558772368</v>
       </c>
       <c r="S58" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$53,S45*S46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$53,S45*S46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>1538.74872370933</v>
       </c>
       <c r="T58" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$53,T45*T46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$53,T45*T46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>1872.07003435866</v>
       </c>
       <c r="U58" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$53,U45*U46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$53,U45*U46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>2226.56360281619</v>
       </c>
       <c r="V58" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$53,V45*V46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$53,V45*V46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>2582.67261946295</v>
       </c>
       <c r="W58" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$53,W45*W46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$53,W45*W46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>3488.29172974594</v>
       </c>
       <c r="X58" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$53,X45*X46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$53,X45*X46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>4314.31768456423</v>
       </c>
       <c r="Y58" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,Y45*Y46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,Y45*Y46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>5238.60618428537</v>
       </c>
       <c r="Z58" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,Z45*Z46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,Z45*Z46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>6540.22271264358</v>
       </c>
       <c r="AA58" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,AA45*AA46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,AA45*AA46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>61379.627621855</v>
       </c>
       <c r="AB58" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,AB45*AB46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,AB45*AB46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>151303.411239544</v>
       </c>
       <c r="AC58" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,AC45*AC46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,AC45*AC46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>301843.208565371</v>
       </c>
       <c r="AD58" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,AD45*AD46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,AD45*AD46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>533126.368452626</v>
       </c>
       <c r="AE58" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,AE45*AE46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,AE45*AE46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>862498.945966112</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B59" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C59" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$53,(C58*Assumptions!$B$29*Assumptions!$B$30+C45*C47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$53,(C58*Assumptions!$B$29*Assumptions!$B$30+C45*C47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v>0</v>
       </c>
       <c r="D59" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$53,(D58*Assumptions!$B$29*Assumptions!$B$30+D45*D47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$53,(D58*Assumptions!$B$29*Assumptions!$B$30+D45*D47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v>0</v>
       </c>
       <c r="E59" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$53,(E58*Assumptions!$B$29*Assumptions!$B$30+E45*E47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$53,(E58*Assumptions!$B$29*Assumptions!$B$30+E45*E47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v>0</v>
       </c>
       <c r="F59" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$53,(F58*Assumptions!$B$29*Assumptions!$B$30+F45*F47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$53,(F58*Assumptions!$B$29*Assumptions!$B$30+F45*F47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v>0</v>
       </c>
       <c r="G59" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$53,(G58*Assumptions!$B$29*Assumptions!$B$30+G45*G47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$53,(G58*Assumptions!$B$29*Assumptions!$B$30+G45*G47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v>0</v>
       </c>
       <c r="H59" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$53,(H58*Assumptions!$B$29*Assumptions!$B$30+H45*H47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$53,(H58*Assumptions!$B$29*Assumptions!$B$30+H45*H47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v>0</v>
       </c>
       <c r="I59" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$53,(I58*Assumptions!$B$29*Assumptions!$B$30+I45*I47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$53,(I58*Assumptions!$B$29*Assumptions!$B$30+I45*I47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v>0</v>
       </c>
       <c r="J59" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$53,(J58*Assumptions!$B$29*Assumptions!$B$30+J45*J47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$53,(J58*Assumptions!$B$29*Assumptions!$B$30+J45*J47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v>0</v>
       </c>
       <c r="K59" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$53,(K58*Assumptions!$B$29*Assumptions!$B$30+K45*K47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$53,(K58*Assumptions!$B$29*Assumptions!$B$30+K45*K47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v>0</v>
       </c>
       <c r="L59" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$53,(L58*Assumptions!$B$29*Assumptions!$B$30+L45*L47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$53,(L58*Assumptions!$B$29*Assumptions!$B$30+L45*L47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v>0</v>
       </c>
       <c r="M59" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$53,(M58*Assumptions!$B$29*Assumptions!$B$30+M45*M47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$53,(M58*Assumptions!$B$29*Assumptions!$B$30+M45*M47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v>0</v>
       </c>
       <c r="N59" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$53,(N58*Assumptions!$B$29*Assumptions!$B$30+N45*N47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$53,(N58*Assumptions!$B$29*Assumptions!$B$30+N45*N47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v>0</v>
       </c>
       <c r="O59" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$53,(O58*Assumptions!$B$29*Assumptions!$B$30+O45*O47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$53,(O58*Assumptions!$B$29*Assumptions!$B$30+O45*O47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v>2.17100238071424</v>
       </c>
       <c r="P59" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$53,(P58*Assumptions!$B$29*Assumptions!$B$30+P45*P47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$53,(P58*Assumptions!$B$29*Assumptions!$B$30+P45*P47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v>2.45694198428858</v>
       </c>
       <c r="Q59" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,(Q58*Assumptions!$B$29*Assumptions!$B$30+Q45*Q47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,(Q58*Assumptions!$B$29*Assumptions!$B$30+Q45*Q47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v>2.82910360941595</v>
       </c>
       <c r="R59" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$53,(R58*Assumptions!$B$29*Assumptions!$B$30+R45*R47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$53,(R58*Assumptions!$B$29*Assumptions!$B$30+R45*R47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v>3.15831202084374</v>
       </c>
       <c r="S59" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$53,(S58*Assumptions!$B$29*Assumptions!$B$30+S45*S47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$53,(S58*Assumptions!$B$29*Assumptions!$B$30+S45*S47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v>3.65452821880965</v>
       </c>
       <c r="T59" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$53,(T58*Assumptions!$B$29*Assumptions!$B$30+T45*T47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$53,(T58*Assumptions!$B$29*Assumptions!$B$30+T45*T47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v>4.44616633160183</v>
       </c>
       <c r="U59" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$53,(U58*Assumptions!$B$29*Assumptions!$B$30+U45*U47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$53,(U58*Assumptions!$B$29*Assumptions!$B$30+U45*U47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v>5.28808855668845</v>
       </c>
       <c r="V59" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$53,(V58*Assumptions!$B$29*Assumptions!$B$30+V45*V47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$53,(V58*Assumptions!$B$29*Assumptions!$B$30+V45*V47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v>6.13384747122452</v>
       </c>
       <c r="W59" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$53,(W58*Assumptions!$B$29*Assumptions!$B$30+W45*W47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$53,(W58*Assumptions!$B$29*Assumptions!$B$30+W45*W47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v>8.28469285814661</v>
       </c>
       <c r="X59" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$53,(X58*Assumptions!$B$29*Assumptions!$B$30+X45*X47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$53,(X58*Assumptions!$B$29*Assumptions!$B$30+X45*X47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v>10.24650450084</v>
       </c>
       <c r="Y59" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,(Y58*Assumptions!$B$29*Assumptions!$B$30+Y45*Y47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,(Y58*Assumptions!$B$29*Assumptions!$B$30+Y45*Y47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v>12.4416896876777</v>
       </c>
       <c r="Z59" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,(Z58*Assumptions!$B$29*Assumptions!$B$30+Z45*Z47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,(Z58*Assumptions!$B$29*Assumptions!$B$30+Z45*Z47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v>15.5330289425285</v>
       </c>
       <c r="AA59" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,(AA58*Assumptions!$B$29*Assumptions!$B$30+AA45*AA47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,(AA58*Assumptions!$B$29*Assumptions!$B$30+AA45*AA47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v>1749.31938722287</v>
       </c>
       <c r="AB59" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,(AB58*Assumptions!$B$29*Assumptions!$B$30+AB45*AB47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,(AB58*Assumptions!$B$29*Assumptions!$B$30+AB45*AB47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v>4312.14722032701</v>
       </c>
       <c r="AC59" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,(AC58*Assumptions!$B$29*Assumptions!$B$30+AC45*AC47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,(AC58*Assumptions!$B$29*Assumptions!$B$30+AC45*AC47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v>8602.53144411307</v>
       </c>
       <c r="AD59" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,(AD58*Assumptions!$B$29*Assumptions!$B$30+AD45*AD47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,(AD58*Assumptions!$B$29*Assumptions!$B$30+AD45*AD47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v>15194.1015008999</v>
       </c>
       <c r="AE59" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,(AE58*Assumptions!$B$29*Assumptions!$B$30+AE45*AE47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,(AE58*Assumptions!$B$29*Assumptions!$B$30+AE45*AE47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v>24581.2199600342</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="C60" s="45" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$49,(C31+C33*Assumptions!$B$138)*Assumptions!$B$137*C7/12,0)</f>
@@ -12749,7 +12884,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B61" s="23" t="s">
         <v>114</v>
@@ -12873,7 +13008,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="46" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B63" s="47"/>
       <c r="C63" s="47"/>
@@ -12908,7 +13043,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B64" s="23" t="s">
         <v>190</v>
@@ -13032,7 +13167,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B65" s="23" t="s">
         <v>190</v>
@@ -13155,7 +13290,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>190</v>
@@ -13279,10 +13414,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C67" s="51" t="n">
         <v>1</v>
@@ -13402,7 +13537,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B68" s="23" t="s">
         <v>190</v>
@@ -13526,7 +13661,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>190</v>
@@ -13650,7 +13785,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>190</v>
@@ -13774,7 +13909,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B71" s="23" t="s">
         <v>190</v>
@@ -13898,7 +14033,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>190</v>
@@ -14022,131 +14157,131 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B73" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C73" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C69*Assumptions!$B$169*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C69*Assumptions!$B$172*C7,0)</f>
         <v>0</v>
       </c>
       <c r="D73" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D69*Assumptions!$B$169*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D69*Assumptions!$B$172*D7,0)</f>
         <v>0</v>
       </c>
       <c r="E73" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E69*Assumptions!$B$169*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E69*Assumptions!$B$172*E7,0)</f>
         <v>0</v>
       </c>
       <c r="F73" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F69*Assumptions!$B$169*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F69*Assumptions!$B$172*F7,0)</f>
         <v>0</v>
       </c>
       <c r="G73" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G69*Assumptions!$B$169*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G69*Assumptions!$B$172*G7,0)</f>
         <v>0</v>
       </c>
       <c r="H73" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H69*Assumptions!$B$169*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H69*Assumptions!$B$172*H7,0)</f>
         <v>0</v>
       </c>
       <c r="I73" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I69*Assumptions!$B$169*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I69*Assumptions!$B$172*I7,0)</f>
         <v>0</v>
       </c>
       <c r="J73" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J69*Assumptions!$B$169*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J69*Assumptions!$B$172*J7,0)</f>
         <v>0</v>
       </c>
       <c r="K73" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K69*Assumptions!$B$169*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K69*Assumptions!$B$172*K7,0)</f>
         <v>0</v>
       </c>
       <c r="L73" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L69*Assumptions!$B$169*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L69*Assumptions!$B$172*L7,0)</f>
         <v>0</v>
       </c>
       <c r="M73" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M69*Assumptions!$B$169*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M69*Assumptions!$B$172*M7,0)</f>
         <v>0</v>
       </c>
       <c r="N73" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N69*Assumptions!$B$169*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N69*Assumptions!$B$172*N7,0)</f>
         <v>0</v>
       </c>
       <c r="O73" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O69*Assumptions!$B$169*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O69*Assumptions!$B$172*O7,0)</f>
         <v>1837.28839262901</v>
       </c>
       <c r="P73" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P69*Assumptions!$B$169*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P69*Assumptions!$B$172*P7,0)</f>
         <v>3544.03999458813</v>
       </c>
       <c r="Q73" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q69*Assumptions!$B$169*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q69*Assumptions!$B$172*Q7,0)</f>
         <v>5136.90494611595</v>
       </c>
       <c r="R73" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R69*Assumptions!$B$169*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R69*Assumptions!$B$172*R7,0)</f>
         <v>7144.40915155978</v>
       </c>
       <c r="S73" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S69*Assumptions!$B$169*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S69*Assumptions!$B$172*S7,0)</f>
         <v>8895.96910678716</v>
       </c>
       <c r="T73" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T69*Assumptions!$B$169*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T69*Assumptions!$B$172*T7,0)</f>
         <v>10281.506118015</v>
       </c>
       <c r="U73" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U69*Assumptions!$B$169*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U69*Assumptions!$B$172*U7,0)</f>
         <v>11569.3572027946</v>
       </c>
       <c r="V73" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V69*Assumptions!$B$169*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V69*Assumptions!$B$172*V7,0)</f>
         <v>12823.6883291317</v>
       </c>
       <c r="W73" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W69*Assumptions!$B$169*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W69*Assumptions!$B$172*W7,0)</f>
         <v>14218.7034663547</v>
       </c>
       <c r="X73" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X69*Assumptions!$B$169*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X69*Assumptions!$B$172*X7,0)</f>
         <v>16286.0000125039</v>
       </c>
       <c r="Y73" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y69*Assumptions!$B$169*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y69*Assumptions!$B$172*Y7,0)</f>
         <v>18094.6579436616</v>
       </c>
       <c r="Z73" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z69*Assumptions!$B$169*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z69*Assumptions!$B$172*Z7,0)</f>
         <v>19546.095075863</v>
       </c>
       <c r="AA73" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA69*Assumptions!$B$169*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA69*Assumptions!$B$172*AA7,0)</f>
         <v>514255.985923226</v>
       </c>
       <c r="AB73" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB69*Assumptions!$B$169*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB69*Assumptions!$B$172*AB7,0)</f>
         <v>896177.60982744</v>
       </c>
       <c r="AC73" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC69*Assumptions!$B$169*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC69*Assumptions!$B$172*AC7,0)</f>
         <v>1369099.96963808</v>
       </c>
       <c r="AD73" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD69*Assumptions!$B$169*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD69*Assumptions!$B$172*AD7,0)</f>
         <v>1821449.8345439</v>
       </c>
       <c r="AE73" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE69*Assumptions!$B$169*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE69*Assumptions!$B$172*AE7,0)</f>
         <v>2135191.13427289</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B74" s="23" t="s">
         <v>114</v>
@@ -14270,7 +14405,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B75" s="23" t="s">
         <v>47</v>
@@ -14394,10 +14529,10 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C76" s="56" t="n">
         <f aca="false">(Assumptions!$B$136+Assumptions!$B$137*IF(C69+C71=0,1,(C69+C71*Assumptions!$B$138)/(C69+C71)))*C7/12</f>
@@ -14518,10 +14653,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C77" s="56" t="n">
         <f aca="false">Assumptions!$B$137*IF(C69+C71=0,1,(C69+C71*Assumptions!$B$138)/(C69+C71))*C7/12</f>
@@ -14642,7 +14777,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B78" s="23" t="s">
         <v>47</v>
@@ -14766,7 +14901,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>47</v>
@@ -14890,7 +15025,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B80" s="23" t="s">
         <v>114</v>
@@ -15014,131 +15149,131 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B81" s="23" t="s">
         <v>190</v>
       </c>
       <c r="C81" s="54" t="n">
-        <f aca="false">C69+C71*Assumptions!$B$172</f>
+        <f aca="false">C69+C71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="D81" s="54" t="n">
-        <f aca="false">D69+D71*Assumptions!$B$172</f>
+        <f aca="false">D69+D71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="E81" s="54" t="n">
-        <f aca="false">E69+E71*Assumptions!$B$172</f>
+        <f aca="false">E69+E71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="F81" s="54" t="n">
-        <f aca="false">F69+F71*Assumptions!$B$172</f>
+        <f aca="false">F69+F71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="G81" s="54" t="n">
-        <f aca="false">G69+G71*Assumptions!$B$172</f>
+        <f aca="false">G69+G71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="H81" s="54" t="n">
-        <f aca="false">H69+H71*Assumptions!$B$172</f>
+        <f aca="false">H69+H71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="I81" s="54" t="n">
-        <f aca="false">I69+I71*Assumptions!$B$172</f>
+        <f aca="false">I69+I71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="J81" s="54" t="n">
-        <f aca="false">J69+J71*Assumptions!$B$172</f>
+        <f aca="false">J69+J71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="K81" s="54" t="n">
-        <f aca="false">K69+K71*Assumptions!$B$172</f>
+        <f aca="false">K69+K71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="L81" s="54" t="n">
-        <f aca="false">L69+L71*Assumptions!$B$172</f>
+        <f aca="false">L69+L71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="M81" s="54" t="n">
-        <f aca="false">M69+M71*Assumptions!$B$172</f>
+        <f aca="false">M69+M71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="N81" s="54" t="n">
-        <f aca="false">N69+N71*Assumptions!$B$172</f>
+        <f aca="false">N69+N71*Assumptions!$B$175</f>
         <v>0</v>
       </c>
       <c r="O81" s="54" t="n">
-        <f aca="false">O69+O71*Assumptions!$B$172</f>
+        <f aca="false">O69+O71*Assumptions!$B$175</f>
         <v>72.4473</v>
       </c>
       <c r="P81" s="54" t="n">
-        <f aca="false">P69+P71*Assumptions!$B$172</f>
+        <f aca="false">P69+P71*Assumptions!$B$175</f>
         <v>143.268193520962</v>
       </c>
       <c r="Q81" s="54" t="n">
-        <f aca="false">Q69+Q71*Assumptions!$B$172</f>
+        <f aca="false">Q69+Q71*Assumptions!$B$175</f>
         <v>212.869069761923</v>
       </c>
       <c r="R81" s="54" t="n">
-        <f aca="false">R69+R71*Assumptions!$B$172</f>
+        <f aca="false">R69+R71*Assumptions!$B$175</f>
         <v>301.872327686181</v>
       </c>
       <c r="S81" s="54" t="n">
-        <f aca="false">S69+S71*Assumptions!$B$172</f>
+        <f aca="false">S69+S71*Assumptions!$B$175</f>
         <v>384.630348735531</v>
       </c>
       <c r="T81" s="54" t="n">
-        <f aca="false">T69+T71*Assumptions!$B$172</f>
+        <f aca="false">T69+T71*Assumptions!$B$175</f>
         <v>456.312072334953</v>
       </c>
       <c r="U81" s="54" t="n">
-        <f aca="false">U69+U71*Assumptions!$B$172</f>
+        <f aca="false">U69+U71*Assumptions!$B$175</f>
         <v>526.797042678844</v>
       </c>
       <c r="V81" s="54" t="n">
-        <f aca="false">V69+V71*Assumptions!$B$172</f>
+        <f aca="false">V69+V71*Assumptions!$B$175</f>
         <v>598.428229627979</v>
       </c>
       <c r="W81" s="54" t="n">
-        <f aca="false">W69+W71*Assumptions!$B$172</f>
+        <f aca="false">W69+W71*Assumptions!$B$175</f>
         <v>678.010546193761</v>
       </c>
       <c r="X81" s="54" t="n">
-        <f aca="false">X69+X71*Assumptions!$B$172</f>
+        <f aca="false">X69+X71*Assumptions!$B$175</f>
         <v>786.775349934666</v>
       </c>
       <c r="Y81" s="54" t="n">
-        <f aca="false">Y69+Y71*Assumptions!$B$172</f>
+        <f aca="false">Y69+Y71*Assumptions!$B$175</f>
         <v>889.303256168486</v>
       </c>
       <c r="Z81" s="54" t="n">
-        <f aca="false">Z69+Z71*Assumptions!$B$172</f>
+        <f aca="false">Z69+Z71*Assumptions!$B$175</f>
         <v>981.211367265718</v>
       </c>
       <c r="AA81" s="54" t="n">
-        <f aca="false">AA69+AA71*Assumptions!$B$172</f>
+        <f aca="false">AA69+AA71*Assumptions!$B$175</f>
         <v>2646.19010151054</v>
       </c>
       <c r="AB81" s="54" t="n">
-        <f aca="false">AB69+AB71*Assumptions!$B$172</f>
+        <f aca="false">AB69+AB71*Assumptions!$B$175</f>
         <v>5296.90547362023</v>
       </c>
       <c r="AC81" s="54" t="n">
-        <f aca="false">AC69+AC71*Assumptions!$B$172</f>
+        <f aca="false">AC69+AC71*Assumptions!$B$175</f>
         <v>9083.67123977318</v>
       </c>
       <c r="AD81" s="54" t="n">
-        <f aca="false">AD69+AD71*Assumptions!$B$172</f>
+        <f aca="false">AD69+AD71*Assumptions!$B$175</f>
         <v>13701.2697766806</v>
       </c>
       <c r="AE81" s="54" t="n">
-        <f aca="false">AE69+AE71*Assumptions!$B$172</f>
+        <f aca="false">AE69+AE71*Assumptions!$B$175</f>
         <v>18599.5639670413</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B82" s="23" t="s">
         <v>190</v>
@@ -15262,10 +15397,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C83" s="28" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$51,C82*Assumptions!$B$143,0)</f>
@@ -15386,7 +15521,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B84" s="23" t="s">
         <v>114</v>
@@ -15510,7 +15645,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B85" s="23" t="s">
         <v>76</v>
@@ -15634,7 +15769,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B86" s="23" t="s">
         <v>114</v>
@@ -15758,10 +15893,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C87" s="45" t="n">
         <f aca="false">C83*C86*Assumptions!$B$7*C7</f>
@@ -15882,7 +16017,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B88" s="23" t="s">
         <v>114</v>
@@ -16006,10 +16141,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C89" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,C84*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
@@ -16130,10 +16265,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C90" s="45" t="n">
         <f aca="false">C83*Assumptions!$B$158*Assumptions!$B$144*C7/12*(1+Assumptions!$B$16)</f>
@@ -16254,7 +16389,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B91" s="23" t="s">
         <v>114</v>
@@ -16378,7 +16513,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B92" s="23" t="s">
         <v>114</v>
@@ -16502,131 +16637,131 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B93" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C93" s="55" t="n">
-        <f aca="false">C88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">C88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="D93" s="55" t="n">
-        <f aca="false">D88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">D88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="E93" s="55" t="n">
-        <f aca="false">E88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">E88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="F93" s="55" t="n">
-        <f aca="false">F88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">F88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="G93" s="55" t="n">
-        <f aca="false">G88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">G88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="H93" s="55" t="n">
-        <f aca="false">H88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">H88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="I93" s="55" t="n">
-        <f aca="false">I88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">I88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="J93" s="55" t="n">
-        <f aca="false">J88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">J88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="K93" s="55" t="n">
-        <f aca="false">K88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">K88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="L93" s="55" t="n">
-        <f aca="false">L88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">L88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="M93" s="55" t="n">
-        <f aca="false">M88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">M88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="N93" s="55" t="n">
-        <f aca="false">N88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">N88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="O93" s="55" t="n">
-        <f aca="false">O88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">O88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="P93" s="55" t="n">
-        <f aca="false">P88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">P88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="Q93" s="55" t="n">
-        <f aca="false">Q88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Q88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="R93" s="55" t="n">
-        <f aca="false">R88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">R88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="S93" s="55" t="n">
-        <f aca="false">S88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">S88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="T93" s="55" t="n">
-        <f aca="false">T88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">T88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="U93" s="55" t="n">
-        <f aca="false">U88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">U88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="V93" s="55" t="n">
-        <f aca="false">V88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">V88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="W93" s="55" t="n">
-        <f aca="false">W88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">W88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0.214098859285734</v>
       </c>
       <c r="X93" s="55" t="n">
-        <f aca="false">X88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">X88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0.456801538826948</v>
       </c>
       <c r="Y93" s="55" t="n">
-        <f aca="false">Y88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Y88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0.750261414789722</v>
       </c>
       <c r="Z93" s="55" t="n">
-        <f aca="false">Z88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Z88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>1.2551837406137</v>
       </c>
       <c r="AA93" s="55" t="n">
-        <f aca="false">AA88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AA88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>267.891437733543</v>
       </c>
       <c r="AB93" s="55" t="n">
-        <f aca="false">AB88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AB88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>724.442885482496</v>
       </c>
       <c r="AC93" s="55" t="n">
-        <f aca="false">AC88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AC88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>1506.99134666575</v>
       </c>
       <c r="AD93" s="55" t="n">
-        <f aca="false">AD88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AD88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>2718.04612835477</v>
       </c>
       <c r="AE93" s="55" t="n">
-        <f aca="false">AE88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AE88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>4452.02132006264</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B94" s="23" t="s">
         <v>114</v>
@@ -16750,7 +16885,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B95" s="23" t="s">
         <v>114</v>
@@ -16874,258 +17009,258 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B96" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C96" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$53,C83*C84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$53,C83*C84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="D96" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$53,D83*D84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$53,D83*D84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="E96" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$53,E83*E84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$53,E83*E84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="F96" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$53,F83*F84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$53,F83*F84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="G96" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$53,G83*G84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$53,G83*G84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="H96" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$53,H83*H84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$53,H83*H84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="I96" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$53,I83*I84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$53,I83*I84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="J96" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$53,J83*J84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$53,J83*J84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="K96" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$53,K83*K84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$53,K83*K84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="L96" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$53,L83*L84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$53,L83*L84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="M96" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$53,M83*M84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$53,M83*M84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="N96" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$53,N83*N84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$53,N83*N84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="O96" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$53,O83*O84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$53,O83*O84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="P96" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$53,P83*P84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$53,P83*P84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="Q96" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,Q83*Q84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,Q83*Q84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="R96" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$53,R83*R84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$53,R83*R84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="S96" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$53,S83*S84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$53,S83*S84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="T96" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$53,T83*T84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$53,T83*T84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="U96" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$53,U83*U84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$53,U83*U84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="V96" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$53,V83*V84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$53,V83*V84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="W96" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$53,W83*W84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$53,W83*W84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>101.951837755112</v>
       </c>
       <c r="X96" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$53,X83*X84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$53,X83*X84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>213.259355194654</v>
       </c>
       <c r="Y96" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,Y83*Y84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,Y83*Y84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>340.25460988196</v>
       </c>
       <c r="Z96" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,Z83*Z84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,Z83*Z84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>524.303985218755</v>
       </c>
       <c r="AA96" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,AA83*AA84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,AA83*AA84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>10630.6126084739</v>
       </c>
       <c r="AB96" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,AB83*AB84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,AB83*AB84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>28747.7335508927</v>
       </c>
       <c r="AC96" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,AC83*AC84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,AC83*AC84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>59801.2439153075</v>
       </c>
       <c r="AD96" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,AD83*AD84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,AD83*AD84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>107858.973347412</v>
       </c>
       <c r="AE96" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,AE83*AE84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,AE83*AE84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>176667.512700899</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B97" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C97" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$53,(C96*Assumptions!$B$29*Assumptions!$B$30+C83*C85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$53,(C96*Assumptions!$B$29*Assumptions!$B$30+C83*C85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v>0</v>
       </c>
       <c r="D97" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$53,(D96*Assumptions!$B$29*Assumptions!$B$30+D83*D85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$53,(D96*Assumptions!$B$29*Assumptions!$B$30+D83*D85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v>0</v>
       </c>
       <c r="E97" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$53,(E96*Assumptions!$B$29*Assumptions!$B$30+E83*E85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$53,(E96*Assumptions!$B$29*Assumptions!$B$30+E83*E85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v>0</v>
       </c>
       <c r="F97" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$53,(F96*Assumptions!$B$29*Assumptions!$B$30+F83*F85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$53,(F96*Assumptions!$B$29*Assumptions!$B$30+F83*F85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v>0</v>
       </c>
       <c r="G97" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$53,(G96*Assumptions!$B$29*Assumptions!$B$30+G83*G85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$53,(G96*Assumptions!$B$29*Assumptions!$B$30+G83*G85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v>0</v>
       </c>
       <c r="H97" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$53,(H96*Assumptions!$B$29*Assumptions!$B$30+H83*H85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$53,(H96*Assumptions!$B$29*Assumptions!$B$30+H83*H85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v>0</v>
       </c>
       <c r="I97" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$53,(I96*Assumptions!$B$29*Assumptions!$B$30+I83*I85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$53,(I96*Assumptions!$B$29*Assumptions!$B$30+I83*I85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v>0</v>
       </c>
       <c r="J97" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$53,(J96*Assumptions!$B$29*Assumptions!$B$30+J83*J85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$53,(J96*Assumptions!$B$29*Assumptions!$B$30+J83*J85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v>0</v>
       </c>
       <c r="K97" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$53,(K96*Assumptions!$B$29*Assumptions!$B$30+K83*K85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$53,(K96*Assumptions!$B$29*Assumptions!$B$30+K83*K85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v>0</v>
       </c>
       <c r="L97" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$53,(L96*Assumptions!$B$29*Assumptions!$B$30+L83*L85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$53,(L96*Assumptions!$B$29*Assumptions!$B$30+L83*L85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v>0</v>
       </c>
       <c r="M97" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$53,(M96*Assumptions!$B$29*Assumptions!$B$30+M83*M85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$53,(M96*Assumptions!$B$29*Assumptions!$B$30+M83*M85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v>0</v>
       </c>
       <c r="N97" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$53,(N96*Assumptions!$B$29*Assumptions!$B$30+N83*N85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$53,(N96*Assumptions!$B$29*Assumptions!$B$30+N83*N85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v>0</v>
       </c>
       <c r="O97" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$53,(O96*Assumptions!$B$29*Assumptions!$B$30+O83*O85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$53,(O96*Assumptions!$B$29*Assumptions!$B$30+O83*O85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v>0</v>
       </c>
       <c r="P97" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$53,(P96*Assumptions!$B$29*Assumptions!$B$30+P83*P85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$53,(P96*Assumptions!$B$29*Assumptions!$B$30+P83*P85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v>0</v>
       </c>
       <c r="Q97" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,(Q96*Assumptions!$B$29*Assumptions!$B$30+Q83*Q85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,(Q96*Assumptions!$B$29*Assumptions!$B$30+Q83*Q85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v>0</v>
       </c>
       <c r="R97" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$53,(R96*Assumptions!$B$29*Assumptions!$B$30+R83*R85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$53,(R96*Assumptions!$B$29*Assumptions!$B$30+R83*R85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v>0</v>
       </c>
       <c r="S97" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$53,(S96*Assumptions!$B$29*Assumptions!$B$30+S83*S85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$53,(S96*Assumptions!$B$29*Assumptions!$B$30+S83*S85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v>0</v>
       </c>
       <c r="T97" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$53,(T96*Assumptions!$B$29*Assumptions!$B$30+T83*T85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$53,(T96*Assumptions!$B$29*Assumptions!$B$30+T83*T85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v>0</v>
       </c>
       <c r="U97" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$53,(U96*Assumptions!$B$29*Assumptions!$B$30+U83*U85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$53,(U96*Assumptions!$B$29*Assumptions!$B$30+U83*U85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v>0</v>
       </c>
       <c r="V97" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$53,(V96*Assumptions!$B$29*Assumptions!$B$30+V83*V85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$53,(V96*Assumptions!$B$29*Assumptions!$B$30+V83*V85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v>0</v>
       </c>
       <c r="W97" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$53,(W96*Assumptions!$B$29*Assumptions!$B$30+W83*W85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$53,(W96*Assumptions!$B$29*Assumptions!$B$30+W83*W85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v>0.24213561466839</v>
       </c>
       <c r="X97" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$53,(X96*Assumptions!$B$29*Assumptions!$B$30+X83*X85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$53,(X96*Assumptions!$B$29*Assumptions!$B$30+X83*X85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v>0.506490968587303</v>
       </c>
       <c r="Y97" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,(Y96*Assumptions!$B$29*Assumptions!$B$30+Y83*Y85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,(Y96*Assumptions!$B$29*Assumptions!$B$30+Y83*Y85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v>0.808104698469655</v>
       </c>
       <c r="Z97" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,(Z96*Assumptions!$B$29*Assumptions!$B$30+Z83*Z85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,(Z96*Assumptions!$B$29*Assumptions!$B$30+Z83*Z85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v>1.24522196489454</v>
       </c>
       <c r="AA97" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,(AA96*Assumptions!$B$29*Assumptions!$B$30+AA83*AA85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,(AA96*Assumptions!$B$29*Assumptions!$B$30+AA83*AA85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v>302.972459341507</v>
       </c>
       <c r="AB97" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,(AB96*Assumptions!$B$29*Assumptions!$B$30+AB83*AB85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,(AB96*Assumptions!$B$29*Assumptions!$B$30+AB83*AB85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v>819.310406200442</v>
       </c>
       <c r="AC97" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,(AC96*Assumptions!$B$29*Assumptions!$B$30+AC83*AC85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,(AC96*Assumptions!$B$29*Assumptions!$B$30+AC83*AC85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v>1704.33545158626</v>
       </c>
       <c r="AD97" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,(AD96*Assumptions!$B$29*Assumptions!$B$30+AD83*AD85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,(AD96*Assumptions!$B$29*Assumptions!$B$30+AD83*AD85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v>3073.98074040123</v>
       </c>
       <c r="AE97" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,(AE96*Assumptions!$B$29*Assumptions!$B$30+AE83*AE85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,(AE96*Assumptions!$B$29*Assumptions!$B$30+AE83*AE85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v>5035.02411197561</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="C98" s="45" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$49,(C69+C71*Assumptions!$B$138)*Assumptions!$B$137*C7/12,0)</f>
@@ -17246,7 +17381,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B99" s="23" t="s">
         <v>114</v>
@@ -17370,7 +17505,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="46" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="B101" s="47"/>
       <c r="C101" s="47"/>
@@ -17405,7 +17540,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B102" s="23" t="s">
         <v>190</v>
@@ -17529,7 +17664,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B103" s="23" t="s">
         <v>190</v>
@@ -17652,7 +17787,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B104" s="23" t="s">
         <v>190</v>
@@ -17776,10 +17911,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B105" s="23" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C105" s="51" t="n">
         <v>1</v>
@@ -17899,7 +18034,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B106" s="23" t="s">
         <v>190</v>
@@ -18023,7 +18158,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B107" s="23" t="s">
         <v>190</v>
@@ -18147,7 +18282,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B108" s="23" t="s">
         <v>190</v>
@@ -18271,7 +18406,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B109" s="23" t="s">
         <v>190</v>
@@ -18395,7 +18530,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B110" s="23" t="s">
         <v>190</v>
@@ -18519,131 +18654,131 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B111" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C111" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C107*Assumptions!$B$170*C7,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$47,C107*Assumptions!$B$173*C7,0)</f>
         <v>5228.20057034509</v>
       </c>
       <c r="D111" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D107*Assumptions!$B$170*D7,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$47,D107*Assumptions!$B$173*D7,0)</f>
         <v>9936.39049123219</v>
       </c>
       <c r="E111" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E107*Assumptions!$B$170*E7,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$47,E107*Assumptions!$B$173*E7,0)</f>
         <v>14202.5443206119</v>
       </c>
       <c r="F111" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F107*Assumptions!$B$170*F7,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$47,F107*Assumptions!$B$173*F7,0)</f>
         <v>19440.9012882141</v>
       </c>
       <c r="G111" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G107*Assumptions!$B$170*G7,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$47,G107*Assumptions!$B$173*G7,0)</f>
         <v>23848.8707570092</v>
       </c>
       <c r="H111" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H107*Assumptions!$B$170*H7,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$47,H107*Assumptions!$B$173*H7,0)</f>
         <v>27212.4460651864</v>
       </c>
       <c r="I111" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I107*Assumptions!$B$170*I7,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$47,I107*Assumptions!$B$173*I7,0)</f>
         <v>30252.9344486068</v>
       </c>
       <c r="J111" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J107*Assumptions!$B$170*J7,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$47,J107*Assumptions!$B$173*J7,0)</f>
         <v>33140.4095035015</v>
       </c>
       <c r="K111" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K107*Assumptions!$B$170*K7,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$47,K107*Assumptions!$B$173*K7,0)</f>
         <v>36291.9607671451</v>
       </c>
       <c r="L111" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L107*Assumptions!$B$170*L7,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$47,L107*Assumptions!$B$173*L7,0)</f>
         <v>40920.5128924508</v>
       </c>
       <c r="M111" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M107*Assumptions!$B$170*M7,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$47,M107*Assumptions!$B$173*M7,0)</f>
         <v>44802.3334874396</v>
       </c>
       <c r="N111" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N107*Assumptions!$B$170*N7,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$47,N107*Assumptions!$B$173*N7,0)</f>
         <v>47772.4379613417</v>
       </c>
       <c r="O111" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O107*Assumptions!$B$170*O7,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$47,O107*Assumptions!$B$173*O7,0)</f>
         <v>62583.918782009</v>
       </c>
       <c r="P111" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P107*Assumptions!$B$170*P7,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$47,P107*Assumptions!$B$173*P7,0)</f>
         <v>76170.49638412</v>
       </c>
       <c r="Q111" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q107*Assumptions!$B$170*Q7,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$47,Q107*Assumptions!$B$173*Q7,0)</f>
         <v>88698.0035359854</v>
       </c>
       <c r="R111" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R107*Assumptions!$B$170*R7,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$47,R107*Assumptions!$B$173*R7,0)</f>
         <v>105003.918287205</v>
       </c>
       <c r="S111" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S107*Assumptions!$B$170*S7,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$47,S107*Assumptions!$B$173*S7,0)</f>
         <v>118931.195541268</v>
       </c>
       <c r="T111" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T107*Assumptions!$B$170*T7,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$47,T107*Assumptions!$B$173*T7,0)</f>
         <v>129522.211475481</v>
       </c>
       <c r="U111" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U107*Assumptions!$B$170*U7,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$47,U107*Assumptions!$B$173*U7,0)</f>
         <v>139226.316894336</v>
       </c>
       <c r="V111" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V107*Assumptions!$B$170*V7,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$47,V107*Assumptions!$B$173*V7,0)</f>
         <v>148622.362498393</v>
       </c>
       <c r="W111" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W107*Assumptions!$B$170*W7,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$47,W107*Assumptions!$B$173*W7,0)</f>
         <v>159250.450705959</v>
       </c>
       <c r="X111" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X107*Assumptions!$B$170*X7,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$47,X107*Assumptions!$B$173*X7,0)</f>
         <v>175758.244616575</v>
       </c>
       <c r="Y111" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y107*Assumptions!$B$170*Y7,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$47,Y107*Assumptions!$B$173*Y7,0)</f>
         <v>189902.825466974</v>
       </c>
       <c r="Z111" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z107*Assumptions!$B$170*Z7,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$47,Z107*Assumptions!$B$173*Z7,0)</f>
         <v>200866.580651102</v>
       </c>
       <c r="AA111" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA107*Assumptions!$B$170*AA7,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$47,AA107*Assumptions!$B$173*AA7,0)</f>
         <v>4417884.00608389</v>
       </c>
       <c r="AB111" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB107*Assumptions!$B$170*AB7,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$47,AB107*Assumptions!$B$173*AB7,0)</f>
         <v>6965572.89061672</v>
       </c>
       <c r="AC111" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC107*Assumptions!$B$170*AC7,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$47,AC107*Assumptions!$B$173*AC7,0)</f>
         <v>9584722.80021558</v>
       </c>
       <c r="AD111" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD107*Assumptions!$B$170*AD7,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$47,AD107*Assumptions!$B$173*AD7,0)</f>
         <v>11210375.0333783</v>
       </c>
       <c r="AE111" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE107*Assumptions!$B$170*AE7,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$47,AE107*Assumptions!$B$173*AE7,0)</f>
         <v>11055324.3558893</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B112" s="23" t="s">
         <v>114</v>
@@ -18767,7 +18902,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="B113" s="23" t="s">
         <v>47</v>
@@ -18891,10 +19026,10 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B114" s="23" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C114" s="56" t="n">
         <f aca="false">(Assumptions!$B$136+Assumptions!$B$137*IF(C107+C109=0,1,(C107+C109*Assumptions!$B$138)/(C107+C109)))*C7/12</f>
@@ -19015,10 +19150,10 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B115" s="23" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C115" s="56" t="n">
         <f aca="false">Assumptions!$B$137*IF(C107+C109=0,1,(C107+C109*Assumptions!$B$138)/(C107+C109))*C7/12</f>
@@ -19139,7 +19274,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B116" s="23" t="s">
         <v>47</v>
@@ -19263,7 +19398,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B117" s="23" t="s">
         <v>47</v>
@@ -19387,7 +19522,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B118" s="23" t="s">
         <v>114</v>
@@ -19511,131 +19646,131 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B119" s="23" t="s">
         <v>190</v>
       </c>
       <c r="C119" s="54" t="n">
-        <f aca="false">C107+C109*Assumptions!$B$172</f>
+        <f aca="false">C107+C109*Assumptions!$B$175</f>
         <v>178.669</v>
       </c>
       <c r="D119" s="54" t="n">
-        <f aca="false">D107+D109*Assumptions!$B$172</f>
+        <f aca="false">D107+D109*Assumptions!$B$175</f>
         <v>348.250261725952</v>
       </c>
       <c r="E119" s="54" t="n">
-        <f aca="false">E107+E109*Assumptions!$B$172</f>
+        <f aca="false">E107+E109*Assumptions!$B$175</f>
         <v>510.544845457189</v>
       </c>
       <c r="F119" s="54" t="n">
-        <f aca="false">F107+F109*Assumptions!$B$172</f>
+        <f aca="false">F107+F109*Assumptions!$B$175</f>
         <v>713.148943932104</v>
       </c>
       <c r="G119" s="54" t="n">
-        <f aca="false">G107+G109*Assumptions!$B$172</f>
+        <f aca="false">G107+G109*Assumptions!$B$175</f>
         <v>896.075325611234</v>
       </c>
       <c r="H119" s="54" t="n">
-        <f aca="false">H107+H109*Assumptions!$B$172</f>
+        <f aca="false">H107+H109*Assumptions!$B$175</f>
         <v>1050.63137490653</v>
       </c>
       <c r="I119" s="54" t="n">
-        <f aca="false">I107+I109*Assumptions!$B$172</f>
+        <f aca="false">I107+I109*Assumptions!$B$175</f>
         <v>1199.73254941302</v>
       </c>
       <c r="J119" s="54" t="n">
-        <f aca="false">J107+J109*Assumptions!$B$172</f>
+        <f aca="false">J107+J109*Assumptions!$B$175</f>
         <v>1348.65436713468</v>
       </c>
       <c r="K119" s="54" t="n">
-        <f aca="false">K107+K109*Assumptions!$B$172</f>
+        <f aca="false">K107+K109*Assumptions!$B$175</f>
         <v>1511.39635457054</v>
       </c>
       <c r="L119" s="54" t="n">
-        <f aca="false">L107+L109*Assumptions!$B$172</f>
+        <f aca="false">L107+L109*Assumptions!$B$175</f>
         <v>1729.8476944193</v>
       </c>
       <c r="M119" s="54" t="n">
-        <f aca="false">M107+M109*Assumptions!$B$172</f>
+        <f aca="false">M107+M109*Assumptions!$B$175</f>
         <v>1930.46740189359</v>
       </c>
       <c r="N119" s="54" t="n">
-        <f aca="false">N107+N109*Assumptions!$B$172</f>
+        <f aca="false">N107+N109*Assumptions!$B$175</f>
         <v>2106.37708445176</v>
       </c>
       <c r="O119" s="54" t="n">
-        <f aca="false">O107+O109*Assumptions!$B$172</f>
+        <f aca="false">O107+O109*Assumptions!$B$175</f>
         <v>2691.88787404417</v>
       </c>
       <c r="P119" s="54" t="n">
-        <f aca="false">P107+P109*Assumptions!$B$172</f>
+        <f aca="false">P107+P109*Assumptions!$B$175</f>
         <v>3260.13806295296</v>
       </c>
       <c r="Q119" s="54" t="n">
-        <f aca="false">Q107+Q109*Assumptions!$B$172</f>
+        <f aca="false">Q107+Q109*Assumptions!$B$175</f>
         <v>3814.76047911621</v>
       </c>
       <c r="R119" s="54" t="n">
-        <f aca="false">R107+R109*Assumptions!$B$172</f>
+        <f aca="false">R107+R109*Assumptions!$B$175</f>
         <v>4519.31259964623</v>
       </c>
       <c r="S119" s="54" t="n">
-        <f aca="false">S107+S109*Assumptions!$B$172</f>
+        <f aca="false">S107+S109*Assumptions!$B$175</f>
         <v>5169.65830054593</v>
       </c>
       <c r="T119" s="54" t="n">
-        <f aca="false">T107+T109*Assumptions!$B$172</f>
+        <f aca="false">T107+T109*Assumptions!$B$175</f>
         <v>5729.12114582439</v>
       </c>
       <c r="U119" s="54" t="n">
-        <f aca="false">U107+U109*Assumptions!$B$172</f>
+        <f aca="false">U107+U109*Assumptions!$B$175</f>
         <v>6275.86450864336</v>
       </c>
       <c r="V119" s="54" t="n">
-        <f aca="false">V107+V109*Assumptions!$B$172</f>
+        <f aca="false">V107+V109*Assumptions!$B$175</f>
         <v>6828.19707762831</v>
       </c>
       <c r="W119" s="54" t="n">
-        <f aca="false">W107+W109*Assumptions!$B$172</f>
+        <f aca="false">W107+W109*Assumptions!$B$175</f>
         <v>7438.23881735861</v>
       </c>
       <c r="X119" s="54" t="n">
-        <f aca="false">X107+X109*Assumptions!$B$172</f>
+        <f aca="false">X107+X109*Assumptions!$B$175</f>
         <v>8266.8656011235</v>
       </c>
       <c r="Y119" s="54" t="n">
-        <f aca="false">Y107+Y109*Assumptions!$B$172</f>
+        <f aca="false">Y107+Y109*Assumptions!$B$175</f>
         <v>9042.14836834422</v>
       </c>
       <c r="Z119" s="54" t="n">
-        <f aca="false">Z107+Z109*Assumptions!$B$172</f>
+        <f aca="false">Z107+Z109*Assumptions!$B$175</f>
         <v>9732.22105640219</v>
       </c>
       <c r="AA119" s="54" t="n">
-        <f aca="false">AA107+AA109*Assumptions!$B$172</f>
+        <f aca="false">AA107+AA109*Assumptions!$B$175</f>
         <v>21314.0928917391</v>
       </c>
       <c r="AB119" s="54" t="n">
-        <f aca="false">AB107+AB109*Assumptions!$B$172</f>
+        <f aca="false">AB107+AB109*Assumptions!$B$175</f>
         <v>38302.9431735575</v>
       </c>
       <c r="AC119" s="54" t="n">
-        <f aca="false">AC107+AC109*Assumptions!$B$172</f>
+        <f aca="false">AC107+AC109*Assumptions!$B$175</f>
         <v>59853.5833790927</v>
       </c>
       <c r="AD119" s="54" t="n">
-        <f aca="false">AD107+AD109*Assumptions!$B$172</f>
+        <f aca="false">AD107+AD109*Assumptions!$B$175</f>
         <v>82097.599874401</v>
       </c>
       <c r="AE119" s="54" t="n">
-        <f aca="false">AE107+AE109*Assumptions!$B$172</f>
+        <f aca="false">AE107+AE109*Assumptions!$B$175</f>
         <v>100411.932330575</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B120" s="23" t="s">
         <v>190</v>
@@ -19759,10 +19894,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="C121" s="28" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$51,C120*Assumptions!$B$143,0)</f>
@@ -19883,7 +20018,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B122" s="23" t="s">
         <v>114</v>
@@ -20007,7 +20142,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B123" s="23" t="s">
         <v>76</v>
@@ -20131,7 +20266,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B124" s="23" t="s">
         <v>114</v>
@@ -20255,10 +20390,10 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C125" s="45" t="n">
         <f aca="false">C121*C124*Assumptions!$B$7*C7</f>
@@ -20379,7 +20514,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B126" s="23" t="s">
         <v>114</v>
@@ -20503,10 +20638,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C127" s="45" t="n">
         <f aca="false">IF(Assumptions!$B$144=0,0,C122*Assumptions!$B$156*Assumptions!$B$7/Assumptions!$B$144)</f>
@@ -20627,10 +20762,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C128" s="45" t="n">
         <f aca="false">C121*Assumptions!$B$158*Assumptions!$B$144*C7/12*(1+Assumptions!$B$16)</f>
@@ -20751,7 +20886,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B129" s="23" t="s">
         <v>114</v>
@@ -20875,7 +21010,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B130" s="23" t="s">
         <v>114</v>
@@ -20999,131 +21134,131 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="6" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B131" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C131" s="55" t="n">
-        <f aca="false">C126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">C126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="D131" s="55" t="n">
-        <f aca="false">D126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">D126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="E131" s="55" t="n">
-        <f aca="false">E126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">E126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="F131" s="55" t="n">
-        <f aca="false">F126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">F126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="G131" s="55" t="n">
-        <f aca="false">G126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">G126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="H131" s="55" t="n">
-        <f aca="false">H126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">H126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="I131" s="55" t="n">
-        <f aca="false">I126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">I126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="J131" s="55" t="n">
-        <f aca="false">J126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">J126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="K131" s="55" t="n">
-        <f aca="false">K126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">K126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="L131" s="55" t="n">
-        <f aca="false">L126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">L126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="M131" s="55" t="n">
-        <f aca="false">M126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">M126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="N131" s="55" t="n">
-        <f aca="false">N126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">N126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>0</v>
       </c>
       <c r="O131" s="55" t="n">
-        <f aca="false">O126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">O126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>4.16351257012109</v>
       </c>
       <c r="P131" s="55" t="n">
-        <f aca="false">P126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">P126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>4.29394441910505</v>
       </c>
       <c r="Q131" s="55" t="n">
-        <f aca="false">Q126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Q126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>4.85083057762754</v>
       </c>
       <c r="R131" s="55" t="n">
-        <f aca="false">R126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">R126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>5.42067730004756</v>
       </c>
       <c r="S131" s="55" t="n">
-        <f aca="false">S126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">S126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>6.40196141052053</v>
       </c>
       <c r="T131" s="55" t="n">
-        <f aca="false">T126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">T126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>7.39695901918176</v>
       </c>
       <c r="U131" s="55" t="n">
-        <f aca="false">U126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">U126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>8.14703088820949</v>
       </c>
       <c r="V131" s="55" t="n">
-        <f aca="false">V126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">V126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>9.66330175326764</v>
       </c>
       <c r="W131" s="55" t="n">
-        <f aca="false">W126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">W126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>14.4258260830205</v>
       </c>
       <c r="X131" s="55" t="n">
-        <f aca="false">X126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">X126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>18.1441688925974</v>
       </c>
       <c r="Y131" s="55" t="n">
-        <f aca="false">Y126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Y126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>22.6244735449518</v>
       </c>
       <c r="Z131" s="55" t="n">
-        <f aca="false">Z126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">Z126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>30.5778556521924</v>
       </c>
       <c r="AA131" s="55" t="n">
-        <f aca="false">AA126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AA126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>2779.85436118174</v>
       </c>
       <c r="AB131" s="55" t="n">
-        <f aca="false">AB126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AB126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>6557.34261299924</v>
       </c>
       <c r="AC131" s="55" t="n">
-        <f aca="false">AC126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AC126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>12555.1932937313</v>
       </c>
       <c r="AD131" s="55" t="n">
-        <f aca="false">AD126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AD126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>21376.2514613152</v>
       </c>
       <c r="AE131" s="55" t="n">
-        <f aca="false">AE126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f aca="false">AE126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v>33952.4335142931</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B132" s="23" t="s">
         <v>114</v>
@@ -21247,7 +21382,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="6" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B133" s="23" t="s">
         <v>114</v>
@@ -21371,258 +21506,258 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="6" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B134" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C134" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$53,C121*C122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$53,C121*C122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="D134" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$53,D121*D122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$53,D121*D122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="E134" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$53,E121*E122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$53,E121*E122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="F134" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$53,F121*F122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$53,F121*F122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="G134" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$53,G121*G122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$53,G121*G122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="H134" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$53,H121*H122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$53,H121*H122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="I134" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$53,I121*I122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$53,I121*I122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="J134" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$53,J121*J122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$53,J121*J122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="K134" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$53,K121*K122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$53,K121*K122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="L134" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$53,L121*L122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$53,L121*L122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="M134" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$53,M121*M122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$53,M121*M122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="N134" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$53,N121*N122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$53,N121*N122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>0</v>
       </c>
       <c r="O134" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$53,O121*O122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$53,O121*O122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>1802.38639399181</v>
       </c>
       <c r="P134" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$53,P121*P122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$53,P121*P122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>2044.73543766907</v>
       </c>
       <c r="Q134" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,Q121*Q122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,Q121*Q122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>2357.06053334671</v>
       </c>
       <c r="R134" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$53,R121*R122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$53,R121*R122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>2633.95398447403</v>
       </c>
       <c r="S134" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$53,S121*S122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$53,S121*S122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>3048.55305262882</v>
       </c>
       <c r="T134" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$53,T121*T122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$53,T121*T122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>3707.74888179537</v>
       </c>
       <c r="U134" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$53,U121*U122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$53,U121*U122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>4408.56649794886</v>
       </c>
       <c r="V134" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$53,V121*V122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$53,V121*V122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>5112.85807051198</v>
       </c>
       <c r="W134" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$53,W121*W122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$53,W121*W122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>6869.44099191454</v>
       </c>
       <c r="X134" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$53,X121*X122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$53,X121*X122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>8470.66708337879</v>
       </c>
       <c r="Y134" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,Y121*Y122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,Y121*Y122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>10260.5322199328</v>
       </c>
       <c r="Z134" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,Z121*Z122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,Z121*Z122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>12772.7049507905</v>
       </c>
       <c r="AA134" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,AA121*AA122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,AA121*AA122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>110311.680999275</v>
       </c>
       <c r="AB134" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,AB121*AB122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,AB121*AB122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>260212.008452351</v>
       </c>
       <c r="AC134" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,AC121*AC122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,AC121*AC122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>498221.956100447</v>
       </c>
       <c r="AD134" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,AD121*AD122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,AD121*AD122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>848263.946877586</v>
       </c>
       <c r="AE134" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,AE121*AE122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,AE121*AE122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v>1347318.79024973</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="6" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B135" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C135" s="55" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$53,(C134*Assumptions!$B$29*Assumptions!$B$30+C121*C123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$53,(C134*Assumptions!$B$29*Assumptions!$B$30+C121*C123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v>0</v>
       </c>
       <c r="D135" s="55" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$53,(D134*Assumptions!$B$29*Assumptions!$B$30+D121*D123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$53,(D134*Assumptions!$B$29*Assumptions!$B$30+D121*D123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v>0</v>
       </c>
       <c r="E135" s="55" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$53,(E134*Assumptions!$B$29*Assumptions!$B$30+E121*E123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$53,(E134*Assumptions!$B$29*Assumptions!$B$30+E121*E123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v>0</v>
       </c>
       <c r="F135" s="55" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$53,(F134*Assumptions!$B$29*Assumptions!$B$30+F121*F123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$53,(F134*Assumptions!$B$29*Assumptions!$B$30+F121*F123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v>0</v>
       </c>
       <c r="G135" s="55" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$53,(G134*Assumptions!$B$29*Assumptions!$B$30+G121*G123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$53,(G134*Assumptions!$B$29*Assumptions!$B$30+G121*G123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v>0</v>
       </c>
       <c r="H135" s="55" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$53,(H134*Assumptions!$B$29*Assumptions!$B$30+H121*H123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$53,(H134*Assumptions!$B$29*Assumptions!$B$30+H121*H123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v>0</v>
       </c>
       <c r="I135" s="55" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$53,(I134*Assumptions!$B$29*Assumptions!$B$30+I121*I123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$53,(I134*Assumptions!$B$29*Assumptions!$B$30+I121*I123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v>0</v>
       </c>
       <c r="J135" s="55" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$53,(J134*Assumptions!$B$29*Assumptions!$B$30+J121*J123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$53,(J134*Assumptions!$B$29*Assumptions!$B$30+J121*J123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v>0</v>
       </c>
       <c r="K135" s="55" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$53,(K134*Assumptions!$B$29*Assumptions!$B$30+K121*K123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$53,(K134*Assumptions!$B$29*Assumptions!$B$30+K121*K123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v>0</v>
       </c>
       <c r="L135" s="55" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$53,(L134*Assumptions!$B$29*Assumptions!$B$30+L121*L123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$53,(L134*Assumptions!$B$29*Assumptions!$B$30+L121*L123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v>0</v>
       </c>
       <c r="M135" s="55" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$53,(M134*Assumptions!$B$29*Assumptions!$B$30+M121*M123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$53,(M134*Assumptions!$B$29*Assumptions!$B$30+M121*M123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v>0</v>
       </c>
       <c r="N135" s="55" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$53,(N134*Assumptions!$B$29*Assumptions!$B$30+N121*N123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$53,(N134*Assumptions!$B$29*Assumptions!$B$30+N121*N123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v>0</v>
       </c>
       <c r="O135" s="55" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$53,(O134*Assumptions!$B$29*Assumptions!$B$30+O121*O123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$53,(O134*Assumptions!$B$29*Assumptions!$B$30+O121*O123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v>4.28066768573056</v>
       </c>
       <c r="P135" s="55" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$53,(P134*Assumptions!$B$29*Assumptions!$B$30+P121*P123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$53,(P134*Assumptions!$B$29*Assumptions!$B$30+P121*P123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v>4.85624666446404</v>
       </c>
       <c r="Q135" s="55" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,(Q134*Assumptions!$B$29*Assumptions!$B$30+Q121*Q123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$53,(Q134*Assumptions!$B$29*Assumptions!$B$30+Q121*Q123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v>5.59801876669844</v>
       </c>
       <c r="R135" s="55" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$53,(R134*Assumptions!$B$29*Assumptions!$B$30+R121*R123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$53,(R134*Assumptions!$B$29*Assumptions!$B$30+R121*R123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v>6.25564071312583</v>
       </c>
       <c r="S135" s="55" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$53,(S134*Assumptions!$B$29*Assumptions!$B$30+S121*S123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$53,(S134*Assumptions!$B$29*Assumptions!$B$30+S121*S123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v>7.24031349999345</v>
       </c>
       <c r="T135" s="55" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$53,(T134*Assumptions!$B$29*Assumptions!$B$30+T121*T123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$53,(T134*Assumptions!$B$29*Assumptions!$B$30+T121*T123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v>8.805903594264</v>
       </c>
       <c r="U135" s="55" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$53,(U134*Assumptions!$B$29*Assumptions!$B$30+U121*U123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$53,(U134*Assumptions!$B$29*Assumptions!$B$30+U121*U123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v>10.4703454326285</v>
       </c>
       <c r="V135" s="55" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$53,(V134*Assumptions!$B$29*Assumptions!$B$30+V121*V123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$53,(V134*Assumptions!$B$29*Assumptions!$B$30+V121*V123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v>12.1430379174659</v>
       </c>
       <c r="W135" s="55" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$53,(W134*Assumptions!$B$29*Assumptions!$B$30+W121*W123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$53,(W134*Assumptions!$B$29*Assumptions!$B$30+W121*W123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v>16.314922355797</v>
       </c>
       <c r="X135" s="55" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$53,(X134*Assumptions!$B$29*Assumptions!$B$30+X121*X123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$53,(X134*Assumptions!$B$29*Assumptions!$B$30+X121*X123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v>20.1178343230246</v>
       </c>
       <c r="Y135" s="55" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,(Y134*Assumptions!$B$29*Assumptions!$B$30+Y121*Y123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$53,(Y134*Assumptions!$B$29*Assumptions!$B$30+Y121*Y123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v>24.3687640223404</v>
       </c>
       <c r="Z135" s="55" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,(Z134*Assumptions!$B$29*Assumptions!$B$30+Z121*Z123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$53,(Z134*Assumptions!$B$29*Assumptions!$B$30+Z121*Z123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v>30.3351742581273</v>
       </c>
       <c r="AA135" s="55" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,(AA134*Assumptions!$B$29*Assumptions!$B$30+AA121*AA123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$53,(AA134*Assumptions!$B$29*Assumptions!$B$30+AA121*AA123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v>3143.88290847934</v>
       </c>
       <c r="AB135" s="55" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,(AB134*Assumptions!$B$29*Assumptions!$B$30+AB121*AB123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$53,(AB134*Assumptions!$B$29*Assumptions!$B$30+AB121*AB123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v>7416.042240892</v>
       </c>
       <c r="AC135" s="55" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,(AC134*Assumptions!$B$29*Assumptions!$B$30+AC121*AC123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$53,(AC134*Assumptions!$B$29*Assumptions!$B$30+AC121*AC123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v>14199.3257488627</v>
       </c>
       <c r="AD135" s="55" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,(AD134*Assumptions!$B$29*Assumptions!$B$30+AD121*AD123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$53,(AD134*Assumptions!$B$29*Assumptions!$B$30+AD121*AD123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v>24175.5224860112</v>
       </c>
       <c r="AE135" s="55" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,(AE134*Assumptions!$B$29*Assumptions!$B$30+AE121*AE123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$53,(AE134*Assumptions!$B$29*Assumptions!$B$30+AE121*AE123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v>38398.5855221172</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B136" s="23" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="C136" s="45" t="n">
         <f aca="false">IF(C2&gt;=Assumptions!$B$49,(C107+C109*Assumptions!$B$138)*Assumptions!$B$137*C7/12,0)</f>
@@ -21743,7 +21878,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B137" s="23" t="s">
         <v>114</v>
@@ -21867,7 +22002,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="46" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="B139" s="47"/>
       <c r="C139" s="47"/>
@@ -21902,126 +22037,126 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B140" s="23" t="s">
         <v>114</v>
       </c>
       <c r="C140" s="58" t="n">
-        <f aca="false">IF(C2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,C5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(C2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,C5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="D140" s="58" t="n">
-        <f aca="false">IF(D2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,D5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(D2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,D5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="E140" s="58" t="n">
-        <f aca="false">IF(E2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,E5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(E2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,E5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="F140" s="58" t="n">
-        <f aca="false">IF(F2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,F5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(F2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,F5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="G140" s="58" t="n">
-        <f aca="false">IF(G2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,G5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(G2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,G5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="H140" s="58" t="n">
-        <f aca="false">IF(H2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,H5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(H2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,H5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="I140" s="58" t="n">
-        <f aca="false">IF(I2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,I5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(I2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,I5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="J140" s="58" t="n">
-        <f aca="false">IF(J2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,J5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(J2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,J5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="K140" s="58" t="n">
-        <f aca="false">IF(K2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,K5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(K2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,K5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="L140" s="58" t="n">
-        <f aca="false">IF(L2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,L5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(L2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,L5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="M140" s="58" t="n">
-        <f aca="false">IF(M2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,M5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(M2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,M5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="N140" s="58" t="n">
-        <f aca="false">IF(N2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,N5)*Assumptions!$B$167,0)</f>
+        <f aca="false">IF(N2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,N5)*Assumptions!$B$170,0)</f>
         <v>0</v>
       </c>
       <c r="O140" s="58" t="n">
-        <f aca="false">IF(O2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,O5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(O2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,O5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="P140" s="58" t="n">
-        <f aca="false">IF(P2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,P5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(P2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,P5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="Q140" s="58" t="n">
-        <f aca="false">IF(Q2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Q5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(Q2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Q5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="R140" s="58" t="n">
-        <f aca="false">IF(R2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,R5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(R2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,R5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="S140" s="58" t="n">
-        <f aca="false">IF(S2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,S5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(S2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,S5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="T140" s="58" t="n">
-        <f aca="false">IF(T2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,T5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(T2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,T5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="U140" s="58" t="n">
-        <f aca="false">IF(U2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,U5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(U2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,U5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="V140" s="58" t="n">
-        <f aca="false">IF(V2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,V5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(V2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,V5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="W140" s="58" t="n">
-        <f aca="false">IF(W2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,W5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(W2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,W5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="X140" s="58" t="n">
-        <f aca="false">IF(X2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,X5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(X2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,X5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="Y140" s="58" t="n">
-        <f aca="false">IF(Y2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Y5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(Y2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Y5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="Z140" s="58" t="n">
-        <f aca="false">IF(Z2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Z5)*Assumptions!$B$167,0)</f>
-        <v>32000000</v>
+        <f aca="false">IF(Z2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Z5)*Assumptions!$B$170,0)</f>
+        <v>18900000</v>
       </c>
       <c r="AA140" s="58" t="n">
-        <f aca="false">IF(AA2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AA5)*Assumptions!$B$167,0)</f>
-        <v>64000000</v>
+        <f aca="false">IF(AA2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AA5)*Assumptions!$B$170,0)</f>
+        <v>56700000</v>
       </c>
       <c r="AB140" s="58" t="n">
-        <f aca="false">IF(AB2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AB5)*Assumptions!$B$167,0)</f>
-        <v>96000000</v>
+        <f aca="false">IF(AB2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AB5)*Assumptions!$B$170,0)</f>
+        <v>94500000</v>
       </c>
       <c r="AC140" s="58" t="n">
-        <f aca="false">IF(AC2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AC5)*Assumptions!$B$167,0)</f>
-        <v>128000000</v>
+        <f aca="false">IF(AC2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AC5)*Assumptions!$B$170,0)</f>
+        <v>132300000</v>
       </c>
       <c r="AD140" s="58" t="n">
-        <f aca="false">IF(AD2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AD5)*Assumptions!$B$167,0)</f>
-        <v>160000000</v>
+        <f aca="false">IF(AD2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AD5)*Assumptions!$B$170,0)</f>
+        <v>170100000</v>
       </c>
       <c r="AE140" s="58" t="n">
-        <f aca="false">IF(AE2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AE5)*Assumptions!$B$167,0)</f>
-        <v>192000000</v>
+        <f aca="false">IF(AE2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AE5)*Assumptions!$B$170,0)</f>
+        <v>207900000</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22081,81 +22216,81 @@
       </c>
       <c r="O141" s="57" t="n">
         <f aca="false">O140*Assumptions!$B$26*O7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="P141" s="57" t="n">
         <f aca="false">P140*Assumptions!$B$26*P7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="Q141" s="57" t="n">
         <f aca="false">Q140*Assumptions!$B$26*Q7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="R141" s="57" t="n">
         <f aca="false">R140*Assumptions!$B$26*R7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="S141" s="57" t="n">
         <f aca="false">S140*Assumptions!$B$26*S7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="T141" s="57" t="n">
         <f aca="false">T140*Assumptions!$B$26*T7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="U141" s="57" t="n">
         <f aca="false">U140*Assumptions!$B$26*U7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="V141" s="57" t="n">
         <f aca="false">V140*Assumptions!$B$26*V7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="W141" s="57" t="n">
         <f aca="false">W140*Assumptions!$B$26*W7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="X141" s="57" t="n">
         <f aca="false">X140*Assumptions!$B$26*X7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="Y141" s="57" t="n">
         <f aca="false">Y140*Assumptions!$B$26*Y7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="Z141" s="57" t="n">
         <f aca="false">Z140*Assumptions!$B$26*Z7/12</f>
-        <v>16666.6666666667</v>
+        <v>9843.75</v>
       </c>
       <c r="AA141" s="57" t="n">
         <f aca="false">AA140*Assumptions!$B$26*AA7/12</f>
-        <v>400000</v>
+        <v>354375</v>
       </c>
       <c r="AB141" s="57" t="n">
         <f aca="false">AB140*Assumptions!$B$26*AB7/12</f>
-        <v>600000</v>
+        <v>590625</v>
       </c>
       <c r="AC141" s="57" t="n">
         <f aca="false">AC140*Assumptions!$B$26*AC7/12</f>
-        <v>800000</v>
+        <v>826875</v>
       </c>
       <c r="AD141" s="57" t="n">
         <f aca="false">AD140*Assumptions!$B$26*AD7/12</f>
-        <v>1000000</v>
+        <v>1063125</v>
       </c>
       <c r="AE141" s="57" t="n">
         <f aca="false">AE140*Assumptions!$B$26*AE7/12</f>
-        <v>1200000</v>
+        <v>1299375</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="9" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="46" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B144" s="47"/>
       <c r="C144" s="47"/>
@@ -22190,7 +22325,7 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="B145" s="23" t="s">
         <v>207</v>
@@ -22314,7 +22449,7 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B146" s="23" t="s">
         <v>207</v>
@@ -22438,7 +22573,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B147" s="23" t="s">
         <v>207</v>
@@ -22562,7 +22697,7 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B148" s="23" t="s">
         <v>207</v>
@@ -22686,7 +22821,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B149" s="23" t="s">
         <v>207</v>
@@ -22810,7 +22945,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B150" s="23" t="s">
         <v>207</v>
@@ -22934,7 +23069,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="B151" s="23" t="s">
         <v>207</v>
@@ -23058,7 +23193,7 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B152" s="23" t="s">
         <v>207</v>
@@ -23182,7 +23317,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B153" s="23" t="s">
         <v>207</v>
@@ -23306,7 +23441,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B154" s="23" t="s">
         <v>207</v>
@@ -23430,7 +23565,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="6" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B155" s="23" t="s">
         <v>207</v>
@@ -23554,7 +23689,7 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B156" s="23" t="s">
         <v>207</v>
@@ -23678,7 +23813,7 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B157" s="23" t="s">
         <v>207</v>
@@ -23802,7 +23937,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B158" s="23" t="s">
         <v>114</v>
@@ -23926,12 +24061,12 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="9" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B160" s="23" t="s">
         <v>114</v>
@@ -24055,7 +24190,7 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="6" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B161" s="23" t="s">
         <v>114</v>
@@ -24179,15 +24314,15 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="9" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="6" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B163" s="23" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C163" s="59" t="n">
         <f aca="false">C145+C146-C147</f>
@@ -24308,7 +24443,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B164" s="23" t="s">
         <v>47</v>
@@ -24432,7 +24567,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="6" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B165" s="23" t="s">
         <v>114</v>
@@ -24556,7 +24691,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B166" s="23" t="s">
         <v>114</v>
@@ -24680,10 +24815,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="6" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B167" s="23" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C167" s="60" t="n">
         <f aca="false">IF(C166=0,0,((C50+C88+C126)/C7)/C166)</f>
@@ -25548,10 +25683,10 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="6" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B175" s="23" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="C175" s="45" t="n">
         <f aca="false">C60+C98+C136</f>
@@ -25672,10 +25807,10 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="6" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="C176" s="45" t="n">
         <f aca="false">C52+C90+C128</f>
@@ -25796,7 +25931,7 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B177" s="23" t="s">
         <v>114</v>
@@ -25851,76 +25986,76 @@
       </c>
       <c r="O177" s="57" t="n">
         <f aca="false">O61+O99+O137+O141</f>
-        <v>28459.5934461904</v>
+        <v>21636.6767795237</v>
       </c>
       <c r="P177" s="57" t="n">
         <f aca="false">P61+P99+P137+P141</f>
-        <v>31190.0540402711</v>
+        <v>24367.1373736044</v>
       </c>
       <c r="Q177" s="57" t="n">
         <f aca="false">Q61+Q99+Q137+Q141</f>
-        <v>33718.2137227841</v>
+        <v>26895.2970561174</v>
       </c>
       <c r="R177" s="57" t="n">
         <f aca="false">R61+R99+R137+R141</f>
-        <v>36980.5786483291</v>
+        <v>30157.6619816624</v>
       </c>
       <c r="S177" s="57" t="n">
         <f aca="false">S61+S99+S137+S141</f>
-        <v>39796.5743002971</v>
+        <v>32973.6576336305</v>
       </c>
       <c r="T177" s="57" t="n">
         <f aca="false">T61+T99+T137+T141</f>
-        <v>42005.1068031822</v>
+        <v>35182.1901365156</v>
       </c>
       <c r="U177" s="57" t="n">
         <f aca="false">U61+U99+U137+U141</f>
-        <v>44030.3104091956</v>
+        <v>37207.3937425289</v>
       </c>
       <c r="V177" s="57" t="n">
         <f aca="false">V61+V99+V137+V141</f>
-        <v>45986.4385124996</v>
+        <v>39163.5218458329</v>
       </c>
       <c r="W177" s="57" t="n">
         <f aca="false">W61+W99+W137+W141</f>
-        <v>48414.9085484592</v>
+        <v>41591.9918817926</v>
       </c>
       <c r="X177" s="57" t="n">
         <f aca="false">X61+X99+X137+X141</f>
-        <v>51998.8169791854</v>
+        <v>45175.9003125187</v>
       </c>
       <c r="Y177" s="57" t="n">
         <f aca="false">Y61+Y99+Y137+Y141</f>
-        <v>55119.5414762608</v>
+        <v>48296.6248095941</v>
       </c>
       <c r="Z177" s="57" t="n">
         <f aca="false">Z61+Z99+Z137+Z141</f>
-        <v>57708.6633991649</v>
+        <v>50885.7467324982</v>
       </c>
       <c r="AA177" s="57" t="n">
         <f aca="false">AA61+AA99+AA137+AA141</f>
-        <v>1438780.16914546</v>
+        <v>1393155.16914546</v>
       </c>
       <c r="AB177" s="57" t="n">
         <f aca="false">AB61+AB99+AB137+AB141</f>
-        <v>2331999.83672874</v>
+        <v>2322624.83672874</v>
       </c>
       <c r="AC177" s="57" t="n">
         <f aca="false">AC61+AC99+AC137+AC141</f>
-        <v>3350945.29603319</v>
+        <v>3377820.29603319</v>
       </c>
       <c r="AD177" s="57" t="n">
         <f aca="false">AD61+AD99+AD137+AD141</f>
-        <v>4275805.31449405</v>
+        <v>4338930.31449405</v>
       </c>
       <c r="AE177" s="57" t="n">
         <f aca="false">AE61+AE99+AE137+AE141</f>
-        <v>4919019.18074238</v>
+        <v>5018394.18074238</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B178" s="23" t="s">
         <v>114</v>
@@ -25975,79 +26110,79 @@
       </c>
       <c r="O178" s="55" t="n">
         <f aca="false">IF(O145=0,0,O177/O145/O7*12)</f>
-        <v>110.43249804661</v>
+        <v>83.957357672997</v>
       </c>
       <c r="P178" s="55" t="n">
         <f aca="false">IF(P145=0,0,P177/P145/P7*12)</f>
-        <v>97.9868025456989</v>
+        <v>76.5518993762713</v>
       </c>
       <c r="Q178" s="55" t="n">
         <f aca="false">IF(Q145=0,0,Q177/Q145/Q7*12)</f>
-        <v>90.0799781386777</v>
+        <v>71.8521980662105</v>
       </c>
       <c r="R178" s="55" t="n">
         <f aca="false">IF(R145=0,0,R177/R145/R7*12)</f>
-        <v>82.720974889227</v>
+        <v>67.4589552323193</v>
       </c>
       <c r="S178" s="55" t="n">
         <f aca="false">IF(S145=0,0,S177/S145/S7*12)</f>
-        <v>78.1229583210641</v>
+        <v>64.72918150108</v>
       </c>
       <c r="T178" s="55" t="n">
         <f aca="false">IF(T145=0,0,T177/T145/T7*12)</f>
-        <v>75.39842612151</v>
+        <v>63.1514109993889</v>
       </c>
       <c r="U178" s="55" t="n">
         <f aca="false">IF(U145=0,0,U177/U145/U7*12)</f>
-        <v>73.2680363545069</v>
+        <v>61.9144551116933</v>
       </c>
       <c r="V178" s="55" t="n">
         <f aca="false">IF(V145=0,0,V177/V145/V7*12)</f>
-        <v>71.4642558084217</v>
+        <v>60.8612459255477</v>
       </c>
       <c r="W178" s="55" t="n">
         <f aca="false">IF(W145=0,0,W177/W145/W7*12)</f>
-        <v>70.0065629793617</v>
+        <v>60.1408220402902</v>
       </c>
       <c r="X178" s="55" t="n">
         <f aca="false">IF(X145=0,0,X177/X145/X7*12)</f>
-        <v>67.8887137730476</v>
+        <v>58.980837332972</v>
       </c>
       <c r="Y178" s="55" t="n">
         <f aca="false">IF(Y145=0,0,Y177/Y145/Y7*12)</f>
-        <v>66.4117758914913</v>
+        <v>58.1910614142466</v>
       </c>
       <c r="Z178" s="55" t="n">
         <f aca="false">IF(Z145=0,0,Z177/Z145/Z7*12)</f>
-        <v>65.5823422483787</v>
+        <v>57.8285176125446</v>
       </c>
       <c r="AA178" s="55" t="n">
         <f aca="false">IF(AA145=0,0,AA177/AA145/AA7*12)</f>
-        <v>71.379360898262</v>
+        <v>69.1158578205698</v>
       </c>
       <c r="AB178" s="55" t="n">
         <f aca="false">IF(AB145=0,0,AB177/AB145/AB7*12)</f>
-        <v>71.1858175048076</v>
+        <v>70.8996395091677</v>
       </c>
       <c r="AC178" s="55" t="n">
         <f aca="false">IF(AC145=0,0,AC177/AC145/AC7*12)</f>
-        <v>71.3321462572104</v>
+        <v>71.9042389836814</v>
       </c>
       <c r="AD178" s="55" t="n">
         <f aca="false">IF(AD145=0,0,AD177/AD145/AD7*12)</f>
-        <v>73.4959815797901</v>
+        <v>74.5810248630981</v>
       </c>
       <c r="AE178" s="55" t="n">
         <f aca="false">IF(AE145=0,0,AE177/AE145/AE7*12)</f>
-        <v>78.5796952134721</v>
+        <v>80.167177783658</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="6" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B179" s="23" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C179" s="59" t="n">
         <f aca="false">C177-(C169+C170+C171+C172+C173+C174+C141)</f>
@@ -26198,35 +26333,35 @@
     </row>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D4" s="61" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="E4" s="61" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="G4" s="61" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H4" s="61" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="I4" s="61" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="J4" s="61" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -26241,7 +26376,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D7" s="36" t="n">
         <f aca="false">SUM(Model!C61:N61)</f>
@@ -26274,7 +26409,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D8" s="36" t="n">
         <f aca="false">SUM(Model!C99:N99)</f>
@@ -26307,7 +26442,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">SUM(Model!C137:N137)</f>
@@ -26340,7 +26475,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="D10" s="36" t="n">
         <f aca="false">SUM(Model!C141:N141)</f>
@@ -26348,32 +26483,32 @@
       </c>
       <c r="E10" s="36" t="n">
         <f aca="false">SUM(Model!O141:Z141)</f>
-        <v>200000</v>
+        <v>118125</v>
       </c>
       <c r="F10" s="36" t="n">
         <f aca="false">Model!AA141</f>
-        <v>400000</v>
+        <v>354375</v>
       </c>
       <c r="G10" s="36" t="n">
         <f aca="false">Model!AB141</f>
-        <v>600000</v>
+        <v>590625</v>
       </c>
       <c r="H10" s="36" t="n">
         <f aca="false">Model!AC141</f>
-        <v>800000</v>
+        <v>826875</v>
       </c>
       <c r="I10" s="36" t="n">
         <f aca="false">Model!AD141</f>
-        <v>1000000</v>
+        <v>1063125</v>
       </c>
       <c r="J10" s="36" t="n">
         <f aca="false">Model!AE141</f>
-        <v>1200000</v>
+        <v>1299375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D11" s="62" t="n">
         <f aca="false">SUM(Model!C177:N177)</f>
@@ -26381,32 +26516,32 @@
       </c>
       <c r="E11" s="62" t="n">
         <f aca="false">SUM(Model!O177:Z177)</f>
-        <v>515408.800285819</v>
+        <v>433533.800285819</v>
       </c>
       <c r="F11" s="62" t="n">
         <f aca="false">Model!AA177</f>
-        <v>1438780.16914546</v>
+        <v>1393155.16914546</v>
       </c>
       <c r="G11" s="62" t="n">
         <f aca="false">Model!AB177</f>
-        <v>2331999.83672874</v>
+        <v>2322624.83672874</v>
       </c>
       <c r="H11" s="62" t="n">
         <f aca="false">Model!AC177</f>
-        <v>3350945.29603319</v>
+        <v>3377820.29603319</v>
       </c>
       <c r="I11" s="62" t="n">
         <f aca="false">Model!AD177</f>
-        <v>4275805.31449405</v>
+        <v>4338930.31449405</v>
       </c>
       <c r="J11" s="62" t="n">
         <f aca="false">Model!AE177</f>
-        <v>4919019.18074238</v>
+        <v>5018394.18074238</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -26421,7 +26556,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D14" s="36" t="n">
         <f aca="false">SUM(Model!C169:N169)</f>
@@ -26454,7 +26589,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D15" s="36" t="n">
         <f aca="false">SUM(Model!C170:N170)</f>
@@ -26487,7 +26622,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="D16" s="36" t="n">
         <f aca="false">SUM(Model!C171:N171)</f>
@@ -26520,7 +26655,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D17" s="36" t="n">
         <f aca="false">SUM(Model!C172:N172)</f>
@@ -26553,7 +26688,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D18" s="36" t="n">
         <f aca="false">SUM(Model!C173:N173)</f>
@@ -26586,7 +26721,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="D19" s="36" t="n">
         <f aca="false">SUM(Model!C174:N174)</f>
@@ -26619,7 +26754,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D20" s="36" t="n">
         <f aca="false">SUM(Model!C141:N141)</f>
@@ -26627,32 +26762,32 @@
       </c>
       <c r="E20" s="36" t="n">
         <f aca="false">SUM(Model!O141:Z141)</f>
-        <v>200000</v>
+        <v>118125</v>
       </c>
       <c r="F20" s="36" t="n">
         <f aca="false">Model!AA141</f>
-        <v>400000</v>
+        <v>354375</v>
       </c>
       <c r="G20" s="36" t="n">
         <f aca="false">Model!AB141</f>
-        <v>600000</v>
+        <v>590625</v>
       </c>
       <c r="H20" s="36" t="n">
         <f aca="false">Model!AC141</f>
-        <v>800000</v>
+        <v>826875</v>
       </c>
       <c r="I20" s="36" t="n">
         <f aca="false">Model!AD141</f>
-        <v>1000000</v>
+        <v>1063125</v>
       </c>
       <c r="J20" s="36" t="n">
         <f aca="false">Model!AE141</f>
-        <v>1200000</v>
+        <v>1299375</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D21" s="62" t="n">
         <f aca="false">SUM(Model!C177:N177)</f>
@@ -26660,32 +26795,32 @@
       </c>
       <c r="E21" s="62" t="n">
         <f aca="false">SUM(Model!O177:Z177)</f>
-        <v>515408.800285819</v>
+        <v>433533.800285819</v>
       </c>
       <c r="F21" s="62" t="n">
         <f aca="false">Model!AA177</f>
-        <v>1438780.16914546</v>
+        <v>1393155.16914546</v>
       </c>
       <c r="G21" s="62" t="n">
         <f aca="false">Model!AB177</f>
-        <v>2331999.83672874</v>
+        <v>2322624.83672874</v>
       </c>
       <c r="H21" s="62" t="n">
         <f aca="false">Model!AC177</f>
-        <v>3350945.29603319</v>
+        <v>3377820.29603319</v>
       </c>
       <c r="I21" s="62" t="n">
         <f aca="false">Model!AD177</f>
-        <v>4275805.31449405</v>
+        <v>4338930.31449405</v>
       </c>
       <c r="J21" s="62" t="n">
         <f aca="false">Model!AE177</f>
-        <v>4919019.18074238</v>
+        <v>5018394.18074238</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -26700,7 +26835,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D24" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D14/D$11)</f>
@@ -26708,32 +26843,32 @@
       </c>
       <c r="E24" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E14/E$11)</f>
-        <v>0.246711610872868</v>
+        <v>0.293304317432077</v>
       </c>
       <c r="F24" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F14/F$11)</f>
-        <v>0.258787222271775</v>
+        <v>0.26726234929111</v>
       </c>
       <c r="G24" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G14/G$11)</f>
-        <v>0.259664133711668</v>
+        <v>0.26071223722587</v>
       </c>
       <c r="H24" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H14/H$11)</f>
-        <v>0.259488274363582</v>
+        <v>0.257423704089755</v>
       </c>
       <c r="I24" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I14/I$11)</f>
-        <v>0.252343808531863</v>
+        <v>0.24867258042747</v>
       </c>
       <c r="J24" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J14/J$11)</f>
-        <v>0.236725956819276</v>
+        <v>0.232038273645804</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D25" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D15/D$11)</f>
@@ -26741,32 +26876,32 @@
       </c>
       <c r="E25" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E15/E$11)</f>
-        <v>0.0188580241483338</v>
+        <v>0.0224194551743043</v>
       </c>
       <c r="F25" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F15/F$11)</f>
-        <v>0.0199625148148651</v>
+        <v>0.0206162752563433</v>
       </c>
       <c r="G25" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G15/G$11)</f>
-        <v>0.0201493239489703</v>
+        <v>0.0202306543080685</v>
       </c>
       <c r="H25" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H15/H$11)</f>
-        <v>0.0203017312947194</v>
+        <v>0.0201402043392487</v>
       </c>
       <c r="I25" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I15/I$11)</f>
-        <v>0.0199579814563884</v>
+        <v>0.0196676224305184</v>
       </c>
       <c r="J25" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J15/J$11)</f>
-        <v>0.0190116030850369</v>
+        <v>0.0186351324475119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D26" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D16/D$11)</f>
@@ -26774,32 +26909,32 @@
       </c>
       <c r="E26" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E16/E$11)</f>
-        <v>0.000403556116901879</v>
+        <v>0.000479769683294068</v>
       </c>
       <c r="F26" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F16/F$11)</f>
-        <v>0.00319333871394325</v>
+        <v>0.00329791865022775</v>
       </c>
       <c r="G26" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G16/G$11)</f>
-        <v>0.00475756099420722</v>
+        <v>0.00477676432554828</v>
       </c>
       <c r="H26" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H16/H$11)</f>
-        <v>0.00646642412273797</v>
+        <v>0.00641497521987518</v>
       </c>
       <c r="I26" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I16/I$11)</f>
-        <v>0.00877707924340257</v>
+        <v>0.00864938575973703</v>
       </c>
       <c r="J26" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J16/J$11)</f>
-        <v>0.0122258983067485</v>
+        <v>0.0119837992207709</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="D27" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D17/D$11)</f>
@@ -26807,32 +26942,32 @@
       </c>
       <c r="E27" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E17/E$11)</f>
-        <v>0.320169969789588</v>
+        <v>0.380635650341463</v>
       </c>
       <c r="F27" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F17/F$11)</f>
-        <v>0.33623164592644</v>
+        <v>0.347243031581926</v>
       </c>
       <c r="G27" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G17/G$11)</f>
-        <v>0.337145808550687</v>
+        <v>0.338506657666386</v>
       </c>
       <c r="H27" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H17/H$11)</f>
-        <v>0.336454197150615</v>
+        <v>0.333777261802977</v>
       </c>
       <c r="I27" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I17/I$11)</f>
-        <v>0.326548465427932</v>
+        <v>0.321797669635872</v>
       </c>
       <c r="J27" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J17/J$11)</f>
-        <v>0.30542241141049</v>
+        <v>0.299374390661067</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D28" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D18/D$11)</f>
@@ -26840,32 +26975,32 @@
       </c>
       <c r="E28" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E18/E$11)</f>
-        <v>0.0253686475280317</v>
+        <v>0.0301596419441262</v>
       </c>
       <c r="F28" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F18/F$11)</f>
-        <v>0.1002004800971</v>
+        <v>0.103481985995136</v>
       </c>
       <c r="G28" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G18/G$11)</f>
-        <v>0.115612699915411</v>
+        <v>0.116079356882377</v>
       </c>
       <c r="H28" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H18/H$11)</f>
-        <v>0.131237551923845</v>
+        <v>0.13019338470983</v>
       </c>
       <c r="I28" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I18/I$11)</f>
-        <v>0.148572134667595</v>
+        <v>0.146410630490041</v>
       </c>
       <c r="J28" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J18/J$11)</f>
-        <v>0.168836150052956</v>
+        <v>0.165492831093298</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D29" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D19/D$11)</f>
@@ -26873,32 +27008,32 @@
       </c>
       <c r="E29" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E19/E$11)</f>
-        <v>0.000446699258754186</v>
+        <v>0.000531060620628132</v>
       </c>
       <c r="F29" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F19/F$11)</f>
-        <v>0.00361151402172153</v>
+        <v>0.00372978894966234</v>
       </c>
       <c r="G29" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G19/G$11)</f>
-        <v>0.00538057493392483</v>
+        <v>0.00540229298722723</v>
       </c>
       <c r="H29" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H19/H$11)</f>
-        <v>0.00731321775785842</v>
+        <v>0.00725503149866836</v>
       </c>
       <c r="I29" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I19/I$11)</f>
-        <v>0.00992645866813386</v>
+        <v>0.00978204341875021</v>
       </c>
       <c r="J29" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J19/J$11)</f>
-        <v>0.0138269087992989</v>
+        <v>0.0135531062615861</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="D30" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D20/D$11)</f>
@@ -26906,32 +27041,32 @@
       </c>
       <c r="E30" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E20/E$11)</f>
-        <v>0.388041492285522</v>
+        <v>0.272470104804107</v>
       </c>
       <c r="F30" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F20/F$11)</f>
-        <v>0.278013284154154</v>
+        <v>0.254368650275595</v>
       </c>
       <c r="G30" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G20/G$11)</f>
-        <v>0.257289897945131</v>
+        <v>0.254292036604524</v>
       </c>
       <c r="H30" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H20/H$11)</f>
-        <v>0.238738603386641</v>
+        <v>0.244795438339647</v>
       </c>
       <c r="I30" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I20/I$11)</f>
-        <v>0.233874072004686</v>
+        <v>0.245020067837611</v>
       </c>
       <c r="J30" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J20/J$11)</f>
-        <v>0.243951071526193</v>
+        <v>0.258922466669962</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D31" s="40" t="n">
         <f aca="false">SUM(D24:D30)</f>
@@ -26964,7 +27099,7 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -26979,7 +27114,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D34" s="37" t="n">
         <f aca="false">SUM(Model!C148:N148)</f>
@@ -27012,7 +27147,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D35" s="64" t="n">
         <f aca="false">Model!N145</f>
@@ -27045,7 +27180,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D36" s="37" t="n">
         <f aca="false">Model!N146</f>
@@ -27078,7 +27213,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="D37" s="37" t="n">
         <f aca="false">Model!N147</f>
@@ -27111,7 +27246,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D38" s="37" t="n">
         <f aca="false">Model!N149</f>
@@ -27144,7 +27279,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D39" s="37" t="n">
         <f aca="false">Model!N151</f>
@@ -27177,7 +27312,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D40" s="62" t="n">
         <f aca="false">Model!N158</f>
@@ -27210,7 +27345,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="D41" s="37" t="n">
         <f aca="false">Model!N150</f>
@@ -27243,7 +27378,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D42" s="62" t="n">
         <f aca="false">Model!N153</f>
@@ -27276,7 +27411,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="D43" s="36" t="n">
         <f aca="false">Model!N178</f>
@@ -27284,32 +27419,32 @@
       </c>
       <c r="E43" s="36" t="n">
         <f aca="false">Model!Z178</f>
-        <v>65.5823422483787</v>
+        <v>57.8285176125446</v>
       </c>
       <c r="F43" s="36" t="n">
         <f aca="false">Model!AA178</f>
-        <v>71.379360898262</v>
+        <v>69.1158578205698</v>
       </c>
       <c r="G43" s="36" t="n">
         <f aca="false">Model!AB178</f>
-        <v>71.1858175048076</v>
+        <v>70.8996395091677</v>
       </c>
       <c r="H43" s="36" t="n">
         <f aca="false">Model!AC178</f>
-        <v>71.3321462572104</v>
+        <v>71.9042389836814</v>
       </c>
       <c r="I43" s="36" t="n">
         <f aca="false">Model!AD178</f>
-        <v>73.4959815797901</v>
+        <v>74.5810248630981</v>
       </c>
       <c r="J43" s="36" t="n">
         <f aca="false">Model!AE178</f>
-        <v>78.5796952134721</v>
+        <v>80.167177783658</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
@@ -1168,7 +1168,7 @@
     <t xml:space="preserve">% of NEW customers</t>
   </si>
   <si>
-    <t xml:space="preserve">LOWERED 2026-08-21 from 0.20. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% was high for an OPTIONAL PAID extra on a savings product, where low single digits to low teens is the normal range. ASSUMPTION.</t>
+    <t xml:space="preserve">SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. ⚠ IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Family plan cancellation rate (incremental)</t>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="B160" s="34" t="n">
         <f aca="false">'Scenario Parameters'!$B$64</f>
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="C160" s="0" t="s">
         <v>335</v>
@@ -6466,16 +6466,16 @@
       </c>
       <c r="B64" s="40" t="n">
         <f aca="false">CHOOSE($C$6,C64,D64,E64)</f>
+        <v>0.15</v>
+      </c>
+      <c r="C64" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E64" s="19" t="n">
         <v>0.08</v>
-      </c>
-      <c r="C64" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D64" s="19" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E64" s="19" t="n">
-        <v>0.04</v>
       </c>
       <c r="F64" s="23" t="s">
         <v>335</v>
@@ -12460,95 +12460,95 @@
       </c>
       <c r="I56" s="54" t="n">
         <f aca="false">IF(I2&gt;=Assumptions!$B$51,H56*(1-Assumptions!$B$163)^I7+I30*Assumptions!$B$160*(1-Assumptions!$B$163)^(I7/2),0)</f>
-        <v>5.11935744580203</v>
+        <v>9.5987952108788</v>
       </c>
       <c r="J56" s="54" t="n">
         <f aca="false">IF(J2&gt;=Assumptions!$B$51,I56*(1-Assumptions!$B$163)^J7+J30*Assumptions!$B$160*(1-Assumptions!$B$163)^(J7/2),0)</f>
-        <v>9.87215193066684</v>
+        <v>18.5102848700003</v>
       </c>
       <c r="K56" s="54" t="n">
         <f aca="false">IF(K2&gt;=Assumptions!$B$51,J56*(1-Assumptions!$B$163)^K7+K30*Assumptions!$B$160*(1-Assumptions!$B$163)^(K7/2),0)</f>
-        <v>14.7658324362463</v>
+        <v>27.6859358179617</v>
       </c>
       <c r="L56" s="54" t="n">
         <f aca="false">IF(L2&gt;=Assumptions!$B$51,K56*(1-Assumptions!$B$163)^L7+L30*Assumptions!$B$160*(1-Assumptions!$B$163)^(L7/2),0)</f>
-        <v>21.2330391071345</v>
+        <v>39.8119483258773</v>
       </c>
       <c r="M56" s="54" t="n">
         <f aca="false">IF(M2&gt;=Assumptions!$B$51,L56*(1-Assumptions!$B$163)^M7+M30*Assumptions!$B$160*(1-Assumptions!$B$163)^(M7/2),0)</f>
-        <v>26.634035188926</v>
+        <v>49.9388159792363</v>
       </c>
       <c r="N56" s="54" t="n">
         <f aca="false">IF(N2&gt;=Assumptions!$B$51,M56*(1-Assumptions!$B$163)^N7+N30*Assumptions!$B$160*(1-Assumptions!$B$163)^(N7/2),0)</f>
-        <v>30.8055968765904</v>
+        <v>57.7604941436069</v>
       </c>
       <c r="O56" s="54" t="n">
         <f aca="false">IF(O2&gt;=Assumptions!$B$51,N56*(1-Assumptions!$B$163)^O7+O30*Assumptions!$B$160*(1-Assumptions!$B$163)^(O7/2),0)</f>
-        <v>49.2450330575337</v>
+        <v>92.3344369828756</v>
       </c>
       <c r="P56" s="54" t="n">
         <f aca="false">IF(P2&gt;=Assumptions!$B$51,O56*(1-Assumptions!$B$163)^P7+P30*Assumptions!$B$160*(1-Assumptions!$B$163)^(P7/2),0)</f>
-        <v>65.8297895438366</v>
+        <v>123.430855394694</v>
       </c>
       <c r="Q56" s="54" t="n">
         <f aca="false">IF(Q2&gt;=Assumptions!$B$51,P56*(1-Assumptions!$B$163)^Q7+Q30*Assumptions!$B$160*(1-Assumptions!$B$163)^(Q7/2),0)</f>
-        <v>80.8164088710829</v>
+        <v>151.53076663328</v>
       </c>
       <c r="R56" s="54" t="n">
         <f aca="false">IF(R2&gt;=Assumptions!$B$51,Q56*(1-Assumptions!$B$163)^R7+R30*Assumptions!$B$160*(1-Assumptions!$B$163)^(R7/2),0)</f>
-        <v>100.134569909906</v>
+        <v>187.752318581074</v>
       </c>
       <c r="S56" s="54" t="n">
         <f aca="false">IF(S2&gt;=Assumptions!$B$51,R56*(1-Assumptions!$B$163)^S7+S30*Assumptions!$B$160*(1-Assumptions!$B$163)^(S7/2),0)</f>
-        <v>116.246182947326</v>
+        <v>217.961593026236</v>
       </c>
       <c r="T56" s="54" t="n">
         <f aca="false">IF(T2&gt;=Assumptions!$B$51,S56*(1-Assumptions!$B$163)^T7+T30*Assumptions!$B$160*(1-Assumptions!$B$163)^(T7/2),0)</f>
-        <v>128.043198400313</v>
+        <v>240.080997000588</v>
       </c>
       <c r="U56" s="54" t="n">
         <f aca="false">IF(U2&gt;=Assumptions!$B$51,T56*(1-Assumptions!$B$163)^U7+U30*Assumptions!$B$160*(1-Assumptions!$B$163)^(U7/2),0)</f>
-        <v>138.612198089098</v>
+        <v>259.897871417059</v>
       </c>
       <c r="V56" s="54" t="n">
         <f aca="false">IF(V2&gt;=Assumptions!$B$51,U56*(1-Assumptions!$B$163)^V7+V30*Assumptions!$B$160*(1-Assumptions!$B$163)^(V7/2),0)</f>
-        <v>148.698247309631</v>
+        <v>278.809213705558</v>
       </c>
       <c r="W56" s="54" t="n">
         <f aca="false">IF(W2&gt;=Assumptions!$B$51,V56*(1-Assumptions!$B$163)^W7+W30*Assumptions!$B$160*(1-Assumptions!$B$163)^(W7/2),0)</f>
-        <v>160.227768156789</v>
+        <v>300.427065293979</v>
       </c>
       <c r="X56" s="54" t="n">
         <f aca="false">IF(X2&gt;=Assumptions!$B$51,W56*(1-Assumptions!$B$163)^X7+X30*Assumptions!$B$160*(1-Assumptions!$B$163)^(X7/2),0)</f>
-        <v>178.976131959872</v>
+        <v>335.580247424761</v>
       </c>
       <c r="Y56" s="54" t="n">
         <f aca="false">IF(Y2&gt;=Assumptions!$B$51,X56*(1-Assumptions!$B$163)^Y7+Y30*Assumptions!$B$160*(1-Assumptions!$B$163)^(Y7/2),0)</f>
-        <v>194.603822853274</v>
+        <v>364.882167849889</v>
       </c>
       <c r="Z56" s="54" t="n">
         <f aca="false">IF(Z2&gt;=Assumptions!$B$51,Y56*(1-Assumptions!$B$163)^Z7+Z30*Assumptions!$B$160*(1-Assumptions!$B$163)^(Z7/2),0)</f>
-        <v>206.133938483063</v>
+        <v>386.501134655743</v>
       </c>
       <c r="AA56" s="54" t="n">
         <f aca="false">IF(AA2&gt;=Assumptions!$B$51,Z56*(1-Assumptions!$B$163)^AA7+AA30*Assumptions!$B$160*(1-Assumptions!$B$163)^(AA7/2),0)</f>
-        <v>398.535895859977</v>
+        <v>747.254804737457</v>
       </c>
       <c r="AB56" s="54" t="n">
         <f aca="false">IF(AB2&gt;=Assumptions!$B$51,AA56*(1-Assumptions!$B$163)^AB7+AB30*Assumptions!$B$160*(1-Assumptions!$B$163)^(AB7/2),0)</f>
-        <v>656.852413731814</v>
+        <v>1231.59827574715</v>
       </c>
       <c r="AC56" s="54" t="n">
         <f aca="false">IF(AC2&gt;=Assumptions!$B$51,AB56*(1-Assumptions!$B$163)^AC7+AC30*Assumptions!$B$160*(1-Assumptions!$B$163)^(AC7/2),0)</f>
-        <v>975.431731849261</v>
+        <v>1828.93449721736</v>
       </c>
       <c r="AD56" s="54" t="n">
         <f aca="false">IF(AD2&gt;=Assumptions!$B$51,AC56*(1-Assumptions!$B$163)^AD7+AD30*Assumptions!$B$160*(1-Assumptions!$B$163)^(AD7/2),0)</f>
-        <v>1262.78871463161</v>
+        <v>2367.72883993427</v>
       </c>
       <c r="AE56" s="54" t="n">
         <f aca="false">IF(AE2&gt;=Assumptions!$B$51,AD56*(1-Assumptions!$B$163)^AE7+AE30*Assumptions!$B$160*(1-Assumptions!$B$163)^(AE7/2),0)</f>
-        <v>1448.35094703283</v>
+        <v>2715.65802568656</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12584,95 +12584,95 @@
       </c>
       <c r="I57" s="55" t="n">
         <f aca="false">I56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*I7</f>
-        <v>25.1701741085266</v>
+        <v>47.1940764534874</v>
       </c>
       <c r="J57" s="55" t="n">
         <f aca="false">J56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*J7</f>
-        <v>48.5380803257786</v>
+        <v>91.0089006108349</v>
       </c>
       <c r="K57" s="55" t="n">
         <f aca="false">K56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*K7</f>
-        <v>72.5986761448774</v>
+        <v>136.122517771645</v>
       </c>
       <c r="L57" s="55" t="n">
         <f aca="false">L56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*L7</f>
-        <v>104.395775610078</v>
+        <v>195.742079268897</v>
       </c>
       <c r="M57" s="55" t="n">
         <f aca="false">M56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*M7</f>
-        <v>130.95067301222</v>
+        <v>245.532511897912</v>
       </c>
       <c r="N57" s="55" t="n">
         <f aca="false">N56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*N7</f>
-        <v>151.460851309903</v>
+        <v>283.989096206067</v>
       </c>
       <c r="O57" s="55" t="n">
         <f aca="false">O56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*O7</f>
-        <v>242.121412532874</v>
+        <v>453.977648499138</v>
       </c>
       <c r="P57" s="55" t="n">
         <f aca="false">P56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*P7</f>
-        <v>323.663131923863</v>
+        <v>606.868372357243</v>
       </c>
       <c r="Q57" s="55" t="n">
         <f aca="false">Q56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Q7</f>
-        <v>397.347343616158</v>
+        <v>745.026269280295</v>
       </c>
       <c r="R57" s="55" t="n">
         <f aca="false">R56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*R7</f>
-        <v>492.328302057039</v>
+        <v>923.115566356948</v>
       </c>
       <c r="S57" s="55" t="n">
         <f aca="false">S56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*S7</f>
-        <v>571.543732824351</v>
+        <v>1071.64449904566</v>
       </c>
       <c r="T57" s="55" t="n">
         <f aca="false">T56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*T7</f>
-        <v>629.545725468208</v>
+        <v>1180.39823525289</v>
       </c>
       <c r="U57" s="55" t="n">
         <f aca="false">U56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*U7</f>
-        <v>681.509973938066</v>
+        <v>1277.83120113387</v>
       </c>
       <c r="V57" s="55" t="n">
         <f aca="false">V56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*V7</f>
-        <v>731.099715939018</v>
+        <v>1370.81196738566</v>
       </c>
       <c r="W57" s="55" t="n">
         <f aca="false">W56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*W7</f>
-        <v>787.786526770879</v>
+        <v>1477.0997376954</v>
       </c>
       <c r="X57" s="55" t="n">
         <f aca="false">X56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*X7</f>
-        <v>879.965982136039</v>
+        <v>1649.93621650507</v>
       </c>
       <c r="Y57" s="55" t="n">
         <f aca="false">Y56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Y7</f>
-        <v>956.802129028597</v>
+        <v>1794.00399192862</v>
       </c>
       <c r="Z57" s="55" t="n">
         <f aca="false">Z56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Z7</f>
-        <v>1013.49186420839</v>
+        <v>1900.29724539074</v>
       </c>
       <c r="AA57" s="55" t="n">
         <f aca="false">AA56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AA7</f>
-        <v>23513.6178557386</v>
+        <v>44088.03347951</v>
       </c>
       <c r="AB57" s="55" t="n">
         <f aca="false">AB56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AB7</f>
-        <v>38754.292410177</v>
+        <v>72664.298269082</v>
       </c>
       <c r="AC57" s="55" t="n">
         <f aca="false">AC56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AC7</f>
-        <v>57550.4721791064</v>
+        <v>107907.135335824</v>
       </c>
       <c r="AD57" s="55" t="n">
         <f aca="false">AD56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AD7</f>
-        <v>74504.534163265</v>
+        <v>139696.001556122</v>
       </c>
       <c r="AE57" s="55" t="n">
         <f aca="false">AE56*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AE7</f>
-        <v>85452.7058749371</v>
+        <v>160223.823515507</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13204,95 +13204,95 @@
       </c>
       <c r="I62" s="57" t="n">
         <f aca="false">I53+I54+I55+I57+I58+I60</f>
-        <v>850.087348362584</v>
+        <v>872.111250707545</v>
       </c>
       <c r="J62" s="57" t="n">
         <f aca="false">J53+J54+J55+J57+J58+J60</f>
-        <v>952.57156546914</v>
+        <v>995.042385754196</v>
       </c>
       <c r="K62" s="57" t="n">
         <f aca="false">K53+K54+K55+K57+K58+K60</f>
-        <v>1063.06201778596</v>
+        <v>1126.58585941272</v>
       </c>
       <c r="L62" s="57" t="n">
         <f aca="false">L53+L54+L55+L57+L58+L60</f>
-        <v>1221.8558241113</v>
+        <v>1313.20212777012</v>
       </c>
       <c r="M62" s="57" t="n">
         <f aca="false">M53+M54+M55+M57+M58+M60</f>
-        <v>1355.11425706884</v>
+        <v>1469.69609595453</v>
       </c>
       <c r="N62" s="57" t="n">
         <f aca="false">N53+N54+N55+N57+N58+N60</f>
-        <v>1457.4515741677</v>
+        <v>1589.97981906387</v>
       </c>
       <c r="O62" s="57" t="n">
         <f aca="false">O53+O54+O55+O57+O58+O60</f>
-        <v>2104.00369064853</v>
+        <v>2315.8599266148</v>
       </c>
       <c r="P62" s="57" t="n">
         <f aca="false">P53+P54+P55+P57+P58+P60</f>
-        <v>2593.06528670891</v>
+        <v>2876.27052714229</v>
       </c>
       <c r="Q62" s="57" t="n">
         <f aca="false">Q53+Q54+Q55+Q57+Q58+Q60</f>
-        <v>3045.58573061087</v>
+        <v>3393.264656275</v>
       </c>
       <c r="R62" s="57" t="n">
         <f aca="false">R53+R54+R55+R57+R58+R60</f>
-        <v>3628.00098939235</v>
+        <v>4058.78825369226</v>
       </c>
       <c r="S62" s="57" t="n">
         <f aca="false">S53+S54+S55+S57+S58+S60</f>
-        <v>4132.12493420944</v>
+        <v>4632.22570043075</v>
       </c>
       <c r="T62" s="57" t="n">
         <f aca="false">T53+T54+T55+T57+T58+T60</f>
-        <v>4532.91239471118</v>
+        <v>5083.76490449586</v>
       </c>
       <c r="U62" s="57" t="n">
         <f aca="false">U53+U54+U55+U57+U58+U60</f>
-        <v>4899.21768824855</v>
+        <v>5495.53891544436</v>
       </c>
       <c r="V62" s="57" t="n">
         <f aca="false">V53+V54+V55+V57+V58+V60</f>
-        <v>5251.94725942362</v>
+        <v>5891.65951087026</v>
       </c>
       <c r="W62" s="57" t="n">
         <f aca="false">W53+W54+W55+W57+W58+W60</f>
-        <v>5713.38169939575</v>
+        <v>6402.69491032027</v>
       </c>
       <c r="X62" s="57" t="n">
         <f aca="false">X53+X54+X55+X57+X58+X60</f>
-        <v>6383.94151310558</v>
+        <v>7153.91174747461</v>
       </c>
       <c r="Y62" s="57" t="n">
         <f aca="false">Y53+Y54+Y55+Y57+Y58+Y60</f>
-        <v>6971.13314903098</v>
+        <v>7808.33501193101</v>
       </c>
       <c r="Z62" s="57" t="n">
         <f aca="false">Z53+Z54+Z55+Z57+Z58+Z60</f>
-        <v>7473.07908098117</v>
+        <v>8359.88446216351</v>
       </c>
       <c r="AA62" s="57" t="n">
         <f aca="false">AA53+AA54+AA55+AA57+AA58+AA60</f>
-        <v>209023.886122908</v>
+        <v>229598.30174668</v>
       </c>
       <c r="AB62" s="57" t="n">
         <f aca="false">AB53+AB54+AB55+AB57+AB58+AB60</f>
-        <v>365469.795352942</v>
+        <v>399379.801211847</v>
       </c>
       <c r="AC62" s="57" t="n">
         <f aca="false">AC53+AC54+AC55+AC57+AC58+AC60</f>
-        <v>572113.620828483</v>
+        <v>622470.283985201</v>
       </c>
       <c r="AD62" s="57" t="n">
         <f aca="false">AD53+AD54+AD55+AD57+AD58+AD60</f>
-        <v>791894.656082807</v>
+        <v>857086.123475664</v>
       </c>
       <c r="AE62" s="57" t="n">
         <f aca="false">AE53+AE54+AE55+AE57+AE58+AE60</f>
-        <v>988799.762143192</v>
+        <v>1063570.87978376</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17105,71 +17105,71 @@
       </c>
       <c r="O95" s="54" t="n">
         <f aca="false">IF(O2&gt;=Assumptions!$B$51,N95*(1-Assumptions!$B$163)^O7+O69*Assumptions!$B$160*(1-Assumptions!$B$163)^(O7/2),0)</f>
-        <v>5.58583611536436</v>
+        <v>10.4734427163082</v>
       </c>
       <c r="P95" s="54" t="n">
         <f aca="false">IF(P2&gt;=Assumptions!$B$51,O95*(1-Assumptions!$B$163)^P7+P69*Assumptions!$B$160*(1-Assumptions!$B$163)^(P7/2),0)</f>
-        <v>10.6489172870269</v>
+        <v>19.9667199131755</v>
       </c>
       <c r="Q95" s="54" t="n">
         <f aca="false">IF(Q2&gt;=Assumptions!$B$51,P95*(1-Assumptions!$B$163)^Q7+Q69*Assumptions!$B$160*(1-Assumptions!$B$163)^(Q7/2),0)</f>
-        <v>15.2577638064469</v>
+        <v>28.6083071370879</v>
       </c>
       <c r="R95" s="54" t="n">
         <f aca="false">IF(R2&gt;=Assumptions!$B$51,Q95*(1-Assumptions!$B$163)^R7+R69*Assumptions!$B$160*(1-Assumptions!$B$163)^(R7/2),0)</f>
-        <v>21.0347176958826</v>
+        <v>39.4400956797798</v>
       </c>
       <c r="S95" s="54" t="n">
         <f aca="false">IF(S2&gt;=Assumptions!$B$51,R95*(1-Assumptions!$B$163)^S7+S69*Assumptions!$B$160*(1-Assumptions!$B$163)^(S7/2),0)</f>
-        <v>25.9191998912747</v>
+        <v>48.5984997961401</v>
       </c>
       <c r="T95" s="54" t="n">
         <f aca="false">IF(T2&gt;=Assumptions!$B$51,S95*(1-Assumptions!$B$163)^T7+T69*Assumptions!$B$160*(1-Assumptions!$B$163)^(T7/2),0)</f>
-        <v>29.6022127918191</v>
+        <v>55.5041489846609</v>
       </c>
       <c r="U95" s="54" t="n">
         <f aca="false">IF(U2&gt;=Assumptions!$B$51,T95*(1-Assumptions!$B$163)^U7+U69*Assumptions!$B$160*(1-Assumptions!$B$163)^(U7/2),0)</f>
-        <v>32.9309576798616</v>
+        <v>61.7455456497404</v>
       </c>
       <c r="V95" s="54" t="n">
         <f aca="false">IF(V2&gt;=Assumptions!$B$51,U95*(1-Assumptions!$B$163)^V7+V69*Assumptions!$B$160*(1-Assumptions!$B$163)^(V7/2),0)</f>
-        <v>36.1112836713636</v>
+        <v>67.7086568838067</v>
       </c>
       <c r="W95" s="54" t="n">
         <f aca="false">IF(W2&gt;=Assumptions!$B$51,V95*(1-Assumptions!$B$163)^W7+W69*Assumptions!$B$160*(1-Assumptions!$B$163)^(W7/2),0)</f>
-        <v>39.6784215512839</v>
+        <v>74.3970404086573</v>
       </c>
       <c r="X95" s="54" t="n">
         <f aca="false">IF(X2&gt;=Assumptions!$B$51,W95*(1-Assumptions!$B$163)^X7+X69*Assumptions!$B$160*(1-Assumptions!$B$163)^(X7/2),0)</f>
-        <v>45.2418363745275</v>
+        <v>84.8284432022391</v>
       </c>
       <c r="Y95" s="54" t="n">
         <f aca="false">IF(Y2&gt;=Assumptions!$B$51,X95*(1-Assumptions!$B$163)^Y7+Y69*Assumptions!$B$160*(1-Assumptions!$B$163)^(Y7/2),0)</f>
-        <v>49.9286128629183</v>
+        <v>93.6161491179718</v>
       </c>
       <c r="Z95" s="54" t="n">
         <f aca="false">IF(Z2&gt;=Assumptions!$B$51,Y95*(1-Assumptions!$B$163)^Z7+Z69*Assumptions!$B$160*(1-Assumptions!$B$163)^(Z7/2),0)</f>
-        <v>53.4631813758219</v>
+        <v>100.243465079666</v>
       </c>
       <c r="AA95" s="54" t="n">
         <f aca="false">IF(AA2&gt;=Assumptions!$B$51,Z95*(1-Assumptions!$B$163)^AA7+AA69*Assumptions!$B$160*(1-Assumptions!$B$163)^(AA7/2),0)</f>
-        <v>107.601718637152</v>
+        <v>201.753222444659</v>
       </c>
       <c r="AB95" s="54" t="n">
         <f aca="false">IF(AB2&gt;=Assumptions!$B$51,AA95*(1-Assumptions!$B$163)^AB7+AB69*Assumptions!$B$160*(1-Assumptions!$B$163)^(AB7/2),0)</f>
-        <v>180.581930756192</v>
+        <v>338.59112016786</v>
       </c>
       <c r="AC95" s="54" t="n">
         <f aca="false">IF(AC2&gt;=Assumptions!$B$51,AB95*(1-Assumptions!$B$163)^AC7+AC69*Assumptions!$B$160*(1-Assumptions!$B$163)^(AC7/2),0)</f>
-        <v>269.057594385576</v>
+        <v>504.482989472956</v>
       </c>
       <c r="AD95" s="54" t="n">
         <f aca="false">IF(AD2&gt;=Assumptions!$B$51,AC95*(1-Assumptions!$B$163)^AD7+AD69*Assumptions!$B$160*(1-Assumptions!$B$163)^(AD7/2),0)</f>
-        <v>348.242766329969</v>
+        <v>652.955186868693</v>
       </c>
       <c r="AE95" s="54" t="n">
         <f aca="false">IF(AE2&gt;=Assumptions!$B$51,AD95*(1-Assumptions!$B$163)^AE7+AE69*Assumptions!$B$160*(1-Assumptions!$B$163)^(AE7/2),0)</f>
-        <v>395.329053566739</v>
+        <v>741.241975437636</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17229,71 +17229,71 @@
       </c>
       <c r="O96" s="55" t="n">
         <f aca="false">O95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*O7</f>
-        <v>27.4636942338748</v>
+        <v>51.4944266885152</v>
       </c>
       <c r="P96" s="55" t="n">
         <f aca="false">P95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*P7</f>
-        <v>52.3571766612157</v>
+        <v>98.1697062397794</v>
       </c>
       <c r="Q96" s="55" t="n">
         <f aca="false">Q95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Q7</f>
-        <v>75.0173387150304</v>
+        <v>140.657510090682</v>
       </c>
       <c r="R96" s="55" t="n">
         <f aca="false">R95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*R7</f>
-        <v>103.420695338089</v>
+        <v>193.913803758917</v>
       </c>
       <c r="S96" s="55" t="n">
         <f aca="false">S95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*S7</f>
-        <v>127.436066132101</v>
+        <v>238.942623997689</v>
       </c>
       <c r="T96" s="55" t="n">
         <f aca="false">T95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*T7</f>
-        <v>145.544212893111</v>
+        <v>272.895399174583</v>
       </c>
       <c r="U96" s="55" t="n">
         <f aca="false">U95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*U7</f>
-        <v>161.910541925986</v>
+        <v>303.582266111224</v>
       </c>
       <c r="V96" s="55" t="n">
         <f aca="false">V95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*V7</f>
-        <v>177.547144717538</v>
+        <v>332.900896345383</v>
       </c>
       <c r="W96" s="55" t="n">
         <f aca="false">W95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*W7</f>
-        <v>195.085572627146</v>
+        <v>365.785448675898</v>
       </c>
       <c r="X96" s="55" t="n">
         <f aca="false">X95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*X7</f>
-        <v>222.439028841427</v>
+        <v>417.073179077675</v>
       </c>
       <c r="Y96" s="55" t="n">
         <f aca="false">Y95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Y7</f>
-        <v>245.482346576015</v>
+        <v>460.279399830028</v>
       </c>
       <c r="Z96" s="55" t="n">
         <f aca="false">Z95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Z7</f>
-        <v>262.860641764458</v>
+        <v>492.863703308358</v>
       </c>
       <c r="AA96" s="55" t="n">
         <f aca="false">AA95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AA7</f>
-        <v>6348.50139959194</v>
+        <v>11903.4401242349</v>
       </c>
       <c r="AB96" s="55" t="n">
         <f aca="false">AB95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AB7</f>
-        <v>10654.3339146153</v>
+        <v>19976.8760899038</v>
       </c>
       <c r="AC96" s="55" t="n">
         <f aca="false">AC95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AC7</f>
-        <v>15874.398068749</v>
+        <v>29764.4963789044</v>
       </c>
       <c r="AD96" s="55" t="n">
         <f aca="false">AD95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AD7</f>
-        <v>20546.3232134682</v>
+        <v>38524.3560252529</v>
       </c>
       <c r="AE96" s="55" t="n">
         <f aca="false">AE95*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AE7</f>
-        <v>23324.4141604376</v>
+        <v>43733.2765508205</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17849,71 +17849,71 @@
       </c>
       <c r="O101" s="57" t="n">
         <f aca="false">O92+O93+O94+O96+O97+O99</f>
-        <v>126.585991890695</v>
+        <v>150.616724345335</v>
       </c>
       <c r="P101" s="57" t="n">
         <f aca="false">P92+P93+P94+P96+P97+P99</f>
-        <v>243.5592702795</v>
+        <v>289.371799858064</v>
       </c>
       <c r="Q101" s="57" t="n">
         <f aca="false">Q92+Q93+Q94+Q96+Q97+Q99</f>
-        <v>352.155007001879</v>
+        <v>417.79517837753</v>
       </c>
       <c r="R101" s="57" t="n">
         <f aca="false">R92+R93+R94+R96+R97+R99</f>
-        <v>488.863858939468</v>
+        <v>579.356967360296</v>
       </c>
       <c r="S101" s="57" t="n">
         <f aca="false">S92+S93+S94+S96+S97+S99</f>
-        <v>607.376450715418</v>
+        <v>718.883008581006</v>
       </c>
       <c r="T101" s="57" t="n">
         <f aca="false">T92+T93+T94+T96+T97+T99</f>
-        <v>700.234763314543</v>
+        <v>827.585949596015</v>
       </c>
       <c r="U101" s="57" t="n">
         <f aca="false">U92+U93+U94+U96+U97+U99</f>
-        <v>786.081071144065</v>
+        <v>927.752795329303</v>
       </c>
       <c r="V101" s="57" t="n">
         <f aca="false">V92+V93+V94+V96+V97+V99</f>
-        <v>869.38924023071</v>
+        <v>1024.74299185856</v>
       </c>
       <c r="W101" s="57" t="n">
         <f aca="false">W92+W93+W94+W96+W97+W99</f>
-        <v>987.00993466082</v>
+        <v>1157.70981070957</v>
       </c>
       <c r="X101" s="57" t="n">
         <f aca="false">X92+X93+X94+X96+X97+X99</f>
-        <v>1150.35316100314</v>
+        <v>1344.98731123939</v>
       </c>
       <c r="Y101" s="57" t="n">
         <f aca="false">Y92+Y93+Y94+Y96+Y97+Y99</f>
-        <v>1295.09255877597</v>
+        <v>1509.88961202998</v>
       </c>
       <c r="Z101" s="57" t="n">
         <f aca="false">Z92+Z93+Z94+Z96+Z97+Z99</f>
-        <v>1421.67409265073</v>
+        <v>1651.67715419463</v>
       </c>
       <c r="AA101" s="57" t="n">
         <f aca="false">AA92+AA93+AA94+AA96+AA97+AA99</f>
-        <v>45589.5945704026</v>
+        <v>51144.5332950456</v>
       </c>
       <c r="AB101" s="57" t="n">
         <f aca="false">AB92+AB93+AB94+AB96+AB97+AB99</f>
-        <v>82671.6722487917</v>
+        <v>91994.2144240801</v>
       </c>
       <c r="AC101" s="57" t="n">
         <f aca="false">AC92+AC93+AC94+AC96+AC97+AC99</f>
-        <v>131247.530915612</v>
+        <v>145137.629225767</v>
       </c>
       <c r="AD101" s="57" t="n">
         <f aca="false">AD92+AD93+AD94+AD96+AD97+AD99</f>
-        <v>182973.601887721</v>
+        <v>200951.634699506</v>
       </c>
       <c r="AE101" s="57" t="n">
         <f aca="false">AE92+AE93+AE94+AE96+AE97+AE99</f>
-        <v>228268.343056317</v>
+        <v>248677.2054467</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21702,95 +21702,95 @@
       </c>
       <c r="I134" s="54" t="n">
         <f aca="false">IF(I2&gt;=Assumptions!$B$51,H134*(1-Assumptions!$B$163)^I7+I108*Assumptions!$B$160*(1-Assumptions!$B$163)^(I7/2),0)</f>
-        <v>11.4960077932737</v>
+        <v>21.5550146123882</v>
       </c>
       <c r="J134" s="54" t="n">
         <f aca="false">IF(J2&gt;=Assumptions!$B$51,I134*(1-Assumptions!$B$163)^J7+J108*Assumptions!$B$160*(1-Assumptions!$B$163)^(J7/2),0)</f>
-        <v>22.1604034749402</v>
+        <v>41.5507565155128</v>
       </c>
       <c r="K134" s="54" t="n">
         <f aca="false">IF(K2&gt;=Assumptions!$B$51,J134*(1-Assumptions!$B$163)^K7+K108*Assumptions!$B$160*(1-Assumptions!$B$163)^(K7/2),0)</f>
-        <v>33.1317371851806</v>
+        <v>62.1220072222137</v>
       </c>
       <c r="L134" s="54" t="n">
         <f aca="false">IF(L2&gt;=Assumptions!$B$51,K134*(1-Assumptions!$B$163)^L7+L108*Assumptions!$B$160*(1-Assumptions!$B$163)^(L7/2),0)</f>
-        <v>47.617916794843</v>
+        <v>89.2835939903306</v>
       </c>
       <c r="M134" s="54" t="n">
         <f aca="false">IF(M2&gt;=Assumptions!$B$51,L134*(1-Assumptions!$B$163)^M7+M108*Assumptions!$B$160*(1-Assumptions!$B$163)^(M7/2),0)</f>
-        <v>59.698747743748</v>
+        <v>111.935152019527</v>
       </c>
       <c r="N134" s="54" t="n">
         <f aca="false">IF(N2&gt;=Assumptions!$B$51,M134*(1-Assumptions!$B$163)^N7+N108*Assumptions!$B$160*(1-Assumptions!$B$163)^(N7/2),0)</f>
-        <v>69.0149993710011</v>
+        <v>129.403123820627</v>
       </c>
       <c r="O134" s="54" t="n">
         <f aca="false">IF(O2&gt;=Assumptions!$B$51,N134*(1-Assumptions!$B$163)^O7+O108*Assumptions!$B$160*(1-Assumptions!$B$163)^(O7/2),0)</f>
-        <v>109.249616808112</v>
+        <v>204.84303151521</v>
       </c>
       <c r="P134" s="54" t="n">
         <f aca="false">IF(P2&gt;=Assumptions!$B$51,O134*(1-Assumptions!$B$163)^P7+P108*Assumptions!$B$160*(1-Assumptions!$B$163)^(P7/2),0)</f>
-        <v>145.291264987259</v>
+        <v>272.421121851111</v>
       </c>
       <c r="Q134" s="54" t="n">
         <f aca="false">IF(Q2&gt;=Assumptions!$B$51,P134*(1-Assumptions!$B$163)^Q7+Q108*Assumptions!$B$160*(1-Assumptions!$B$163)^(Q7/2),0)</f>
-        <v>177.71831470163</v>
+        <v>333.221840065556</v>
       </c>
       <c r="R134" s="54" t="n">
         <f aca="false">IF(R2&gt;=Assumptions!$B$51,Q134*(1-Assumptions!$B$163)^R7+R108*Assumptions!$B$160*(1-Assumptions!$B$163)^(R7/2),0)</f>
-        <v>219.398513585537</v>
+        <v>411.372212972882</v>
       </c>
       <c r="S134" s="54" t="n">
         <f aca="false">IF(S2&gt;=Assumptions!$B$51,R134*(1-Assumptions!$B$163)^S7+S108*Assumptions!$B$160*(1-Assumptions!$B$163)^(S7/2),0)</f>
-        <v>253.934311140179</v>
+        <v>476.126833387836</v>
       </c>
       <c r="T134" s="54" t="n">
         <f aca="false">IF(T2&gt;=Assumptions!$B$51,S134*(1-Assumptions!$B$163)^T7+T108*Assumptions!$B$160*(1-Assumptions!$B$163)^(T7/2),0)</f>
-        <v>279.006104773389</v>
+        <v>523.136446450103</v>
       </c>
       <c r="U134" s="54" t="n">
         <f aca="false">IF(U2&gt;=Assumptions!$B$51,T134*(1-Assumptions!$B$163)^U7+U108*Assumptions!$B$160*(1-Assumptions!$B$163)^(U7/2),0)</f>
-        <v>301.313685738903</v>
+        <v>564.963160760443</v>
       </c>
       <c r="V134" s="54" t="n">
         <f aca="false">IF(V2&gt;=Assumptions!$B$51,U134*(1-Assumptions!$B$163)^V7+V108*Assumptions!$B$160*(1-Assumptions!$B$163)^(V7/2),0)</f>
-        <v>322.465327488216</v>
+        <v>604.622489040405</v>
       </c>
       <c r="W134" s="54" t="n">
         <f aca="false">IF(W2&gt;=Assumptions!$B$51,V134*(1-Assumptions!$B$163)^W7+W108*Assumptions!$B$160*(1-Assumptions!$B$163)^(W7/2),0)</f>
-        <v>346.561815915396</v>
+        <v>649.803404841368</v>
       </c>
       <c r="X134" s="54" t="n">
         <f aca="false">IF(X2&gt;=Assumptions!$B$51,W134*(1-Assumptions!$B$163)^X7+X108*Assumptions!$B$160*(1-Assumptions!$B$163)^(X7/2),0)</f>
-        <v>385.797526888244</v>
+        <v>723.370362915458</v>
       </c>
       <c r="Y134" s="54" t="n">
         <f aca="false">IF(Y2&gt;=Assumptions!$B$51,X134*(1-Assumptions!$B$163)^Y7+Y108*Assumptions!$B$160*(1-Assumptions!$B$163)^(Y7/2),0)</f>
-        <v>418.129221385593</v>
+        <v>783.992290097987</v>
       </c>
       <c r="Z134" s="54" t="n">
         <f aca="false">IF(Z2&gt;=Assumptions!$B$51,Y134*(1-Assumptions!$B$163)^Z7+Z108*Assumptions!$B$160*(1-Assumptions!$B$163)^(Z7/2),0)</f>
-        <v>441.591086428113</v>
+        <v>827.983287052711</v>
       </c>
       <c r="AA134" s="54" t="n">
         <f aca="false">IF(AA2&gt;=Assumptions!$B$51,Z134*(1-Assumptions!$B$163)^AA7+AA108*Assumptions!$B$160*(1-Assumptions!$B$163)^(AA7/2),0)</f>
-        <v>777.243672836373</v>
+        <v>1457.3318865682</v>
       </c>
       <c r="AB134" s="54" t="n">
         <f aca="false">IF(AB2&gt;=Assumptions!$B$51,AA134*(1-Assumptions!$B$163)^AB7+AB108*Assumptions!$B$160*(1-Assumptions!$B$163)^(AB7/2),0)</f>
-        <v>1193.51594750131</v>
+        <v>2237.84240156496</v>
       </c>
       <c r="AC134" s="54" t="n">
         <f aca="false">IF(AC2&gt;=Assumptions!$B$51,AB134*(1-Assumptions!$B$163)^AC7+AC108*Assumptions!$B$160*(1-Assumptions!$B$163)^(AC7/2),0)</f>
-        <v>1599.61727098122</v>
+        <v>2999.28238308978</v>
       </c>
       <c r="AD134" s="54" t="n">
         <f aca="false">IF(AD2&gt;=Assumptions!$B$51,AC134*(1-Assumptions!$B$163)^AD7+AD108*Assumptions!$B$160*(1-Assumptions!$B$163)^(AD7/2),0)</f>
-        <v>1802.76038574335</v>
+        <v>3380.17572326878</v>
       </c>
       <c r="AE134" s="54" t="n">
         <f aca="false">IF(AE2&gt;=Assumptions!$B$51,AD134*(1-Assumptions!$B$163)^AE7+AE108*Assumptions!$B$160*(1-Assumptions!$B$163)^(AE7/2),0)</f>
-        <v>1684.64609880934</v>
+        <v>3158.71143526751</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21826,95 +21826,95 @@
       </c>
       <c r="I135" s="55" t="n">
         <f aca="false">I134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*I7</f>
-        <v>56.522038316929</v>
+        <v>105.978821844242</v>
       </c>
       <c r="J135" s="55" t="n">
         <f aca="false">J134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*J7</f>
-        <v>108.955317085123</v>
+        <v>204.291219534605</v>
       </c>
       <c r="K135" s="55" t="n">
         <f aca="false">K134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*K7</f>
-        <v>162.897707827138</v>
+        <v>305.433202175884</v>
       </c>
       <c r="L135" s="55" t="n">
         <f aca="false">L134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*L7</f>
-        <v>234.121424241311</v>
+        <v>438.977670452459</v>
       </c>
       <c r="M135" s="55" t="n">
         <f aca="false">M134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*M7</f>
-        <v>293.518843073428</v>
+        <v>550.347830762677</v>
       </c>
       <c r="N135" s="55" t="n">
         <f aca="false">N134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*N7</f>
-        <v>339.323746907422</v>
+        <v>636.232025451416</v>
       </c>
       <c r="O135" s="55" t="n">
         <f aca="false">O134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*O7</f>
-        <v>537.143949306551</v>
+        <v>1007.14490494978</v>
       </c>
       <c r="P135" s="55" t="n">
         <f aca="false">P134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*P7</f>
-        <v>714.348719520691</v>
+        <v>1339.4038491013</v>
       </c>
       <c r="Q135" s="55" t="n">
         <f aca="false">Q134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Q7</f>
-        <v>873.78171394968</v>
+        <v>1638.34071365565</v>
       </c>
       <c r="R135" s="55" t="n">
         <f aca="false">R134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*R7</f>
-        <v>1078.70935846222</v>
+        <v>2022.58004711667</v>
       </c>
       <c r="S135" s="55" t="n">
         <f aca="false">S134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*S7</f>
-        <v>1248.51036310588</v>
+        <v>2340.95693082353</v>
       </c>
       <c r="T135" s="55" t="n">
         <f aca="false">T134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*T7</f>
-        <v>1371.78001513583</v>
+        <v>2572.08752837967</v>
       </c>
       <c r="U135" s="55" t="n">
         <f aca="false">U134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*U7</f>
-        <v>1481.45895488294</v>
+        <v>2777.73554040551</v>
       </c>
       <c r="V135" s="55" t="n">
         <f aca="false">V134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*V7</f>
-        <v>1585.45452681706</v>
+        <v>2972.72723778199</v>
       </c>
       <c r="W135" s="55" t="n">
         <f aca="false">W134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*W7</f>
-        <v>1703.9289282507</v>
+        <v>3194.86674047006</v>
       </c>
       <c r="X135" s="55" t="n">
         <f aca="false">X134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*X7</f>
-        <v>1896.83784053387</v>
+        <v>3556.570951001</v>
       </c>
       <c r="Y135" s="55" t="n">
         <f aca="false">Y134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Y7</f>
-        <v>2055.80200514583</v>
+        <v>3854.62875964843</v>
       </c>
       <c r="Z135" s="55" t="n">
         <f aca="false">Z134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*Z7</f>
-        <v>2171.15617493822</v>
+        <v>4070.91782800916</v>
       </c>
       <c r="AA135" s="55" t="n">
         <f aca="false">AA134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AA7</f>
-        <v>45857.376697346</v>
+        <v>85982.5813075237</v>
       </c>
       <c r="AB135" s="55" t="n">
         <f aca="false">AB134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AB7</f>
-        <v>70417.4409025775</v>
+        <v>132032.701692333</v>
       </c>
       <c r="AC135" s="55" t="n">
         <f aca="false">AC134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AC7</f>
-        <v>94377.4189878918</v>
+        <v>176957.660602297</v>
       </c>
       <c r="AD135" s="55" t="n">
         <f aca="false">AD134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AD7</f>
-        <v>106362.862758858</v>
+        <v>199430.367672858</v>
       </c>
       <c r="AE135" s="55" t="n">
         <f aca="false">AE134*(Assumptions!$B$25+MAX(0,Assumptions!$B$162-1)*Assumptions!$B$26)/12*AE7</f>
-        <v>99394.119829751</v>
+        <v>186363.974680783</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22446,95 +22446,95 @@
       </c>
       <c r="I140" s="57" t="n">
         <f aca="false">I131+I132+I133+I135+I136+I138</f>
-        <v>1669.17151628572</v>
+        <v>1718.62829981303</v>
       </c>
       <c r="J140" s="57" t="n">
         <f aca="false">J131+J132+J133+J135+J136+J138</f>
-        <v>1875.52325700788</v>
+        <v>1970.85915945737</v>
       </c>
       <c r="K140" s="57" t="n">
         <f aca="false">K131+K132+K133+K135+K136+K138</f>
-        <v>2097.46083872023</v>
+        <v>2239.99633306898</v>
       </c>
       <c r="L140" s="57" t="n">
         <f aca="false">L131+L132+L133+L135+L136+L138</f>
-        <v>2415.41209759168</v>
+        <v>2620.26834380282</v>
       </c>
       <c r="M140" s="57" t="n">
         <f aca="false">M131+M132+M133+M135+M136+M138</f>
-        <v>2681.73211980666</v>
+        <v>2938.56110749591</v>
       </c>
       <c r="N140" s="57" t="n">
         <f aca="false">N131+N132+N133+N135+N136+N138</f>
-        <v>2885.86009268005</v>
+        <v>3182.76837122405</v>
       </c>
       <c r="O140" s="57" t="n">
         <f aca="false">O131+O132+O133+O135+O136+O138</f>
-        <v>4184.01868251805</v>
+        <v>4654.01963816129</v>
       </c>
       <c r="P140" s="57" t="n">
         <f aca="false">P131+P132+P133+P135+P136+P138</f>
-        <v>5137.72248020664</v>
+        <v>5762.77760978725</v>
       </c>
       <c r="Q140" s="57" t="n">
         <f aca="false">Q131+Q132+Q133+Q135+Q136+Q138</f>
-        <v>6016.41224255095</v>
+        <v>6780.97124225692</v>
       </c>
       <c r="R140" s="57" t="n">
         <f aca="false">R131+R132+R133+R135+R136+R138</f>
-        <v>7142.25708818195</v>
+        <v>8086.12777683639</v>
       </c>
       <c r="S140" s="57" t="n">
         <f aca="false">S131+S132+S133+S135+S136+S138</f>
-        <v>8112.06928218102</v>
+        <v>9204.51584989866</v>
       </c>
       <c r="T140" s="57" t="n">
         <f aca="false">T131+T132+T133+T135+T136+T138</f>
-        <v>8881.55806482821</v>
+        <v>10081.8655780721</v>
       </c>
       <c r="U140" s="57" t="n">
         <f aca="false">U131+U132+U133+U135+U136+U138</f>
-        <v>9580.46246381538</v>
+        <v>10876.7390493379</v>
       </c>
       <c r="V140" s="57" t="n">
         <f aca="false">V131+V132+V133+V135+V136+V138</f>
-        <v>10248.8087914111</v>
+        <v>11636.081502376</v>
       </c>
       <c r="W140" s="57" t="n">
         <f aca="false">W131+W132+W133+W135+W136+W138</f>
-        <v>11136.8102200315</v>
+        <v>12627.7480322508</v>
       </c>
       <c r="X140" s="57" t="n">
         <f aca="false">X131+X132+X133+X135+X136+X138</f>
-        <v>12414.4905696649</v>
+        <v>14074.223680132</v>
       </c>
       <c r="Y140" s="57" t="n">
         <f aca="false">Y131+Y132+Y133+Y135+Y136+Y138</f>
-        <v>13525.5423721096</v>
+        <v>15324.3691266122</v>
       </c>
       <c r="Z140" s="57" t="n">
         <f aca="false">Z131+Z132+Z133+Z135+Z136+Z138</f>
-        <v>14476.1420453664</v>
+        <v>16375.9036984374</v>
       </c>
       <c r="AA140" s="57" t="n">
         <f aca="false">AA131+AA132+AA133+AA135+AA136+AA138</f>
-        <v>376122.760006728</v>
+        <v>416247.964616906</v>
       </c>
       <c r="AB140" s="57" t="n">
         <f aca="false">AB131+AB132+AB133+AB135+AB136+AB138</f>
-        <v>617460.465860395</v>
+        <v>679075.72665015</v>
       </c>
       <c r="AC140" s="57" t="n">
         <f aca="false">AC131+AC132+AC133+AC135+AC136+AC138</f>
-        <v>887946.824252366</v>
+        <v>970527.065866771</v>
       </c>
       <c r="AD140" s="57" t="n">
         <f aca="false">AD131+AD132+AD133+AD135+AD136+AD138</f>
-        <v>1106093.11274249</v>
+        <v>1199160.61765649</v>
       </c>
       <c r="AE140" s="57" t="n">
         <f aca="false">AE131+AE132+AE133+AE135+AE136+AE138</f>
-        <v>1207743.6154512</v>
+        <v>1294713.47030224</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25879,95 +25879,95 @@
       </c>
       <c r="I175" s="55" t="n">
         <f aca="false">I57+I96+I135</f>
-        <v>81.6922124254556</v>
+        <v>153.172898297729</v>
       </c>
       <c r="J175" s="55" t="n">
         <f aca="false">J57+J96+J135</f>
-        <v>157.493397410901</v>
+        <v>295.30012014544</v>
       </c>
       <c r="K175" s="55" t="n">
         <f aca="false">K57+K96+K135</f>
-        <v>235.496383972015</v>
+        <v>441.555719947529</v>
       </c>
       <c r="L175" s="55" t="n">
         <f aca="false">L57+L96+L135</f>
-        <v>338.51719985139</v>
+        <v>634.719749721356</v>
       </c>
       <c r="M175" s="55" t="n">
         <f aca="false">M57+M96+M135</f>
-        <v>424.469516085647</v>
+        <v>795.880342660589</v>
       </c>
       <c r="N175" s="55" t="n">
         <f aca="false">N57+N96+N135</f>
-        <v>490.784598217325</v>
+        <v>920.221121657484</v>
       </c>
       <c r="O175" s="55" t="n">
         <f aca="false">O57+O96+O135</f>
-        <v>806.729056073299</v>
+        <v>1512.61698013744</v>
       </c>
       <c r="P175" s="55" t="n">
         <f aca="false">P57+P96+P135</f>
-        <v>1090.36902810577</v>
+        <v>2044.44192769832</v>
       </c>
       <c r="Q175" s="55" t="n">
         <f aca="false">Q57+Q96+Q135</f>
-        <v>1346.14639628087</v>
+        <v>2524.02449302663</v>
       </c>
       <c r="R175" s="55" t="n">
         <f aca="false">R57+R96+R135</f>
-        <v>1674.45835585735</v>
+        <v>3139.60941723254</v>
       </c>
       <c r="S175" s="55" t="n">
         <f aca="false">S57+S96+S135</f>
-        <v>1947.49016206233</v>
+        <v>3651.54405386688</v>
       </c>
       <c r="T175" s="55" t="n">
         <f aca="false">T57+T96+T135</f>
-        <v>2146.86995349715</v>
+        <v>4025.38116280715</v>
       </c>
       <c r="U175" s="55" t="n">
         <f aca="false">U57+U96+U135</f>
-        <v>2324.87947074699</v>
+        <v>4359.14900765061</v>
       </c>
       <c r="V175" s="55" t="n">
         <f aca="false">V57+V96+V135</f>
-        <v>2494.10138747362</v>
+        <v>4676.44010151303</v>
       </c>
       <c r="W175" s="55" t="n">
         <f aca="false">W57+W96+W135</f>
-        <v>2686.80102764872</v>
+        <v>5037.75192684135</v>
       </c>
       <c r="X175" s="55" t="n">
         <f aca="false">X57+X96+X135</f>
-        <v>2999.24285151133</v>
+        <v>5623.58034658375</v>
       </c>
       <c r="Y175" s="55" t="n">
         <f aca="false">Y57+Y96+Y135</f>
-        <v>3258.08648075044</v>
+        <v>6108.91215140708</v>
       </c>
       <c r="Z175" s="55" t="n">
         <f aca="false">Z57+Z96+Z135</f>
-        <v>3447.50868091107</v>
+        <v>6464.07877670826</v>
       </c>
       <c r="AA175" s="55" t="n">
         <f aca="false">AA57+AA96+AA135</f>
-        <v>75719.4959526766</v>
+        <v>141974.054911269</v>
       </c>
       <c r="AB175" s="55" t="n">
         <f aca="false">AB57+AB96+AB135</f>
-        <v>119826.06722737</v>
+        <v>224673.876051319</v>
       </c>
       <c r="AC175" s="55" t="n">
         <f aca="false">AC57+AC96+AC135</f>
-        <v>167802.289235747</v>
+        <v>314629.292317026</v>
       </c>
       <c r="AD175" s="55" t="n">
         <f aca="false">AD57+AD96+AD135</f>
-        <v>201413.720135591</v>
+        <v>377650.725254233</v>
       </c>
       <c r="AE175" s="55" t="n">
         <f aca="false">AE57+AE96+AE135</f>
-        <v>208171.239865126</v>
+        <v>390321.074747111</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26499,95 +26499,95 @@
       </c>
       <c r="I180" s="57" t="n">
         <f aca="false">I62+I101+I140+I144</f>
-        <v>2519.2588646483</v>
+        <v>2590.73955052058</v>
       </c>
       <c r="J180" s="57" t="n">
         <f aca="false">J62+J101+J140+J144</f>
-        <v>2828.09482247702</v>
+        <v>2965.90154521156</v>
       </c>
       <c r="K180" s="57" t="n">
         <f aca="false">K62+K101+K140+K144</f>
-        <v>3160.52285650619</v>
+        <v>3366.5821924817</v>
       </c>
       <c r="L180" s="57" t="n">
         <f aca="false">L62+L101+L140+L144</f>
-        <v>3637.26792170298</v>
+        <v>3933.47047157295</v>
       </c>
       <c r="M180" s="57" t="n">
         <f aca="false">M62+M101+M140+M144</f>
-        <v>4036.8463768755</v>
+        <v>4408.25720345044</v>
       </c>
       <c r="N180" s="57" t="n">
         <f aca="false">N62+N101+N140+N144</f>
-        <v>4343.31166684776</v>
+        <v>4772.74819028792</v>
       </c>
       <c r="O180" s="57" t="n">
         <f aca="false">O62+O101+O140+O144</f>
-        <v>16258.3583650573</v>
+        <v>16964.2462891214</v>
       </c>
       <c r="P180" s="57" t="n">
         <f aca="false">P62+P101+P140+P144</f>
-        <v>17818.097037195</v>
+        <v>18772.1699367876</v>
       </c>
       <c r="Q180" s="57" t="n">
         <f aca="false">Q62+Q101+Q140+Q144</f>
-        <v>19257.9029801637</v>
+        <v>20435.7810769095</v>
       </c>
       <c r="R180" s="57" t="n">
         <f aca="false">R62+R101+R140+R144</f>
-        <v>21102.8719365138</v>
+        <v>22568.0229978889</v>
       </c>
       <c r="S180" s="57" t="n">
         <f aca="false">S62+S101+S140+S144</f>
-        <v>22695.3206671059</v>
+        <v>24399.3745589104</v>
       </c>
       <c r="T180" s="57" t="n">
         <f aca="false">T62+T101+T140+T144</f>
-        <v>23958.4552228539</v>
+        <v>25836.9664321639</v>
       </c>
       <c r="U180" s="57" t="n">
         <f aca="false">U62+U101+U140+U144</f>
-        <v>25109.511223208</v>
+        <v>27143.7807601116</v>
       </c>
       <c r="V180" s="57" t="n">
         <f aca="false">V62+V101+V140+V144</f>
-        <v>26213.8952910654</v>
+        <v>28396.2340051048</v>
       </c>
       <c r="W180" s="57" t="n">
         <f aca="false">W62+W101+W140+W144</f>
-        <v>27680.9518540881</v>
+        <v>30031.9027532807</v>
       </c>
       <c r="X180" s="57" t="n">
         <f aca="false">X62+X101+X140+X144</f>
-        <v>29792.5352437736</v>
+        <v>32416.872738846</v>
       </c>
       <c r="Y180" s="57" t="n">
         <f aca="false">Y62+Y101+Y140+Y144</f>
-        <v>31635.5180799166</v>
+        <v>34486.3437505732</v>
       </c>
       <c r="Z180" s="57" t="n">
         <f aca="false">Z62+Z101+Z140+Z144</f>
-        <v>33214.6452189983</v>
+        <v>36231.2153147955</v>
       </c>
       <c r="AA180" s="57" t="n">
         <f aca="false">AA62+AA101+AA140+AA144</f>
-        <v>985111.240700039</v>
+        <v>1051365.79965863</v>
       </c>
       <c r="AB180" s="57" t="n">
         <f aca="false">AB62+AB101+AB140+AB144</f>
-        <v>1656226.93346213</v>
+        <v>1761074.74228608</v>
       </c>
       <c r="AC180" s="57" t="n">
         <f aca="false">AC62+AC101+AC140+AC144</f>
-        <v>2418182.97599646</v>
+        <v>2565009.97907774</v>
       </c>
       <c r="AD180" s="57" t="n">
         <f aca="false">AD62+AD101+AD140+AD144</f>
-        <v>3144086.37071301</v>
+        <v>3320323.37583166</v>
       </c>
       <c r="AE180" s="57" t="n">
         <f aca="false">AE62+AE101+AE140+AE144</f>
-        <v>3724186.72065071</v>
+        <v>3906336.5555327</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26623,95 +26623,95 @@
       </c>
       <c r="I181" s="55" t="n">
         <f aca="false">IF(I148=0,0,I180/I148/I7*12)</f>
-        <v>20.7575551058063</v>
+        <v>21.3465236698612</v>
       </c>
       <c r="J181" s="55" t="n">
         <f aca="false">IF(J148=0,0,J180/J148/J7*12)</f>
-        <v>21.2691660867207</v>
+        <v>22.3055648843892</v>
       </c>
       <c r="K181" s="55" t="n">
         <f aca="false">IF(K148=0,0,K180/K148/K7*12)</f>
-        <v>21.7020578292688</v>
+        <v>23.1169856208509</v>
       </c>
       <c r="L181" s="55" t="n">
         <f aca="false">IF(L148=0,0,L180/L148/L7*12)</f>
-        <v>22.1465299648432</v>
+        <v>23.9500425978325</v>
       </c>
       <c r="M181" s="55" t="n">
         <f aca="false">IF(M148=0,0,M180/M148/M7*12)</f>
-        <v>22.4458839753235</v>
+        <v>24.5110218433968</v>
       </c>
       <c r="N181" s="55" t="n">
         <f aca="false">IF(N148=0,0,N180/N148/N7*12)</f>
-        <v>22.6448655986698</v>
+        <v>24.8838327975216</v>
       </c>
       <c r="O181" s="55" t="n">
         <f aca="false">IF(O148=0,0,O180/O148/O7*12)</f>
-        <v>63.0877293375607</v>
+        <v>65.826804544054</v>
       </c>
       <c r="P181" s="55" t="n">
         <f aca="false">IF(P148=0,0,P180/P148/P7*12)</f>
-        <v>55.9774072167193</v>
+        <v>58.9747265771113</v>
       </c>
       <c r="Q181" s="55" t="n">
         <f aca="false">IF(Q148=0,0,Q180/Q148/Q7*12)</f>
-        <v>51.4484988354444</v>
+        <v>54.595262008524</v>
       </c>
       <c r="R181" s="55" t="n">
         <f aca="false">IF(R148=0,0,R180/R148/R7*12)</f>
-        <v>47.2045112152349</v>
+        <v>50.4818727002861</v>
       </c>
       <c r="S181" s="55" t="n">
         <f aca="false">IF(S148=0,0,S180/S148/S7*12)</f>
-        <v>44.5522164088947</v>
+        <v>47.8973719532326</v>
       </c>
       <c r="T181" s="55" t="n">
         <f aca="false">IF(T148=0,0,T180/T148/T7*12)</f>
-        <v>43.005004714546</v>
+        <v>46.3768992153084</v>
       </c>
       <c r="U181" s="55" t="n">
         <f aca="false">IF(U148=0,0,U180/U148/U7*12)</f>
-        <v>41.783139025104</v>
+        <v>45.1682374493384</v>
       </c>
       <c r="V181" s="55" t="n">
         <f aca="false">IF(V148=0,0,V180/V148/V7*12)</f>
-        <v>40.7371516345342</v>
+        <v>44.1285691298974</v>
       </c>
       <c r="W181" s="55" t="n">
         <f aca="false">IF(W148=0,0,W180/W148/W7*12)</f>
-        <v>40.0258589224076</v>
+        <v>43.4252661942603</v>
       </c>
       <c r="X181" s="55" t="n">
         <f aca="false">IF(X148=0,0,X180/X148/X7*12)</f>
-        <v>38.8965944849783</v>
+        <v>42.3228819929838</v>
       </c>
       <c r="Y181" s="55" t="n">
         <f aca="false">IF(Y148=0,0,Y180/Y148/Y7*12)</f>
-        <v>38.1166258039265</v>
+        <v>41.5514946448965</v>
       </c>
       <c r="Z181" s="55" t="n">
         <f aca="false">IF(Z148=0,0,Z180/Z148/Z7*12)</f>
-        <v>37.7463989305001</v>
+        <v>41.1745450837111</v>
       </c>
       <c r="AA181" s="55" t="n">
         <f aca="false">IF(AA148=0,0,AA180/AA148/AA7*12)</f>
-        <v>48.8723797302725</v>
+        <v>52.1593364012623</v>
       </c>
       <c r="AB181" s="55" t="n">
         <f aca="false">IF(AB148=0,0,AB180/AB148/AB7*12)</f>
-        <v>50.5574084419185</v>
+        <v>53.7579562580755</v>
       </c>
       <c r="AC181" s="55" t="n">
         <f aca="false">IF(AC148=0,0,AC180/AC148/AC7*12)</f>
-        <v>51.476275045335</v>
+        <v>54.6018065992818</v>
       </c>
       <c r="AD181" s="55" t="n">
         <f aca="false">IF(AD148=0,0,AD180/AD148/AD7*12)</f>
-        <v>54.043085919719</v>
+        <v>57.0723893442622</v>
       </c>
       <c r="AE181" s="55" t="n">
         <f aca="false">IF(AE148=0,0,AE180/AE148/AE7*12)</f>
-        <v>59.4926440971159</v>
+        <v>62.4024271213916</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26917,31 +26917,31 @@
       </c>
       <c r="D7" s="36" t="n">
         <f aca="false">SUM(Model!C62:N62)</f>
-        <v>9620.05661317061</v>
+        <v>10086.5315648681</v>
       </c>
       <c r="E7" s="36" t="n">
         <f aca="false">SUM(Model!O62:Z62)</f>
-        <v>56728.3934164669</v>
+        <v>63472.198526855</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">Model!AA62</f>
-        <v>209023.886122908</v>
+        <v>229598.30174668</v>
       </c>
       <c r="G7" s="36" t="n">
         <f aca="false">Model!AB62</f>
-        <v>365469.795352942</v>
+        <v>399379.801211847</v>
       </c>
       <c r="H7" s="36" t="n">
         <f aca="false">Model!AC62</f>
-        <v>572113.620828483</v>
+        <v>622470.283985201</v>
       </c>
       <c r="I7" s="36" t="n">
         <f aca="false">Model!AD62</f>
-        <v>791894.656082807</v>
+        <v>857086.123475664</v>
       </c>
       <c r="J7" s="36" t="n">
         <f aca="false">Model!AE62</f>
-        <v>988799.762143192</v>
+        <v>1063570.87978376</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26954,27 +26954,27 @@
       </c>
       <c r="E8" s="36" t="n">
         <f aca="false">SUM(Model!O101:Z101)</f>
-        <v>9028.37540060694</v>
+        <v>10600.3693034797</v>
       </c>
       <c r="F8" s="36" t="n">
         <f aca="false">Model!AA101</f>
-        <v>45589.5945704026</v>
+        <v>51144.5332950456</v>
       </c>
       <c r="G8" s="36" t="n">
         <f aca="false">Model!AB101</f>
-        <v>82671.6722487917</v>
+        <v>91994.2144240801</v>
       </c>
       <c r="H8" s="36" t="n">
         <f aca="false">Model!AC101</f>
-        <v>131247.530915612</v>
+        <v>145137.629225767</v>
       </c>
       <c r="I8" s="36" t="n">
         <f aca="false">Model!AD101</f>
-        <v>182973.601887721</v>
+        <v>200951.634699506</v>
       </c>
       <c r="J8" s="36" t="n">
         <f aca="false">Model!AE101</f>
-        <v>228268.343056317</v>
+        <v>248677.2054467</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26983,31 +26983,31 @@
       </c>
       <c r="D9" s="36" t="n">
         <f aca="false">SUM(Model!C140:N140)</f>
-        <v>18948.7512929894</v>
+        <v>19994.6729857593</v>
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">SUM(Model!O140:Z140)</f>
-        <v>110856.294302866</v>
+        <v>125485.342784159</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">Model!AA140</f>
-        <v>376122.760006728</v>
+        <v>416247.964616906</v>
       </c>
       <c r="G9" s="36" t="n">
         <f aca="false">Model!AB140</f>
-        <v>617460.465860395</v>
+        <v>679075.72665015</v>
       </c>
       <c r="H9" s="36" t="n">
         <f aca="false">Model!AC140</f>
-        <v>887946.824252366</v>
+        <v>970527.065866771</v>
       </c>
       <c r="I9" s="36" t="n">
         <f aca="false">Model!AD140</f>
-        <v>1106093.11274249</v>
+        <v>1199160.61765649</v>
       </c>
       <c r="J9" s="36" t="n">
         <f aca="false">Model!AE140</f>
-        <v>1207743.6154512</v>
+        <v>1294713.47030224</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27049,31 +27049,31 @@
       </c>
       <c r="D11" s="62" t="n">
         <f aca="false">SUM(Model!C180:N180)</f>
-        <v>28568.80790616</v>
+        <v>30081.2045506274</v>
       </c>
       <c r="E11" s="62" t="n">
         <f aca="false">SUM(Model!O180:Z180)</f>
-        <v>294738.06311994</v>
+        <v>317682.910614494</v>
       </c>
       <c r="F11" s="62" t="n">
         <f aca="false">Model!AA180</f>
-        <v>985111.240700039</v>
+        <v>1051365.79965863</v>
       </c>
       <c r="G11" s="62" t="n">
         <f aca="false">Model!AB180</f>
-        <v>1656226.93346213</v>
+        <v>1761074.74228608</v>
       </c>
       <c r="H11" s="62" t="n">
         <f aca="false">Model!AC180</f>
-        <v>2418182.97599646</v>
+        <v>2565009.97907774</v>
       </c>
       <c r="I11" s="62" t="n">
         <f aca="false">Model!AD180</f>
-        <v>3144086.37071301</v>
+        <v>3320323.37583166</v>
       </c>
       <c r="J11" s="62" t="n">
         <f aca="false">Model!AE180</f>
-        <v>3724186.72065071</v>
+        <v>3906336.5555327</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27196,31 +27196,31 @@
       </c>
       <c r="D17" s="36" t="n">
         <f aca="false">SUM(Model!C175:N175)</f>
-        <v>1728.45330796273</v>
+        <v>3240.84995243013</v>
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">SUM(Model!O175:Z175)</f>
-        <v>26222.6828509189</v>
+        <v>49167.530345473</v>
       </c>
       <c r="F17" s="36" t="n">
         <f aca="false">Model!AA175</f>
-        <v>75719.4959526766</v>
+        <v>141974.054911269</v>
       </c>
       <c r="G17" s="36" t="n">
         <f aca="false">Model!AB175</f>
-        <v>119826.06722737</v>
+        <v>224673.876051319</v>
       </c>
       <c r="H17" s="36" t="n">
         <f aca="false">Model!AC175</f>
-        <v>167802.289235747</v>
+        <v>314629.292317026</v>
       </c>
       <c r="I17" s="36" t="n">
         <f aca="false">Model!AD175</f>
-        <v>201413.720135591</v>
+        <v>377650.725254233</v>
       </c>
       <c r="J17" s="36" t="n">
         <f aca="false">Model!AE175</f>
-        <v>208171.239865126</v>
+        <v>390321.074747111</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27328,31 +27328,31 @@
       </c>
       <c r="D21" s="62" t="n">
         <f aca="false">SUM(Model!C180:N180)</f>
-        <v>28568.80790616</v>
+        <v>30081.2045506274</v>
       </c>
       <c r="E21" s="62" t="n">
         <f aca="false">SUM(Model!O180:Z180)</f>
-        <v>294738.06311994</v>
+        <v>317682.910614494</v>
       </c>
       <c r="F21" s="62" t="n">
         <f aca="false">Model!AA180</f>
-        <v>985111.240700039</v>
+        <v>1051365.79965863</v>
       </c>
       <c r="G21" s="62" t="n">
         <f aca="false">Model!AB180</f>
-        <v>1656226.93346213</v>
+        <v>1761074.74228608</v>
       </c>
       <c r="H21" s="62" t="n">
         <f aca="false">Model!AC180</f>
-        <v>2418182.97599646</v>
+        <v>2565009.97907774</v>
       </c>
       <c r="I21" s="62" t="n">
         <f aca="false">Model!AD180</f>
-        <v>3144086.37071301</v>
+        <v>3320323.37583166</v>
       </c>
       <c r="J21" s="62" t="n">
         <f aca="false">Model!AE180</f>
-        <v>3724186.72065071</v>
+        <v>3906336.5555327</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27376,31 +27376,31 @@
       </c>
       <c r="D24" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D14/D$11)</f>
-        <v>0.873068016164452</v>
+        <v>0.82917266164776</v>
       </c>
       <c r="E24" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E14/E$11)</f>
-        <v>0.431424886322951</v>
+        <v>0.400264953285043</v>
       </c>
       <c r="F24" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F14/F$11)</f>
-        <v>0.37796535868201</v>
+        <v>0.354146885464378</v>
       </c>
       <c r="G24" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G14/G$11)</f>
-        <v>0.365612166536939</v>
+        <v>0.343844984474574</v>
       </c>
       <c r="H24" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H14/H$11)</f>
-        <v>0.359580321665323</v>
+        <v>0.338997126501262</v>
       </c>
       <c r="I24" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I14/I$11)</f>
-        <v>0.343175368097639</v>
+        <v>0.324960214855565</v>
       </c>
       <c r="J24" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J14/J$11)</f>
-        <v>0.312674849442068</v>
+        <v>0.298095032422217</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27409,31 +27409,31 @@
       </c>
       <c r="D25" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D15/D$11)</f>
-        <v>0.0664305686683422</v>
+        <v>0.0630906303033419</v>
       </c>
       <c r="E25" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E15/E$11)</f>
-        <v>0.0329770491777252</v>
+        <v>0.0305952611150947</v>
       </c>
       <c r="F25" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F15/F$11)</f>
-        <v>0.0291557635881713</v>
+        <v>0.0273184370760644</v>
       </c>
       <c r="G25" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G15/G$11)</f>
-        <v>0.0283706412508161</v>
+        <v>0.0266815592949776</v>
       </c>
       <c r="H25" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H15/H$11)</f>
-        <v>0.0281326895684297</v>
+        <v>0.0265223104542581</v>
       </c>
       <c r="I25" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I15/I$11)</f>
-        <v>0.0271418889673972</v>
+        <v>0.0257012445832704</v>
       </c>
       <c r="J25" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J15/J$11)</f>
-        <v>0.0251111040467964</v>
+        <v>0.0239401902274661</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27446,27 +27446,27 @@
       </c>
       <c r="E26" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E16/E$11)</f>
-        <v>0.000705699059899705</v>
+        <v>0.000654729502629129</v>
       </c>
       <c r="F26" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F16/F$11)</f>
-        <v>0.00466395288690552</v>
+        <v>0.00437004172713039</v>
       </c>
       <c r="G26" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G16/G$11)</f>
-        <v>0.00669873870395668</v>
+        <v>0.0062999208354531</v>
       </c>
       <c r="H26" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H16/H$11)</f>
-        <v>0.00896070880960337</v>
+        <v>0.00844777746402196</v>
       </c>
       <c r="I26" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I16/I$11)</f>
-        <v>0.0119364030276831</v>
+        <v>0.0113028394607125</v>
       </c>
       <c r="J26" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J16/J$11)</f>
-        <v>0.0161483386263173</v>
+        <v>0.0153953525042598</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27475,31 +27475,31 @@
       </c>
       <c r="D27" s="63" t="n">
         <f aca="false">IF(D$11=0,0,D17/D$11)</f>
-        <v>0.0605014151672057</v>
+        <v>0.107736708048898</v>
       </c>
       <c r="E27" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E17/E$11)</f>
-        <v>0.0889694482393609</v>
+        <v>0.15476920130947</v>
       </c>
       <c r="F27" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F17/F$11)</f>
-        <v>0.0768639041199741</v>
+        <v>0.135037733733936</v>
       </c>
       <c r="G27" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G17/G$11)</f>
-        <v>0.0723488217746158</v>
+        <v>0.127577706190747</v>
       </c>
       <c r="H27" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H17/H$11)</f>
-        <v>0.0693918908955187</v>
+        <v>0.122662014917444</v>
       </c>
       <c r="I27" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I17/I$11)</f>
-        <v>0.064061128222096</v>
+        <v>0.113739139989532</v>
       </c>
       <c r="J27" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J17/J$11)</f>
-        <v>0.0558971006235565</v>
+        <v>0.0999199810866997</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27512,27 +27512,27 @@
       </c>
       <c r="E28" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E18/E$11)</f>
-        <v>0.0443621839978498</v>
+        <v>0.041158097431194</v>
       </c>
       <c r="F28" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F18/F$11)</f>
-        <v>0.14634536461092</v>
+        <v>0.137123029633808</v>
       </c>
       <c r="G28" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G18/G$11)</f>
-        <v>0.162784937184257</v>
+        <v>0.153093330369684</v>
       </c>
       <c r="H28" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H18/H$11)</f>
-        <v>0.181859628343842</v>
+        <v>0.171449569736271</v>
       </c>
       <c r="I28" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I18/I$11)</f>
-        <v>0.202050913395665</v>
+        <v>0.191326401404595</v>
       </c>
       <c r="J28" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J18/J$11)</f>
-        <v>0.223003926174807</v>
+        <v>0.212605403734839</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27545,27 +27545,27 @@
       </c>
       <c r="E29" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E19/E$11)</f>
-        <v>0.000781143523187808</v>
+        <v>0.000724724942231614</v>
       </c>
       <c r="F29" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F19/F$11)</f>
-        <v>0.00527470862209553</v>
+        <v>0.00494230909615937</v>
       </c>
       <c r="G29" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G19/G$11)</f>
-        <v>0.00757595448661768</v>
+        <v>0.00712491046866719</v>
       </c>
       <c r="H29" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H19/H$11)</f>
-        <v>0.0101341349632419</v>
+        <v>0.00955403403669151</v>
       </c>
       <c r="I29" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I19/I$11)</f>
-        <v>0.0134995034241655</v>
+        <v>0.0127829731996153</v>
       </c>
       <c r="J29" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J19/J$11)</f>
-        <v>0.0182630020178588</v>
+        <v>0.0174114105702938</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27578,27 +27578,27 @@
       </c>
       <c r="E30" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E20/E$11)</f>
-        <v>0.400779589679025</v>
+        <v>0.371833032414337</v>
       </c>
       <c r="F30" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F20/F$11)</f>
-        <v>0.359730947489924</v>
+        <v>0.337061563268524</v>
       </c>
       <c r="G30" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G20/G$11)</f>
-        <v>0.356608740062797</v>
+        <v>0.335377588365898</v>
       </c>
       <c r="H30" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H20/H$11)</f>
-        <v>0.341940625754041</v>
+        <v>0.322367166890051</v>
       </c>
       <c r="I30" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I20/I$11)</f>
-        <v>0.338134794865354</v>
+        <v>0.32018718650671</v>
       </c>
       <c r="J30" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J20/J$11)</f>
-        <v>0.348901679068596</v>
+        <v>0.332632629454225</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27952,31 +27952,31 @@
       </c>
       <c r="D43" s="36" t="n">
         <f aca="false">Model!N181</f>
-        <v>22.6448655986698</v>
+        <v>24.8838327975216</v>
       </c>
       <c r="E43" s="36" t="n">
         <f aca="false">Model!Z181</f>
-        <v>37.7463989305001</v>
+        <v>41.1745450837111</v>
       </c>
       <c r="F43" s="36" t="n">
         <f aca="false">Model!AA181</f>
-        <v>48.8723797302725</v>
+        <v>52.1593364012623</v>
       </c>
       <c r="G43" s="36" t="n">
         <f aca="false">Model!AB181</f>
-        <v>50.5574084419185</v>
+        <v>53.7579562580755</v>
       </c>
       <c r="H43" s="36" t="n">
         <f aca="false">Model!AC181</f>
-        <v>51.476275045335</v>
+        <v>54.6018065992818</v>
       </c>
       <c r="I43" s="36" t="n">
         <f aca="false">Model!AD181</f>
-        <v>54.043085919719</v>
+        <v>57.0723893442622</v>
       </c>
       <c r="J43" s="36" t="n">
         <f aca="false">Model!AE181</f>
-        <v>59.4926440971159</v>
+        <v>62.4024271213916</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
@@ -391,7 +391,7 @@
     <t xml:space="preserve">USD/yr</t>
   </si>
   <si>
-    <t xml:space="preserve">RE-PRICED 2026-08-21 from USD 120/yr. THE OLD PRICE WAS ABOVE TRUST &amp; WILL'S PREMIUM US MEMBERSHIP (USD 49/yr) AND WAS 33% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR - a USD 30/month saver puts away USD 360, and we were charging 120 of it. THE INDUSTRY MODEL IS A ONE-OFF FEE PLUS A SMALL ANNUAL UPDATE LAYER, and it is the annual layer this row represents: Trust &amp; Will USD 199 one-off + USD 49/yr; Farewill GBP 100 + GBP 10/yr; Epilogue C$139 with NO subscription at all; other platforms renew updates at ~C$4.50/yr. Formal UAE will registration is a different product entirely and one-off - DIFC AED 10,000 single / 15,000 mirror, Abu Dhabi Civil Court AED 950 as the cheapest formal route. Indian online wills run INR 500-4,000 basic. Family add-ons on finance apps are usually BUNDLED FREE; where charged it is USD 5-15/month for a WHOLE HOUSEHOLD (Monarch 99.99/yr, Zeta 59.99/yr, Greenlight 5.99/mo). SET AT USD 50/yr, client instruction 2026-08-21. That is essentially TRUST &amp; WILL'S USD 49/yr MEMBERSHIP - a defensible anchor in that it matches the best-known product in the category, but ⚠ NOTE WHOSE PRODUCT IT IS: Trust &amp; Will sells to US customers who paid 199-599 up front for an estate plan, not to a migrant worker saving USD 30 a month. At 50 the plan is 14% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR, against 10% at 36 and 33% at the original 120. It is no longer absurd, but it is priced at a developed-market benchmark for an emerging-market customer, and that is the line an adviser would push on. ⚠ A ONE-OFF SETUP FEE IS NOT MODELLED - if the client wants the full industry structure, that is a second row, not a bigger number here. CITED comparators, ASSUMPTION on the point in the range.</t>
+    <t xml:space="preserve">RE-PRICED 2026-08-21 from USD 120/yr. THE OLD PRICE WAS ABOVE TRUST &amp; WILL'S PREMIUM US MEMBERSHIP (USD 49/yr) AND WAS 33% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR - a USD 30/month saver puts away USD 360, and we were charging 120 of it. THE INDUSTRY MODEL IS A ONE-OFF FEE PLUS A SMALL ANNUAL UPDATE LAYER, and it is the annual layer this row represents: Trust &amp; Will USD 199 one-off + USD 49/yr; Farewill GBP 100 + GBP 10/yr; Epilogue C$139 with NO subscription at all; other platforms renew updates at ~C$4.50/yr. Formal UAE will registration is a different product entirely and one-off - DIFC AED 10,000 single / 15,000 mirror, Abu Dhabi Civil Court AED 950 as the cheapest formal route. Indian online wills run INR 500-4,000 basic. Family add-ons on finance apps are usually BUNDLED FREE; where charged it is USD 5-15/month for a WHOLE HOUSEHOLD (Monarch 99.99/yr, Zeta 59.99/yr, Greenlight 5.99/mo). SET AT USD 50/yr, client instruction 2026-08-21. That is essentially TRUST &amp; WILL'S USD 49/yr MEMBERSHIP - a defensible anchor in that it matches the best-known product in the category, but NOTE WHOSE PRODUCT IT IS: Trust &amp; Will sells to US customers who paid 199-599 up front for an estate plan, not to a migrant worker saving USD 30 a month. At 50 the plan is 14% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR, against 10% at 36 and 33% at the original 120. It is no longer absurd, but it is priced at a developed-market benchmark for an emerging-market customer, and that is the line an adviser would push on. A ONE-OFF SETUP FEE IS NOT MODELLED - if the client wants the full industry structure, that is a second row, not a bigger number here. CITED comparators, ASSUMPTION on the point in the range.</t>
   </si>
   <si>
     <t xml:space="preserve">Additional beneficiary fee</t>
@@ -400,7 +400,7 @@
     <t xml:space="preserve">USD/yr each</t>
   </si>
   <si>
-    <t xml:space="preserve">ADDED 2026-08-21, client instruction. Charged per named beneficiary BEYOND THE FIRST, which the plan includes - the standard shape for this kind of add-on, and the reason the formula carries a MAX(0, n-1) rather than charging every beneficiary. ⚠ NO COMPARABLE EXISTS: will services price PER WILL, not per beneficiary. DIFC charges more for a MIRROR will (two people) and more again for guardianship, but nobody publishes a per-beneficiary tariff. So this is priced on COST RECOVERY, which is the defensible basis available: every named beneficiary needs identity capture and AML screening, and Sumsub screening already sits in this model at ~USD 1.85 per check in the redemption cost memo. USD 6/yr covers that with margin without becoming a second subscription. DELIBERATELY SMALL. At 1.5 chargeable beneficiaries it adds USD 9/yr to a USD 50 plan - an 18% uplift on a stream worth ~3.5% of revenue, so it cannot move the model and should not be tuned to try. ASSUMPTION on a cost-recovery basis.</t>
+    <t xml:space="preserve">ADDED 2026-08-21, client instruction. Charged per named beneficiary BEYOND THE FIRST, which the plan includes - the standard shape for this kind of add-on, and the reason the formula carries a MAX(0, n-1) rather than charging every beneficiary. NO COMPARABLE EXISTS: will services price PER WILL, not per beneficiary. DIFC charges more for a MIRROR will (two people) and more again for guardianship, but nobody publishes a per-beneficiary tariff. So this is priced on COST RECOVERY, which is the defensible basis available: every named beneficiary needs identity capture and AML screening, and Sumsub screening already sits in this model at ~USD 1.85 per check in the redemption cost memo. USD 6/yr covers that with margin without becoming a second subscription. DELIBERATELY SMALL. At 1.5 chargeable beneficiaries it adds USD 9/yr to a USD 50 plan - an 18% uplift on a stream worth ~3.5% of revenue, so it cannot move the model and should not be tuned to try. ASSUMPTION on a cost-recovery basis.</t>
   </si>
   <si>
     <t xml:space="preserve">B2B platform fee</t>
@@ -463,13 +463,13 @@
     <t xml:space="preserve">Spot ticket - Oman and Bahrain</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ INFERRED - THE WEAKEST OF THE THREE. No GCC platform outside the UAE publishes an average ticket; this is a CONFIRMED NEGATIVE, not a gap in the search. Taken as the UAE figure scaled by the regional income gap (SIP 26.00/33.60 = 0.77x). Do not present this as sourced.</t>
+    <t xml:space="preserve">INFERRED - THE WEAKEST OF THE THREE. No GCC platform outside the UAE publishes an average ticket; this is a CONFIRMED NEGATIVE, not a gap in the search. Taken as the UAE figure scaled by the regional income gap (SIP 26.00/33.60 = 0.77x). Do not present this as sourced.</t>
   </si>
   <si>
     <t xml:space="preserve">Spot ticket - India</t>
   </si>
   <si>
-    <t xml:space="preserve">OBSERVED, PROXY. Augmont: average festive-season purchase Rs 3,300, Times of India, Sep 2025 (= ~USD 38). Augmont is a licensed refiner and digital gold platform; a festive lump is structurally the same act as a spot purchase, which is why it is preferred to the alternatives. REJECTED: SafeGold Rs 5,000-8,000 (May 2026) - that book skews to investors, while Aurumix's Indian customer saves USD 30 a month; MMTC-PAMP Rs 800-1,200 - closer to routine micro-saving than a lump; Rs 230 industry-wide - a LinkedIn aggregate, not a citable source. ⚠ WEAKER THAN THE UAE FIGURE: right country and right behaviour, but Aurumix's Indian customer is poorer than Augmont's average buyer, so 40 may be generous.</t>
+    <t xml:space="preserve">OBSERVED, PROXY. Augmont: average festive-season purchase Rs 3,300, Times of India, Sep 2025 (= ~USD 38). Augmont is a licensed refiner and digital gold platform; a festive lump is structurally the same act as a spot purchase, which is why it is preferred to the alternatives. REJECTED: SafeGold Rs 5,000-8,000 (May 2026) - that book skews to investors, while Aurumix's Indian customer saves USD 30 a month; MMTC-PAMP Rs 800-1,200 - closer to routine micro-saving than a lump; Rs 230 industry-wide - a LinkedIn aggregate, not a citable source. WEAKER THAN THE UAE FIGURE: right country and right behaviour, but Aurumix's Indian customer is poorer than Augmont's average buyer, so 40 may be generous.</t>
   </si>
   <si>
     <t xml:space="preserve">Spot attach rate - UAE</t>
@@ -478,7 +478,7 @@
     <t xml:space="preserve">% of customers/yr</t>
   </si>
   <si>
-    <t xml:space="preserve">Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. ⚠ NO PUBLISHED BENCHMARK EXISTS - confirmed negative. ⚠ KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
+    <t xml:space="preserve">Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. NO PUBLISHED BENCHMARK EXISTS - confirmed negative. KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
   </si>
   <si>
     <t xml:space="preserve">Spot attach rate - Oman and Bahrain</t>
@@ -514,7 +514,7 @@
     <t xml:space="preserve">USD</t>
   </si>
   <si>
-    <t xml:space="preserve">RE-CUT 2026-08-20 from 4.20: the outbound bank transfer fee (USD 1.00-2.50) is REMOVED - that is the customer's cost to bear, not Aurumix's. What remains is Sumsub AML re-screening at 1.85 plus operational handling at ~1.35, both of which Aurumix genuinely pays. ⚠ NOT IN THE REVENUE MODEL: redemption is a COST and arrives with the cost build. This row is carried so the driver is documented and the unit rate already agreed. THE FINDING IT CARRIES IS UNCHANGED AND IS THE POINT - VARA Annex 2 III.E.4 forbids charging ANY fee on redemption, verified verbatim at primary source, so the cost is 100% absorbed, no offsetting revenue exists or can exist, and THERE CAN NEVER BE AN EXIT FEE. DERIVED.</t>
+    <t xml:space="preserve">RE-CUT 2026-08-20 from 4.20: the outbound bank transfer fee (USD 1.00-2.50) is REMOVED - that is the customer's cost to bear, not Aurumix's. What remains is Sumsub AML re-screening at 1.85 plus operational handling at ~1.35, both of which Aurumix genuinely pays. NOT IN THE REVENUE MODEL: redemption is a COST and arrives with the cost build. This row is carried so the driver is documented and the unit rate already agreed. THE FINDING IT CARRIES IS UNCHANGED AND IS THE POINT - VARA Annex 2 III.E.4 forbids charging ANY fee on redemption, verified verbatim at primary source, so the cost is 100% absorbed, no offsetting revenue exists or can exist, and THERE CAN NEVER BE AN EXIT FEE. DERIVED.</t>
   </si>
   <si>
     <t xml:space="preserve">ACTIVATION CALENDAR - the single source of every activation period</t>
@@ -586,7 +586,7 @@
     <t xml:space="preserve">Region opens - India</t>
   </si>
   <si>
-    <t xml:space="preserve">M1 (client decision 2026-08-20, moved earlier from M13). The India payment route is ASSUMED SOLVED in this model. ⚠ That is a live assumption, not a settled fact - if the route is not solved, this region does not open at all and roughly a quarter of terminal revenue goes with it.</t>
+    <t xml:space="preserve">M1 (client decision 2026-08-20, moved earlier from M13). The India payment route is ASSUMED SOLVED in this model. That is a live assumption, not a settled fact - if the route is not solved, this region does not open at all and roughly a quarter of terminal revenue goes with it.</t>
   </si>
   <si>
     <t xml:space="preserve">SEASONALITY VECTORS (raw - the Model normalises to exactly 12.000)</t>
@@ -691,7 +691,7 @@
     <t xml:space="preserve">Source population</t>
   </si>
   <si>
-    <t xml:space="preserve">UPDATED 2026-08-20. UAE-Indian is 4.36m - the Indian consulate's official count at December 2024, also given as 4.3m by the Embassy of India. The brief carried 3.5m, which is roughly a 2021-22 vintage: the community was 3.89m at December 2023 and 4.36m a year later, having doubled from 2.2m over the decade. UAE-other South Asian is 3.46m, the sum of Pakistani 1.90m, Bangladeshi 0.84m, Nepali 0.36m and Sri Lankan 0.36m - the brief's 3.4m was already correct. These are TOTAL RESIDENT NATIONALS including dependants, which is why the economically-active filter below applies. Oman and Bahrain is an expatriate WORKER count. INDIA IS NOT A DEMOGRAPHIC BASE - it is sized BEHAVIOURALLY from gold ETF folios intersected with active digital-gold holders, so its filters are 100%. ⚠ HELD STATIC over the horizon, which is conservative: the UAE Indian community grew ~12% in the single year to Dec 2024.</t>
+    <t xml:space="preserve">UPDATED 2026-08-20. UAE-Indian is 4.36m - the Indian consulate's official count at December 2024, also given as 4.3m by the Embassy of India. The brief carried 3.5m, which is roughly a 2021-22 vintage: the community was 3.89m at December 2023 and 4.36m a year later, having doubled from 2.2m over the decade. UAE-other South Asian is 3.46m, the sum of Pakistani 1.90m, Bangladeshi 0.84m, Nepali 0.36m and Sri Lankan 0.36m - the brief's 3.4m was already correct. These are TOTAL RESIDENT NATIONALS including dependants, which is why the economically-active filter below applies. Oman and Bahrain is an expatriate WORKER count. INDIA IS NOT A DEMOGRAPHIC BASE - it is sized BEHAVIOURALLY from gold ETF folios intersected with active digital-gold holders, so its filters are 100%. HELD STATIC over the horizon, which is conservative: the UAE Indian community grew ~12% in the single year to Dec 2024.</t>
   </si>
   <si>
     <t xml:space="preserve">  x Economically active</t>
@@ -760,7 +760,7 @@
     <t xml:space="preserve">Total reachable SIP accounts</t>
   </si>
   <si>
-    <t xml:space="preserve">~181,150, against the brief's 165,750. ⚠ THE BRIEF'S 'base x ceiling is the invariant' RULE IS DELIBERATELY BROKEN HERE, and the distinction matters: that rule guards against a METHODOLOGICAL re-cut quietly inflating the market by re-tuning filters, which proves nothing. This is not that - it is a DATA CORRECTION. The UAE Indian population really is 4.36m rather than 3.5m, so the addressable market really is larger. Holding the invariant would mean asserting that penetration falls exactly as population rises, which has no basis. The penetration ceilings are untouched.</t>
+    <t xml:space="preserve">~181,150, against the brief's 165,750. THE BRIEF'S 'base x ceiling is the invariant' RULE IS DELIBERATELY BROKEN HERE, and the distinction matters: that rule guards against a METHODOLOGICAL re-cut quietly inflating the market by re-tuning filters, which proves nothing. This is not that - it is a DATA CORRECTION. The UAE Indian population really is 4.36m rather than 3.5m, so the addressable market really is larger. Holding the invariant would mean asserting that penetration falls exactly as population rises, which has no basis. The penetration ceilings are untouched.</t>
   </si>
   <si>
     <t xml:space="preserve">CROSS-CHECK vs observed market evidence (memo - feeds nothing)</t>
@@ -781,7 +781,7 @@
     <t xml:space="preserve">x observed</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ LIVE, SO IT MOVES IF ANYONE RAISES A CEILING - which is the point. Two INDEPENDENT methods landing within ~2x is the strongest defence of the funnel in this model: the funnel says the UAE can reach ~113,000 SIP accounts, and a real UAE gold app in the same segment has ~75,000 active users today. Our addressable base of ~1.43m sits against 775,000 who explored that product - same order again. If this multiple drifts far above ~2x, the ceiling has stopped being defensible by evidence and is being set by the answer someone wanted. DERIVED from a cited observation.</t>
+    <t xml:space="preserve">LIVE, SO IT MOVES IF ANYONE RAISES A CEILING - which is the point. Two INDEPENDENT methods landing within ~2x is the strongest defence of the funnel in this model: the funnel says the UAE can reach ~113,000 SIP accounts, and a real UAE gold app in the same segment has ~75,000 active users today. Our addressable base of ~1.43m sits against 775,000 who explored that product - same order again. If this multiple drifts far above ~2x, the ceiling has stopped being defensible by evidence and is being set by the answer someone wanted. DERIVED from a cited observation.</t>
   </si>
   <si>
     <t xml:space="preserve">  Oman &amp; Bahrain / India (no comparable figure)</t>
@@ -793,7 +793,7 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">CONFIRMED NEGATIVE, recorded so it is not re-searched. No GCC platform outside the UAE publishes a user count. India publishes only REGISTERED counts (Jar 35m, Augmont 42m) which cannot be deduplicated or converted to active users, so no comparable cross-check can be built. ⚠ NOTE THAT INDIA'S OWN BASE IS ALREADY user-derived - its 12.5m is 'holds a gold ETF folio or actively buys digital gold', which is why its three filters all sit at 1.00 - AND IT IS THE LEAST TRACEABLE BASE IN THE MODEL. That is the evidence that a user-based method does not automatically produce a better-sourced number.</t>
+    <t xml:space="preserve">CONFIRMED NEGATIVE, recorded so it is not re-searched. No GCC platform outside the UAE publishes a user count. India publishes only REGISTERED counts (Jar 35m, Augmont 42m) which cannot be deduplicated or converted to active users, so no comparable cross-check can be built. NOTE THAT INDIA'S OWN BASE IS ALREADY user-derived - its 12.5m is 'holds a gold ETF folio or actively buys digital gold', which is why its three filters all sit at 1.00 - AND IT IS THE LEAST TRACEABLE BASE IN THE MODEL. That is the evidence that a user-based method does not automatically produce a better-sourced number.</t>
   </si>
   <si>
     <t xml:space="preserve">Active agents - Y1</t>
@@ -802,7 +802,7 @@
     <t xml:space="preserve">agents</t>
   </si>
   <si>
-    <t xml:space="preserve">RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+    <t xml:space="preserve">RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
   </si>
   <si>
     <t xml:space="preserve">Active agents - Y2</t>
@@ -826,7 +826,7 @@
     <t xml:space="preserve">Marketing spend - Y1</t>
   </si>
   <si>
-    <t xml:space="preserve">RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+    <t xml:space="preserve">RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
   </si>
   <si>
     <t xml:space="preserve">Marketing spend - Y2</t>
@@ -880,7 +880,7 @@
     <t xml:space="preserve">% of salesforce</t>
   </si>
   <si>
-    <t xml:space="preserve">REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. ⚠ IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. ⚠ NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
+    <t xml:space="preserve">REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
   </si>
   <si>
     <t xml:space="preserve">Share of salesforce deployed - Oman and Bahrain</t>
@@ -898,7 +898,7 @@
     <t xml:space="preserve">%/yr</t>
   </si>
   <si>
-    <t xml:space="preserve">ADDED 2026-08-21, client instruction, replacing a flat price. 8.1% is the COMPOUND ANNUAL GROWTH RATE SINCE 1971, the end of the gold standard - chosen because it is the LONGEST window and therefore the least cherry-picked. The shorter the window the better gold looks: ~8.6% over 50 years, ~9-10% over 20, ~13-14% over 10, and over 20% over the last 5. Taking the recent decade would have flattered the model on a rally. CITED. ⚠ THIS IS A NOMINAL RATE AND NOTHING ELSE IN THE MODEL INFLATES. SIP tickets, spot tickets, CAC, card fees and the B2B fee are all frozen in 2027 dollars. There is NO CONSENSUS POSITIVE LONG-RUN REAL RETURN for gold - it is generally treated as a store of value with a near-zero real yield - so most of this 8.1% IS INFLATION. Applying it to the metal while freezing everything else quietly asserts that gold outruns wages, prices and costs by 8% a year for seven years, which is not a claim anyone would defend out loud. The Model therefore also carries AUM AT THE CONSTANT M1 PRICE, and that is the honest series for judging whether the BUSINESS grew. Conservative is set at 0.0% deliberately: it restores the original flat-price design, under which every revenue change is attributable to the business rather than the metal.</t>
+    <t xml:space="preserve">ADDED 2026-08-21, client instruction, replacing a flat price. 8.1% is the COMPOUND ANNUAL GROWTH RATE SINCE 1971, the end of the gold standard - chosen because it is the LONGEST window and therefore the least cherry-picked. The shorter the window the better gold looks: ~8.6% over 50 years, ~9-10% over 20, ~13-14% over 10, and over 20% over the last 5. Taking the recent decade would have flattered the model on a rally. CITED. THIS IS A NOMINAL RATE AND NOTHING ELSE IN THE MODEL INFLATES. SIP tickets, spot tickets, CAC, card fees and the B2B fee are all frozen in 2027 dollars. There is NO CONSENSUS POSITIVE LONG-RUN REAL RETURN for gold - it is generally treated as a store of value with a near-zero real yield - so most of this 8.1% IS INFLATION. Applying it to the metal while freezing everything else quietly asserts that gold outruns wages, prices and costs by 8% a year for seven years, which is not a claim anyone would defend out loud. The Model therefore also carries AUM AT THE CONSTANT M1 PRICE, and that is the honest series for judging whether the BUSINESS grew. Conservative is set at 0.0% deliberately: it restores the original flat-price design, under which every revenue change is attributable to the business rather than the metal.</t>
   </si>
   <si>
     <t xml:space="preserve">Persistency - customers still paying after 12 months</t>
@@ -925,7 +925,7 @@
     <t xml:space="preserve">accounts/agent/month</t>
   </si>
   <si>
-    <t xml:space="preserve">RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. ⚠ COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
+    <t xml:space="preserve">RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
   </si>
   <si>
     <t xml:space="preserve">Marketing CAC - UAE</t>
@@ -934,7 +934,7 @@
     <t xml:space="preserve">USD per customer</t>
   </si>
   <si>
-    <t xml:space="preserve">REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; ⚠ note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
+    <t xml:space="preserve">REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
   </si>
   <si>
     <t xml:space="preserve">Marketing CAC - Oman and Bahrain</t>
@@ -964,7 +964,7 @@
     <t xml:space="preserve">referrals/customer/yr</t>
   </si>
   <si>
-    <t xml:space="preserve">RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. ⚠ IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
+    <t xml:space="preserve">RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Referral conversion</t>
@@ -979,7 +979,7 @@
     <t xml:space="preserve">% of direct</t>
   </si>
   <si>
-    <t xml:space="preserve">RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. ⚠ NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
+    <t xml:space="preserve">RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Seasonality amplitude</t>
@@ -1015,7 +1015,7 @@
     <t xml:space="preserve">% of AUM/yr</t>
   </si>
   <si>
-    <t xml:space="preserve">HALVED 2026-08-21 from 0.12, client instruction. ⚠ NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
+    <t xml:space="preserve">HALVED 2026-08-21 from 0.12, client instruction. NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Redemption rate</t>
@@ -1030,7 +1030,7 @@
     <t xml:space="preserve">x the paying rate</t>
   </si>
   <si>
-    <t xml:space="preserve">LOWERED 2026-08-21 from 2.2, client instruction. ⚠ THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
+    <t xml:space="preserve">LOWERED 2026-08-21 from 2.2, client instruction. THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
   </si>
   <si>
     <t xml:space="preserve">Spot attach scenario multiplier</t>
@@ -1048,7 +1048,7 @@
     <t xml:space="preserve">x the observed ticket</t>
   </si>
   <si>
-    <t xml:space="preserve">REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. ⚠ WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
+    <t xml:space="preserve">REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
   </si>
   <si>
     <t xml:space="preserve">Spot frequency</t>
@@ -1057,7 +1057,7 @@
     <t xml:space="preserve">events/attacher/yr</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
+    <t xml:space="preserve">PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
   </si>
   <si>
     <t xml:space="preserve">Programme manager share of interchange</t>
@@ -1072,7 +1072,7 @@
     <t xml:space="preserve">% of gate-cleared</t>
   </si>
   <si>
-    <t xml:space="preserve">RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. ⚠ THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
+    <t xml:space="preserve">RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
   </si>
   <si>
     <t xml:space="preserve">Transactions per drawdown event</t>
@@ -1081,7 +1081,7 @@
     <t xml:space="preserve">transactions/draw</t>
   </si>
   <si>
-    <t xml:space="preserve">RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
+    <t xml:space="preserve">RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Foreign spend share (mean)</t>
@@ -1168,7 +1168,7 @@
     <t xml:space="preserve">% of NEW customers</t>
   </si>
   <si>
-    <t xml:space="preserve">SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. ⚠ IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
+    <t xml:space="preserve">SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Family plan cancellation rate (incremental)</t>
@@ -1183,7 +1183,7 @@
     <t xml:space="preserve">beneficiaries</t>
   </si>
   <si>
-    <t xml:space="preserve">ADDED 2026-08-21. THE FIRST IS INCLUDED IN THE PLAN PRICE, so only the excess over 1.0 is charged - at 2.5 that is 1.5 chargeable. No platform publishes beneficiaries-per-will. What anchors it is who these customers are: South Asian migrant workers who remit ~80% of income to families at home, typically supporting a spouse, children and parents. Household sizes in the source countries run ~4.4 in India, ~4.5 in Bangladesh and ~6.8 in Pakistan, so naming 2-3 beneficiaries is conservative against the family they actually support. ⚠ NOT THE SAME AS HOUSEHOLD SIZE - a beneficiary is a named, identity-verified person on a legal instrument, and people name fewer than they support. ASSUMPTION anchored on demographics.</t>
+    <t xml:space="preserve">ADDED 2026-08-21. THE FIRST IS INCLUDED IN THE PLAN PRICE, so only the excess over 1.0 is charged - at 2.5 that is 1.5 chargeable. No platform publishes beneficiaries-per-will. What anchors it is who these customers are: South Asian migrant workers who remit ~80% of income to families at home, typically supporting a spouse, children and parents. Household sizes in the source countries run ~4.4 in India, ~4.5 in Bangladesh and ~6.8 in Pakistan, so naming 2-3 beneficiaries is conservative against the family they actually support. NOT THE SAME AS HOUSEHOLD SIZE - a beneficiary is a named, identity-verified person on a legal instrument, and people name fewer than they support. ASSUMPTION anchored on demographics.</t>
   </si>
   <si>
     <t xml:space="preserve">Family plan monthly churn, combined (derived)</t>
@@ -1198,7 +1198,7 @@
     <t xml:space="preserve">partners</t>
   </si>
   <si>
-    <t xml:space="preserve">RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+    <t xml:space="preserve">RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
   </si>
   <si>
     <t xml:space="preserve">B2B partners - Y2</t>
@@ -1225,7 +1225,7 @@
     <t xml:space="preserve">active users</t>
   </si>
   <si>
-    <t xml:space="preserve">THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. ⚠ USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
+    <t xml:space="preserve">THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
   </si>
   <si>
     <t xml:space="preserve">Partner users adopting gold (mature)</t>
@@ -1234,7 +1234,7 @@
     <t xml:space="preserve">% of partner users</t>
   </si>
   <si>
-    <t xml:space="preserve">OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. ⚠ THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
+    <t xml:space="preserve">OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
   </si>
   <si>
     <t xml:space="preserve">AUM per adopting partner user</t>
@@ -1519,7 +1519,7 @@
     <t xml:space="preserve">Gold price (this period)</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ RISING GOLD CUTS BOTH WAYS AND THE MODEL CAPTURES BOTH. Metal already held appreciates, but a fixed USD contribution BUYS FEWER GRAMS each year - so AUM does NOT simply compound at the headline rate. Only the collateral-linked streams move with this row (card limit, and lending through it); the entry fee is a percentage of a USD contribution and is untouched by the gold price.</t>
+    <t xml:space="preserve">RISING GOLD CUTS BOTH WAYS AND THE MODEL CAPTURES BOTH. Metal already held appreciates, but a fixed USD contribution BUYS FEWER GRAMS each year - so AUM does NOT simply compound at the headline rate. Only the collateral-linked streams move with this row (card limit, and lending through it); the entry fee is a percentage of a USD contribution and is untouched by the gold price.</t>
   </si>
   <si>
     <t xml:space="preserve">Open-region salesforce share (renormalisation base)</t>
@@ -1723,7 +1723,7 @@
     <t xml:space="preserve">GOLD UNDER CUSTODY (comparable headline)</t>
   </si>
   <si>
-    <t xml:space="preserve">THE NUMBER TO QUOTE AGAINST OTHER GOLD PLATFORMS, and the only one that compares like for like. Collateral-eligible AUM above is SMALLER because it also removes gold moved out of Aurumix's control - a token in a private wallet cannot back a credit limit, but THE METAL IS STILL IN THE VAULT, so it is still gold under custody. PAXG, Kinesis and Comtech all publish the custody measure. ⚠ COMPARE IN GRAMS, NOT DOLLARS: every published USD figure carries the gold price of its own vintage, so a comparison in dollars is really a comparison of gold prices. Comtech Gold, the closest comparable - Dubai, DMCC-licensed, tokenised gold - holds ~141,000 g.</t>
+    <t xml:space="preserve">THE NUMBER TO QUOTE AGAINST OTHER GOLD PLATFORMS, and the only one that compares like for like. Collateral-eligible AUM above is SMALLER because it also removes gold moved out of Aurumix's control - a token in a private wallet cannot back a credit limit, but THE METAL IS STILL IN THE VAULT, so it is still gold under custody. PAXG, Kinesis and Comtech all publish the custody measure. COMPARE IN GRAMS, NOT DOLLARS: every published USD figure carries the gold price of its own vintage, so a comparison in dollars is really a comparison of gold prices. Comtech Gold, the closest comparable - Dubai, DMCC-licensed, tokenised gold - holds ~141,000 g.</t>
   </si>
   <si>
     <t xml:space="preserve">  Gold under custody at the CONSTANT M1 price (memo)</t>
@@ -1732,7 +1732,7 @@
     <t xml:space="preserve">  of which is the metal moving, not the business</t>
   </si>
   <si>
-    <t xml:space="preserve">THE HONEST SERIES FOR JUDGING EXECUTION is the constant-price row: it strips the gold price out and leaves grams accumulated, which is the part Aurumix controls. The headline above will grow even if the business does not. ⚠ SET GOLD APPRECIATION TO THE CONSERVATIVE SCENARIO (0.0%) TO RECOVER THE ORIGINAL FLAT-PRICE MODEL, under which these two rows are identical by construction.</t>
+    <t xml:space="preserve">THE HONEST SERIES FOR JUDGING EXECUTION is the constant-price row: it strips the gold price out and leaves grams accumulated, which is the part Aurumix controls. The headline above will grow even if the business does not. SET GOLD APPRECIATION TO THE CONSERVATIVE SCENARIO (0.0%) TO RECOVER THE ORIGINAL FLAT-PRICE MODEL, under which these two rows are identical by construction.</t>
   </si>
   <si>
     <t xml:space="preserve">CHECK: paying + holders = cumulative ever acquired</t>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
@@ -1054,7 +1054,7 @@
     <t xml:space="preserve">Programme manager share of interchange</t>
   </si>
   <si>
-    <t xml:space="preserve">SIZES THE LARGEST STREAM. No UAE/MENA figure is published. FLOOR IS 36% - take that into the sponsor conversation as the walk-away. TRIANGULATED.</t>
+    <t xml:space="preserve">BANDS CORRECTED 2026-08-21 - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
   </si>
   <si>
     <t xml:space="preserve">Facility take-up - customers who take AND use the card</t>
@@ -6039,10 +6039,10 @@
         <v>0.72</v>
       </c>
       <c r="D44" s="19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E44" s="19" t="n">
         <v>0.85</v>
-      </c>
-      <c r="E44" s="19" t="n">
-        <v>0.55</v>
       </c>
       <c r="F44" s="23" t="s">
         <v>245</v>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model_calculated.xlsx
@@ -1054,7 +1054,7 @@
     <t xml:space="preserve">Programme manager share of interchange</t>
   </si>
   <si>
-    <t xml:space="preserve">BANDS CORRECTED 2026-08-21 - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
+    <t xml:space="preserve">LOWERED 2026-08-21 from 0.72, client instruction - AURUMIX NOW KEEPS 40% RATHER THAN 28%. 0.60 sits comfortably inside the 36-85% observed range and is roughly its midpoint, so the base case moves from the pessimistic end to a neutral one. It assumes a NEGOTIATED deal rather than a take-it-or-leave-it one, which is reasonable for a programme with a gold-collateral proposition the manager cannot source elsewhere - but it IS an assumption about a contract that does not exist yet, and the only honest way to hold it is to treat 40% as a target to negotiate to, not a rate already won. BANDS CORRECTED earlier the same day - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
   </si>
   <si>
     <t xml:space="preserve">Facility take-up - customers who take AND use the card</t>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B142" s="34" t="n">
         <f aca="false">'Scenario Parameters'!$B$44</f>
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="C142" s="0" t="s">
         <v>245</v>
@@ -6033,10 +6033,10 @@
       </c>
       <c r="B44" s="40" t="n">
         <f aca="false">CHOOSE($C$6,C44,D44,E44)</f>
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="C44" s="19" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>0.36</v>
@@ -12512,71 +12512,71 @@
       </c>
       <c r="O56" s="55" t="n">
         <f aca="false">O51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1.63946438106254</v>
+        <v>2.34209197294648</v>
       </c>
       <c r="P56" s="55" t="n">
         <f aca="false">P51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1.69616037012857</v>
+        <v>2.42308624304082</v>
       </c>
       <c r="Q56" s="55" t="n">
         <f aca="false">Q51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1.90552982178332</v>
+        <v>2.72218545969046</v>
       </c>
       <c r="R56" s="55" t="n">
         <f aca="false">R51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>2.12646524360413</v>
+        <v>3.03780749086304</v>
       </c>
       <c r="S56" s="55" t="n">
         <f aca="false">S51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>2.48672767906611</v>
+        <v>3.55246811295158</v>
       </c>
       <c r="T56" s="55" t="n">
         <f aca="false">T51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>2.82511939861288</v>
+        <v>4.03588485516125</v>
       </c>
       <c r="U56" s="55" t="n">
         <f aca="false">U51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3.05503714664227</v>
+        <v>4.36433878091753</v>
       </c>
       <c r="V56" s="55" t="n">
         <f aca="false">V51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3.55688213782489</v>
+        <v>5.08126019689269</v>
       </c>
       <c r="W56" s="55" t="n">
         <f aca="false">W51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>5.25235239439205</v>
+        <v>7.50336056341721</v>
       </c>
       <c r="X56" s="55" t="n">
         <f aca="false">X51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>6.58289875184579</v>
+        <v>9.40414107406541</v>
       </c>
       <c r="Y56" s="55" t="n">
         <f aca="false">Y51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>8.13192298401265</v>
+        <v>11.6170328343038</v>
       </c>
       <c r="Z56" s="55" t="n">
         <f aca="false">Z51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>10.8371945463668</v>
+        <v>15.4817064948096</v>
       </c>
       <c r="AA56" s="55" t="n">
         <f aca="false">AA51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>910.258390023829</v>
+        <v>1300.36912860547</v>
       </c>
       <c r="AB56" s="55" t="n">
         <f aca="false">AB51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1990.88891248501</v>
+        <v>2844.12701783573</v>
       </c>
       <c r="AC56" s="55" t="n">
         <f aca="false">AC51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3582.78438349205</v>
+        <v>5118.26340498864</v>
       </c>
       <c r="AD56" s="55" t="n">
         <f aca="false">AD51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>5624.33218013085</v>
+        <v>8034.76025732979</v>
       </c>
       <c r="AE56" s="55" t="n">
         <f aca="false">AE51*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>7925.24479729131</v>
+        <v>11321.7782818447</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13380,71 +13380,71 @@
       </c>
       <c r="O63" s="57" t="n">
         <f aca="false">O54+O55+O56+O58+O59+O61</f>
-        <v>2302.97612126652</v>
+        <v>2303.6787488584</v>
       </c>
       <c r="P63" s="57" t="n">
         <f aca="false">P54+P55+P56+P58+P59+P61</f>
-        <v>2861.60408394796</v>
+        <v>2862.33100982087</v>
       </c>
       <c r="Q63" s="57" t="n">
         <f aca="false">Q54+Q55+Q56+Q58+Q59+Q61</f>
-        <v>3376.25499123492</v>
+        <v>3377.07164687283</v>
       </c>
       <c r="R63" s="57" t="n">
         <f aca="false">R54+R55+R56+R58+R59+R61</f>
-        <v>4039.60702424243</v>
+        <v>4040.51836648969</v>
       </c>
       <c r="S63" s="57" t="n">
         <f aca="false">S54+S55+S56+S58+S59+S61</f>
-        <v>4609.85148485446</v>
+        <v>4610.91722528834</v>
       </c>
       <c r="T63" s="57" t="n">
         <f aca="false">T54+T55+T56+T58+T59+T61</f>
-        <v>5055.96210472257</v>
+        <v>5057.17287017911</v>
       </c>
       <c r="U63" s="57" t="n">
         <f aca="false">U54+U55+U56+U58+U59+U61</f>
-        <v>5462.50451002751</v>
+        <v>5463.81381166178</v>
       </c>
       <c r="V63" s="57" t="n">
         <f aca="false">V54+V55+V56+V58+V59+V61</f>
-        <v>5853.44125059046</v>
+        <v>5854.96562864952</v>
       </c>
       <c r="W63" s="57" t="n">
         <f aca="false">W54+W55+W56+W58+W59+W61</f>
-        <v>6351.90040462269</v>
+        <v>6354.15141279172</v>
       </c>
       <c r="X63" s="57" t="n">
         <f aca="false">X54+X55+X56+X58+X59+X61</f>
-        <v>7090.32092504897</v>
+        <v>7093.14216737119</v>
       </c>
       <c r="Y63" s="57" t="n">
         <f aca="false">Y54+Y55+Y56+Y58+Y59+Y61</f>
-        <v>7731.13243038532</v>
+        <v>7734.61754023561</v>
       </c>
       <c r="Z63" s="57" t="n">
         <f aca="false">Z54+Z55+Z56+Z58+Z59+Z61</f>
-        <v>8264.13584310114</v>
+        <v>8268.78035504959</v>
       </c>
       <c r="AA63" s="57" t="n">
         <f aca="false">AA54+AA55+AA56+AA58+AA59+AA61</f>
-        <v>220700.02638662</v>
+        <v>221090.137125202</v>
       </c>
       <c r="AB63" s="57" t="n">
         <f aca="false">AB54+AB55+AB56+AB58+AB59+AB61</f>
-        <v>378317.678400733</v>
+        <v>379170.916506084</v>
       </c>
       <c r="AC63" s="57" t="n">
         <f aca="false">AC54+AC55+AC56+AC58+AC59+AC61</f>
-        <v>581187.606379716</v>
+        <v>582723.085401212</v>
       </c>
       <c r="AD63" s="57" t="n">
         <f aca="false">AD54+AD55+AD56+AD58+AD59+AD61</f>
-        <v>785277.681872278</v>
+        <v>787688.109949477</v>
       </c>
       <c r="AE63" s="57" t="n">
         <f aca="false">AE54+AE55+AE56+AE58+AE59+AE61</f>
-        <v>949662.795101751</v>
+        <v>953059.328586305</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17289,39 +17289,39 @@
       </c>
       <c r="W96" s="55" t="n">
         <f aca="false">W91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>0.172688951734677</v>
+        <v>0.24669850247811</v>
       </c>
       <c r="X96" s="55" t="n">
         <f aca="false">X91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>0.36367872538033</v>
+        <v>0.519541036257614</v>
       </c>
       <c r="Y96" s="55" t="n">
         <f aca="false">Y91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>0.587137418439322</v>
+        <v>0.838767740627603</v>
       </c>
       <c r="Z96" s="55" t="n">
         <f aca="false">Z91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>0.961681791045065</v>
+        <v>1.37383113006438</v>
       </c>
       <c r="AA96" s="55" t="n">
         <f aca="false">AA91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>166.863963083519</v>
+        <v>238.377090119313</v>
       </c>
       <c r="AB96" s="55" t="n">
         <f aca="false">AB91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>392.845175697338</v>
+        <v>561.20739385334</v>
       </c>
       <c r="AC96" s="55" t="n">
         <f aca="false">AC91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>727.997549931585</v>
+        <v>1039.99649990226</v>
       </c>
       <c r="AD96" s="55" t="n">
         <f aca="false">AD91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1158.1335047371</v>
+        <v>1654.47643533872</v>
       </c>
       <c r="AE96" s="55" t="n">
         <f aca="false">AE91*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1638.08576322009</v>
+        <v>2340.12251888585</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18157,39 +18157,39 @@
       </c>
       <c r="W103" s="57" t="n">
         <f aca="false">W94+W95+W96+W98+W99+W101</f>
-        <v>1155.76359903911</v>
+        <v>1155.83760858985</v>
       </c>
       <c r="X103" s="57" t="n">
         <f aca="false">X94+X95+X96+X98+X99+X101</f>
-        <v>1340.89172276463</v>
+        <v>1341.04758507551</v>
       </c>
       <c r="Y103" s="57" t="n">
         <f aca="false">Y94+Y95+Y96+Y98+Y99+Y101</f>
-        <v>1503.36219445377</v>
+        <v>1503.61382477596</v>
       </c>
       <c r="Z103" s="57" t="n">
         <f aca="false">Z94+Z95+Z96+Z98+Z99+Z101</f>
-        <v>1641.67585734232</v>
+        <v>1642.08800668134</v>
       </c>
       <c r="AA103" s="57" t="n">
         <f aca="false">AA94+AA95+AA96+AA98+AA99+AA101</f>
-        <v>49257.4518417325</v>
+        <v>49328.9649687683</v>
       </c>
       <c r="AB103" s="57" t="n">
         <f aca="false">AB94+AB95+AB96+AB98+AB99+AB101</f>
-        <v>87121.5995334432</v>
+        <v>87289.9617515992</v>
       </c>
       <c r="AC103" s="57" t="n">
         <f aca="false">AC94+AC95+AC96+AC98+AC99+AC101</f>
-        <v>135243.911148384</v>
+        <v>135555.910098355</v>
       </c>
       <c r="AD103" s="57" t="n">
         <f aca="false">AD94+AD95+AD96+AD98+AD99+AD101</f>
-        <v>183529.982111776</v>
+        <v>184026.325042377</v>
       </c>
       <c r="AE103" s="57" t="n">
         <f aca="false">AE94+AE95+AE96+AE98+AE99+AE101</f>
-        <v>221021.19241832</v>
+        <v>221723.229173986</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22002,71 +22002,71 @@
       </c>
       <c r="O136" s="55" t="n">
         <f aca="false">O131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3.2265946766555</v>
+        <v>4.60942096665072</v>
       </c>
       <c r="P136" s="55" t="n">
         <f aca="false">P131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3.34415160271667</v>
+        <v>4.77735943245239</v>
       </c>
       <c r="Q136" s="55" t="n">
         <f aca="false">Q131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3.75959810218154</v>
+        <v>5.37085443168792</v>
       </c>
       <c r="R136" s="55" t="n">
         <f aca="false">R131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>4.198222212821</v>
+        <v>5.99746030403001</v>
       </c>
       <c r="S136" s="55" t="n">
         <f aca="false">S131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>4.90936976293557</v>
+        <v>7.01338537562224</v>
       </c>
       <c r="T136" s="55" t="n">
         <f aca="false">T131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>5.57427259767526</v>
+        <v>7.96324656810751</v>
       </c>
       <c r="U136" s="55" t="n">
         <f aca="false">U131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>6.02456762531877</v>
+        <v>8.60652517902681</v>
       </c>
       <c r="V136" s="55" t="n">
         <f aca="false">V131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>7.01103927228932</v>
+        <v>10.0157703889847</v>
       </c>
       <c r="W136" s="55" t="n">
         <f aca="false">W131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>10.2950862515356</v>
+        <v>14.7072660736222</v>
       </c>
       <c r="X136" s="55" t="n">
         <f aca="false">X131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>12.858510220029</v>
+        <v>18.3693003143271</v>
       </c>
       <c r="Y136" s="55" t="n">
         <f aca="false">Y131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>15.8386085395762</v>
+        <v>22.626583627966</v>
       </c>
       <c r="Z136" s="55" t="n">
         <f aca="false">Z131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>21.0368879241544</v>
+        <v>30.0526970345063</v>
       </c>
       <c r="AA136" s="55" t="n">
         <f aca="false">AA131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>1600.54171459423</v>
+        <v>2286.48816370604</v>
       </c>
       <c r="AB136" s="55" t="n">
         <f aca="false">AB131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>3312.45563186364</v>
+        <v>4732.07947409092</v>
       </c>
       <c r="AC136" s="55" t="n">
         <f aca="false">AC131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>5584.83444236091</v>
+        <v>7978.33491765845</v>
       </c>
       <c r="AD136" s="55" t="n">
         <f aca="false">AD131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>8108.09316038188</v>
+        <v>11582.990229117</v>
       </c>
       <c r="AE136" s="55" t="n">
         <f aca="false">AE131*IF(Assumptions!$B$178=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
-        <v>10383.7583082959</v>
+        <v>14833.9404404227</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22870,71 +22870,71 @@
       </c>
       <c r="O143" s="57" t="n">
         <f aca="false">O134+O135+O136+O138+O139+O141</f>
-        <v>4625.19209695194</v>
+        <v>4626.57492324194</v>
       </c>
       <c r="P143" s="57" t="n">
         <f aca="false">P134+P135+P136+P138+P139+P141</f>
-        <v>5729.84813882029</v>
+        <v>5731.28134665002</v>
       </c>
       <c r="Q143" s="57" t="n">
         <f aca="false">Q134+Q135+Q136+Q138+Q139+Q141</f>
-        <v>6742.74208501814</v>
+        <v>6744.35334134765</v>
       </c>
       <c r="R143" s="57" t="n">
         <f aca="false">R134+R135+R136+R138+R139+R141</f>
-        <v>8042.98552207297</v>
+        <v>8044.78476016418</v>
       </c>
       <c r="S143" s="57" t="n">
         <f aca="false">S134+S135+S136+S138+S139+S141</f>
-        <v>9154.22461298518</v>
+        <v>9156.32862859787</v>
       </c>
       <c r="T143" s="57" t="n">
         <f aca="false">T134+T135+T136+T138+T139+T141</f>
-        <v>10019.5823257497</v>
+        <v>10021.9712997202</v>
       </c>
       <c r="U143" s="57" t="n">
         <f aca="false">U134+U135+U136+U138+U139+U141</f>
-        <v>10802.8258004017</v>
+        <v>10805.4077579554</v>
       </c>
       <c r="V143" s="57" t="n">
         <f aca="false">V134+V135+V136+V138+V139+V141</f>
-        <v>11550.6574237996</v>
+        <v>11553.6621549163</v>
       </c>
       <c r="W143" s="57" t="n">
         <f aca="false">W134+W135+W136+W138+W139+W141</f>
-        <v>12514.7343302613</v>
+        <v>12519.1465100833</v>
       </c>
       <c r="X143" s="57" t="n">
         <f aca="false">X134+X135+X136+X138+X139+X141</f>
-        <v>13933.373119992</v>
+        <v>13938.8839100863</v>
       </c>
       <c r="Y143" s="57" t="n">
         <f aca="false">Y134+Y135+Y136+Y138+Y139+Y141</f>
-        <v>15153.9086340652</v>
+        <v>15160.6966091536</v>
       </c>
       <c r="Z143" s="57" t="n">
         <f aca="false">Z134+Z135+Z136+Z138+Z139+Z141</f>
-        <v>16165.2349362255</v>
+        <v>16174.2507453358</v>
       </c>
       <c r="AA143" s="57" t="n">
         <f aca="false">AA134+AA135+AA136+AA138+AA139+AA141</f>
-        <v>398267.480972361</v>
+        <v>398953.427421473</v>
       </c>
       <c r="AB143" s="57" t="n">
         <f aca="false">AB134+AB135+AB136+AB138+AB139+AB141</f>
-        <v>638803.042779799</v>
+        <v>640222.666622026</v>
       </c>
       <c r="AC143" s="57" t="n">
         <f aca="false">AC134+AC135+AC136+AC138+AC139+AC141</f>
-        <v>895641.010552015</v>
+        <v>898034.511027313</v>
       </c>
       <c r="AD143" s="57" t="n">
         <f aca="false">AD134+AD135+AD136+AD138+AD139+AD141</f>
-        <v>1075704.63157371</v>
+        <v>1079179.52864244</v>
       </c>
       <c r="AE143" s="57" t="n">
         <f aca="false">AE134+AE135+AE136+AE138+AE139+AE141</f>
-        <v>1107734.71391493</v>
+        <v>1112184.89604705</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26179,71 +26179,71 @@
       </c>
       <c r="O177" s="55" t="n">
         <f aca="false">O56+O96+O136</f>
-        <v>4.86605905771804</v>
+        <v>6.95151293959719</v>
       </c>
       <c r="P177" s="55" t="n">
         <f aca="false">P56+P96+P136</f>
-        <v>5.04031197284524</v>
+        <v>7.2004456754932</v>
       </c>
       <c r="Q177" s="55" t="n">
         <f aca="false">Q56+Q96+Q136</f>
-        <v>5.66512792396486</v>
+        <v>8.09303989137838</v>
       </c>
       <c r="R177" s="55" t="n">
         <f aca="false">R56+R96+R136</f>
-        <v>6.32468745642513</v>
+        <v>9.03526779489304</v>
       </c>
       <c r="S177" s="55" t="n">
         <f aca="false">S56+S96+S136</f>
-        <v>7.39609744200167</v>
+        <v>10.5658534885738</v>
       </c>
       <c r="T177" s="55" t="n">
         <f aca="false">T56+T96+T136</f>
-        <v>8.39939199628813</v>
+        <v>11.9991314232688</v>
       </c>
       <c r="U177" s="55" t="n">
         <f aca="false">U56+U96+U136</f>
-        <v>9.07960477196104</v>
+        <v>12.9708639599443</v>
       </c>
       <c r="V177" s="55" t="n">
         <f aca="false">V56+V96+V136</f>
-        <v>10.5679214101142</v>
+        <v>15.0970305858774</v>
       </c>
       <c r="W177" s="55" t="n">
         <f aca="false">W56+W96+W136</f>
-        <v>15.7201275976623</v>
+        <v>22.4573251395176</v>
       </c>
       <c r="X177" s="55" t="n">
         <f aca="false">X56+X96+X136</f>
-        <v>19.8050876972551</v>
+        <v>28.2929824246501</v>
       </c>
       <c r="Y177" s="55" t="n">
         <f aca="false">Y56+Y96+Y136</f>
-        <v>24.5576689420282</v>
+        <v>35.0823842028974</v>
       </c>
       <c r="Z177" s="55" t="n">
         <f aca="false">Z56+Z96+Z136</f>
-        <v>32.8357642615662</v>
+        <v>46.9082346593803</v>
       </c>
       <c r="AA177" s="55" t="n">
         <f aca="false">AA56+AA96+AA136</f>
-        <v>2677.66406770158</v>
+        <v>3825.23438243083</v>
       </c>
       <c r="AB177" s="55" t="n">
         <f aca="false">AB56+AB96+AB136</f>
-        <v>5696.18972004599</v>
+        <v>8137.41388577998</v>
       </c>
       <c r="AC177" s="55" t="n">
         <f aca="false">AC56+AC96+AC136</f>
-        <v>9895.61637578455</v>
+        <v>14136.5948225494</v>
       </c>
       <c r="AD177" s="55" t="n">
         <f aca="false">AD56+AD96+AD136</f>
-        <v>14890.5588452498</v>
+        <v>21272.2269217855</v>
       </c>
       <c r="AE177" s="55" t="n">
         <f aca="false">AE56+AE96+AE136</f>
-        <v>19947.0888688073</v>
+        <v>28495.8412411533</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26923,71 +26923,71 @@
       </c>
       <c r="O183" s="57" t="n">
         <f aca="false">O63+O103+O143+O147</f>
-        <v>18891.2849425638</v>
+        <v>18893.3703964457</v>
       </c>
       <c r="P183" s="57" t="n">
         <f aca="false">P63+P103+P143+P147</f>
-        <v>20693.3240226263</v>
+        <v>20695.484156329</v>
       </c>
       <c r="Q183" s="57" t="n">
         <f aca="false">Q63+Q103+Q143+Q147</f>
-        <v>22349.2922546306</v>
+        <v>22351.720166598</v>
       </c>
       <c r="R183" s="57" t="n">
         <f aca="false">R63+R103+R143+R147</f>
-        <v>24474.4495136757</v>
+        <v>24477.1600940142</v>
       </c>
       <c r="S183" s="57" t="n">
         <f aca="false">S63+S103+S143+S147</f>
-        <v>26295.4591064206</v>
+        <v>26298.6288624672</v>
       </c>
       <c r="T183" s="57" t="n">
         <f aca="false">T63+T103+T143+T147</f>
-        <v>27715.6303800683</v>
+        <v>27719.2301194953</v>
       </c>
       <c r="U183" s="57" t="n">
         <f aca="false">U63+U103+U143+U147</f>
-        <v>29005.5831057585</v>
+        <v>29009.4743649465</v>
       </c>
       <c r="V183" s="57" t="n">
         <f aca="false">V63+V103+V143+V147</f>
-        <v>30241.3416662486</v>
+        <v>30245.8707754243</v>
       </c>
       <c r="W183" s="57" t="n">
         <f aca="false">W63+W103+W143+W147</f>
-        <v>31834.8983339231</v>
+        <v>31841.6355314649</v>
       </c>
       <c r="X183" s="57" t="n">
         <f aca="false">X63+X103+X143+X147</f>
-        <v>34177.0857678056</v>
+        <v>34185.573662533</v>
       </c>
       <c r="Y183" s="57" t="n">
         <f aca="false">Y63+Y103+Y143+Y147</f>
-        <v>36200.9032589043</v>
+        <v>36211.4279741651</v>
       </c>
       <c r="Z183" s="57" t="n">
         <f aca="false">Z63+Z103+Z143+Z147</f>
-        <v>37883.546636669</v>
+        <v>37897.6191070668</v>
       </c>
       <c r="AA183" s="57" t="n">
         <f aca="false">AA63+AA103+AA143+AA147</f>
-        <v>1093474.95920071</v>
+        <v>1094622.52951544</v>
       </c>
       <c r="AB183" s="57" t="n">
         <f aca="false">AB63+AB103+AB143+AB147</f>
-        <v>1812992.32071398</v>
+        <v>1815433.54487971</v>
       </c>
       <c r="AC183" s="57" t="n">
         <f aca="false">AC63+AC103+AC143+AC147</f>
-        <v>2604322.52808011</v>
+        <v>2608563.50652688</v>
       </c>
       <c r="AD183" s="57" t="n">
         <f aca="false">AD63+AD103+AD143+AD147</f>
-        <v>3320262.29555776</v>
+        <v>3326643.9636343</v>
       </c>
       <c r="AE183" s="57" t="n">
         <f aca="false">AE63+AE103+AE143+AE147</f>
-        <v>3837668.701435</v>
+        <v>3846217.45380734</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27047,71 +27047,71 @@
       </c>
       <c r="O184" s="55" t="n">
         <f aca="false">IF(O151=0,0,O183/O151/O7*12)</f>
-        <v>73.3043425747494</v>
+        <v>73.3124348154967</v>
       </c>
       <c r="P184" s="55" t="n">
         <f aca="false">IF(P151=0,0,P183/P151/P7*12)</f>
-        <v>65.010232184953</v>
+        <v>65.0170184699117</v>
       </c>
       <c r="Q184" s="55" t="n">
         <f aca="false">IF(Q151=0,0,Q183/Q151/Q7*12)</f>
-        <v>59.7073075775561</v>
+        <v>59.7137938718404</v>
       </c>
       <c r="R184" s="55" t="n">
         <f aca="false">IF(R151=0,0,R183/R151/R7*12)</f>
-        <v>54.7463127308284</v>
+        <v>54.7523759633767</v>
       </c>
       <c r="S184" s="55" t="n">
         <f aca="false">IF(S151=0,0,S183/S151/S7*12)</f>
-        <v>51.619494690748</v>
+        <v>51.6257171037036</v>
       </c>
       <c r="T184" s="55" t="n">
         <f aca="false">IF(T151=0,0,T183/T151/T7*12)</f>
-        <v>49.7490678791548</v>
+        <v>49.7555293479593</v>
       </c>
       <c r="U184" s="55" t="n">
         <f aca="false">IF(U151=0,0,U183/U151/U7*12)</f>
-        <v>48.2663442007566</v>
+        <v>48.2728193974336</v>
       </c>
       <c r="V184" s="55" t="n">
         <f aca="false">IF(V151=0,0,V183/V151/V7*12)</f>
-        <v>46.9959198131693</v>
+        <v>47.0029581798528</v>
       </c>
       <c r="W184" s="55" t="n">
         <f aca="false">IF(W151=0,0,W183/W151/W7*12)</f>
-        <v>46.0323458614957</v>
+        <v>46.0420876550498</v>
       </c>
       <c r="X184" s="55" t="n">
         <f aca="false">IF(X151=0,0,X183/X151/X7*12)</f>
-        <v>44.6209842469344</v>
+        <v>44.6320658885785</v>
       </c>
       <c r="Y184" s="55" t="n">
         <f aca="false">IF(Y151=0,0,Y183/Y151/Y7*12)</f>
-        <v>43.6173126609797</v>
+        <v>43.6299935544071</v>
       </c>
       <c r="Z184" s="55" t="n">
         <f aca="false">IF(Z151=0,0,Z183/Z151/Z7*12)</f>
-        <v>43.0523178803063</v>
+        <v>43.0683103763294</v>
       </c>
       <c r="AA184" s="55" t="n">
         <f aca="false">IF(AA151=0,0,AA183/AA151/AA7*12)</f>
-        <v>54.2484150253178</v>
+        <v>54.3053471664522</v>
       </c>
       <c r="AB184" s="55" t="n">
         <f aca="false">IF(AB151=0,0,AB183/AB151/AB7*12)</f>
-        <v>55.3427742349258</v>
+        <v>55.4172941963826</v>
       </c>
       <c r="AC184" s="55" t="n">
         <f aca="false">IF(AC151=0,0,AC183/AC151/AC7*12)</f>
-        <v>55.4386595608927</v>
+        <v>55.5289379952188</v>
       </c>
       <c r="AD184" s="55" t="n">
         <f aca="false">IF(AD151=0,0,AD183/AD151/AD7*12)</f>
-        <v>57.0713394473762</v>
+        <v>57.1810326922514</v>
       </c>
       <c r="AE184" s="55" t="n">
         <f aca="false">IF(AE151=0,0,AE183/AE151/AE7*12)</f>
-        <v>61.3054809929673</v>
+        <v>61.4420444685691</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27321,27 +27321,27 @@
       </c>
       <c r="E7" s="36" t="n">
         <f aca="false">SUM(Model!O63:Z63)</f>
-        <v>62999.6911740449</v>
+        <v>63021.1607832686</v>
       </c>
       <c r="F7" s="36" t="n">
         <f aca="false">Model!AA63</f>
-        <v>220700.02638662</v>
+        <v>221090.137125202</v>
       </c>
       <c r="G7" s="36" t="n">
         <f aca="false">Model!AB63</f>
-        <v>378317.678400733</v>
+        <v>379170.916506084</v>
       </c>
       <c r="H7" s="36" t="n">
         <f aca="false">Model!AC63</f>
-        <v>581187.606379716</v>
+        <v>582723.085401212</v>
       </c>
       <c r="I7" s="36" t="n">
         <f aca="false">Model!AD63</f>
-        <v>785277.681872278</v>
+        <v>787688.109949477</v>
       </c>
       <c r="J7" s="36" t="n">
         <f aca="false">Model!AE63</f>
-        <v>949662.795101751</v>
+        <v>953059.328586305</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27354,27 +27354,27 @@
       </c>
       <c r="E8" s="36" t="n">
         <f aca="false">SUM(Model!O103:Z103)</f>
-        <v>10577.7987889059</v>
+        <v>10578.6924404288</v>
       </c>
       <c r="F8" s="36" t="n">
         <f aca="false">Model!AA103</f>
-        <v>49257.4518417325</v>
+        <v>49328.9649687683</v>
       </c>
       <c r="G8" s="36" t="n">
         <f aca="false">Model!AB103</f>
-        <v>87121.5995334432</v>
+        <v>87289.9617515992</v>
       </c>
       <c r="H8" s="36" t="n">
         <f aca="false">Model!AC103</f>
-        <v>135243.911148384</v>
+        <v>135555.910098355</v>
       </c>
       <c r="I8" s="36" t="n">
         <f aca="false">Model!AD103</f>
-        <v>183529.982111776</v>
+        <v>184026.325042377</v>
       </c>
       <c r="J8" s="36" t="n">
         <f aca="false">Model!AE103</f>
-        <v>221021.19241832</v>
+        <v>221723.229173986</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27387,27 +27387,27 @@
       </c>
       <c r="E9" s="36" t="n">
         <f aca="false">SUM(Model!O143:Z143)</f>
-        <v>124435.309026343</v>
+        <v>124477.341987253</v>
       </c>
       <c r="F9" s="36" t="n">
         <f aca="false">Model!AA143</f>
-        <v>398267.480972361</v>
+        <v>398953.427421473</v>
       </c>
       <c r="G9" s="36" t="n">
         <f aca="false">Model!AB143</f>
-        <v>638803.042779799</v>
+        <v>640222.666622026</v>
       </c>
       <c r="H9" s="36" t="n">
         <f aca="false">Model!AC143</f>
-        <v>895641.010552015</v>
+        <v>898034.511027313</v>
       </c>
       <c r="I9" s="36" t="n">
         <f aca="false">Model!AD143</f>
-        <v>1075704.63157371</v>
+        <v>1079179.52864244</v>
       </c>
       <c r="J9" s="36" t="n">
         <f aca="false">Model!AE143</f>
-        <v>1107734.71391493</v>
+        <v>1112184.89604705</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27453,27 +27453,27 @@
       </c>
       <c r="E11" s="62" t="n">
         <f aca="false">SUM(Model!O183:Z183)</f>
-        <v>339762.798989294</v>
+        <v>339827.19521095</v>
       </c>
       <c r="F11" s="62" t="n">
         <f aca="false">Model!AA183</f>
-        <v>1093474.95920071</v>
+        <v>1094622.52951544</v>
       </c>
       <c r="G11" s="62" t="n">
         <f aca="false">Model!AB183</f>
-        <v>1812992.32071398</v>
+        <v>1815433.54487971</v>
       </c>
       <c r="H11" s="62" t="n">
         <f aca="false">Model!AC183</f>
-        <v>2604322.52808011</v>
+        <v>2608563.50652688</v>
       </c>
       <c r="I11" s="62" t="n">
         <f aca="false">Model!AD183</f>
-        <v>3320262.29555776</v>
+        <v>3326643.9636343</v>
       </c>
       <c r="J11" s="62" t="n">
         <f aca="false">Model!AE183</f>
-        <v>3837668.701435</v>
+        <v>3846217.45380734</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27567,27 +27567,27 @@
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">SUM(Model!O177:Z177)</f>
-        <v>150.25785052983</v>
+        <v>214.654072185472</v>
       </c>
       <c r="F16" s="36" t="n">
         <f aca="false">Model!AA177</f>
-        <v>2677.66406770158</v>
+        <v>3825.23438243083</v>
       </c>
       <c r="G16" s="36" t="n">
         <f aca="false">Model!AB177</f>
-        <v>5696.18972004599</v>
+        <v>8137.41388577998</v>
       </c>
       <c r="H16" s="36" t="n">
         <f aca="false">Model!AC177</f>
-        <v>9895.61637578455</v>
+        <v>14136.5948225494</v>
       </c>
       <c r="I16" s="36" t="n">
         <f aca="false">Model!AD177</f>
-        <v>14890.5588452498</v>
+        <v>21272.2269217855</v>
       </c>
       <c r="J16" s="36" t="n">
         <f aca="false">Model!AE177</f>
-        <v>19947.0888688073</v>
+        <v>28495.8412411533</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27732,27 +27732,27 @@
       </c>
       <c r="E21" s="62" t="n">
         <f aca="false">SUM(Model!O183:Z183)</f>
-        <v>339762.798989294</v>
+        <v>339827.19521095</v>
       </c>
       <c r="F21" s="62" t="n">
         <f aca="false">Model!AA183</f>
-        <v>1093474.95920071</v>
+        <v>1094622.52951544</v>
       </c>
       <c r="G21" s="62" t="n">
         <f aca="false">Model!AB183</f>
-        <v>1812992.32071398</v>
+        <v>1815433.54487971</v>
       </c>
       <c r="H21" s="62" t="n">
         <f aca="false">Model!AC183</f>
-        <v>2604322.52808011</v>
+        <v>2608563.50652688</v>
       </c>
       <c r="I21" s="62" t="n">
         <f aca="false">Model!AD183</f>
-        <v>3320262.29555776</v>
+        <v>3326643.9636343</v>
       </c>
       <c r="J21" s="62" t="n">
         <f aca="false">Model!AE183</f>
-        <v>3837668.701435</v>
+        <v>3846217.45380734</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27780,27 +27780,27 @@
       </c>
       <c r="E24" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E14/E$11)</f>
-        <v>0.374253260671347</v>
+        <v>0.374182340814816</v>
       </c>
       <c r="F24" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F14/F$11)</f>
-        <v>0.340508870642117</v>
+        <v>0.340151891079469</v>
       </c>
       <c r="G24" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G14/G$11)</f>
-        <v>0.333998500987281</v>
+        <v>0.333549371238506</v>
       </c>
       <c r="H24" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H14/H$11)</f>
-        <v>0.333879925769189</v>
+        <v>0.333337106870799</v>
       </c>
       <c r="I24" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I14/I$11)</f>
-        <v>0.324966192894997</v>
+        <v>0.324342793937422</v>
       </c>
       <c r="J24" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J14/J$11)</f>
-        <v>0.303428881638009</v>
+        <v>0.302754468814789</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27813,27 +27813,27 @@
       </c>
       <c r="E25" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E15/E$11)</f>
-        <v>0.0286069917924122</v>
+        <v>0.0286015708543286</v>
       </c>
       <c r="F25" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F15/F$11)</f>
-        <v>0.0262664180832223</v>
+        <v>0.0262388811370571</v>
       </c>
       <c r="G25" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G15/G$11)</f>
-        <v>0.0259174954148117</v>
+        <v>0.0258826440062871</v>
       </c>
       <c r="H25" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H15/H$11)</f>
-        <v>0.0261219531182726</v>
+        <v>0.0260794842882499</v>
       </c>
       <c r="I25" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I15/I$11)</f>
-        <v>0.0257017173890064</v>
+        <v>0.0256524124945944</v>
       </c>
       <c r="J25" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J15/J$11)</f>
-        <v>0.024368554846068</v>
+        <v>0.0243143923491336</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27846,27 +27846,27 @@
       </c>
       <c r="E26" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E16/E$11)</f>
-        <v>0.000442243385611397</v>
+        <v>0.00063165654547519</v>
       </c>
       <c r="F26" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F16/F$11)</f>
-        <v>0.00244876578578338</v>
+        <v>0.0034945693874254</v>
       </c>
       <c r="G26" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G16/G$11)</f>
-        <v>0.00314187195111934</v>
+        <v>0.00448235293918135</v>
       </c>
       <c r="H26" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H16/H$11)</f>
-        <v>0.00379968927392396</v>
+        <v>0.00541930253458588</v>
       </c>
       <c r="I26" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I16/I$11)</f>
-        <v>0.00448475376935496</v>
+        <v>0.0063945006301624</v>
       </c>
       <c r="J26" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J16/J$11)</f>
-        <v>0.00519770996942717</v>
+        <v>0.00740879619610313</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27879,27 +27879,27 @@
       </c>
       <c r="E27" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E17/E$11)</f>
-        <v>0.144711341240812</v>
+        <v>0.144683918881042</v>
       </c>
       <c r="F27" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F17/F$11)</f>
-        <v>0.129837499904932</v>
+        <v>0.12970138205918</v>
       </c>
       <c r="G27" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G17/G$11)</f>
-        <v>0.123924339603843</v>
+        <v>0.123757697815485</v>
       </c>
       <c r="H27" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H17/H$11)</f>
-        <v>0.120810417651675</v>
+        <v>0.1206140051909</v>
       </c>
       <c r="I27" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I17/I$11)</f>
-        <v>0.113741232359714</v>
+        <v>0.113523036845114</v>
       </c>
       <c r="J27" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J17/J$11)</f>
-        <v>0.101707860973294</v>
+        <v>0.101481801129246</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27912,27 +27912,27 @@
       </c>
       <c r="E28" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E18/E$11)</f>
-        <v>0.0342699510347229</v>
+        <v>0.0342634569830577</v>
       </c>
       <c r="F28" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F18/F$11)</f>
-        <v>0.109027743025992</v>
+        <v>0.108913441522044</v>
       </c>
       <c r="G28" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G18/G$11)</f>
-        <v>0.118122626342778</v>
+        <v>0.117963786152367</v>
       </c>
       <c r="H28" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H18/H$11)</f>
-        <v>0.129461693106865</v>
+        <v>0.129251215482389</v>
       </c>
       <c r="I28" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I18/I$11)</f>
-        <v>0.140855383319811</v>
+        <v>0.140585173368591</v>
       </c>
       <c r="J28" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J18/J$11)</f>
-        <v>0.151662674317086</v>
+        <v>0.151325582963715</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27945,27 +27945,27 @@
       </c>
       <c r="E29" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E19/E$11)</f>
-        <v>0.000513385604328451</v>
+        <v>0.000513288319315253</v>
       </c>
       <c r="F29" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F19/F$11)</f>
-        <v>0.00301290803429898</v>
+        <v>0.00300974938944384</v>
       </c>
       <c r="G29" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G19/G$11)</f>
-        <v>0.00396686892674896</v>
+        <v>0.00396153465477101</v>
       </c>
       <c r="H29" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H19/H$11)</f>
-        <v>0.00492512429993497</v>
+        <v>0.00491711707835443</v>
       </c>
       <c r="I29" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I19/I$11)</f>
-        <v>0.00601902817855839</v>
+        <v>0.00600748157471417</v>
       </c>
       <c r="J29" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J19/J$11)</f>
-        <v>0.00733296154521509</v>
+        <v>0.00731666301993438</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27978,27 +27978,27 @@
       </c>
       <c r="E30" s="63" t="n">
         <f aca="false">IF(E$11=0,0,E20/E$11)</f>
-        <v>0.417202826270767</v>
+        <v>0.417123767601965</v>
       </c>
       <c r="F30" s="63" t="n">
         <f aca="false">IF(F$11=0,0,F20/F$11)</f>
-        <v>0.388897794523654</v>
+        <v>0.38849008542538</v>
       </c>
       <c r="G30" s="63" t="n">
         <f aca="false">IF(G$11=0,0,G20/G$11)</f>
-        <v>0.390928296773418</v>
+        <v>0.390402613193402</v>
       </c>
       <c r="H30" s="63" t="n">
         <f aca="false">IF(H$11=0,0,H20/H$11)</f>
-        <v>0.381001196780139</v>
+        <v>0.380381768554721</v>
       </c>
       <c r="I30" s="63" t="n">
         <f aca="false">IF(I$11=0,0,I20/I$11)</f>
-        <v>0.384231692088558</v>
+        <v>0.383494601149402</v>
       </c>
       <c r="J30" s="63" t="n">
         <f aca="false">IF(J$11=0,0,J20/J$11)</f>
-        <v>0.406301356710901</v>
+        <v>0.405398295527079</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28356,27 +28356,27 @@
       </c>
       <c r="E43" s="36" t="n">
         <f aca="false">Model!Z184</f>
-        <v>43.0523178803063</v>
+        <v>43.0683103763294</v>
       </c>
       <c r="F43" s="36" t="n">
         <f aca="false">Model!AA184</f>
-        <v>54.2484150253178</v>
+        <v>54.3053471664522</v>
       </c>
       <c r="G43" s="36" t="n">
         <f aca="false">Model!AB184</f>
-        <v>55.3427742349258</v>
+        <v>55.4172941963826</v>
       </c>
       <c r="H43" s="36" t="n">
         <f aca="false">Model!AC184</f>
-        <v>55.4386595608927</v>
+        <v>55.5289379952188</v>
       </c>
       <c r="I43" s="36" t="n">
         <f aca="false">Model!AD184</f>
-        <v>57.0713394473762</v>
+        <v>57.1810326922514</v>
       </c>
       <c r="J43" s="36" t="n">
         <f aca="false">Model!AE184</f>
-        <v>61.3054809929673</v>
+        <v>61.4420444685691</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
